--- a/Updated_185_Count_Sheet_BEK_v2.xlsx
+++ b/Updated_185_Count_Sheet_BEK_v2.xlsx
@@ -24,7 +24,7 @@
     <numFmt numFmtId="167" formatCode="+0.00%;-0.00%"/>
     <numFmt numFmtId="168" formatCode="\$#,##0.00"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,13 +36,17 @@
       <b val="1"/>
     </font>
     <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <family val="2"/>
       <b val="1"/>
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -67,6 +71,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CC0000"/>
       </patternFill>
     </fill>
     <fill>
@@ -116,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -193,9 +202,27 @@
     <xf numFmtId="167" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -572,7 +599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S240"/>
+  <dimension ref="A1:S241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1152,64 +1179,64 @@
       <c r="S9" s="20" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="inlineStr">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>506121</t>
         </is>
       </c>
-      <c r="C10" s="15" t="inlineStr">
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>Beef Patty 3/1 Thick N Tender</t>
         </is>
       </c>
-      <c r="D10" s="15" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t>Beef Ground Patty 3-1 75/25 Au Jus Frozen</t>
         </is>
       </c>
-      <c r="E10" s="14" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
         <is>
           <t>60/5.33 OZ</t>
         </is>
       </c>
-      <c r="F10" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" s="16" t="n">
+      <c r="F10" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="22" t="n">
         <v>88.78</v>
       </c>
-      <c r="H10" s="17" t="n">
+      <c r="H10" s="23" t="n">
         <v>84.52</v>
       </c>
-      <c r="I10" s="18" t="n">
-        <v>0.07100000000000017</v>
-      </c>
-      <c r="J10" s="19" t="n">
-        <v>0.05040227165168021</v>
-      </c>
-      <c r="K10" s="17" t="n">
-        <v>1.479666666666667</v>
-      </c>
-      <c r="L10" s="15" t="inlineStr">
+      <c r="I10" s="24" t="n">
+        <v>4.260000000000005</v>
+      </c>
+      <c r="J10" s="25" t="n">
+        <v>0.05040227165168014</v>
+      </c>
+      <c r="K10" s="23" t="n">
+        <v>88.78</v>
+      </c>
+      <c r="L10" s="21" t="inlineStr">
         <is>
           <t>per Case (60/5.33 OZ)</t>
         </is>
       </c>
-      <c r="M10" s="14" t="n"/>
-      <c r="N10" s="16">
+      <c r="M10" s="20" t="n"/>
+      <c r="N10" s="22">
         <f>M10*G10</f>
         <v/>
       </c>
-      <c r="O10" s="14" t="n"/>
-      <c r="P10" s="14" t="n"/>
-      <c r="Q10" s="14" t="n"/>
-      <c r="R10" s="14" t="n"/>
-      <c r="S10" s="14" t="n"/>
+      <c r="O10" s="20" t="n"/>
+      <c r="P10" s="20" t="n"/>
+      <c r="Q10" s="20" t="n"/>
+      <c r="R10" s="20" t="n"/>
+      <c r="S10" s="20" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
@@ -1247,13 +1274,13 @@
         <v>83.22</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>-0.7034999999999998</v>
+        <v>-28.14</v>
       </c>
       <c r="J11" s="13" t="n">
-        <v>-0.3381398702235039</v>
+        <v>-0.338139870223504</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>1.377</v>
+        <v>55.08</v>
       </c>
       <c r="L11" s="9" t="inlineStr">
         <is>
@@ -1272,64 +1299,64 @@
       <c r="S11" s="8" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="inlineStr">
+      <c r="A12" s="20" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>188849</t>
         </is>
       </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="C12" s="21" t="inlineStr">
         <is>
           <t>Beef Steak Fritter Raw Breaded</t>
         </is>
       </c>
-      <c r="D12" s="15" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t>Beef Steak Fritter Chopped Frozen Formed Breaded With Black Pepper</t>
         </is>
       </c>
-      <c r="E12" s="14" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>40/4 OZ</t>
         </is>
       </c>
-      <c r="F12" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" s="16" t="n">
+      <c r="F12" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="22" t="n">
         <v>66.23</v>
       </c>
-      <c r="H12" s="17" t="n">
+      <c r="H12" s="23" t="n">
         <v>64.04000000000001</v>
       </c>
-      <c r="I12" s="18" t="n">
-        <v>0.05474999999999985</v>
-      </c>
-      <c r="J12" s="19" t="n">
-        <v>0.03419737663960015</v>
-      </c>
-      <c r="K12" s="17" t="n">
-        <v>1.65575</v>
-      </c>
-      <c r="L12" s="15" t="inlineStr">
+      <c r="I12" s="24" t="n">
+        <v>2.189999999999998</v>
+      </c>
+      <c r="J12" s="25" t="n">
+        <v>0.03419737663960021</v>
+      </c>
+      <c r="K12" s="23" t="n">
+        <v>66.23</v>
+      </c>
+      <c r="L12" s="21" t="inlineStr">
         <is>
           <t>per Case (40/4 OZ)</t>
         </is>
       </c>
-      <c r="M12" s="14" t="n"/>
-      <c r="N12" s="16">
+      <c r="M12" s="20" t="n"/>
+      <c r="N12" s="22">
         <f>M12*G12</f>
         <v/>
       </c>
-      <c r="O12" s="14" t="n"/>
-      <c r="P12" s="14" t="n"/>
-      <c r="Q12" s="14" t="n"/>
-      <c r="R12" s="14" t="n"/>
-      <c r="S12" s="14" t="n"/>
+      <c r="O12" s="20" t="n"/>
+      <c r="P12" s="20" t="n"/>
+      <c r="Q12" s="20" t="n"/>
+      <c r="R12" s="20" t="n"/>
+      <c r="S12" s="20" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1651,13 +1678,13 @@
         <v>48.96</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>-0.03333333333333333</v>
+        <v>-1.600000000000001</v>
       </c>
       <c r="J18" s="13" t="n">
-        <v>-0.0326797385620915</v>
+        <v>-0.03267973856209153</v>
       </c>
       <c r="K18" s="11" t="n">
-        <v>0.9866666666666667</v>
+        <v>47.36</v>
       </c>
       <c r="L18" s="9" t="inlineStr">
         <is>
@@ -1711,13 +1738,13 @@
         <v>76.54000000000001</v>
       </c>
       <c r="I19" s="24" t="n">
-        <v>0.8641666666666667</v>
+        <v>31.11</v>
       </c>
       <c r="J19" s="25" t="n">
-        <v>0.406454141625294</v>
+        <v>0.4064541416252939</v>
       </c>
       <c r="K19" s="23" t="n">
-        <v>2.990277777777778</v>
+        <v>107.65</v>
       </c>
       <c r="L19" s="21" t="inlineStr">
         <is>
@@ -1891,7 +1918,7 @@
         <v>0</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>0.7075</v>
+        <v>50.94</v>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
@@ -2018,64 +2045,64 @@
       <c r="S24" s="2" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" s="14" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" s="14" t="inlineStr">
         <is>
           <t>301629</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C25" s="15" t="inlineStr">
         <is>
           <t>Sauce Cocktail Cups Gf</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D25" s="15" t="inlineStr">
         <is>
           <t>Cocktail Sauce</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E25" s="14" t="inlineStr">
         <is>
           <t>100/1.5 OZ</t>
         </is>
       </c>
-      <c r="F25" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" s="4" t="n">
+      <c r="F25" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="16" t="n">
         <v>28.94</v>
       </c>
-      <c r="H25" s="5" t="n">
+      <c r="H25" s="17" t="n">
         <v>28.6</v>
       </c>
-      <c r="I25" s="6" t="n">
-        <v>0.003399999999999959</v>
-      </c>
-      <c r="J25" s="7" t="n">
-        <v>0.01188811188811174</v>
-      </c>
-      <c r="K25" s="5" t="n">
-        <v>0.2894</v>
-      </c>
-      <c r="L25" s="3" t="inlineStr">
+      <c r="I25" s="18" t="n">
+        <v>0.3399999999999999</v>
+      </c>
+      <c r="J25" s="19" t="n">
+        <v>0.01188811188811188</v>
+      </c>
+      <c r="K25" s="17" t="n">
+        <v>28.94</v>
+      </c>
+      <c r="L25" s="15" t="inlineStr">
         <is>
           <t>per Case (100/1.5 OZ)</t>
         </is>
       </c>
-      <c r="M25" s="2" t="n"/>
-      <c r="N25" s="4">
+      <c r="M25" s="14" t="n"/>
+      <c r="N25" s="16">
         <f>M25*G25</f>
         <v/>
       </c>
-      <c r="O25" s="2" t="n"/>
-      <c r="P25" s="2" t="n"/>
-      <c r="Q25" s="2" t="n"/>
-      <c r="R25" s="2" t="n"/>
-      <c r="S25" s="2" t="n"/>
+      <c r="O25" s="14" t="n"/>
+      <c r="P25" s="14" t="n"/>
+      <c r="Q25" s="14" t="n"/>
+      <c r="R25" s="14" t="n"/>
+      <c r="S25" s="14" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n"/>
@@ -2155,7 +2182,7 @@
         <v>0</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>0.632</v>
+        <v>37.92</v>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
@@ -2865,13 +2892,13 @@
         <v>24.52</v>
       </c>
       <c r="I40" s="18" t="n">
-        <v>0.07000000000000028</v>
+        <v>0.1400000000000006</v>
       </c>
       <c r="J40" s="19" t="n">
         <v>0.005709624796084852</v>
       </c>
       <c r="K40" s="17" t="n">
-        <v>12.33</v>
+        <v>24.66</v>
       </c>
       <c r="L40" s="15" t="inlineStr">
         <is>
@@ -2890,52 +2917,52 @@
       <c r="S40" s="14" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="A41" s="26" t="inlineStr">
         <is>
           <t>SLEEVE</t>
         </is>
       </c>
-      <c r="B41" s="2" t="n"/>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="B41" s="26" t="n"/>
+      <c r="C41" s="27" t="inlineStr">
         <is>
           <t>Chili</t>
         </is>
       </c>
-      <c r="D41" s="3" t="n"/>
-      <c r="E41" s="2" t="n"/>
-      <c r="F41" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G41" s="4" t="n">
+      <c r="D41" s="27" t="n"/>
+      <c r="E41" s="26" t="n"/>
+      <c r="F41" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="28" t="n">
         <v>17.8</v>
       </c>
-      <c r="H41" s="5" t="n">
+      <c r="H41" s="29" t="n">
         <v>17.8</v>
       </c>
-      <c r="I41" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" s="5" t="n">
+      <c r="I41" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="29" t="n">
         <v>17.8</v>
       </c>
-      <c r="L41" s="3" t="inlineStr">
+      <c r="L41" s="27" t="inlineStr">
         <is>
           <t>per Sleeve (None)</t>
         </is>
       </c>
-      <c r="M41" s="2" t="n"/>
-      <c r="N41" s="4">
+      <c r="M41" s="26" t="n"/>
+      <c r="N41" s="28">
         <f>M41*G41</f>
         <v/>
       </c>
-      <c r="O41" s="2" t="n"/>
-      <c r="P41" s="2" t="n"/>
-      <c r="Q41" s="2" t="n"/>
-      <c r="R41" s="2" t="n"/>
-      <c r="S41" s="2" t="n"/>
+      <c r="O41" s="26" t="n"/>
+      <c r="P41" s="26" t="n"/>
+      <c r="Q41" s="26" t="n"/>
+      <c r="R41" s="26" t="n"/>
+      <c r="S41" s="26" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n"/>
@@ -2969,7 +2996,7 @@
         <v>0</v>
       </c>
       <c r="K42" s="5" t="n">
-        <v>0.7757999999999999</v>
+        <v>77.58</v>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
@@ -3023,13 +3050,13 @@
         <v>90.16</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>-0.2349999999999994</v>
+        <v>-0.9399999999999977</v>
       </c>
       <c r="J43" s="13" t="n">
         <v>-0.01042590949423245</v>
       </c>
       <c r="K43" s="11" t="n">
-        <v>22.305</v>
+        <v>89.22</v>
       </c>
       <c r="L43" s="9" t="inlineStr">
         <is>
@@ -4143,7 +4170,7 @@
         <v>0</v>
       </c>
       <c r="K63" s="5" t="n">
-        <v>1.051</v>
+        <v>84.08</v>
       </c>
       <c r="L63" s="3" t="inlineStr">
         <is>
@@ -4162,184 +4189,184 @@
       <c r="S63" s="2" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="A64" s="8" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B64" s="8" t="inlineStr">
         <is>
           <t>370013</t>
         </is>
       </c>
-      <c r="C64" s="3" t="inlineStr">
+      <c r="C64" s="9" t="inlineStr">
         <is>
           <t>Corn Dog Chicken Jalapeno</t>
         </is>
       </c>
-      <c r="D64" s="3" t="inlineStr">
+      <c r="D64" s="9" t="inlineStr">
         <is>
           <t>Corn Dog Cheese Jalapeno With Bag Frozen</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E64" s="8" t="inlineStr">
         <is>
           <t>36/4 OZ</t>
         </is>
       </c>
-      <c r="F64" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G64" s="4" t="n">
+      <c r="F64" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" s="10" t="n">
         <v>27.31</v>
       </c>
-      <c r="H64" s="5" t="n">
+      <c r="H64" s="11" t="n">
         <v>27.54</v>
       </c>
-      <c r="I64" s="6" t="n">
-        <v>-0.006388888888888888</v>
-      </c>
-      <c r="J64" s="7" t="n">
-        <v>-0.008351488743645606</v>
-      </c>
-      <c r="K64" s="5" t="n">
-        <v>0.7586111111111111</v>
-      </c>
-      <c r="L64" s="3" t="inlineStr">
+      <c r="I64" s="12" t="n">
+        <v>-0.2300000000000004</v>
+      </c>
+      <c r="J64" s="13" t="n">
+        <v>-0.008351488743645621</v>
+      </c>
+      <c r="K64" s="11" t="n">
+        <v>27.31</v>
+      </c>
+      <c r="L64" s="9" t="inlineStr">
         <is>
           <t>per Case (36/4 OZ)</t>
         </is>
       </c>
-      <c r="M64" s="2" t="n"/>
-      <c r="N64" s="4">
+      <c r="M64" s="8" t="n"/>
+      <c r="N64" s="10">
         <f>M64*G64</f>
         <v/>
       </c>
-      <c r="O64" s="2" t="n"/>
-      <c r="P64" s="2" t="n"/>
-      <c r="Q64" s="2" t="n"/>
-      <c r="R64" s="2" t="n"/>
-      <c r="S64" s="2" t="n"/>
+      <c r="O64" s="8" t="n"/>
+      <c r="P64" s="8" t="n"/>
+      <c r="Q64" s="8" t="n"/>
+      <c r="R64" s="8" t="n"/>
+      <c r="S64" s="8" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="A65" s="14" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B65" s="14" t="inlineStr">
         <is>
           <t>370008</t>
         </is>
       </c>
-      <c r="C65" s="3" t="inlineStr">
+      <c r="C65" s="15" t="inlineStr">
         <is>
           <t>Corn Dog Chicken</t>
         </is>
       </c>
-      <c r="D65" s="3" t="inlineStr">
+      <c r="D65" s="15" t="inlineStr">
         <is>
           <t>Corn Dog Chicken Battered Honey Crunch On Stick Frozen</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E65" s="14" t="inlineStr">
         <is>
           <t>72/4 OZ</t>
         </is>
       </c>
-      <c r="F65" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G65" s="4" t="n">
+      <c r="F65" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" s="16" t="n">
         <v>43.77</v>
       </c>
-      <c r="H65" s="5" t="n">
+      <c r="H65" s="17" t="n">
         <v>43.55</v>
       </c>
-      <c r="I65" s="6" t="n">
-        <v>0.003055555555555589</v>
-      </c>
-      <c r="J65" s="7" t="n">
-        <v>0.005051664753157346</v>
-      </c>
-      <c r="K65" s="5" t="n">
-        <v>0.6079166666666667</v>
-      </c>
-      <c r="L65" s="3" t="inlineStr">
+      <c r="I65" s="18" t="n">
+        <v>0.220000000000006</v>
+      </c>
+      <c r="J65" s="19" t="n">
+        <v>0.005051664753157428</v>
+      </c>
+      <c r="K65" s="17" t="n">
+        <v>43.77</v>
+      </c>
+      <c r="L65" s="15" t="inlineStr">
         <is>
           <t>per Case (72/4 OZ)</t>
         </is>
       </c>
-      <c r="M65" s="2" t="n"/>
-      <c r="N65" s="4">
+      <c r="M65" s="14" t="n"/>
+      <c r="N65" s="16">
         <f>M65*G65</f>
         <v/>
       </c>
-      <c r="O65" s="2" t="n"/>
-      <c r="P65" s="2" t="n"/>
-      <c r="Q65" s="2" t="n"/>
-      <c r="R65" s="2" t="n"/>
-      <c r="S65" s="2" t="n"/>
+      <c r="O65" s="14" t="n"/>
+      <c r="P65" s="14" t="n"/>
+      <c r="Q65" s="14" t="n"/>
+      <c r="R65" s="14" t="n"/>
+      <c r="S65" s="14" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="A66" s="8" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B66" s="8" t="inlineStr">
         <is>
           <t>370049</t>
         </is>
       </c>
-      <c r="C66" s="3" t="inlineStr">
+      <c r="C66" s="9" t="inlineStr">
         <is>
           <t>Corn Dog Chili Cheese</t>
         </is>
       </c>
-      <c r="D66" s="3" t="inlineStr">
+      <c r="D66" s="9" t="inlineStr">
         <is>
           <t>Corn Dog Chili Lovers With Bag Frozen</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E66" s="8" t="inlineStr">
         <is>
           <t>36/4 OZ</t>
         </is>
       </c>
-      <c r="F66" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G66" s="4" t="n">
+      <c r="F66" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" s="10" t="n">
         <v>28.13</v>
       </c>
-      <c r="H66" s="5" t="n">
+      <c r="H66" s="11" t="n">
         <v>29.18</v>
       </c>
-      <c r="I66" s="6" t="n">
-        <v>-0.02916666666666667</v>
-      </c>
-      <c r="J66" s="7" t="n">
-        <v>-0.03598355037697053</v>
-      </c>
-      <c r="K66" s="5" t="n">
-        <v>0.7813888888888889</v>
-      </c>
-      <c r="L66" s="3" t="inlineStr">
+      <c r="I66" s="12" t="n">
+        <v>-1.050000000000001</v>
+      </c>
+      <c r="J66" s="13" t="n">
+        <v>-0.03598355037697056</v>
+      </c>
+      <c r="K66" s="11" t="n">
+        <v>28.13</v>
+      </c>
+      <c r="L66" s="9" t="inlineStr">
         <is>
           <t>per Case (36/4 OZ)</t>
         </is>
       </c>
-      <c r="M66" s="2" t="n"/>
-      <c r="N66" s="4">
+      <c r="M66" s="8" t="n"/>
+      <c r="N66" s="10">
         <f>M66*G66</f>
         <v/>
       </c>
-      <c r="O66" s="2" t="n"/>
-      <c r="P66" s="2" t="n"/>
-      <c r="Q66" s="2" t="n"/>
-      <c r="R66" s="2" t="n"/>
-      <c r="S66" s="2" t="n"/>
+      <c r="O66" s="8" t="n"/>
+      <c r="P66" s="8" t="n"/>
+      <c r="Q66" s="8" t="n"/>
+      <c r="R66" s="8" t="n"/>
+      <c r="S66" s="8" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -4383,7 +4410,7 @@
         <v>0</v>
       </c>
       <c r="K67" s="5" t="n">
-        <v>0.7970833333333334</v>
+        <v>57.39</v>
       </c>
       <c r="L67" s="3" t="inlineStr">
         <is>
@@ -4456,52 +4483,52 @@
       <c r="S68" s="2" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="A69" s="26" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="B69" s="2" t="n"/>
-      <c r="C69" s="3" t="inlineStr">
+      <c r="B69" s="26" t="n"/>
+      <c r="C69" s="27" t="inlineStr">
         <is>
           <t>Donut Apple</t>
         </is>
       </c>
-      <c r="D69" s="3" t="n"/>
-      <c r="E69" s="2" t="n"/>
-      <c r="F69" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G69" s="4" t="n">
+      <c r="D69" s="27" t="n"/>
+      <c r="E69" s="26" t="n"/>
+      <c r="F69" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" s="28" t="n">
         <v>33.26</v>
       </c>
-      <c r="H69" s="5" t="n">
+      <c r="H69" s="29" t="n">
         <v>33.26</v>
       </c>
-      <c r="I69" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J69" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K69" s="5" t="n">
+      <c r="I69" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" s="29" t="n">
         <v>33.26</v>
       </c>
-      <c r="L69" s="3" t="inlineStr">
+      <c r="L69" s="27" t="inlineStr">
         <is>
           <t>per Case (None)</t>
         </is>
       </c>
-      <c r="M69" s="2" t="n"/>
-      <c r="N69" s="4">
+      <c r="M69" s="26" t="n"/>
+      <c r="N69" s="28">
         <f>M69*G69</f>
         <v/>
       </c>
-      <c r="O69" s="2" t="n"/>
-      <c r="P69" s="2" t="n"/>
-      <c r="Q69" s="2" t="n"/>
-      <c r="R69" s="2" t="n"/>
-      <c r="S69" s="2" t="n"/>
+      <c r="O69" s="26" t="n"/>
+      <c r="P69" s="26" t="n"/>
+      <c r="Q69" s="26" t="n"/>
+      <c r="R69" s="26" t="n"/>
+      <c r="S69" s="26" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -4545,7 +4572,7 @@
         <v>0</v>
       </c>
       <c r="K70" s="5" t="n">
-        <v>0.3206547619047619</v>
+        <v>53.87</v>
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
@@ -4741,7 +4768,7 @@
         <v>0</v>
       </c>
       <c r="K74" s="5" t="n">
-        <v>0.3928125</v>
+        <v>62.85</v>
       </c>
       <c r="L74" s="3" t="inlineStr">
         <is>
@@ -4797,7 +4824,7 @@
         <v>0</v>
       </c>
       <c r="K75" s="5" t="n">
-        <v>0.99025</v>
+        <v>79.22</v>
       </c>
       <c r="L75" s="3" t="inlineStr">
         <is>
@@ -4851,7 +4878,7 @@
         <v>0</v>
       </c>
       <c r="K76" s="5" t="n">
-        <v>0.45475</v>
+        <v>72.76000000000001</v>
       </c>
       <c r="L76" s="3" t="inlineStr">
         <is>
@@ -4907,7 +4934,7 @@
         <v>0</v>
       </c>
       <c r="K77" s="5" t="n">
-        <v>1.1685</v>
+        <v>93.48</v>
       </c>
       <c r="L77" s="3" t="inlineStr">
         <is>
@@ -4961,13 +4988,13 @@
         <v>72.45999999999999</v>
       </c>
       <c r="I78" s="24" t="n">
-        <v>0.09518518518518526</v>
+        <v>10.28</v>
       </c>
       <c r="J78" s="25" t="n">
-        <v>0.1418713773116203</v>
+        <v>0.1418713773116202</v>
       </c>
       <c r="K78" s="23" t="n">
-        <v>0.7661111111111111</v>
+        <v>82.73999999999999</v>
       </c>
       <c r="L78" s="21" t="inlineStr">
         <is>
@@ -4986,64 +5013,64 @@
       <c r="S78" s="20" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="A79" s="14" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="B79" s="14" t="inlineStr">
         <is>
           <t>674189</t>
         </is>
       </c>
-      <c r="C79" s="3" t="inlineStr">
+      <c r="C79" s="15" t="inlineStr">
         <is>
           <t>Dressing Pc Honey Mustard Cup</t>
         </is>
       </c>
-      <c r="D79" s="3" t="inlineStr">
+      <c r="D79" s="15" t="inlineStr">
         <is>
           <t>Dressing Honey Mustard Portion Cup Refrigerated</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E79" s="14" t="inlineStr">
         <is>
           <t>100/1.5 OZ</t>
         </is>
       </c>
-      <c r="F79" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G79" s="4" t="n">
+      <c r="F79" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" s="16" t="n">
         <v>28.88</v>
       </c>
-      <c r="H79" s="5" t="n">
+      <c r="H79" s="17" t="n">
         <v>28.31</v>
       </c>
-      <c r="I79" s="6" t="n">
-        <v>0.005700000000000038</v>
-      </c>
-      <c r="J79" s="7" t="n">
-        <v>0.0201342281879196</v>
-      </c>
-      <c r="K79" s="5" t="n">
-        <v>0.2888</v>
-      </c>
-      <c r="L79" s="3" t="inlineStr">
+      <c r="I79" s="18" t="n">
+        <v>0.5700000000000003</v>
+      </c>
+      <c r="J79" s="19" t="n">
+        <v>0.02013422818791948</v>
+      </c>
+      <c r="K79" s="17" t="n">
+        <v>28.88</v>
+      </c>
+      <c r="L79" s="15" t="inlineStr">
         <is>
           <t>per Case (100/1.5 OZ)</t>
         </is>
       </c>
-      <c r="M79" s="2" t="n"/>
-      <c r="N79" s="4">
+      <c r="M79" s="14" t="n"/>
+      <c r="N79" s="16">
         <f>M79*G79</f>
         <v/>
       </c>
-      <c r="O79" s="2" t="n"/>
-      <c r="P79" s="2" t="n"/>
-      <c r="Q79" s="2" t="n"/>
-      <c r="R79" s="2" t="n"/>
-      <c r="S79" s="2" t="n"/>
+      <c r="O79" s="14" t="n"/>
+      <c r="P79" s="14" t="n"/>
+      <c r="Q79" s="14" t="n"/>
+      <c r="R79" s="14" t="n"/>
+      <c r="S79" s="14" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="20" t="inlineStr">
@@ -5081,13 +5108,13 @@
         <v>18.39</v>
       </c>
       <c r="I80" s="24" t="n">
-        <v>0.08810000000000001</v>
+        <v>8.809999999999999</v>
       </c>
       <c r="J80" s="25" t="n">
-        <v>0.4790647090810223</v>
+        <v>0.4790647090810222</v>
       </c>
       <c r="K80" s="23" t="n">
-        <v>0.272</v>
+        <v>27.2</v>
       </c>
       <c r="L80" s="21" t="inlineStr">
         <is>
@@ -5106,64 +5133,64 @@
       <c r="S80" s="20" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+      <c r="A81" s="14" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="B81" s="14" t="inlineStr">
         <is>
           <t>674216</t>
         </is>
       </c>
-      <c r="C81" s="3" t="inlineStr">
+      <c r="C81" s="15" t="inlineStr">
         <is>
           <t>Dressing Pc Ranch Cup</t>
         </is>
       </c>
-      <c r="D81" s="3" t="inlineStr">
+      <c r="D81" s="15" t="inlineStr">
         <is>
           <t>Dressing Ranch Portion Control Cup Refrigerated</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E81" s="14" t="inlineStr">
         <is>
           <t>100/1.5 OZ</t>
         </is>
       </c>
-      <c r="F81" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G81" s="4" t="n">
+      <c r="F81" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" s="16" t="n">
         <v>27.2</v>
       </c>
-      <c r="H81" s="5" t="n">
+      <c r="H81" s="17" t="n">
         <v>26.64</v>
       </c>
-      <c r="I81" s="6" t="n">
-        <v>0.005599999999999994</v>
-      </c>
-      <c r="J81" s="7" t="n">
-        <v>0.02102102102102099</v>
-      </c>
-      <c r="K81" s="5" t="n">
-        <v>0.272</v>
-      </c>
-      <c r="L81" s="3" t="inlineStr">
+      <c r="I81" s="18" t="n">
+        <v>0.5599999999999987</v>
+      </c>
+      <c r="J81" s="19" t="n">
+        <v>0.02102102102102097</v>
+      </c>
+      <c r="K81" s="17" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="L81" s="15" t="inlineStr">
         <is>
           <t>per Case (100/1.5 OZ)</t>
         </is>
       </c>
-      <c r="M81" s="2" t="n"/>
-      <c r="N81" s="4">
+      <c r="M81" s="14" t="n"/>
+      <c r="N81" s="16">
         <f>M81*G81</f>
         <v/>
       </c>
-      <c r="O81" s="2" t="n"/>
-      <c r="P81" s="2" t="n"/>
-      <c r="Q81" s="2" t="n"/>
-      <c r="R81" s="2" t="n"/>
-      <c r="S81" s="2" t="n"/>
+      <c r="O81" s="14" t="n"/>
+      <c r="P81" s="14" t="n"/>
+      <c r="Q81" s="14" t="n"/>
+      <c r="R81" s="14" t="n"/>
+      <c r="S81" s="14" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="14" t="inlineStr">
@@ -5226,64 +5253,64 @@
       <c r="S82" s="14" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="14" t="inlineStr">
+      <c r="A83" s="20" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="B83" s="14" t="inlineStr">
+      <c r="B83" s="20" t="inlineStr">
         <is>
           <t>380237</t>
         </is>
       </c>
-      <c r="C83" s="15" t="inlineStr">
+      <c r="C83" s="21" t="inlineStr">
         <is>
           <t>Egg Roll Pork &amp; Vegetable</t>
         </is>
       </c>
-      <c r="D83" s="15" t="inlineStr">
+      <c r="D83" s="21" t="inlineStr">
         <is>
           <t>Eggroll Pork And Vegetable Frozen</t>
         </is>
       </c>
-      <c r="E83" s="14" t="inlineStr">
+      <c r="E83" s="20" t="inlineStr">
         <is>
           <t>72/3 OZ</t>
         </is>
       </c>
-      <c r="F83" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="G83" s="16" t="n">
+      <c r="F83" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" s="22" t="n">
         <v>56.23</v>
       </c>
-      <c r="H83" s="17" t="n">
+      <c r="H83" s="23" t="n">
         <v>53.08</v>
       </c>
-      <c r="I83" s="18" t="n">
-        <v>0.04374999999999996</v>
-      </c>
-      <c r="J83" s="19" t="n">
-        <v>0.05934438583270529</v>
-      </c>
-      <c r="K83" s="17" t="n">
-        <v>0.7809722222222222</v>
-      </c>
-      <c r="L83" s="15" t="inlineStr">
+      <c r="I83" s="24" t="n">
+        <v>3.149999999999999</v>
+      </c>
+      <c r="J83" s="25" t="n">
+        <v>0.05934438583270533</v>
+      </c>
+      <c r="K83" s="23" t="n">
+        <v>56.23</v>
+      </c>
+      <c r="L83" s="21" t="inlineStr">
         <is>
           <t>per Case (72/3 OZ)</t>
         </is>
       </c>
-      <c r="M83" s="14" t="n"/>
-      <c r="N83" s="16">
+      <c r="M83" s="20" t="n"/>
+      <c r="N83" s="22">
         <f>M83*G83</f>
         <v/>
       </c>
-      <c r="O83" s="14" t="n"/>
-      <c r="P83" s="14" t="n"/>
-      <c r="Q83" s="14" t="n"/>
-      <c r="R83" s="14" t="n"/>
-      <c r="S83" s="14" t="n"/>
+      <c r="O83" s="20" t="n"/>
+      <c r="P83" s="20" t="n"/>
+      <c r="Q83" s="20" t="n"/>
+      <c r="R83" s="20" t="n"/>
+      <c r="S83" s="20" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -6177,13 +6204,13 @@
         <v>34.62</v>
       </c>
       <c r="I99" s="24" t="n">
-        <v>0.03565000000000002</v>
+        <v>7.130000000000003</v>
       </c>
       <c r="J99" s="25" t="n">
-        <v>0.2059503177354132</v>
+        <v>0.2059503177354131</v>
       </c>
       <c r="K99" s="23" t="n">
-        <v>0.20875</v>
+        <v>41.75</v>
       </c>
       <c r="L99" s="21" t="inlineStr">
         <is>
@@ -6202,64 +6229,64 @@
       <c r="S99" s="20" t="n"/>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+      <c r="A100" s="14" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
+      <c r="B100" s="14" t="inlineStr">
         <is>
           <t>370955</t>
         </is>
       </c>
-      <c r="C100" s="3" t="inlineStr">
+      <c r="C100" s="15" t="inlineStr">
         <is>
           <t>Pizza Stick Pepperoni</t>
         </is>
       </c>
-      <c r="D100" s="3" t="inlineStr">
+      <c r="D100" s="15" t="inlineStr">
         <is>
           <t>Hot Pocket Pizza Stix Pepperoni Mozzarella Cheese Fry Or Oven Bulk Frozen</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E100" s="14" t="inlineStr">
         <is>
           <t>48/3 OZ</t>
         </is>
       </c>
-      <c r="F100" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G100" s="4" t="n">
+      <c r="F100" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G100" s="16" t="n">
         <v>32.73</v>
       </c>
-      <c r="H100" s="5" t="n">
+      <c r="H100" s="17" t="n">
         <v>32.61</v>
       </c>
-      <c r="I100" s="6" t="n">
-        <v>0.002499999999999947</v>
-      </c>
-      <c r="J100" s="7" t="n">
+      <c r="I100" s="18" t="n">
+        <v>0.1199999999999974</v>
+      </c>
+      <c r="J100" s="19" t="n">
         <v>0.003679852805887686</v>
       </c>
-      <c r="K100" s="5" t="n">
-        <v>0.6818749999999999</v>
-      </c>
-      <c r="L100" s="3" t="inlineStr">
+      <c r="K100" s="17" t="n">
+        <v>32.73</v>
+      </c>
+      <c r="L100" s="15" t="inlineStr">
         <is>
           <t>per Case (48/3 OZ)</t>
         </is>
       </c>
-      <c r="M100" s="2" t="n"/>
-      <c r="N100" s="4">
+      <c r="M100" s="14" t="n"/>
+      <c r="N100" s="16">
         <f>M100*G100</f>
         <v/>
       </c>
-      <c r="O100" s="2" t="n"/>
-      <c r="P100" s="2" t="n"/>
-      <c r="Q100" s="2" t="n"/>
-      <c r="R100" s="2" t="n"/>
-      <c r="S100" s="2" t="n"/>
+      <c r="O100" s="14" t="n"/>
+      <c r="P100" s="14" t="n"/>
+      <c r="Q100" s="14" t="n"/>
+      <c r="R100" s="14" t="n"/>
+      <c r="S100" s="14" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="20" t="inlineStr">
@@ -6413,7 +6440,7 @@
         <v>0</v>
       </c>
       <c r="K103" s="5" t="n">
-        <v>0.12835</v>
+        <v>25.67</v>
       </c>
       <c r="L103" s="3" t="inlineStr">
         <is>
@@ -6432,124 +6459,124 @@
       <c r="S103" s="2" t="n"/>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+      <c r="A104" s="8" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
+      <c r="B104" s="8" t="inlineStr">
         <is>
           <t>677079</t>
         </is>
       </c>
-      <c r="C104" s="3" t="inlineStr">
+      <c r="C104" s="9" t="inlineStr">
         <is>
           <t>Jelly Pc Assorted Plastic Cup</t>
         </is>
       </c>
-      <c r="D104" s="3" t="inlineStr">
+      <c r="D104" s="9" t="inlineStr">
         <is>
           <t>Jelly Assorted #3 Cup 80 Grape 40 Apple 80 Mixed Fruit</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E104" s="8" t="inlineStr">
         <is>
           <t>200/0.5 OZ</t>
         </is>
       </c>
-      <c r="F104" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G104" s="4" t="n">
+      <c r="F104" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G104" s="10" t="n">
         <v>17.61</v>
       </c>
-      <c r="H104" s="5" t="n">
+      <c r="H104" s="11" t="n">
         <v>17.79</v>
       </c>
-      <c r="I104" s="6" t="n">
-        <v>-0.000899999999999998</v>
-      </c>
-      <c r="J104" s="7" t="n">
+      <c r="I104" s="12" t="n">
+        <v>-0.1799999999999997</v>
+      </c>
+      <c r="J104" s="13" t="n">
         <v>-0.01011804384485664</v>
       </c>
-      <c r="K104" s="5" t="n">
-        <v>0.08805</v>
-      </c>
-      <c r="L104" s="3" t="inlineStr">
+      <c r="K104" s="11" t="n">
+        <v>17.61</v>
+      </c>
+      <c r="L104" s="9" t="inlineStr">
         <is>
           <t>per Case (200/0.5 OZ)</t>
         </is>
       </c>
-      <c r="M104" s="2" t="n"/>
-      <c r="N104" s="4">
+      <c r="M104" s="8" t="n"/>
+      <c r="N104" s="10">
         <f>M104*G104</f>
         <v/>
       </c>
-      <c r="O104" s="2" t="n"/>
-      <c r="P104" s="2" t="n"/>
-      <c r="Q104" s="2" t="n"/>
-      <c r="R104" s="2" t="n"/>
-      <c r="S104" s="2" t="n"/>
+      <c r="O104" s="8" t="n"/>
+      <c r="P104" s="8" t="n"/>
+      <c r="Q104" s="8" t="n"/>
+      <c r="R104" s="8" t="n"/>
+      <c r="S104" s="8" t="n"/>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+      <c r="A105" s="14" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
+      <c r="B105" s="14" t="inlineStr">
         <is>
           <t>190754</t>
         </is>
       </c>
-      <c r="C105" s="3" t="inlineStr">
+      <c r="C105" s="15" t="inlineStr">
         <is>
           <t>Jelly Pc Grape Pouch</t>
         </is>
       </c>
-      <c r="D105" s="3" t="inlineStr">
+      <c r="D105" s="15" t="inlineStr">
         <is>
           <t>Jelly Grape Pouch</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E105" s="14" t="inlineStr">
         <is>
           <t>200/0.5 OZ</t>
         </is>
       </c>
-      <c r="F105" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G105" s="4" t="n">
+      <c r="F105" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G105" s="16" t="n">
         <v>21.11</v>
       </c>
-      <c r="H105" s="5" t="n">
+      <c r="H105" s="17" t="n">
         <v>20.64</v>
       </c>
-      <c r="I105" s="6" t="n">
-        <v>0.002349999999999991</v>
-      </c>
-      <c r="J105" s="7" t="n">
-        <v>0.02277131782945728</v>
-      </c>
-      <c r="K105" s="5" t="n">
-        <v>0.10555</v>
-      </c>
-      <c r="L105" s="3" t="inlineStr">
+      <c r="I105" s="18" t="n">
+        <v>0.4699999999999989</v>
+      </c>
+      <c r="J105" s="19" t="n">
+        <v>0.02277131782945731</v>
+      </c>
+      <c r="K105" s="17" t="n">
+        <v>21.11</v>
+      </c>
+      <c r="L105" s="15" t="inlineStr">
         <is>
           <t>per Case (200/0.5 OZ)</t>
         </is>
       </c>
-      <c r="M105" s="2" t="n"/>
-      <c r="N105" s="4">
+      <c r="M105" s="14" t="n"/>
+      <c r="N105" s="16">
         <f>M105*G105</f>
         <v/>
       </c>
-      <c r="O105" s="2" t="n"/>
-      <c r="P105" s="2" t="n"/>
-      <c r="Q105" s="2" t="n"/>
-      <c r="R105" s="2" t="n"/>
-      <c r="S105" s="2" t="n"/>
+      <c r="O105" s="14" t="n"/>
+      <c r="P105" s="14" t="n"/>
+      <c r="Q105" s="14" t="n"/>
+      <c r="R105" s="14" t="n"/>
+      <c r="S105" s="14" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n"/>
@@ -6583,7 +6610,7 @@
         <v>0</v>
       </c>
       <c r="K106" s="5" t="n">
-        <v>0.0764</v>
+        <v>15.28</v>
       </c>
       <c r="L106" s="3" t="inlineStr">
         <is>
@@ -6602,124 +6629,124 @@
       <c r="S106" s="2" t="n"/>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+      <c r="A107" s="8" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
+      <c r="B107" s="8" t="inlineStr">
         <is>
           <t>146968</t>
         </is>
       </c>
-      <c r="C107" s="3" t="inlineStr">
+      <c r="C107" s="9" t="inlineStr">
         <is>
           <t>Ketchup Individual 9 Gram Pc</t>
         </is>
       </c>
-      <c r="D107" s="3" t="inlineStr">
+      <c r="D107" s="9" t="inlineStr">
         <is>
           <t>Ketchup Dipping Cup</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E107" s="8" t="inlineStr">
         <is>
           <t>1000/9 GRM</t>
         </is>
       </c>
-      <c r="F107" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G107" s="4" t="n">
+      <c r="F107" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G107" s="10" t="n">
         <v>23.32</v>
       </c>
-      <c r="H107" s="5" t="n">
+      <c r="H107" s="11" t="n">
         <v>37.3</v>
       </c>
-      <c r="I107" s="6" t="n">
-        <v>-0.01398</v>
-      </c>
-      <c r="J107" s="7" t="n">
+      <c r="I107" s="12" t="n">
+        <v>-13.98</v>
+      </c>
+      <c r="J107" s="13" t="n">
         <v>-0.374798927613941</v>
       </c>
-      <c r="K107" s="5" t="n">
-        <v>0.02332</v>
-      </c>
-      <c r="L107" s="3" t="inlineStr">
+      <c r="K107" s="11" t="n">
+        <v>23.32</v>
+      </c>
+      <c r="L107" s="9" t="inlineStr">
         <is>
           <t>per Case (1000/9 GRM)</t>
         </is>
       </c>
-      <c r="M107" s="2" t="n"/>
-      <c r="N107" s="4">
+      <c r="M107" s="8" t="n"/>
+      <c r="N107" s="10">
         <f>M107*G107</f>
         <v/>
       </c>
-      <c r="O107" s="2" t="n"/>
-      <c r="P107" s="2" t="n"/>
-      <c r="Q107" s="2" t="n"/>
-      <c r="R107" s="2" t="n"/>
-      <c r="S107" s="2" t="n"/>
+      <c r="O107" s="8" t="n"/>
+      <c r="P107" s="8" t="n"/>
+      <c r="Q107" s="8" t="n"/>
+      <c r="R107" s="8" t="n"/>
+      <c r="S107" s="8" t="n"/>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+      <c r="A108" s="8" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
+      <c r="B108" s="8" t="inlineStr">
         <is>
           <t>146968</t>
         </is>
       </c>
-      <c r="C108" s="3" t="inlineStr">
+      <c r="C108" s="9" t="inlineStr">
         <is>
           <t>Ketchup Individual 9 Gram Pc</t>
         </is>
       </c>
-      <c r="D108" s="3" t="inlineStr">
+      <c r="D108" s="9" t="inlineStr">
         <is>
           <t>Ketchup Fancy Foil</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E108" s="8" t="inlineStr">
         <is>
           <t>1000/9 GRM</t>
         </is>
       </c>
-      <c r="F108" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G108" s="4" t="n">
+      <c r="F108" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G108" s="10" t="n">
         <v>23.32</v>
       </c>
-      <c r="H108" s="5" t="n">
+      <c r="H108" s="11" t="n">
         <v>27.51</v>
       </c>
-      <c r="I108" s="6" t="n">
-        <v>-0.004190000000000003</v>
-      </c>
-      <c r="J108" s="7" t="n">
-        <v>-0.1523082515448929</v>
-      </c>
-      <c r="K108" s="5" t="n">
-        <v>0.02332</v>
-      </c>
-      <c r="L108" s="3" t="inlineStr">
+      <c r="I108" s="12" t="n">
+        <v>-4.190000000000001</v>
+      </c>
+      <c r="J108" s="13" t="n">
+        <v>-0.1523082515448928</v>
+      </c>
+      <c r="K108" s="11" t="n">
+        <v>23.32</v>
+      </c>
+      <c r="L108" s="9" t="inlineStr">
         <is>
           <t>per Case (1000/9 GRM)</t>
         </is>
       </c>
-      <c r="M108" s="2" t="n"/>
-      <c r="N108" s="4">
+      <c r="M108" s="8" t="n"/>
+      <c r="N108" s="10">
         <f>M108*G108</f>
         <v/>
       </c>
-      <c r="O108" s="2" t="n"/>
-      <c r="P108" s="2" t="n"/>
-      <c r="Q108" s="2" t="n"/>
-      <c r="R108" s="2" t="n"/>
-      <c r="S108" s="2" t="n"/>
+      <c r="O108" s="8" t="n"/>
+      <c r="P108" s="8" t="n"/>
+      <c r="Q108" s="8" t="n"/>
+      <c r="R108" s="8" t="n"/>
+      <c r="S108" s="8" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -7145,7 +7172,7 @@
         <v>0</v>
       </c>
       <c r="K116" s="5" t="n">
-        <v>0.08646604938271606</v>
+        <v>56.03</v>
       </c>
       <c r="L116" s="3" t="inlineStr">
         <is>
@@ -7265,7 +7292,7 @@
         <v>0</v>
       </c>
       <c r="K118" s="5" t="n">
-        <v>0.08545</v>
+        <v>17.09</v>
       </c>
       <c r="L118" s="3" t="inlineStr">
         <is>
@@ -7373,13 +7400,13 @@
         <v>40.7</v>
       </c>
       <c r="I120" s="12" t="n">
-        <v>-0.08427083333333341</v>
+        <v>-8.090000000000003</v>
       </c>
       <c r="J120" s="13" t="n">
-        <v>-0.1987714987714989</v>
+        <v>-0.1987714987714988</v>
       </c>
       <c r="K120" s="11" t="n">
-        <v>0.3396875</v>
+        <v>32.61</v>
       </c>
       <c r="L120" s="9" t="inlineStr">
         <is>
@@ -7435,7 +7462,7 @@
         <v>0</v>
       </c>
       <c r="K121" s="5" t="n">
-        <v>1.209583333333333</v>
+        <v>58.06</v>
       </c>
       <c r="L121" s="3" t="inlineStr">
         <is>
@@ -7495,7 +7522,7 @@
         <v>0</v>
       </c>
       <c r="K122" s="5" t="n">
-        <v>0.03925</v>
+        <v>7.85</v>
       </c>
       <c r="L122" s="3" t="inlineStr">
         <is>
@@ -8063,13 +8090,13 @@
         <v>37.24</v>
       </c>
       <c r="I132" s="24" t="n">
-        <v>1.649166666666667</v>
+        <v>19.79</v>
       </c>
       <c r="J132" s="25" t="n">
-        <v>0.5314178302900108</v>
+        <v>0.5314178302900107</v>
       </c>
       <c r="K132" s="23" t="n">
-        <v>4.7525</v>
+        <v>57.03</v>
       </c>
       <c r="L132" s="21" t="inlineStr">
         <is>
@@ -8465,13 +8492,13 @@
         <v>35.46</v>
       </c>
       <c r="I139" s="24" t="n">
-        <v>0.52125</v>
+        <v>20.85</v>
       </c>
       <c r="J139" s="25" t="n">
-        <v>0.5879864636209813</v>
+        <v>0.5879864636209814</v>
       </c>
       <c r="K139" s="23" t="n">
-        <v>1.40775</v>
+        <v>56.31</v>
       </c>
       <c r="L139" s="21" t="inlineStr">
         <is>
@@ -8664,64 +8691,64 @@
       <c r="S142" s="2" t="n"/>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+      <c r="A143" s="14" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
+      <c r="B143" s="14" t="inlineStr">
         <is>
           <t>384952</t>
         </is>
       </c>
-      <c r="C143" s="3" t="inlineStr">
+      <c r="C143" s="15" t="inlineStr">
         <is>
           <t>Pizza Puff Ham &amp; Cheese</t>
         </is>
       </c>
-      <c r="D143" s="3" t="inlineStr">
+      <c r="D143" s="15" t="inlineStr">
         <is>
           <t>Puff Pastry Ham And Cheese Frozen</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E143" s="14" t="inlineStr">
         <is>
           <t>48/6 OZ</t>
         </is>
       </c>
-      <c r="F143" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G143" s="4" t="n">
+      <c r="F143" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G143" s="16" t="n">
         <v>80.63</v>
       </c>
-      <c r="H143" s="5" t="n">
+      <c r="H143" s="17" t="n">
         <v>80.43000000000001</v>
       </c>
-      <c r="I143" s="6" t="n">
-        <v>0.00416666666666643</v>
-      </c>
-      <c r="J143" s="7" t="n">
+      <c r="I143" s="18" t="n">
+        <v>0.1999999999999886</v>
+      </c>
+      <c r="J143" s="19" t="n">
         <v>0.0024866343404201</v>
       </c>
-      <c r="K143" s="5" t="n">
-        <v>1.679791666666667</v>
-      </c>
-      <c r="L143" s="3" t="inlineStr">
+      <c r="K143" s="17" t="n">
+        <v>80.63</v>
+      </c>
+      <c r="L143" s="15" t="inlineStr">
         <is>
           <t>per Case (48/6 OZ)</t>
         </is>
       </c>
-      <c r="M143" s="2" t="n"/>
-      <c r="N143" s="4">
+      <c r="M143" s="14" t="n"/>
+      <c r="N143" s="16">
         <f>M143*G143</f>
         <v/>
       </c>
-      <c r="O143" s="2" t="n"/>
-      <c r="P143" s="2" t="n"/>
-      <c r="Q143" s="2" t="n"/>
-      <c r="R143" s="2" t="n"/>
-      <c r="S143" s="2" t="n"/>
+      <c r="O143" s="14" t="n"/>
+      <c r="P143" s="14" t="n"/>
+      <c r="Q143" s="14" t="n"/>
+      <c r="R143" s="14" t="n"/>
+      <c r="S143" s="14" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="14" t="inlineStr">
@@ -8759,13 +8786,13 @@
         <v>69.34999999999999</v>
       </c>
       <c r="I144" s="18" t="n">
-        <v>0.0325000000000002</v>
+        <v>1.560000000000002</v>
       </c>
       <c r="J144" s="19" t="n">
-        <v>0.0224945926459987</v>
+        <v>0.02249459264599859</v>
       </c>
       <c r="K144" s="17" t="n">
-        <v>1.477291666666667</v>
+        <v>70.91</v>
       </c>
       <c r="L144" s="15" t="inlineStr">
         <is>
@@ -9273,13 +9300,13 @@
         <v>13.49</v>
       </c>
       <c r="I153" s="18" t="n">
-        <v>0.3049999999999997</v>
+        <v>1.219999999999999</v>
       </c>
       <c r="J153" s="19" t="n">
         <v>0.02260934025203852</v>
       </c>
       <c r="K153" s="17" t="n">
-        <v>13.795</v>
+        <v>55.18</v>
       </c>
       <c r="L153" s="15" t="inlineStr">
         <is>
@@ -9298,64 +9325,64 @@
       <c r="S153" s="14" t="n"/>
     </row>
     <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+      <c r="A154" s="14" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
+      <c r="B154" s="14" t="inlineStr">
         <is>
           <t>107535</t>
         </is>
       </c>
-      <c r="C154" s="3" t="inlineStr">
+      <c r="C154" s="15" t="inlineStr">
         <is>
           <t>Sauce Pc Bbq Original Cups</t>
         </is>
       </c>
-      <c r="D154" s="3" t="inlineStr">
+      <c r="D154" s="15" t="inlineStr">
         <is>
           <t>Sauce Barbecue Original Portion Cup</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E154" s="14" t="inlineStr">
         <is>
           <t>100/1.5 OZ</t>
         </is>
       </c>
-      <c r="F154" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G154" s="4" t="n">
+      <c r="F154" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G154" s="16" t="n">
         <v>26.63</v>
       </c>
-      <c r="H154" s="5" t="n">
+      <c r="H154" s="17" t="n">
         <v>26.06</v>
       </c>
-      <c r="I154" s="6" t="n">
-        <v>0.005699999999999983</v>
-      </c>
-      <c r="J154" s="7" t="n">
-        <v>0.02187260168841129</v>
-      </c>
-      <c r="K154" s="5" t="n">
-        <v>0.2663</v>
-      </c>
-      <c r="L154" s="3" t="inlineStr">
+      <c r="I154" s="18" t="n">
+        <v>0.5700000000000003</v>
+      </c>
+      <c r="J154" s="19" t="n">
+        <v>0.02187260168841137</v>
+      </c>
+      <c r="K154" s="17" t="n">
+        <v>26.63</v>
+      </c>
+      <c r="L154" s="15" t="inlineStr">
         <is>
           <t>per Case (100/1.5 OZ)</t>
         </is>
       </c>
-      <c r="M154" s="2" t="n"/>
-      <c r="N154" s="4">
+      <c r="M154" s="14" t="n"/>
+      <c r="N154" s="16">
         <f>M154*G154</f>
         <v/>
       </c>
-      <c r="O154" s="2" t="n"/>
-      <c r="P154" s="2" t="n"/>
-      <c r="Q154" s="2" t="n"/>
-      <c r="R154" s="2" t="n"/>
-      <c r="S154" s="2" t="n"/>
+      <c r="O154" s="14" t="n"/>
+      <c r="P154" s="14" t="n"/>
+      <c r="Q154" s="14" t="n"/>
+      <c r="R154" s="14" t="n"/>
+      <c r="S154" s="14" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="20" t="inlineStr">
@@ -9418,124 +9445,124 @@
       <c r="S155" s="20" t="n"/>
     </row>
     <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+      <c r="A156" s="8" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
+      <c r="B156" s="8" t="inlineStr">
         <is>
           <t>301629</t>
         </is>
       </c>
-      <c r="C156" s="3" t="inlineStr">
+      <c r="C156" s="9" t="inlineStr">
         <is>
           <t>Sauce Cocktail Cups Gf</t>
         </is>
       </c>
-      <c r="D156" s="3" t="inlineStr">
+      <c r="D156" s="9" t="inlineStr">
         <is>
           <t>Sauce Cocktail</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E156" s="8" t="inlineStr">
         <is>
           <t>100/1.5 OZ</t>
         </is>
       </c>
-      <c r="F156" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G156" s="4" t="n">
+      <c r="F156" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G156" s="10" t="n">
         <v>28.94</v>
       </c>
-      <c r="H156" s="5" t="n">
+      <c r="H156" s="11" t="n">
         <v>29.95</v>
       </c>
-      <c r="I156" s="6" t="n">
-        <v>-0.0101</v>
-      </c>
-      <c r="J156" s="7" t="n">
-        <v>-0.03372287145242069</v>
-      </c>
-      <c r="K156" s="5" t="n">
-        <v>0.2894</v>
-      </c>
-      <c r="L156" s="3" t="inlineStr">
+      <c r="I156" s="12" t="n">
+        <v>-1.009999999999998</v>
+      </c>
+      <c r="J156" s="13" t="n">
+        <v>-0.03372287145242064</v>
+      </c>
+      <c r="K156" s="11" t="n">
+        <v>28.94</v>
+      </c>
+      <c r="L156" s="9" t="inlineStr">
         <is>
           <t>per Case (100/1.5 OZ)</t>
         </is>
       </c>
-      <c r="M156" s="2" t="n"/>
-      <c r="N156" s="4">
+      <c r="M156" s="8" t="n"/>
+      <c r="N156" s="10">
         <f>M156*G156</f>
         <v/>
       </c>
-      <c r="O156" s="2" t="n"/>
-      <c r="P156" s="2" t="n"/>
-      <c r="Q156" s="2" t="n"/>
-      <c r="R156" s="2" t="n"/>
-      <c r="S156" s="2" t="n"/>
+      <c r="O156" s="8" t="n"/>
+      <c r="P156" s="8" t="n"/>
+      <c r="Q156" s="8" t="n"/>
+      <c r="R156" s="8" t="n"/>
+      <c r="S156" s="8" t="n"/>
     </row>
     <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+      <c r="A157" s="14" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
+      <c r="B157" s="14" t="inlineStr">
         <is>
           <t>674170</t>
         </is>
       </c>
-      <c r="C157" s="3" t="inlineStr">
+      <c r="C157" s="15" t="inlineStr">
         <is>
           <t>Sauce Pc Hot Texas Pete</t>
         </is>
       </c>
-      <c r="D157" s="3" t="inlineStr">
+      <c r="D157" s="15" t="inlineStr">
         <is>
           <t>Sauce Hot Original Packet Texas Pete</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E157" s="14" t="inlineStr">
         <is>
           <t>200/7 GRM</t>
         </is>
       </c>
-      <c r="F157" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G157" s="4" t="n">
+      <c r="F157" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G157" s="16" t="n">
         <v>15.68</v>
       </c>
-      <c r="H157" s="5" t="n">
+      <c r="H157" s="17" t="n">
         <v>14.55</v>
       </c>
-      <c r="I157" s="6" t="n">
-        <v>0.005649999999999988</v>
-      </c>
-      <c r="J157" s="7" t="n">
-        <v>0.07766323024054966</v>
-      </c>
-      <c r="K157" s="5" t="n">
-        <v>0.0784</v>
-      </c>
-      <c r="L157" s="3" t="inlineStr">
+      <c r="I157" s="18" t="n">
+        <v>1.129999999999999</v>
+      </c>
+      <c r="J157" s="19" t="n">
+        <v>0.07766323024054976</v>
+      </c>
+      <c r="K157" s="17" t="n">
+        <v>15.68</v>
+      </c>
+      <c r="L157" s="15" t="inlineStr">
         <is>
           <t>per Case (200/7 GRM)</t>
         </is>
       </c>
-      <c r="M157" s="2" t="n"/>
-      <c r="N157" s="4">
+      <c r="M157" s="14" t="n"/>
+      <c r="N157" s="16">
         <f>M157*G157</f>
         <v/>
       </c>
-      <c r="O157" s="2" t="n"/>
-      <c r="P157" s="2" t="n"/>
-      <c r="Q157" s="2" t="n"/>
-      <c r="R157" s="2" t="n"/>
-      <c r="S157" s="2" t="n"/>
+      <c r="O157" s="14" t="n"/>
+      <c r="P157" s="14" t="n"/>
+      <c r="Q157" s="14" t="n"/>
+      <c r="R157" s="14" t="n"/>
+      <c r="S157" s="14" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -9592,64 +9619,64 @@
       <c r="S158" s="2" t="n"/>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+      <c r="A159" s="14" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
+      <c r="B159" s="14" t="inlineStr">
         <is>
           <t>115983</t>
         </is>
       </c>
-      <c r="C159" s="3" t="inlineStr">
+      <c r="C159" s="15" t="inlineStr">
         <is>
           <t>Sauce Pc Sweet N Sour Cup</t>
         </is>
       </c>
-      <c r="D159" s="3" t="inlineStr">
+      <c r="D159" s="15" t="inlineStr">
         <is>
           <t>Sauce Sweet And Sour Cup</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E159" s="14" t="inlineStr">
         <is>
           <t>100/1 OZ</t>
         </is>
       </c>
-      <c r="F159" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G159" s="4" t="n">
+      <c r="F159" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G159" s="16" t="n">
         <v>20.31</v>
       </c>
-      <c r="H159" s="5" t="n">
+      <c r="H159" s="17" t="n">
         <v>19.86</v>
       </c>
-      <c r="I159" s="6" t="n">
-        <v>0.004499999999999976</v>
-      </c>
-      <c r="J159" s="7" t="n">
-        <v>0.0226586102719032</v>
-      </c>
-      <c r="K159" s="5" t="n">
-        <v>0.2031</v>
-      </c>
-      <c r="L159" s="3" t="inlineStr">
+      <c r="I159" s="18" t="n">
+        <v>0.4499999999999993</v>
+      </c>
+      <c r="J159" s="19" t="n">
+        <v>0.02265861027190329</v>
+      </c>
+      <c r="K159" s="17" t="n">
+        <v>20.31</v>
+      </c>
+      <c r="L159" s="15" t="inlineStr">
         <is>
           <t>per Case (100/1 OZ)</t>
         </is>
       </c>
-      <c r="M159" s="2" t="n"/>
-      <c r="N159" s="4">
+      <c r="M159" s="14" t="n"/>
+      <c r="N159" s="16">
         <f>M159*G159</f>
         <v/>
       </c>
-      <c r="O159" s="2" t="n"/>
-      <c r="P159" s="2" t="n"/>
-      <c r="Q159" s="2" t="n"/>
-      <c r="R159" s="2" t="n"/>
-      <c r="S159" s="2" t="n"/>
+      <c r="O159" s="14" t="n"/>
+      <c r="P159" s="14" t="n"/>
+      <c r="Q159" s="14" t="n"/>
+      <c r="R159" s="14" t="n"/>
+      <c r="S159" s="14" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -9708,64 +9735,64 @@
       <c r="S160" s="2" t="n"/>
     </row>
     <row r="161">
-      <c r="A161" s="2" t="inlineStr">
+      <c r="A161" s="14" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
+      <c r="B161" s="14" t="inlineStr">
         <is>
           <t>674626</t>
         </is>
       </c>
-      <c r="C161" s="3" t="inlineStr">
+      <c r="C161" s="15" t="inlineStr">
         <is>
           <t>Sauce Pc Tartar Cup</t>
         </is>
       </c>
-      <c r="D161" s="3" t="inlineStr">
+      <c r="D161" s="15" t="inlineStr">
         <is>
           <t>Sauce Tartar Portion Cup Refrigerated</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="E161" s="14" t="inlineStr">
         <is>
           <t>100/1.5 OZ</t>
         </is>
       </c>
-      <c r="F161" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G161" s="4" t="n">
+      <c r="F161" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G161" s="16" t="n">
         <v>32.02</v>
       </c>
-      <c r="H161" s="5" t="n">
+      <c r="H161" s="17" t="n">
         <v>31.45</v>
       </c>
-      <c r="I161" s="6" t="n">
-        <v>0.005700000000000038</v>
-      </c>
-      <c r="J161" s="7" t="n">
+      <c r="I161" s="18" t="n">
+        <v>0.5700000000000038</v>
+      </c>
+      <c r="J161" s="19" t="n">
         <v>0.0181240063593006</v>
       </c>
-      <c r="K161" s="5" t="n">
-        <v>0.3202</v>
-      </c>
-      <c r="L161" s="3" t="inlineStr">
+      <c r="K161" s="17" t="n">
+        <v>32.02</v>
+      </c>
+      <c r="L161" s="15" t="inlineStr">
         <is>
           <t>per Case (100/1.5 OZ)</t>
         </is>
       </c>
-      <c r="M161" s="2" t="n"/>
-      <c r="N161" s="4">
+      <c r="M161" s="14" t="n"/>
+      <c r="N161" s="16">
         <f>M161*G161</f>
         <v/>
       </c>
-      <c r="O161" s="2" t="n"/>
-      <c r="P161" s="2" t="n"/>
-      <c r="Q161" s="2" t="n"/>
-      <c r="R161" s="2" t="n"/>
-      <c r="S161" s="2" t="n"/>
+      <c r="O161" s="14" t="n"/>
+      <c r="P161" s="14" t="n"/>
+      <c r="Q161" s="14" t="n"/>
+      <c r="R161" s="14" t="n"/>
+      <c r="S161" s="14" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="14" t="inlineStr">
@@ -9989,7 +10016,7 @@
         <v>0</v>
       </c>
       <c r="K165" s="5" t="n">
-        <v>0.60575</v>
+        <v>48.46</v>
       </c>
       <c r="L165" s="3" t="inlineStr">
         <is>
@@ -10538,52 +10565,52 @@
       <c r="S174" s="8" t="n"/>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="inlineStr">
+      <c r="A175" s="26" t="inlineStr">
         <is>
           <t>CAN</t>
         </is>
       </c>
-      <c r="B175" s="2" t="n"/>
-      <c r="C175" s="3" t="inlineStr">
+      <c r="B175" s="26" t="n"/>
+      <c r="C175" s="27" t="inlineStr">
         <is>
           <t>Soup Cream of Mushroom</t>
         </is>
       </c>
-      <c r="D175" s="3" t="n"/>
-      <c r="E175" s="2" t="n"/>
-      <c r="F175" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G175" s="4" t="n">
+      <c r="D175" s="27" t="n"/>
+      <c r="E175" s="26" t="n"/>
+      <c r="F175" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G175" s="28" t="n">
         <v>5.79</v>
       </c>
-      <c r="H175" s="5" t="n">
+      <c r="H175" s="29" t="n">
         <v>5.79</v>
       </c>
-      <c r="I175" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J175" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K175" s="5" t="n">
+      <c r="I175" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J175" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K175" s="29" t="n">
         <v>5.79</v>
       </c>
-      <c r="L175" s="3" t="inlineStr">
+      <c r="L175" s="27" t="inlineStr">
         <is>
           <t>per Can (None)</t>
         </is>
       </c>
-      <c r="M175" s="2" t="n"/>
-      <c r="N175" s="4">
+      <c r="M175" s="26" t="n"/>
+      <c r="N175" s="28">
         <f>M175*G175</f>
         <v/>
       </c>
-      <c r="O175" s="2" t="n"/>
-      <c r="P175" s="2" t="n"/>
-      <c r="Q175" s="2" t="n"/>
-      <c r="R175" s="2" t="n"/>
-      <c r="S175" s="2" t="n"/>
+      <c r="O175" s="26" t="n"/>
+      <c r="P175" s="26" t="n"/>
+      <c r="Q175" s="26" t="n"/>
+      <c r="R175" s="26" t="n"/>
+      <c r="S175" s="26" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -10760,64 +10787,64 @@
       <c r="S178" s="8" t="n"/>
     </row>
     <row r="179">
-      <c r="A179" s="2" t="inlineStr">
+      <c r="A179" s="20" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="B179" s="2" t="inlineStr">
+      <c r="B179" s="20" t="inlineStr">
         <is>
           <t>008128</t>
         </is>
       </c>
-      <c r="C179" s="3" t="inlineStr">
+      <c r="C179" s="21" t="inlineStr">
         <is>
           <t>Syrup Pc Pancake Maple Premium</t>
         </is>
       </c>
-      <c r="D179" s="3" t="inlineStr">
+      <c r="D179" s="21" t="inlineStr">
         <is>
           <t>Syrup Breakfast Maple Imitation 1.4 Ounce Portion Cup</t>
         </is>
       </c>
-      <c r="E179" s="2" t="inlineStr">
+      <c r="E179" s="20" t="inlineStr">
         <is>
           <t>100/1.5 OZ</t>
         </is>
       </c>
-      <c r="F179" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G179" s="4" t="n">
+      <c r="F179" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G179" s="22" t="n">
         <v>18.85</v>
       </c>
-      <c r="H179" s="5" t="n">
+      <c r="H179" s="23" t="n">
         <v>16.18</v>
       </c>
-      <c r="I179" s="6" t="n">
-        <v>0.0267</v>
-      </c>
-      <c r="J179" s="7" t="n">
-        <v>0.1650185414091471</v>
-      </c>
-      <c r="K179" s="5" t="n">
-        <v>0.1885</v>
-      </c>
-      <c r="L179" s="3" t="inlineStr">
+      <c r="I179" s="24" t="n">
+        <v>2.670000000000002</v>
+      </c>
+      <c r="J179" s="25" t="n">
+        <v>0.1650185414091472</v>
+      </c>
+      <c r="K179" s="23" t="n">
+        <v>18.85</v>
+      </c>
+      <c r="L179" s="21" t="inlineStr">
         <is>
           <t>per Case (100/1.5 OZ)</t>
         </is>
       </c>
-      <c r="M179" s="2" t="n"/>
-      <c r="N179" s="4">
+      <c r="M179" s="20" t="n"/>
+      <c r="N179" s="22">
         <f>M179*G179</f>
         <v/>
       </c>
-      <c r="O179" s="2" t="n"/>
-      <c r="P179" s="2" t="n"/>
-      <c r="Q179" s="2" t="n"/>
-      <c r="R179" s="2" t="n"/>
-      <c r="S179" s="2" t="n"/>
+      <c r="O179" s="20" t="n"/>
+      <c r="P179" s="20" t="n"/>
+      <c r="Q179" s="20" t="n"/>
+      <c r="R179" s="20" t="n"/>
+      <c r="S179" s="20" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -11782,244 +11809,244 @@
       <c r="S196" s="20" t="n"/>
     </row>
     <row r="197">
-      <c r="A197" s="2" t="inlineStr">
+      <c r="A197" s="26" t="inlineStr">
         <is>
           <t>EACH</t>
         </is>
       </c>
-      <c r="B197" s="2" t="n"/>
-      <c r="C197" s="3" t="inlineStr">
+      <c r="B197" s="26" t="n"/>
+      <c r="C197" s="27" t="inlineStr">
         <is>
           <t>Lettuce Head</t>
         </is>
       </c>
-      <c r="D197" s="3" t="n"/>
-      <c r="E197" s="2" t="n"/>
-      <c r="F197" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G197" s="4" t="n">
+      <c r="D197" s="27" t="n"/>
+      <c r="E197" s="26" t="n"/>
+      <c r="F197" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G197" s="28" t="n">
         <v>3.99</v>
       </c>
-      <c r="H197" s="5" t="n">
+      <c r="H197" s="29" t="n">
         <v>3.99</v>
       </c>
-      <c r="I197" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J197" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K197" s="5" t="n">
+      <c r="I197" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J197" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K197" s="29" t="n">
         <v>3.99</v>
       </c>
-      <c r="L197" s="3" t="inlineStr">
+      <c r="L197" s="27" t="inlineStr">
         <is>
           <t>per Each (None)</t>
         </is>
       </c>
-      <c r="M197" s="2" t="n"/>
-      <c r="N197" s="4">
+      <c r="M197" s="26" t="n"/>
+      <c r="N197" s="28">
         <f>M197*G197</f>
         <v/>
       </c>
-      <c r="O197" s="2" t="n"/>
-      <c r="P197" s="2" t="n"/>
-      <c r="Q197" s="2" t="n"/>
-      <c r="R197" s="2" t="n"/>
-      <c r="S197" s="2" t="n"/>
+      <c r="O197" s="26" t="n"/>
+      <c r="P197" s="26" t="n"/>
+      <c r="Q197" s="26" t="n"/>
+      <c r="R197" s="26" t="n"/>
+      <c r="S197" s="26" t="n"/>
     </row>
     <row r="198">
-      <c r="A198" s="2" t="inlineStr">
+      <c r="A198" s="26" t="inlineStr">
         <is>
           <t>EACH</t>
         </is>
       </c>
-      <c r="B198" s="2" t="n"/>
-      <c r="C198" s="3" t="inlineStr">
+      <c r="B198" s="26" t="n"/>
+      <c r="C198" s="27" t="inlineStr">
         <is>
           <t>Tomato</t>
         </is>
       </c>
-      <c r="D198" s="3" t="n"/>
-      <c r="E198" s="2" t="n"/>
-      <c r="F198" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G198" s="4" t="n">
+      <c r="D198" s="27" t="n"/>
+      <c r="E198" s="26" t="n"/>
+      <c r="F198" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G198" s="28" t="n">
         <v>2.49</v>
       </c>
-      <c r="H198" s="5" t="n">
+      <c r="H198" s="29" t="n">
         <v>2.49</v>
       </c>
-      <c r="I198" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J198" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K198" s="5" t="n">
+      <c r="I198" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J198" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K198" s="29" t="n">
         <v>2.49</v>
       </c>
-      <c r="L198" s="3" t="inlineStr">
+      <c r="L198" s="27" t="inlineStr">
         <is>
           <t>per Each (None)</t>
         </is>
       </c>
-      <c r="M198" s="2" t="n"/>
-      <c r="N198" s="4">
+      <c r="M198" s="26" t="n"/>
+      <c r="N198" s="28">
         <f>M198*G198</f>
         <v/>
       </c>
-      <c r="O198" s="2" t="n"/>
-      <c r="P198" s="2" t="n"/>
-      <c r="Q198" s="2" t="n"/>
-      <c r="R198" s="2" t="n"/>
-      <c r="S198" s="2" t="n"/>
+      <c r="O198" s="26" t="n"/>
+      <c r="P198" s="26" t="n"/>
+      <c r="Q198" s="26" t="n"/>
+      <c r="R198" s="26" t="n"/>
+      <c r="S198" s="26" t="n"/>
     </row>
     <row r="199">
-      <c r="A199" s="2" t="inlineStr">
+      <c r="A199" s="26" t="inlineStr">
         <is>
           <t>BAG</t>
         </is>
       </c>
-      <c r="B199" s="2" t="n"/>
-      <c r="C199" s="3" t="inlineStr">
+      <c r="B199" s="26" t="n"/>
+      <c r="C199" s="27" t="inlineStr">
         <is>
           <t>Creole Marinade</t>
         </is>
       </c>
-      <c r="D199" s="3" t="n"/>
-      <c r="E199" s="2" t="n"/>
-      <c r="F199" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G199" s="4" t="n">
+      <c r="D199" s="27" t="n"/>
+      <c r="E199" s="26" t="n"/>
+      <c r="F199" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G199" s="28" t="n">
         <v>1.81</v>
       </c>
-      <c r="H199" s="5" t="n">
+      <c r="H199" s="29" t="n">
         <v>1.81</v>
       </c>
-      <c r="I199" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J199" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K199" s="5" t="n">
+      <c r="I199" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J199" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K199" s="29" t="n">
         <v>1.81</v>
       </c>
-      <c r="L199" s="3" t="inlineStr">
+      <c r="L199" s="27" t="inlineStr">
         <is>
           <t>per Bag (None)</t>
         </is>
       </c>
-      <c r="M199" s="2" t="n"/>
-      <c r="N199" s="4">
+      <c r="M199" s="26" t="n"/>
+      <c r="N199" s="28">
         <f>M199*G199</f>
         <v/>
       </c>
-      <c r="O199" s="2" t="n"/>
-      <c r="P199" s="2" t="n"/>
-      <c r="Q199" s="2" t="n"/>
-      <c r="R199" s="2" t="n"/>
-      <c r="S199" s="2" t="n"/>
+      <c r="O199" s="26" t="n"/>
+      <c r="P199" s="26" t="n"/>
+      <c r="Q199" s="26" t="n"/>
+      <c r="R199" s="26" t="n"/>
+      <c r="S199" s="26" t="n"/>
     </row>
     <row r="200">
-      <c r="A200" s="2" t="inlineStr">
+      <c r="A200" s="26" t="inlineStr">
         <is>
           <t>BAG</t>
         </is>
       </c>
-      <c r="B200" s="2" t="n"/>
-      <c r="C200" s="3" t="inlineStr">
+      <c r="B200" s="26" t="n"/>
+      <c r="C200" s="27" t="inlineStr">
         <is>
           <t>Spicy Marinade</t>
         </is>
       </c>
-      <c r="D200" s="3" t="n"/>
-      <c r="E200" s="2" t="n"/>
-      <c r="F200" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G200" s="4" t="n">
+      <c r="D200" s="27" t="n"/>
+      <c r="E200" s="26" t="n"/>
+      <c r="F200" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G200" s="28" t="n">
         <v>5.27</v>
       </c>
-      <c r="H200" s="5" t="n">
+      <c r="H200" s="29" t="n">
         <v>5.27</v>
       </c>
-      <c r="I200" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J200" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K200" s="5" t="n">
+      <c r="I200" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J200" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K200" s="29" t="n">
         <v>5.27</v>
       </c>
-      <c r="L200" s="3" t="inlineStr">
+      <c r="L200" s="27" t="inlineStr">
         <is>
           <t>per Bag (None)</t>
         </is>
       </c>
-      <c r="M200" s="2" t="n"/>
-      <c r="N200" s="4">
+      <c r="M200" s="26" t="n"/>
+      <c r="N200" s="28">
         <f>M200*G200</f>
         <v/>
       </c>
-      <c r="O200" s="2" t="n"/>
-      <c r="P200" s="2" t="n"/>
-      <c r="Q200" s="2" t="n"/>
-      <c r="R200" s="2" t="n"/>
-      <c r="S200" s="2" t="n"/>
+      <c r="O200" s="26" t="n"/>
+      <c r="P200" s="26" t="n"/>
+      <c r="Q200" s="26" t="n"/>
+      <c r="R200" s="26" t="n"/>
+      <c r="S200" s="26" t="n"/>
     </row>
     <row r="201">
-      <c r="A201" s="2" t="inlineStr">
+      <c r="A201" s="26" t="inlineStr">
         <is>
           <t>BAG</t>
         </is>
       </c>
-      <c r="B201" s="2" t="n"/>
-      <c r="C201" s="3" t="inlineStr">
+      <c r="B201" s="26" t="n"/>
+      <c r="C201" s="27" t="inlineStr">
         <is>
           <t>Batter Mix</t>
         </is>
       </c>
-      <c r="D201" s="3" t="n"/>
-      <c r="E201" s="2" t="n"/>
-      <c r="F201" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G201" s="4" t="n">
+      <c r="D201" s="27" t="n"/>
+      <c r="E201" s="26" t="n"/>
+      <c r="F201" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G201" s="28" t="n">
         <v>2.5</v>
       </c>
-      <c r="H201" s="5" t="n">
+      <c r="H201" s="29" t="n">
         <v>2.5</v>
       </c>
-      <c r="I201" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J201" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K201" s="5" t="n">
+      <c r="I201" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J201" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K201" s="29" t="n">
         <v>2.5</v>
       </c>
-      <c r="L201" s="3" t="inlineStr">
+      <c r="L201" s="27" t="inlineStr">
         <is>
           <t>per Bag (None)</t>
         </is>
       </c>
-      <c r="M201" s="2" t="n"/>
-      <c r="N201" s="4">
+      <c r="M201" s="26" t="n"/>
+      <c r="N201" s="28">
         <f>M201*G201</f>
         <v/>
       </c>
-      <c r="O201" s="2" t="n"/>
-      <c r="P201" s="2" t="n"/>
-      <c r="Q201" s="2" t="n"/>
-      <c r="R201" s="2" t="n"/>
-      <c r="S201" s="2" t="n"/>
+      <c r="O201" s="26" t="n"/>
+      <c r="P201" s="26" t="n"/>
+      <c r="Q201" s="26" t="n"/>
+      <c r="R201" s="26" t="n"/>
+      <c r="S201" s="26" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n"/>
@@ -12054,1659 +12081,1669 @@
       <c r="S202" s="2" t="n"/>
     </row>
     <row r="203">
-      <c r="A203" s="2" t="inlineStr">
+      <c r="A203" s="26" t="inlineStr">
         <is>
           <t>PACK</t>
         </is>
       </c>
-      <c r="B203" s="2" t="n"/>
-      <c r="C203" s="3" t="inlineStr">
+      <c r="B203" s="26" t="n"/>
+      <c r="C203" s="27" t="inlineStr">
         <is>
           <t>Bayou Blend Pork</t>
         </is>
       </c>
-      <c r="D203" s="3" t="n"/>
-      <c r="E203" s="2" t="inlineStr">
+      <c r="D203" s="27" t="n"/>
+      <c r="E203" s="26" t="inlineStr">
         <is>
           <t>5 Packs</t>
         </is>
       </c>
-      <c r="F203" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G203" s="4" t="n">
+      <c r="F203" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G203" s="28" t="n">
         <v>7.48</v>
       </c>
-      <c r="H203" s="5" t="n">
+      <c r="H203" s="29" t="n">
         <v>7.48</v>
       </c>
-      <c r="I203" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J203" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K203" s="5" t="n">
+      <c r="I203" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J203" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K203" s="29" t="n">
         <v>1.496</v>
       </c>
-      <c r="L203" s="3" t="inlineStr">
+      <c r="L203" s="27" t="inlineStr">
         <is>
           <t>per Pack (5 Packs)</t>
         </is>
       </c>
-      <c r="M203" s="2" t="n"/>
-      <c r="N203" s="4">
+      <c r="M203" s="26" t="n"/>
+      <c r="N203" s="28">
         <f>M203*G203</f>
         <v/>
       </c>
-      <c r="O203" s="2" t="n"/>
-      <c r="P203" s="2" t="n"/>
-      <c r="Q203" s="2" t="n"/>
-      <c r="R203" s="2" t="n"/>
-      <c r="S203" s="2" t="n"/>
+      <c r="O203" s="26" t="n"/>
+      <c r="P203" s="26" t="n"/>
+      <c r="Q203" s="26" t="n"/>
+      <c r="R203" s="26" t="n"/>
+      <c r="S203" s="26" t="n"/>
     </row>
     <row r="204">
-      <c r="A204" s="2" t="inlineStr">
+      <c r="A204" s="26" t="inlineStr">
         <is>
           <t>PACK</t>
         </is>
       </c>
-      <c r="B204" s="2" t="n"/>
-      <c r="C204" s="3" t="inlineStr">
+      <c r="B204" s="26" t="n"/>
+      <c r="C204" s="27" t="inlineStr">
         <is>
           <t>Bayou Blend Alligator</t>
         </is>
       </c>
-      <c r="D204" s="3" t="n"/>
-      <c r="E204" s="2" t="inlineStr">
+      <c r="D204" s="27" t="n"/>
+      <c r="E204" s="26" t="inlineStr">
         <is>
           <t>5 Pack</t>
         </is>
       </c>
-      <c r="F204" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G204" s="4" t="n">
+      <c r="F204" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G204" s="28" t="n">
         <v>9.890000000000001</v>
       </c>
-      <c r="H204" s="5" t="n">
+      <c r="H204" s="29" t="n">
         <v>9.890000000000001</v>
       </c>
-      <c r="I204" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J204" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K204" s="5" t="n">
+      <c r="I204" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J204" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K204" s="29" t="n">
         <v>1.978</v>
       </c>
-      <c r="L204" s="3" t="inlineStr">
+      <c r="L204" s="27" t="inlineStr">
         <is>
           <t>per Pack (5 Pack)</t>
         </is>
       </c>
-      <c r="M204" s="2" t="n"/>
-      <c r="N204" s="4">
+      <c r="M204" s="26" t="n"/>
+      <c r="N204" s="28">
         <f>M204*G204</f>
         <v/>
       </c>
-      <c r="O204" s="2" t="n"/>
-      <c r="P204" s="2" t="n"/>
-      <c r="Q204" s="2" t="n"/>
-      <c r="R204" s="2" t="n"/>
-      <c r="S204" s="2" t="n"/>
+      <c r="O204" s="26" t="n"/>
+      <c r="P204" s="26" t="n"/>
+      <c r="Q204" s="26" t="n"/>
+      <c r="R204" s="26" t="n"/>
+      <c r="S204" s="26" t="n"/>
     </row>
     <row r="205">
-      <c r="A205" s="2" t="inlineStr">
+      <c r="A205" s="26" t="inlineStr">
         <is>
           <t>PACK</t>
         </is>
       </c>
-      <c r="B205" s="2" t="n"/>
-      <c r="C205" s="3" t="inlineStr">
+      <c r="B205" s="26" t="n"/>
+      <c r="C205" s="27" t="inlineStr">
         <is>
           <t>Bayou Blend Crawfish</t>
         </is>
       </c>
-      <c r="D205" s="3" t="n"/>
-      <c r="E205" s="2" t="inlineStr">
+      <c r="D205" s="27" t="n"/>
+      <c r="E205" s="26" t="inlineStr">
         <is>
           <t>5 Packs</t>
         </is>
       </c>
-      <c r="F205" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G205" s="4" t="n">
+      <c r="F205" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G205" s="28" t="n">
         <v>9.1</v>
       </c>
-      <c r="H205" s="5" t="n">
+      <c r="H205" s="29" t="n">
         <v>9.1</v>
       </c>
-      <c r="I205" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J205" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K205" s="5" t="n">
+      <c r="I205" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J205" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K205" s="29" t="n">
         <v>1.82</v>
       </c>
-      <c r="L205" s="3" t="inlineStr">
+      <c r="L205" s="27" t="inlineStr">
         <is>
           <t>per Pack (5 Packs)</t>
         </is>
       </c>
-      <c r="M205" s="2" t="n"/>
-      <c r="N205" s="4">
+      <c r="M205" s="26" t="n"/>
+      <c r="N205" s="28">
         <f>M205*G205</f>
         <v/>
       </c>
-      <c r="O205" s="2" t="n"/>
-      <c r="P205" s="2" t="n"/>
-      <c r="Q205" s="2" t="n"/>
-      <c r="R205" s="2" t="n"/>
-      <c r="S205" s="2" t="n"/>
+      <c r="O205" s="26" t="n"/>
+      <c r="P205" s="26" t="n"/>
+      <c r="Q205" s="26" t="n"/>
+      <c r="R205" s="26" t="n"/>
+      <c r="S205" s="26" t="n"/>
     </row>
     <row r="206">
-      <c r="A206" s="2" t="inlineStr">
+      <c r="A206" s="26" t="inlineStr">
         <is>
           <t>PACK</t>
         </is>
       </c>
-      <c r="B206" s="2" t="n"/>
-      <c r="C206" s="3" t="inlineStr">
+      <c r="B206" s="26" t="n"/>
+      <c r="C206" s="27" t="inlineStr">
         <is>
           <t>Bayou Blend Shrimp</t>
         </is>
       </c>
-      <c r="D206" s="3" t="n"/>
-      <c r="E206" s="2" t="inlineStr">
+      <c r="D206" s="27" t="n"/>
+      <c r="E206" s="26" t="inlineStr">
         <is>
           <t>5 Packs</t>
         </is>
       </c>
-      <c r="F206" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G206" s="4" t="n">
+      <c r="F206" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G206" s="28" t="n">
         <v>8.08</v>
       </c>
-      <c r="H206" s="5" t="n">
+      <c r="H206" s="29" t="n">
         <v>8.08</v>
       </c>
-      <c r="I206" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J206" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K206" s="5" t="n">
+      <c r="I206" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J206" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K206" s="29" t="n">
         <v>1.616</v>
       </c>
-      <c r="L206" s="3" t="inlineStr">
+      <c r="L206" s="27" t="inlineStr">
         <is>
           <t>per Pack (5 Packs)</t>
         </is>
       </c>
-      <c r="M206" s="2" t="n"/>
-      <c r="N206" s="4">
+      <c r="M206" s="26" t="n"/>
+      <c r="N206" s="28">
         <f>M206*G206</f>
         <v/>
       </c>
-      <c r="O206" s="2" t="n"/>
-      <c r="P206" s="2" t="n"/>
-      <c r="Q206" s="2" t="n"/>
-      <c r="R206" s="2" t="n"/>
-      <c r="S206" s="2" t="n"/>
+      <c r="O206" s="26" t="n"/>
+      <c r="P206" s="26" t="n"/>
+      <c r="Q206" s="26" t="n"/>
+      <c r="R206" s="26" t="n"/>
+      <c r="S206" s="26" t="n"/>
     </row>
     <row r="207">
-      <c r="A207" s="2" t="inlineStr">
+      <c r="A207" s="26" t="inlineStr">
         <is>
           <t>CAN</t>
         </is>
       </c>
-      <c r="B207" s="2" t="n"/>
-      <c r="C207" s="3" t="inlineStr">
+      <c r="B207" s="26" t="n"/>
+      <c r="C207" s="27" t="inlineStr">
         <is>
           <t>Peanuts Regular/Cajun</t>
         </is>
       </c>
-      <c r="D207" s="3" t="n"/>
-      <c r="E207" s="2" t="inlineStr">
+      <c r="D207" s="27" t="n"/>
+      <c r="E207" s="26" t="inlineStr">
         <is>
           <t>6 Cans</t>
         </is>
       </c>
-      <c r="F207" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G207" s="4" t="n">
+      <c r="F207" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G207" s="28" t="n">
         <v>8.33</v>
       </c>
-      <c r="H207" s="5" t="n">
+      <c r="H207" s="29" t="n">
         <v>8.33</v>
       </c>
-      <c r="I207" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J207" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K207" s="5" t="n">
+      <c r="I207" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J207" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K207" s="29" t="n">
         <v>1.388333333333333</v>
       </c>
-      <c r="L207" s="3" t="inlineStr">
+      <c r="L207" s="27" t="inlineStr">
         <is>
           <t>per Can (6 Cans)</t>
         </is>
       </c>
-      <c r="M207" s="2" t="n"/>
-      <c r="N207" s="4">
+      <c r="M207" s="26" t="n"/>
+      <c r="N207" s="28">
         <f>M207*G207</f>
         <v/>
       </c>
-      <c r="O207" s="2" t="n"/>
-      <c r="P207" s="2" t="n"/>
-      <c r="Q207" s="2" t="n"/>
-      <c r="R207" s="2" t="n"/>
-      <c r="S207" s="2" t="n"/>
+      <c r="O207" s="26" t="n"/>
+      <c r="P207" s="26" t="n"/>
+      <c r="Q207" s="26" t="n"/>
+      <c r="R207" s="26" t="n"/>
+      <c r="S207" s="26" t="n"/>
     </row>
     <row r="208">
-      <c r="A208" s="2" t="inlineStr">
+      <c r="A208" s="26" t="inlineStr">
         <is>
           <t>SLEEVE</t>
         </is>
       </c>
-      <c r="B208" s="2" t="n"/>
-      <c r="C208" s="3" t="inlineStr">
+      <c r="B208" s="26" t="n"/>
+      <c r="C208" s="27" t="inlineStr">
         <is>
           <t>16oz Peanut Cup</t>
         </is>
       </c>
-      <c r="D208" s="3" t="n"/>
-      <c r="E208" s="2" t="inlineStr">
+      <c r="D208" s="27" t="n"/>
+      <c r="E208" s="26" t="inlineStr">
         <is>
           <t>20 Sleeves</t>
         </is>
       </c>
-      <c r="F208" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G208" s="4" t="n">
+      <c r="F208" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G208" s="28" t="n">
         <v>8.01</v>
       </c>
-      <c r="H208" s="5" t="n">
+      <c r="H208" s="29" t="n">
         <v>8.01</v>
       </c>
-      <c r="I208" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J208" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K208" s="5" t="n">
+      <c r="I208" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J208" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K208" s="29" t="n">
         <v>0.4005</v>
       </c>
-      <c r="L208" s="3" t="inlineStr">
+      <c r="L208" s="27" t="inlineStr">
         <is>
           <t>per Sleeve (20 Sleeves)</t>
         </is>
       </c>
-      <c r="M208" s="2" t="n"/>
-      <c r="N208" s="4">
+      <c r="M208" s="26" t="n"/>
+      <c r="N208" s="28">
         <f>M208*G208</f>
         <v/>
       </c>
-      <c r="O208" s="2" t="n"/>
-      <c r="P208" s="2" t="n"/>
-      <c r="Q208" s="2" t="n"/>
-      <c r="R208" s="2" t="n"/>
-      <c r="S208" s="2" t="n"/>
+      <c r="O208" s="26" t="n"/>
+      <c r="P208" s="26" t="n"/>
+      <c r="Q208" s="26" t="n"/>
+      <c r="R208" s="26" t="n"/>
+      <c r="S208" s="26" t="n"/>
     </row>
     <row r="209">
-      <c r="A209" s="2" t="inlineStr">
+      <c r="A209" s="26" t="inlineStr">
         <is>
           <t>SLEEVE</t>
         </is>
       </c>
-      <c r="B209" s="2" t="n"/>
-      <c r="C209" s="3" t="inlineStr">
+      <c r="B209" s="26" t="n"/>
+      <c r="C209" s="27" t="inlineStr">
         <is>
           <t>32oz Peanut Cup</t>
         </is>
       </c>
-      <c r="D209" s="3" t="n"/>
-      <c r="E209" s="2" t="inlineStr">
+      <c r="D209" s="27" t="n"/>
+      <c r="E209" s="26" t="inlineStr">
         <is>
           <t>20 Sleeves</t>
         </is>
       </c>
-      <c r="F209" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G209" s="4" t="n">
+      <c r="F209" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G209" s="28" t="n">
         <v>10.22</v>
       </c>
-      <c r="H209" s="5" t="n">
+      <c r="H209" s="29" t="n">
         <v>10.22</v>
       </c>
-      <c r="I209" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J209" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K209" s="5" t="n">
+      <c r="I209" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J209" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K209" s="29" t="n">
         <v>0.511</v>
       </c>
-      <c r="L209" s="3" t="inlineStr">
+      <c r="L209" s="27" t="inlineStr">
         <is>
           <t>per Sleeve (20 Sleeves)</t>
         </is>
       </c>
-      <c r="M209" s="2" t="n"/>
-      <c r="N209" s="4">
+      <c r="M209" s="26" t="n"/>
+      <c r="N209" s="28">
         <f>M209*G209</f>
         <v/>
       </c>
-      <c r="O209" s="2" t="n"/>
-      <c r="P209" s="2" t="n"/>
-      <c r="Q209" s="2" t="n"/>
-      <c r="R209" s="2" t="n"/>
-      <c r="S209" s="2" t="n"/>
+      <c r="O209" s="26" t="n"/>
+      <c r="P209" s="26" t="n"/>
+      <c r="Q209" s="26" t="n"/>
+      <c r="R209" s="26" t="n"/>
+      <c r="S209" s="26" t="n"/>
     </row>
     <row r="210">
-      <c r="A210" s="2" t="inlineStr">
+      <c r="A210" s="26" t="inlineStr">
         <is>
           <t>SLEEVE</t>
         </is>
       </c>
-      <c r="B210" s="2" t="n"/>
-      <c r="C210" s="3" t="inlineStr">
+      <c r="B210" s="26" t="n"/>
+      <c r="C210" s="27" t="inlineStr">
         <is>
           <t>Peanut Cup Lid</t>
         </is>
       </c>
-      <c r="D210" s="3" t="n"/>
-      <c r="E210" s="2" t="inlineStr">
+      <c r="D210" s="27" t="n"/>
+      <c r="E210" s="26" t="inlineStr">
         <is>
           <t>10 Sleeves</t>
         </is>
       </c>
-      <c r="F210" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G210" s="4" t="n">
+      <c r="F210" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G210" s="28" t="n">
         <v>5.01</v>
       </c>
-      <c r="H210" s="5" t="n">
+      <c r="H210" s="29" t="n">
         <v>5.01</v>
       </c>
-      <c r="I210" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J210" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K210" s="5" t="n">
+      <c r="I210" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J210" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K210" s="29" t="n">
         <v>0.501</v>
       </c>
-      <c r="L210" s="3" t="inlineStr">
+      <c r="L210" s="27" t="inlineStr">
         <is>
           <t>per Sleeve (10 Sleeves)</t>
         </is>
       </c>
-      <c r="M210" s="2" t="n"/>
-      <c r="N210" s="4">
+      <c r="M210" s="26" t="n"/>
+      <c r="N210" s="28">
         <f>M210*G210</f>
         <v/>
       </c>
-      <c r="O210" s="2" t="n"/>
-      <c r="P210" s="2" t="n"/>
-      <c r="Q210" s="2" t="n"/>
-      <c r="R210" s="2" t="n"/>
-      <c r="S210" s="2" t="n"/>
+      <c r="O210" s="26" t="n"/>
+      <c r="P210" s="26" t="n"/>
+      <c r="Q210" s="26" t="n"/>
+      <c r="R210" s="26" t="n"/>
+      <c r="S210" s="26" t="n"/>
     </row>
     <row r="211">
-      <c r="A211" s="2" t="inlineStr">
+      <c r="A211" s="26" t="inlineStr">
         <is>
           <t>BAG</t>
         </is>
       </c>
-      <c r="B211" s="2" t="n"/>
-      <c r="C211" s="3" t="inlineStr">
+      <c r="B211" s="26" t="n"/>
+      <c r="C211" s="27" t="inlineStr">
         <is>
           <t>Gizzards</t>
         </is>
       </c>
-      <c r="D211" s="3" t="n"/>
-      <c r="E211" s="2" t="inlineStr">
+      <c r="D211" s="27" t="n"/>
+      <c r="E211" s="26" t="inlineStr">
         <is>
           <t>4/Box</t>
         </is>
       </c>
-      <c r="F211" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G211" s="4" t="n">
+      <c r="F211" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G211" s="28" t="n">
         <v>19.8</v>
       </c>
-      <c r="H211" s="5" t="n">
+      <c r="H211" s="29" t="n">
         <v>19.8</v>
       </c>
-      <c r="I211" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J211" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K211" s="5" t="n">
+      <c r="I211" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J211" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K211" s="29" t="n">
         <v>4.95</v>
       </c>
-      <c r="L211" s="3" t="inlineStr">
+      <c r="L211" s="27" t="inlineStr">
         <is>
           <t>per Bag (4/Box)</t>
         </is>
       </c>
-      <c r="M211" s="2" t="n"/>
-      <c r="N211" s="4">
+      <c r="M211" s="26" t="n"/>
+      <c r="N211" s="28">
         <f>M211*G211</f>
         <v/>
       </c>
-      <c r="O211" s="2" t="n"/>
-      <c r="P211" s="2" t="n"/>
-      <c r="Q211" s="2" t="n"/>
-      <c r="R211" s="2" t="n"/>
-      <c r="S211" s="2" t="n"/>
+      <c r="O211" s="26" t="n"/>
+      <c r="P211" s="26" t="n"/>
+      <c r="Q211" s="26" t="n"/>
+      <c r="R211" s="26" t="n"/>
+      <c r="S211" s="26" t="n"/>
     </row>
     <row r="212">
-      <c r="A212" s="2" t="inlineStr">
+      <c r="A212" s="26" t="inlineStr">
         <is>
           <t>BAG</t>
         </is>
       </c>
-      <c r="B212" s="2" t="n"/>
-      <c r="C212" s="3" t="inlineStr">
+      <c r="B212" s="26" t="n"/>
+      <c r="C212" s="27" t="inlineStr">
         <is>
           <t>Livers</t>
         </is>
       </c>
-      <c r="D212" s="3" t="n"/>
-      <c r="E212" s="2" t="inlineStr">
+      <c r="D212" s="27" t="n"/>
+      <c r="E212" s="26" t="inlineStr">
         <is>
           <t>4/Box</t>
         </is>
       </c>
-      <c r="F212" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G212" s="4" t="n">
+      <c r="F212" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G212" s="28" t="n">
         <v>14.78</v>
       </c>
-      <c r="H212" s="5" t="n">
+      <c r="H212" s="29" t="n">
         <v>14.78</v>
       </c>
-      <c r="I212" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J212" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K212" s="5" t="n">
+      <c r="I212" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J212" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K212" s="29" t="n">
         <v>3.695</v>
       </c>
-      <c r="L212" s="3" t="inlineStr">
+      <c r="L212" s="27" t="inlineStr">
         <is>
           <t>per Bag (4/Box)</t>
         </is>
       </c>
-      <c r="M212" s="2" t="n"/>
-      <c r="N212" s="4">
+      <c r="M212" s="26" t="n"/>
+      <c r="N212" s="28">
         <f>M212*G212</f>
         <v/>
       </c>
-      <c r="O212" s="2" t="n"/>
-      <c r="P212" s="2" t="n"/>
-      <c r="Q212" s="2" t="n"/>
-      <c r="R212" s="2" t="n"/>
-      <c r="S212" s="2" t="n"/>
+      <c r="O212" s="26" t="n"/>
+      <c r="P212" s="26" t="n"/>
+      <c r="Q212" s="26" t="n"/>
+      <c r="R212" s="26" t="n"/>
+      <c r="S212" s="26" t="n"/>
     </row>
     <row r="213">
-      <c r="A213" s="2" t="inlineStr">
+      <c r="A213" s="26" t="inlineStr">
         <is>
           <t>BAG</t>
         </is>
       </c>
-      <c r="B213" s="2" t="n"/>
-      <c r="C213" s="3" t="inlineStr">
+      <c r="B213" s="26" t="n"/>
+      <c r="C213" s="27" t="inlineStr">
         <is>
           <t>Brisket</t>
         </is>
       </c>
-      <c r="D213" s="3" t="n"/>
-      <c r="E213" s="2" t="n"/>
-      <c r="F213" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G213" s="4" t="n">
+      <c r="D213" s="27" t="n"/>
+      <c r="E213" s="26" t="n"/>
+      <c r="F213" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G213" s="28" t="n">
         <v>29.44</v>
       </c>
-      <c r="H213" s="5" t="n">
+      <c r="H213" s="29" t="n">
         <v>29.44</v>
       </c>
-      <c r="I213" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J213" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K213" s="5" t="n">
+      <c r="I213" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J213" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K213" s="29" t="n">
         <v>29.44</v>
       </c>
-      <c r="L213" s="3" t="inlineStr">
+      <c r="L213" s="27" t="inlineStr">
         <is>
           <t>per Bag (None)</t>
         </is>
       </c>
-      <c r="M213" s="2" t="n"/>
-      <c r="N213" s="4">
+      <c r="M213" s="26" t="n"/>
+      <c r="N213" s="28">
         <f>M213*G213</f>
         <v/>
       </c>
-      <c r="O213" s="2" t="n"/>
-      <c r="P213" s="2" t="n"/>
-      <c r="Q213" s="2" t="n"/>
-      <c r="R213" s="2" t="n"/>
-      <c r="S213" s="2" t="n"/>
+      <c r="O213" s="26" t="n"/>
+      <c r="P213" s="26" t="n"/>
+      <c r="Q213" s="26" t="n"/>
+      <c r="R213" s="26" t="n"/>
+      <c r="S213" s="26" t="n"/>
     </row>
     <row r="214">
-      <c r="A214" s="2" t="inlineStr">
+      <c r="A214" s="26" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="B214" s="2" t="n"/>
-      <c r="C214" s="3" t="inlineStr">
+      <c r="B214" s="26" t="n"/>
+      <c r="C214" s="27" t="inlineStr">
         <is>
           <t>Kolache Boudin Link Org</t>
         </is>
       </c>
-      <c r="D214" s="3" t="n"/>
-      <c r="E214" s="2" t="n"/>
-      <c r="F214" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G214" s="4" t="n">
+      <c r="D214" s="27" t="n"/>
+      <c r="E214" s="26" t="n"/>
+      <c r="F214" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G214" s="28" t="n">
         <v>69.77</v>
       </c>
-      <c r="H214" s="5" t="n">
+      <c r="H214" s="29" t="n">
         <v>69.77</v>
       </c>
-      <c r="I214" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J214" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K214" s="5" t="n">
+      <c r="I214" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J214" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K214" s="29" t="n">
         <v>69.77</v>
       </c>
-      <c r="L214" s="3" t="inlineStr">
+      <c r="L214" s="27" t="inlineStr">
         <is>
           <t>per Case (None)</t>
         </is>
       </c>
-      <c r="M214" s="2" t="n"/>
-      <c r="N214" s="4">
+      <c r="M214" s="26" t="n"/>
+      <c r="N214" s="28">
         <f>M214*G214</f>
         <v/>
       </c>
-      <c r="O214" s="2" t="n"/>
-      <c r="P214" s="2" t="n"/>
-      <c r="Q214" s="2" t="n"/>
-      <c r="R214" s="2" t="n"/>
-      <c r="S214" s="2" t="n"/>
+      <c r="O214" s="26" t="n"/>
+      <c r="P214" s="26" t="n"/>
+      <c r="Q214" s="26" t="n"/>
+      <c r="R214" s="26" t="n"/>
+      <c r="S214" s="26" t="n"/>
     </row>
     <row r="215">
-      <c r="A215" s="2" t="inlineStr">
+      <c r="A215" s="26" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="B215" s="2" t="n"/>
-      <c r="C215" s="3" t="inlineStr">
+      <c r="B215" s="26" t="n"/>
+      <c r="C215" s="27" t="inlineStr">
         <is>
           <t>Kolache Sausage Egg &amp; Cheese</t>
         </is>
       </c>
-      <c r="D215" s="3" t="n"/>
-      <c r="E215" s="2" t="n"/>
-      <c r="F215" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G215" s="4" t="n">
+      <c r="D215" s="27" t="n"/>
+      <c r="E215" s="26" t="n"/>
+      <c r="F215" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G215" s="28" t="n">
         <v>69.77</v>
       </c>
-      <c r="H215" s="5" t="n">
+      <c r="H215" s="29" t="n">
         <v>69.77</v>
       </c>
-      <c r="I215" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J215" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K215" s="5" t="n">
+      <c r="I215" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J215" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K215" s="29" t="n">
         <v>69.77</v>
       </c>
-      <c r="L215" s="3" t="inlineStr">
+      <c r="L215" s="27" t="inlineStr">
         <is>
           <t>per Case (None)</t>
         </is>
       </c>
-      <c r="M215" s="2" t="n"/>
-      <c r="N215" s="4">
+      <c r="M215" s="26" t="n"/>
+      <c r="N215" s="28">
         <f>M215*G215</f>
         <v/>
       </c>
-      <c r="O215" s="2" t="n"/>
-      <c r="P215" s="2" t="n"/>
-      <c r="Q215" s="2" t="n"/>
-      <c r="R215" s="2" t="n"/>
-      <c r="S215" s="2" t="n"/>
+      <c r="O215" s="26" t="n"/>
+      <c r="P215" s="26" t="n"/>
+      <c r="Q215" s="26" t="n"/>
+      <c r="R215" s="26" t="n"/>
+      <c r="S215" s="26" t="n"/>
     </row>
     <row r="216">
-      <c r="A216" s="2" t="inlineStr">
+      <c r="A216" s="26" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="B216" s="2" t="n"/>
-      <c r="C216" s="3" t="inlineStr">
+      <c r="B216" s="26" t="n"/>
+      <c r="C216" s="27" t="inlineStr">
         <is>
           <t>Wrap Jalapeno Popper</t>
         </is>
       </c>
-      <c r="D216" s="3" t="n"/>
-      <c r="E216" s="2" t="n"/>
-      <c r="F216" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G216" s="4" t="n">
+      <c r="D216" s="27" t="n"/>
+      <c r="E216" s="26" t="n"/>
+      <c r="F216" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G216" s="28" t="n">
         <v>93.03</v>
       </c>
-      <c r="H216" s="5" t="n">
+      <c r="H216" s="29" t="n">
         <v>93.03</v>
       </c>
-      <c r="I216" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J216" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K216" s="5" t="n">
+      <c r="I216" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J216" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K216" s="29" t="n">
         <v>93.03</v>
       </c>
-      <c r="L216" s="3" t="inlineStr">
+      <c r="L216" s="27" t="inlineStr">
         <is>
           <t>per Case (None)</t>
         </is>
       </c>
-      <c r="M216" s="2" t="n"/>
-      <c r="N216" s="4">
+      <c r="M216" s="26" t="n"/>
+      <c r="N216" s="28">
         <f>M216*G216</f>
         <v/>
       </c>
-      <c r="O216" s="2" t="n"/>
-      <c r="P216" s="2" t="n"/>
-      <c r="Q216" s="2" t="n"/>
-      <c r="R216" s="2" t="n"/>
-      <c r="S216" s="2" t="n"/>
+      <c r="O216" s="26" t="n"/>
+      <c r="P216" s="26" t="n"/>
+      <c r="Q216" s="26" t="n"/>
+      <c r="R216" s="26" t="n"/>
+      <c r="S216" s="26" t="n"/>
     </row>
     <row r="217">
-      <c r="A217" s="2" t="inlineStr">
+      <c r="A217" s="26" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="B217" s="2" t="n"/>
-      <c r="C217" s="3" t="inlineStr">
+      <c r="B217" s="26" t="n"/>
+      <c r="C217" s="27" t="inlineStr">
         <is>
           <t>Deer Burrito</t>
         </is>
       </c>
-      <c r="D217" s="3" t="n"/>
-      <c r="E217" s="2" t="n"/>
-      <c r="F217" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G217" s="4" t="n">
+      <c r="D217" s="27" t="n"/>
+      <c r="E217" s="26" t="n"/>
+      <c r="F217" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G217" s="28" t="n">
         <v>449</v>
       </c>
-      <c r="H217" s="5" t="n">
+      <c r="H217" s="29" t="n">
         <v>449</v>
       </c>
-      <c r="I217" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J217" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K217" s="5" t="n">
+      <c r="I217" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J217" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K217" s="29" t="n">
         <v>449</v>
       </c>
-      <c r="L217" s="3" t="inlineStr">
+      <c r="L217" s="27" t="inlineStr">
         <is>
           <t>per Case (None)</t>
         </is>
       </c>
-      <c r="M217" s="2" t="n"/>
-      <c r="N217" s="4">
+      <c r="M217" s="26" t="n"/>
+      <c r="N217" s="28">
         <f>M217*G217</f>
         <v/>
       </c>
-      <c r="O217" s="2" t="n"/>
-      <c r="P217" s="2" t="n"/>
-      <c r="Q217" s="2" t="n"/>
-      <c r="R217" s="2" t="n"/>
-      <c r="S217" s="2" t="n"/>
+      <c r="O217" s="26" t="n"/>
+      <c r="P217" s="26" t="n"/>
+      <c r="Q217" s="26" t="n"/>
+      <c r="R217" s="26" t="n"/>
+      <c r="S217" s="26" t="n"/>
     </row>
     <row r="218">
-      <c r="A218" s="2" t="inlineStr">
+      <c r="A218" s="26" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="B218" s="2" t="n"/>
-      <c r="C218" s="3" t="inlineStr">
+      <c r="B218" s="26" t="n"/>
+      <c r="C218" s="27" t="inlineStr">
         <is>
           <t>Jalapeno Cheddar Kolache</t>
         </is>
       </c>
-      <c r="D218" s="3" t="n"/>
-      <c r="E218" s="2" t="n"/>
-      <c r="F218" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G218" s="4" t="n">
+      <c r="D218" s="27" t="n"/>
+      <c r="E218" s="26" t="n"/>
+      <c r="F218" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G218" s="28" t="n">
         <v>69.77</v>
       </c>
-      <c r="H218" s="5" t="n">
+      <c r="H218" s="29" t="n">
         <v>69.77</v>
       </c>
-      <c r="I218" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J218" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K218" s="5" t="n">
+      <c r="I218" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J218" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K218" s="29" t="n">
         <v>69.77</v>
       </c>
-      <c r="L218" s="3" t="inlineStr">
+      <c r="L218" s="27" t="inlineStr">
         <is>
           <t>per Case (None)</t>
         </is>
       </c>
-      <c r="M218" s="2" t="n"/>
-      <c r="N218" s="4">
+      <c r="M218" s="26" t="n"/>
+      <c r="N218" s="28">
         <f>M218*G218</f>
         <v/>
       </c>
-      <c r="O218" s="2" t="n"/>
-      <c r="P218" s="2" t="n"/>
-      <c r="Q218" s="2" t="n"/>
-      <c r="R218" s="2" t="n"/>
-      <c r="S218" s="2" t="n"/>
+      <c r="O218" s="26" t="n"/>
+      <c r="P218" s="26" t="n"/>
+      <c r="Q218" s="26" t="n"/>
+      <c r="R218" s="26" t="n"/>
+      <c r="S218" s="26" t="n"/>
     </row>
     <row r="219">
-      <c r="A219" s="2" t="inlineStr">
+      <c r="A219" s="26" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="B219" s="2" t="n"/>
-      <c r="C219" s="3" t="inlineStr">
+      <c r="B219" s="26" t="n"/>
+      <c r="C219" s="27" t="inlineStr">
         <is>
           <t>Chicken Fajita</t>
         </is>
       </c>
-      <c r="D219" s="3" t="n"/>
-      <c r="E219" s="2" t="n"/>
-      <c r="F219" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G219" s="4" t="n">
+      <c r="D219" s="27" t="n"/>
+      <c r="E219" s="26" t="n"/>
+      <c r="F219" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G219" s="28" t="n">
         <v>57.99</v>
       </c>
-      <c r="H219" s="5" t="n">
+      <c r="H219" s="29" t="n">
         <v>57.99</v>
       </c>
-      <c r="I219" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J219" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K219" s="5" t="n">
+      <c r="I219" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J219" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K219" s="29" t="n">
         <v>57.99</v>
       </c>
-      <c r="L219" s="3" t="inlineStr">
+      <c r="L219" s="27" t="inlineStr">
         <is>
           <t>per Case (None)</t>
         </is>
       </c>
-      <c r="M219" s="2" t="n"/>
-      <c r="N219" s="4">
+      <c r="M219" s="26" t="n"/>
+      <c r="N219" s="28">
         <f>M219*G219</f>
         <v/>
       </c>
-      <c r="O219" s="2" t="n"/>
-      <c r="P219" s="2" t="n"/>
-      <c r="Q219" s="2" t="n"/>
-      <c r="R219" s="2" t="n"/>
-      <c r="S219" s="2" t="n"/>
+      <c r="O219" s="26" t="n"/>
+      <c r="P219" s="26" t="n"/>
+      <c r="Q219" s="26" t="n"/>
+      <c r="R219" s="26" t="n"/>
+      <c r="S219" s="26" t="n"/>
     </row>
     <row r="220">
-      <c r="A220" s="2" t="inlineStr">
+      <c r="A220" s="26" t="inlineStr">
         <is>
           <t>BAG</t>
         </is>
       </c>
-      <c r="B220" s="2" t="n"/>
-      <c r="C220" s="3" t="inlineStr">
+      <c r="B220" s="26" t="n"/>
+      <c r="C220" s="27" t="inlineStr">
         <is>
           <t>Mac And Cheese</t>
         </is>
       </c>
-      <c r="D220" s="3" t="n"/>
-      <c r="E220" s="2" t="inlineStr">
+      <c r="D220" s="27" t="n"/>
+      <c r="E220" s="26" t="inlineStr">
         <is>
           <t>6 Bags</t>
         </is>
       </c>
-      <c r="F220" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G220" s="4" t="n">
+      <c r="F220" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G220" s="28" t="n">
         <v>7.1</v>
       </c>
-      <c r="H220" s="5" t="n">
+      <c r="H220" s="29" t="n">
         <v>7.1</v>
       </c>
-      <c r="I220" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J220" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K220" s="5" t="n">
+      <c r="I220" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J220" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K220" s="29" t="n">
         <v>1.183333333333333</v>
       </c>
-      <c r="L220" s="3" t="inlineStr">
+      <c r="L220" s="27" t="inlineStr">
         <is>
           <t>per Bag (6 Bags)</t>
         </is>
       </c>
-      <c r="M220" s="2" t="n"/>
-      <c r="N220" s="4">
+      <c r="M220" s="26" t="n"/>
+      <c r="N220" s="28">
         <f>M220*G220</f>
         <v/>
       </c>
-      <c r="O220" s="2" t="n"/>
-      <c r="P220" s="2" t="n"/>
-      <c r="Q220" s="2" t="n"/>
-      <c r="R220" s="2" t="n"/>
-      <c r="S220" s="2" t="n"/>
+      <c r="O220" s="26" t="n"/>
+      <c r="P220" s="26" t="n"/>
+      <c r="Q220" s="26" t="n"/>
+      <c r="R220" s="26" t="n"/>
+      <c r="S220" s="26" t="n"/>
     </row>
     <row r="221">
-      <c r="A221" s="2" t="inlineStr">
+      <c r="A221" s="26" t="inlineStr">
         <is>
           <t>BAG</t>
         </is>
       </c>
-      <c r="B221" s="2" t="n"/>
-      <c r="C221" s="3" t="inlineStr">
+      <c r="B221" s="26" t="n"/>
+      <c r="C221" s="27" t="inlineStr">
         <is>
           <t>Mashed Potatoes</t>
         </is>
       </c>
-      <c r="D221" s="3" t="n"/>
-      <c r="E221" s="2" t="inlineStr">
+      <c r="D221" s="27" t="n"/>
+      <c r="E221" s="26" t="inlineStr">
         <is>
           <t>4 Bags</t>
         </is>
       </c>
-      <c r="F221" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G221" s="4" t="n">
+      <c r="F221" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G221" s="28" t="n">
         <v>9.640000000000001</v>
       </c>
-      <c r="H221" s="5" t="n">
+      <c r="H221" s="29" t="n">
         <v>9.640000000000001</v>
       </c>
-      <c r="I221" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J221" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K221" s="5" t="n">
+      <c r="I221" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J221" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K221" s="29" t="n">
         <v>2.41</v>
       </c>
-      <c r="L221" s="3" t="inlineStr">
+      <c r="L221" s="27" t="inlineStr">
         <is>
           <t>per Bag (4 Bags)</t>
         </is>
       </c>
-      <c r="M221" s="2" t="n"/>
-      <c r="N221" s="4">
+      <c r="M221" s="26" t="n"/>
+      <c r="N221" s="28">
         <f>M221*G221</f>
         <v/>
       </c>
-      <c r="O221" s="2" t="n"/>
-      <c r="P221" s="2" t="n"/>
-      <c r="Q221" s="2" t="n"/>
-      <c r="R221" s="2" t="n"/>
-      <c r="S221" s="2" t="n"/>
+      <c r="O221" s="26" t="n"/>
+      <c r="P221" s="26" t="n"/>
+      <c r="Q221" s="26" t="n"/>
+      <c r="R221" s="26" t="n"/>
+      <c r="S221" s="26" t="n"/>
     </row>
     <row r="222">
-      <c r="A222" s="2" t="inlineStr">
+      <c r="A222" s="26" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="B222" s="2" t="n"/>
-      <c r="C222" s="3" t="inlineStr">
+      <c r="B222" s="26" t="n"/>
+      <c r="C222" s="27" t="inlineStr">
         <is>
           <t>Mini Taco Beef</t>
         </is>
       </c>
-      <c r="D222" s="3" t="n"/>
-      <c r="E222" s="2" t="inlineStr">
+      <c r="D222" s="27" t="n"/>
+      <c r="E222" s="26" t="inlineStr">
         <is>
           <t>case</t>
         </is>
       </c>
-      <c r="F222" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G222" s="4" t="n">
+      <c r="F222" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G222" s="28" t="n">
         <v>27.91</v>
       </c>
-      <c r="H222" s="5" t="n">
+      <c r="H222" s="29" t="n">
         <v>27.91</v>
       </c>
-      <c r="I222" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J222" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K222" s="5" t="n">
+      <c r="I222" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J222" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K222" s="29" t="n">
         <v>27.91</v>
       </c>
-      <c r="L222" s="3" t="inlineStr">
+      <c r="L222" s="27" t="inlineStr">
         <is>
           <t>per Case (case)</t>
         </is>
       </c>
-      <c r="M222" s="2" t="n"/>
-      <c r="N222" s="4">
+      <c r="M222" s="26" t="n"/>
+      <c r="N222" s="28">
         <f>M222*G222</f>
         <v/>
       </c>
-      <c r="O222" s="2" t="n"/>
-      <c r="P222" s="2" t="n"/>
-      <c r="Q222" s="2" t="n"/>
-      <c r="R222" s="2" t="n"/>
-      <c r="S222" s="2" t="n"/>
+      <c r="O222" s="26" t="n"/>
+      <c r="P222" s="26" t="n"/>
+      <c r="Q222" s="26" t="n"/>
+      <c r="R222" s="26" t="n"/>
+      <c r="S222" s="26" t="n"/>
     </row>
     <row r="223">
-      <c r="A223" s="2" t="inlineStr">
+      <c r="A223" s="26" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="B223" s="2" t="n"/>
-      <c r="C223" s="3" t="inlineStr">
+      <c r="B223" s="26" t="n"/>
+      <c r="C223" s="27" t="inlineStr">
         <is>
           <t>Mini Taco Chicken</t>
         </is>
       </c>
-      <c r="D223" s="3" t="n"/>
-      <c r="E223" s="2" t="inlineStr">
+      <c r="D223" s="27" t="n"/>
+      <c r="E223" s="26" t="inlineStr">
         <is>
           <t>case</t>
         </is>
       </c>
-      <c r="F223" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G223" s="4" t="n">
+      <c r="F223" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G223" s="28" t="n">
         <v>27.91</v>
       </c>
-      <c r="H223" s="5" t="n">
+      <c r="H223" s="29" t="n">
         <v>27.91</v>
       </c>
-      <c r="I223" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J223" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K223" s="5" t="n">
+      <c r="I223" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J223" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K223" s="29" t="n">
         <v>27.91</v>
       </c>
-      <c r="L223" s="3" t="inlineStr">
+      <c r="L223" s="27" t="inlineStr">
         <is>
           <t>per Case (case)</t>
         </is>
       </c>
-      <c r="M223" s="2" t="n"/>
-      <c r="N223" s="4">
+      <c r="M223" s="26" t="n"/>
+      <c r="N223" s="28">
         <f>M223*G223</f>
         <v/>
       </c>
-      <c r="O223" s="2" t="n"/>
-      <c r="P223" s="2" t="n"/>
-      <c r="Q223" s="2" t="n"/>
-      <c r="R223" s="2" t="n"/>
-      <c r="S223" s="2" t="n"/>
+      <c r="O223" s="26" t="n"/>
+      <c r="P223" s="26" t="n"/>
+      <c r="Q223" s="26" t="n"/>
+      <c r="R223" s="26" t="n"/>
+      <c r="S223" s="26" t="n"/>
     </row>
     <row r="224">
-      <c r="A224" s="2" t="inlineStr">
+      <c r="A224" s="26" t="inlineStr">
         <is>
           <t>BAG</t>
         </is>
       </c>
-      <c r="B224" s="2" t="n"/>
-      <c r="C224" s="3" t="inlineStr">
+      <c r="B224" s="26" t="n"/>
+      <c r="C224" s="27" t="inlineStr">
         <is>
           <t>Red Beans</t>
         </is>
       </c>
-      <c r="D224" s="3" t="n"/>
-      <c r="E224" s="2" t="inlineStr">
+      <c r="D224" s="27" t="n"/>
+      <c r="E224" s="26" t="inlineStr">
         <is>
           <t>9 Bags</t>
         </is>
       </c>
-      <c r="F224" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G224" s="4" t="n">
+      <c r="F224" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G224" s="28" t="n">
         <v>6.49</v>
       </c>
-      <c r="H224" s="5" t="n">
+      <c r="H224" s="29" t="n">
         <v>6.49</v>
       </c>
-      <c r="I224" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J224" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K224" s="5" t="n">
+      <c r="I224" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J224" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K224" s="29" t="n">
         <v>0.7211111111111111</v>
       </c>
-      <c r="L224" s="3" t="inlineStr">
+      <c r="L224" s="27" t="inlineStr">
         <is>
           <t>per Bag (9 Bags)</t>
         </is>
       </c>
-      <c r="M224" s="2" t="n"/>
-      <c r="N224" s="4">
+      <c r="M224" s="26" t="n"/>
+      <c r="N224" s="28">
         <f>M224*G224</f>
         <v/>
       </c>
-      <c r="O224" s="2" t="n"/>
-      <c r="P224" s="2" t="n"/>
-      <c r="Q224" s="2" t="n"/>
-      <c r="R224" s="2" t="n"/>
-      <c r="S224" s="2" t="n"/>
+      <c r="O224" s="26" t="n"/>
+      <c r="P224" s="26" t="n"/>
+      <c r="Q224" s="26" t="n"/>
+      <c r="R224" s="26" t="n"/>
+      <c r="S224" s="26" t="n"/>
     </row>
     <row r="225">
-      <c r="A225" s="2" t="inlineStr">
+      <c r="A225" s="26" t="inlineStr">
         <is>
           <t>PACK</t>
         </is>
       </c>
-      <c r="B225" s="2" t="n"/>
-      <c r="C225" s="3" t="inlineStr">
+      <c r="B225" s="26" t="n"/>
+      <c r="C225" s="27" t="inlineStr">
         <is>
           <t>Beef Sausage Dogs</t>
         </is>
       </c>
-      <c r="D225" s="3" t="n"/>
-      <c r="E225" s="2" t="n"/>
-      <c r="F225" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G225" s="4" t="n">
+      <c r="D225" s="27" t="n"/>
+      <c r="E225" s="26" t="n"/>
+      <c r="F225" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G225" s="28" t="n">
         <v>20.34</v>
       </c>
-      <c r="H225" s="5" t="n">
+      <c r="H225" s="29" t="n">
         <v>20.34</v>
       </c>
-      <c r="I225" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J225" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K225" s="5" t="n">
+      <c r="I225" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J225" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K225" s="29" t="n">
         <v>20.34</v>
       </c>
-      <c r="L225" s="3" t="inlineStr">
+      <c r="L225" s="27" t="inlineStr">
         <is>
           <t>per Pack (None)</t>
         </is>
       </c>
-      <c r="M225" s="2" t="n"/>
-      <c r="N225" s="4">
+      <c r="M225" s="26" t="n"/>
+      <c r="N225" s="28">
         <f>M225*G225</f>
         <v/>
       </c>
-      <c r="O225" s="2" t="n"/>
-      <c r="P225" s="2" t="n"/>
-      <c r="Q225" s="2" t="n"/>
-      <c r="R225" s="2" t="n"/>
-      <c r="S225" s="2" t="n"/>
+      <c r="O225" s="26" t="n"/>
+      <c r="P225" s="26" t="n"/>
+      <c r="Q225" s="26" t="n"/>
+      <c r="R225" s="26" t="n"/>
+      <c r="S225" s="26" t="n"/>
     </row>
     <row r="226">
-      <c r="A226" s="2" t="inlineStr">
+      <c r="A226" s="26" t="inlineStr">
         <is>
           <t>BAG</t>
         </is>
       </c>
-      <c r="B226" s="2" t="n"/>
-      <c r="C226" s="3" t="inlineStr">
+      <c r="B226" s="26" t="n"/>
+      <c r="C226" s="27" t="inlineStr">
         <is>
           <t>Seasoned Corn</t>
         </is>
       </c>
-      <c r="D226" s="3" t="n"/>
-      <c r="E226" s="2" t="inlineStr">
+      <c r="D226" s="27" t="n"/>
+      <c r="E226" s="26" t="inlineStr">
         <is>
           <t>6 Bags</t>
         </is>
       </c>
-      <c r="F226" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G226" s="4" t="n">
+      <c r="F226" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G226" s="28" t="n">
         <v>6.18</v>
       </c>
-      <c r="H226" s="5" t="n">
+      <c r="H226" s="29" t="n">
         <v>6.18</v>
       </c>
-      <c r="I226" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J226" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K226" s="5" t="n">
+      <c r="I226" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J226" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K226" s="29" t="n">
         <v>1.03</v>
       </c>
-      <c r="L226" s="3" t="inlineStr">
+      <c r="L226" s="27" t="inlineStr">
         <is>
           <t>per Bag (6 Bags)</t>
         </is>
       </c>
-      <c r="M226" s="2" t="n"/>
-      <c r="N226" s="4">
+      <c r="M226" s="26" t="n"/>
+      <c r="N226" s="28">
         <f>M226*G226</f>
         <v/>
       </c>
-      <c r="O226" s="2" t="n"/>
-      <c r="P226" s="2" t="n"/>
-      <c r="Q226" s="2" t="n"/>
-      <c r="R226" s="2" t="n"/>
-      <c r="S226" s="2" t="n"/>
+      <c r="O226" s="26" t="n"/>
+      <c r="P226" s="26" t="n"/>
+      <c r="Q226" s="26" t="n"/>
+      <c r="R226" s="26" t="n"/>
+      <c r="S226" s="26" t="n"/>
     </row>
     <row r="227">
-      <c r="A227" s="2" t="inlineStr">
+      <c r="A227" s="26" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="B227" s="2" t="n"/>
-      <c r="C227" s="3" t="inlineStr">
+      <c r="B227" s="26" t="n"/>
+      <c r="C227" s="27" t="inlineStr">
         <is>
           <t>Stuffed Nacho</t>
         </is>
       </c>
-      <c r="D227" s="3" t="n"/>
-      <c r="E227" s="2" t="inlineStr">
+      <c r="D227" s="27" t="n"/>
+      <c r="E227" s="26" t="inlineStr">
         <is>
           <t>case</t>
         </is>
       </c>
-      <c r="F227" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G227" s="4" t="n">
+      <c r="F227" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G227" s="28" t="n">
         <v>37.28</v>
       </c>
-      <c r="H227" s="5" t="n">
+      <c r="H227" s="29" t="n">
         <v>37.28</v>
       </c>
-      <c r="I227" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J227" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K227" s="5" t="n">
+      <c r="I227" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J227" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K227" s="29" t="n">
         <v>37.28</v>
       </c>
-      <c r="L227" s="3" t="inlineStr">
+      <c r="L227" s="27" t="inlineStr">
         <is>
           <t>per Case (case)</t>
         </is>
       </c>
-      <c r="M227" s="2" t="n"/>
-      <c r="N227" s="4">
+      <c r="M227" s="26" t="n"/>
+      <c r="N227" s="28">
         <f>M227*G227</f>
         <v/>
       </c>
-      <c r="O227" s="2" t="n"/>
-      <c r="P227" s="2" t="n"/>
-      <c r="Q227" s="2" t="n"/>
-      <c r="R227" s="2" t="n"/>
-      <c r="S227" s="2" t="n"/>
+      <c r="O227" s="26" t="n"/>
+      <c r="P227" s="26" t="n"/>
+      <c r="Q227" s="26" t="n"/>
+      <c r="R227" s="26" t="n"/>
+      <c r="S227" s="26" t="n"/>
     </row>
     <row r="228">
-      <c r="A228" s="2" t="inlineStr">
+      <c r="A228" s="26" t="inlineStr">
         <is>
           <t>BAG</t>
         </is>
       </c>
-      <c r="B228" s="2" t="n"/>
-      <c r="C228" s="3" t="inlineStr">
+      <c r="B228" s="26" t="n"/>
+      <c r="C228" s="27" t="inlineStr">
         <is>
           <t>Tomato Gravy</t>
         </is>
       </c>
-      <c r="D228" s="3" t="n"/>
-      <c r="E228" s="2" t="inlineStr">
+      <c r="D228" s="27" t="n"/>
+      <c r="E228" s="26" t="inlineStr">
         <is>
           <t>4 bags</t>
         </is>
       </c>
-      <c r="F228" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G228" s="4" t="n">
+      <c r="F228" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G228" s="28" t="n">
         <v>12.34</v>
       </c>
-      <c r="H228" s="5" t="n">
+      <c r="H228" s="29" t="n">
         <v>12.34</v>
       </c>
-      <c r="I228" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J228" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K228" s="5" t="n">
+      <c r="I228" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J228" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K228" s="29" t="n">
         <v>3.085</v>
       </c>
-      <c r="L228" s="3" t="inlineStr">
+      <c r="L228" s="27" t="inlineStr">
         <is>
           <t>per Bag (4 bags)</t>
         </is>
       </c>
-      <c r="M228" s="2" t="n"/>
-      <c r="N228" s="4">
+      <c r="M228" s="26" t="n"/>
+      <c r="N228" s="28">
         <f>M228*G228</f>
         <v/>
       </c>
-      <c r="O228" s="2" t="n"/>
-      <c r="P228" s="2" t="n"/>
-      <c r="Q228" s="2" t="n"/>
-      <c r="R228" s="2" t="n"/>
-      <c r="S228" s="2" t="n"/>
+      <c r="O228" s="26" t="n"/>
+      <c r="P228" s="26" t="n"/>
+      <c r="Q228" s="26" t="n"/>
+      <c r="R228" s="26" t="n"/>
+      <c r="S228" s="26" t="n"/>
     </row>
     <row r="229">
-      <c r="A229" s="2" t="inlineStr">
+      <c r="A229" s="26" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="B229" s="2" t="n"/>
-      <c r="C229" s="3" t="inlineStr">
+      <c r="B229" s="26" t="n"/>
+      <c r="C229" s="27" t="inlineStr">
         <is>
           <t>Spicy Chicken Patty</t>
         </is>
       </c>
-      <c r="D229" s="3" t="n"/>
-      <c r="E229" s="2" t="n"/>
-      <c r="F229" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G229" s="4" t="n">
+      <c r="D229" s="27" t="n"/>
+      <c r="E229" s="26" t="n"/>
+      <c r="F229" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G229" s="28" t="n">
         <v>52.87</v>
       </c>
-      <c r="H229" s="5" t="n">
+      <c r="H229" s="29" t="n">
         <v>52.87</v>
       </c>
-      <c r="I229" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J229" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K229" s="5" t="n">
+      <c r="I229" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J229" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K229" s="29" t="n">
         <v>52.87</v>
       </c>
-      <c r="L229" s="3" t="inlineStr">
+      <c r="L229" s="27" t="inlineStr">
         <is>
           <t>per Case (None)</t>
         </is>
       </c>
-      <c r="M229" s="2" t="n"/>
-      <c r="N229" s="4">
+      <c r="M229" s="26" t="n"/>
+      <c r="N229" s="28">
         <f>M229*G229</f>
         <v/>
       </c>
-      <c r="O229" s="2" t="n"/>
-      <c r="P229" s="2" t="n"/>
-      <c r="Q229" s="2" t="n"/>
-      <c r="R229" s="2" t="n"/>
-      <c r="S229" s="2" t="n"/>
+      <c r="O229" s="26" t="n"/>
+      <c r="P229" s="26" t="n"/>
+      <c r="Q229" s="26" t="n"/>
+      <c r="R229" s="26" t="n"/>
+      <c r="S229" s="26" t="n"/>
     </row>
     <row r="230">
-      <c r="A230" s="2" t="inlineStr">
+      <c r="A230" s="26" t="inlineStr">
         <is>
           <t>EACH</t>
         </is>
       </c>
-      <c r="B230" s="2" t="n"/>
-      <c r="C230" s="3" t="inlineStr">
+      <c r="B230" s="26" t="n"/>
+      <c r="C230" s="27" t="inlineStr">
         <is>
           <t>Crooked Letter Cookies</t>
         </is>
       </c>
-      <c r="D230" s="3" t="n"/>
-      <c r="E230" s="2" t="n"/>
-      <c r="F230" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G230" s="4" t="n">
+      <c r="D230" s="27" t="n"/>
+      <c r="E230" s="26" t="n"/>
+      <c r="F230" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G230" s="28" t="n">
         <v>1.9</v>
       </c>
-      <c r="H230" s="5" t="n">
+      <c r="H230" s="29" t="n">
         <v>1.9</v>
       </c>
-      <c r="I230" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J230" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K230" s="5" t="n">
+      <c r="I230" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J230" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K230" s="29" t="n">
         <v>1.9</v>
       </c>
-      <c r="L230" s="3" t="inlineStr">
+      <c r="L230" s="27" t="inlineStr">
         <is>
           <t>per Each (None)</t>
         </is>
       </c>
-      <c r="M230" s="2" t="n"/>
-      <c r="N230" s="4">
+      <c r="M230" s="26" t="n"/>
+      <c r="N230" s="28">
         <f>M230*G230</f>
         <v/>
       </c>
-      <c r="O230" s="2" t="n"/>
-      <c r="P230" s="2" t="n"/>
-      <c r="Q230" s="2" t="n"/>
-      <c r="R230" s="2" t="n"/>
-      <c r="S230" s="2" t="n"/>
+      <c r="O230" s="26" t="n"/>
+      <c r="P230" s="26" t="n"/>
+      <c r="Q230" s="26" t="n"/>
+      <c r="R230" s="26" t="n"/>
+      <c r="S230" s="26" t="n"/>
     </row>
     <row r="231">
-      <c r="A231" s="2" t="inlineStr">
+      <c r="A231" s="26" t="inlineStr">
         <is>
           <t>EACH</t>
         </is>
       </c>
-      <c r="B231" s="2" t="n"/>
-      <c r="C231" s="3" t="inlineStr">
+      <c r="B231" s="26" t="n"/>
+      <c r="C231" s="27" t="inlineStr">
         <is>
           <t>Strawberry/Blueberry Cream Cheese King Cake</t>
         </is>
       </c>
-      <c r="D231" s="3" t="n"/>
-      <c r="E231" s="2" t="n"/>
-      <c r="F231" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G231" s="4" t="n">
+      <c r="D231" s="27" t="n"/>
+      <c r="E231" s="26" t="n"/>
+      <c r="F231" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G231" s="28" t="n">
         <v>31</v>
       </c>
-      <c r="H231" s="5" t="n">
+      <c r="H231" s="29" t="n">
         <v>31</v>
       </c>
-      <c r="I231" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J231" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K231" s="5" t="n">
+      <c r="I231" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J231" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K231" s="29" t="n">
         <v>31</v>
       </c>
-      <c r="L231" s="3" t="inlineStr">
+      <c r="L231" s="27" t="inlineStr">
         <is>
           <t>per Each (None)</t>
         </is>
       </c>
-      <c r="M231" s="2" t="n"/>
-      <c r="N231" s="4">
+      <c r="M231" s="26" t="n"/>
+      <c r="N231" s="28">
         <f>M231*G231</f>
         <v/>
       </c>
-      <c r="O231" s="2" t="n"/>
-      <c r="P231" s="2" t="n"/>
-      <c r="Q231" s="2" t="n"/>
-      <c r="R231" s="2" t="n"/>
-      <c r="S231" s="2" t="n"/>
+      <c r="O231" s="26" t="n"/>
+      <c r="P231" s="26" t="n"/>
+      <c r="Q231" s="26" t="n"/>
+      <c r="R231" s="26" t="n"/>
+      <c r="S231" s="26" t="n"/>
     </row>
     <row r="232">
-      <c r="A232" s="2" t="inlineStr">
+      <c r="A232" s="26" t="inlineStr">
         <is>
           <t>EACH</t>
         </is>
       </c>
-      <c r="B232" s="2" t="n"/>
-      <c r="C232" s="3" t="inlineStr">
+      <c r="B232" s="26" t="n"/>
+      <c r="C232" s="27" t="inlineStr">
         <is>
           <t>Traditional King Cake</t>
         </is>
       </c>
-      <c r="D232" s="3" t="n"/>
-      <c r="E232" s="2" t="n"/>
-      <c r="F232" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G232" s="4" t="n">
+      <c r="D232" s="27" t="n"/>
+      <c r="E232" s="26" t="n"/>
+      <c r="F232" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G232" s="28" t="n">
         <v>26</v>
       </c>
-      <c r="H232" s="5" t="n">
+      <c r="H232" s="29" t="n">
         <v>26</v>
       </c>
-      <c r="I232" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J232" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K232" s="5" t="n">
+      <c r="I232" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J232" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K232" s="29" t="n">
         <v>26</v>
       </c>
-      <c r="L232" s="3" t="inlineStr">
+      <c r="L232" s="27" t="inlineStr">
         <is>
           <t>per Each (None)</t>
         </is>
       </c>
-      <c r="M232" s="2" t="n"/>
-      <c r="N232" s="4">
+      <c r="M232" s="26" t="n"/>
+      <c r="N232" s="28">
         <f>M232*G232</f>
         <v/>
       </c>
-      <c r="O232" s="2" t="n"/>
-      <c r="P232" s="2" t="n"/>
-      <c r="Q232" s="2" t="n"/>
-      <c r="R232" s="2" t="n"/>
-      <c r="S232" s="2" t="n"/>
+      <c r="O232" s="26" t="n"/>
+      <c r="P232" s="26" t="n"/>
+      <c r="Q232" s="26" t="n"/>
+      <c r="R232" s="26" t="n"/>
+      <c r="S232" s="26" t="n"/>
     </row>
     <row r="233">
-      <c r="A233" s="2" t="inlineStr">
+      <c r="A233" s="26" t="inlineStr">
         <is>
           <t>EACH</t>
         </is>
       </c>
-      <c r="B233" s="2" t="n"/>
-      <c r="C233" s="3" t="inlineStr">
+      <c r="B233" s="26" t="n"/>
+      <c r="C233" s="27" t="inlineStr">
         <is>
           <t>Cream Cheese King Cake</t>
         </is>
       </c>
-      <c r="D233" s="3" t="n"/>
-      <c r="E233" s="2" t="n"/>
-      <c r="F233" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G233" s="4" t="n">
+      <c r="D233" s="27" t="n"/>
+      <c r="E233" s="26" t="n"/>
+      <c r="F233" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G233" s="28" t="n">
         <v>28</v>
       </c>
-      <c r="H233" s="5" t="n">
+      <c r="H233" s="29" t="n">
         <v>28</v>
       </c>
-      <c r="I233" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J233" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K233" s="5" t="n">
+      <c r="I233" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J233" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K233" s="29" t="n">
         <v>28</v>
       </c>
-      <c r="L233" s="3" t="inlineStr">
+      <c r="L233" s="27" t="inlineStr">
         <is>
           <t>per Each (None)</t>
         </is>
       </c>
-      <c r="M233" s="2" t="n"/>
-      <c r="N233" s="4">
+      <c r="M233" s="26" t="n"/>
+      <c r="N233" s="28">
         <f>M233*G233</f>
         <v/>
       </c>
-      <c r="O233" s="2" t="n"/>
-      <c r="P233" s="2" t="n"/>
-      <c r="Q233" s="2" t="n"/>
-      <c r="R233" s="2" t="n"/>
-      <c r="S233" s="2" t="n"/>
+      <c r="O233" s="26" t="n"/>
+      <c r="P233" s="26" t="n"/>
+      <c r="Q233" s="26" t="n"/>
+      <c r="R233" s="26" t="n"/>
+      <c r="S233" s="26" t="n"/>
     </row>
     <row r="234">
-      <c r="A234" s="2" t="inlineStr">
+      <c r="A234" s="26" t="inlineStr">
         <is>
           <t>EACH</t>
         </is>
       </c>
-      <c r="B234" s="2" t="n"/>
-      <c r="C234" s="3" t="inlineStr">
+      <c r="B234" s="26" t="n"/>
+      <c r="C234" s="27" t="inlineStr">
         <is>
           <t>Pecan Praline King Cake</t>
         </is>
       </c>
-      <c r="D234" s="3" t="n"/>
-      <c r="E234" s="2" t="n"/>
-      <c r="F234" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G234" s="4" t="n">
+      <c r="D234" s="27" t="n"/>
+      <c r="E234" s="26" t="n"/>
+      <c r="F234" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G234" s="28" t="n">
         <v>30</v>
       </c>
-      <c r="H234" s="5" t="n">
+      <c r="H234" s="29" t="n">
         <v>30</v>
       </c>
-      <c r="I234" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J234" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K234" s="5" t="n">
+      <c r="I234" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J234" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K234" s="29" t="n">
         <v>30</v>
       </c>
-      <c r="L234" s="3" t="inlineStr">
+      <c r="L234" s="27" t="inlineStr">
         <is>
           <t>per Each (None)</t>
         </is>
       </c>
-      <c r="M234" s="2" t="n"/>
-      <c r="N234" s="4">
+      <c r="M234" s="26" t="n"/>
+      <c r="N234" s="28">
         <f>M234*G234</f>
         <v/>
       </c>
-      <c r="O234" s="2" t="n"/>
-      <c r="P234" s="2" t="n"/>
-      <c r="Q234" s="2" t="n"/>
-      <c r="R234" s="2" t="n"/>
-      <c r="S234" s="2" t="n"/>
+      <c r="O234" s="26" t="n"/>
+      <c r="P234" s="26" t="n"/>
+      <c r="Q234" s="26" t="n"/>
+      <c r="R234" s="26" t="n"/>
+      <c r="S234" s="26" t="n"/>
     </row>
     <row r="236">
-      <c r="A236" s="26" t="inlineStr">
+      <c r="A236" s="32" t="inlineStr">
         <is>
           <t>COLOR LEGEND</t>
         </is>
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="21" t="inlineStr">
-        <is>
-          <t>RED    — Per-unit price UP  ≥ 10%  or  ≥ $2.00/unit</t>
-        </is>
-      </c>
-      <c r="B237" s="27" t="n"/>
-      <c r="C237" s="27" t="n"/>
-      <c r="D237" s="27" t="n"/>
+      <c r="A237" s="27" t="inlineStr">
+        <is>
+          <t>DARK RED — No BEK item number matched</t>
+        </is>
+      </c>
+      <c r="B237" s="33" t="n"/>
+      <c r="C237" s="33" t="n"/>
+      <c r="D237" s="33" t="n"/>
     </row>
     <row r="238">
-      <c r="A238" s="15" t="inlineStr">
-        <is>
-          <t>YELLOW — Per-unit price increased (under threshold)</t>
-        </is>
-      </c>
-      <c r="B238" s="27" t="n"/>
-      <c r="C238" s="27" t="n"/>
-      <c r="D238" s="27" t="n"/>
+      <c r="A238" s="21" t="inlineStr">
+        <is>
+          <t>PINK/RED — Price UP ≥ 10% or ≥ $2.00/unit</t>
+        </is>
+      </c>
+      <c r="B238" s="33" t="n"/>
+      <c r="C238" s="33" t="n"/>
+      <c r="D238" s="33" t="n"/>
     </row>
     <row r="239">
-      <c r="A239" s="9" t="inlineStr">
-        <is>
-          <t>GREEN  — Per-unit price decreased</t>
-        </is>
-      </c>
-      <c r="B239" s="27" t="n"/>
-      <c r="C239" s="27" t="n"/>
-      <c r="D239" s="27" t="n"/>
+      <c r="A239" s="15" t="inlineStr">
+        <is>
+          <t>YELLOW   — Price increased (under threshold)</t>
+        </is>
+      </c>
+      <c r="B239" s="33" t="n"/>
+      <c r="C239" s="33" t="n"/>
+      <c r="D239" s="33" t="n"/>
     </row>
     <row r="240">
-      <c r="A240" s="3" t="inlineStr">
-        <is>
-          <t>WHITE  — No change  /  no BEK match</t>
-        </is>
-      </c>
-      <c r="B240" s="27" t="n"/>
-      <c r="C240" s="27" t="n"/>
-      <c r="D240" s="27" t="n"/>
+      <c r="A240" s="9" t="inlineStr">
+        <is>
+          <t>GREEN    — Price decreased</t>
+        </is>
+      </c>
+      <c r="B240" s="33" t="n"/>
+      <c r="C240" s="33" t="n"/>
+      <c r="D240" s="33" t="n"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="3" t="inlineStr">
+        <is>
+          <t>WHITE    — No change</t>
+        </is>
+      </c>
+      <c r="B241" s="33" t="n"/>
+      <c r="C241" s="33" t="n"/>
+      <c r="D241" s="33" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13730,795 +13767,795 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="28" t="inlineStr">
+      <c r="A1" s="34" t="inlineStr">
         <is>
           <t>PRODUCT</t>
         </is>
       </c>
-      <c r="B1" s="28" t="inlineStr">
+      <c r="B1" s="34" t="inlineStr">
         <is>
           <t>SIZE/DESCRIPTION</t>
         </is>
       </c>
-      <c r="C1" s="28" t="inlineStr">
+      <c r="C1" s="34" t="inlineStr">
         <is>
           <t>ON HAND (QTY)</t>
         </is>
       </c>
-      <c r="D1" s="28" t="inlineStr">
+      <c r="D1" s="34" t="inlineStr">
         <is>
           <t>COST</t>
         </is>
       </c>
-      <c r="E1" s="28" t="inlineStr">
+      <c r="E1" s="34" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="29" t="inlineStr">
+      <c r="A2" s="35" t="inlineStr">
         <is>
           <t>SIGNATURE BLEND</t>
         </is>
       </c>
-      <c r="B2" s="29" t="inlineStr">
+      <c r="B2" s="35" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="C2" s="30" t="n">
+      <c r="C2" s="36" t="n">
         <v>1.5</v>
       </c>
-      <c r="D2" s="30" t="n"/>
-      <c r="E2" s="30" t="n"/>
+      <c r="D2" s="36" t="n"/>
+      <c r="E2" s="36" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="29" t="inlineStr">
+      <c r="A3" s="35" t="inlineStr">
         <is>
           <t>AMERICAN CLASSIC</t>
         </is>
       </c>
-      <c r="B3" s="29" t="inlineStr">
+      <c r="B3" s="35" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="C3" s="30" t="n">
+      <c r="C3" s="36" t="n">
         <v>1.75</v>
       </c>
-      <c r="D3" s="30" t="n"/>
-      <c r="E3" s="30" t="n"/>
+      <c r="D3" s="36" t="n"/>
+      <c r="E3" s="36" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="35" t="inlineStr">
         <is>
           <t>PECAN PRALINE</t>
         </is>
       </c>
-      <c r="B4" s="29" t="inlineStr">
+      <c r="B4" s="35" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="C4" s="30" t="n">
+      <c r="C4" s="36" t="n">
         <v>1.5</v>
       </c>
-      <c r="D4" s="30" t="n"/>
-      <c r="E4" s="30" t="n"/>
+      <c r="D4" s="36" t="n"/>
+      <c r="E4" s="36" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="29" t="inlineStr">
+      <c r="A5" s="35" t="inlineStr">
         <is>
           <t>BREAKFAST BLEND</t>
         </is>
       </c>
-      <c r="B5" s="29" t="inlineStr">
+      <c r="B5" s="35" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="C5" s="30" t="n">
+      <c r="C5" s="36" t="n">
         <v>1.75</v>
       </c>
-      <c r="D5" s="30" t="n"/>
-      <c r="E5" s="30" t="n"/>
+      <c r="D5" s="36" t="n"/>
+      <c r="E5" s="36" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="29" t="inlineStr">
+      <c r="A6" s="35" t="inlineStr">
         <is>
           <t>DB ESPRESSO</t>
         </is>
       </c>
-      <c r="B6" s="29" t="inlineStr">
+      <c r="B6" s="35" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="C6" s="30" t="n">
+      <c r="C6" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="D6" s="30" t="n"/>
-      <c r="E6" s="30" t="n"/>
+      <c r="D6" s="36" t="n"/>
+      <c r="E6" s="36" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="29" t="inlineStr">
+      <c r="A7" s="35" t="inlineStr">
         <is>
           <t>Creamer Cups (Irish Cream, French Vanilla, Caramel)</t>
         </is>
       </c>
-      <c r="B7" s="29" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="C7" s="30" t="n">
+      <c r="C7" s="36" t="n">
         <v>3.5</v>
       </c>
-      <c r="D7" s="30" t="n"/>
-      <c r="E7" s="30" t="n"/>
+      <c r="D7" s="36" t="n"/>
+      <c r="E7" s="36" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="29" t="inlineStr">
+      <c r="A8" s="35" t="inlineStr">
         <is>
           <t>Coffee Mate</t>
         </is>
       </c>
-      <c r="B8" s="29" t="inlineStr">
+      <c r="B8" s="35" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="C8" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="30" t="n"/>
-      <c r="E8" s="30" t="n"/>
+      <c r="C8" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="36" t="n"/>
+      <c r="E8" s="36" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="29" t="inlineStr">
+      <c r="A9" s="35" t="inlineStr">
         <is>
           <t>Sweet Cream Creamer</t>
         </is>
       </c>
-      <c r="B9" s="29" t="inlineStr">
+      <c r="B9" s="35" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="C9" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="30" t="n"/>
-      <c r="E9" s="30" t="n"/>
+      <c r="C9" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="36" t="n"/>
+      <c r="E9" s="36" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="A10" s="35" t="inlineStr">
         <is>
           <t>Hazelnut Creamer</t>
         </is>
       </c>
-      <c r="B10" s="29" t="inlineStr">
+      <c r="B10" s="35" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="C10" s="30" t="n">
+      <c r="C10" s="36" t="n">
         <v>1.1</v>
       </c>
-      <c r="D10" s="30" t="n"/>
-      <c r="E10" s="30" t="n"/>
+      <c r="D10" s="36" t="n"/>
+      <c r="E10" s="36" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="29" t="inlineStr">
+      <c r="A11" s="35" t="inlineStr">
         <is>
           <t>Half And Half</t>
         </is>
       </c>
-      <c r="B11" s="29" t="inlineStr">
+      <c r="B11" s="35" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="C11" s="30" t="n">
+      <c r="C11" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="D11" s="30" t="n"/>
-      <c r="E11" s="30" t="n"/>
+      <c r="D11" s="36" t="n"/>
+      <c r="E11" s="36" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="29" t="inlineStr">
+      <c r="A12" s="35" t="inlineStr">
         <is>
           <t>Original Creamer</t>
         </is>
       </c>
-      <c r="B12" s="29" t="inlineStr">
+      <c r="B12" s="35" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="C12" s="30" t="n">
+      <c r="C12" s="36" t="n">
         <v>1.25</v>
       </c>
-      <c r="D12" s="30" t="n"/>
-      <c r="E12" s="30" t="n"/>
+      <c r="D12" s="36" t="n"/>
+      <c r="E12" s="36" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="29" t="inlineStr">
+      <c r="A13" s="35" t="inlineStr">
         <is>
           <t>Caramel Syrup Pump</t>
         </is>
       </c>
-      <c r="B13" s="29" t="inlineStr">
+      <c r="B13" s="35" t="inlineStr">
         <is>
           <t>BOTTLE</t>
         </is>
       </c>
-      <c r="C13" s="30" t="n">
+      <c r="C13" s="36" t="n">
         <v>1.5</v>
       </c>
-      <c r="D13" s="30" t="n"/>
-      <c r="E13" s="30" t="n"/>
+      <c r="D13" s="36" t="n"/>
+      <c r="E13" s="36" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="29" t="inlineStr">
+      <c r="A14" s="35" t="inlineStr">
         <is>
           <t>Hazelnut Syrup Pump</t>
         </is>
       </c>
-      <c r="B14" s="29" t="inlineStr">
+      <c r="B14" s="35" t="inlineStr">
         <is>
           <t>BOTTLE</t>
         </is>
       </c>
-      <c r="C14" s="30" t="n">
+      <c r="C14" s="36" t="n">
         <v>1.5</v>
       </c>
-      <c r="D14" s="30" t="n"/>
-      <c r="E14" s="30" t="n"/>
+      <c r="D14" s="36" t="n"/>
+      <c r="E14" s="36" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="29" t="inlineStr">
+      <c r="A15" s="35" t="inlineStr">
         <is>
           <t>French Vanilla Syrup Pump</t>
         </is>
       </c>
-      <c r="B15" s="29" t="inlineStr">
+      <c r="B15" s="35" t="inlineStr">
         <is>
           <t>BOTTLE</t>
         </is>
       </c>
-      <c r="C15" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" s="30" t="n"/>
-      <c r="E15" s="30" t="n"/>
+      <c r="C15" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="36" t="n"/>
+      <c r="E15" s="36" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="29" t="inlineStr">
+      <c r="A16" s="35" t="inlineStr">
         <is>
           <t>Hold &amp; Go Lids 12-24oz</t>
         </is>
       </c>
-      <c r="B16" s="29" t="inlineStr">
+      <c r="B16" s="35" t="inlineStr">
         <is>
           <t>SLEEVE</t>
         </is>
       </c>
-      <c r="C16" s="30" t="n">
+      <c r="C16" s="36" t="n">
         <v>14</v>
       </c>
-      <c r="D16" s="30" t="n"/>
-      <c r="E16" s="30" t="n"/>
+      <c r="D16" s="36" t="n"/>
+      <c r="E16" s="36" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="29" t="inlineStr">
+      <c r="A17" s="35" t="inlineStr">
         <is>
           <t>Lid SW 16/20oz</t>
         </is>
       </c>
-      <c r="B17" s="29" t="inlineStr">
+      <c r="B17" s="35" t="inlineStr">
         <is>
           <t>SLEEVE</t>
         </is>
       </c>
-      <c r="C17" s="30" t="n"/>
-      <c r="D17" s="30" t="n"/>
-      <c r="E17" s="30" t="n"/>
+      <c r="C17" s="36" t="n"/>
+      <c r="D17" s="36" t="n"/>
+      <c r="E17" s="36" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="29" t="inlineStr">
+      <c r="A18" s="35" t="inlineStr">
         <is>
           <t>Cappuccino French Vanilla</t>
         </is>
       </c>
-      <c r="B18" s="29" t="inlineStr">
+      <c r="B18" s="35" t="inlineStr">
         <is>
           <t>BAG</t>
         </is>
       </c>
-      <c r="C18" s="30" t="n">
+      <c r="C18" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="D18" s="30" t="n"/>
-      <c r="E18" s="30" t="n"/>
+      <c r="D18" s="36" t="n"/>
+      <c r="E18" s="36" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="29" t="inlineStr">
+      <c r="A19" s="35" t="inlineStr">
         <is>
           <t>Sugar Free Cappuccino French Vanilla</t>
         </is>
       </c>
-      <c r="B19" s="29" t="inlineStr">
+      <c r="B19" s="35" t="inlineStr">
         <is>
           <t>BAG</t>
         </is>
       </c>
-      <c r="C19" s="30" t="n">
+      <c r="C19" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="D19" s="30" t="n"/>
-      <c r="E19" s="30" t="n"/>
+      <c r="D19" s="36" t="n"/>
+      <c r="E19" s="36" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="29" t="inlineStr">
+      <c r="A20" s="35" t="inlineStr">
         <is>
           <t>Hot Chocolate</t>
         </is>
       </c>
-      <c r="B20" s="29" t="inlineStr">
+      <c r="B20" s="35" t="inlineStr">
         <is>
           <t>BAG</t>
         </is>
       </c>
-      <c r="C20" s="30" t="n">
+      <c r="C20" s="36" t="n">
         <v>11</v>
       </c>
-      <c r="D20" s="30" t="n"/>
-      <c r="E20" s="30" t="n"/>
+      <c r="D20" s="36" t="n"/>
+      <c r="E20" s="36" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="29" t="inlineStr">
+      <c r="A21" s="35" t="inlineStr">
         <is>
           <t>Creamer Packs</t>
         </is>
       </c>
-      <c r="B21" s="29" t="inlineStr">
+      <c r="B21" s="35" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="C21" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" s="30" t="n"/>
-      <c r="E21" s="30" t="n"/>
+      <c r="C21" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="36" t="n"/>
+      <c r="E21" s="36" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="29" t="inlineStr">
+      <c r="A22" s="35" t="inlineStr">
         <is>
           <t>Sugar Pack</t>
         </is>
       </c>
-      <c r="B22" s="29" t="inlineStr">
+      <c r="B22" s="35" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="C22" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" s="30" t="n"/>
-      <c r="E22" s="30" t="n"/>
+      <c r="C22" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="36" t="n"/>
+      <c r="E22" s="36" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="29" t="inlineStr">
+      <c r="A23" s="35" t="inlineStr">
         <is>
           <t>Blue Sweetener</t>
         </is>
       </c>
-      <c r="B23" s="29" t="inlineStr">
+      <c r="B23" s="35" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="C23" s="30" t="n">
+      <c r="C23" s="36" t="n">
         <v>0.75</v>
       </c>
-      <c r="D23" s="30" t="n"/>
-      <c r="E23" s="30" t="n"/>
+      <c r="D23" s="36" t="n"/>
+      <c r="E23" s="36" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="29" t="inlineStr">
+      <c r="A24" s="35" t="inlineStr">
         <is>
           <t>Yellow Sweetener</t>
         </is>
       </c>
-      <c r="B24" s="29" t="inlineStr">
+      <c r="B24" s="35" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="C24" s="30" t="n">
+      <c r="C24" s="36" t="n">
         <v>0.25</v>
       </c>
-      <c r="D24" s="30" t="n"/>
-      <c r="E24" s="30" t="n"/>
+      <c r="D24" s="36" t="n"/>
+      <c r="E24" s="36" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="29" t="inlineStr">
+      <c r="A25" s="35" t="inlineStr">
         <is>
           <t>Pink Sweetener</t>
         </is>
       </c>
-      <c r="B25" s="29" t="inlineStr">
+      <c r="B25" s="35" t="inlineStr">
         <is>
           <t>BAG</t>
         </is>
       </c>
-      <c r="C25" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" s="30" t="n"/>
-      <c r="E25" s="30" t="n"/>
+      <c r="C25" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="36" t="n"/>
+      <c r="E25" s="36" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="29" t="inlineStr">
+      <c r="A26" s="35" t="inlineStr">
         <is>
           <t>Sugar Packets</t>
         </is>
       </c>
-      <c r="B26" s="29" t="inlineStr">
+      <c r="B26" s="35" t="inlineStr">
         <is>
           <t>EACH</t>
         </is>
       </c>
-      <c r="C26" s="30" t="n">
+      <c r="C26" s="36" t="n">
         <v>45</v>
       </c>
-      <c r="D26" s="30" t="n"/>
-      <c r="E26" s="30" t="n"/>
+      <c r="D26" s="36" t="n"/>
+      <c r="E26" s="36" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="29" t="inlineStr">
+      <c r="A27" s="35" t="inlineStr">
         <is>
           <t>Sugar Canister</t>
         </is>
       </c>
-      <c r="B27" s="29" t="inlineStr">
+      <c r="B27" s="35" t="inlineStr">
         <is>
           <t>EACH</t>
         </is>
       </c>
-      <c r="C27" s="30" t="n">
+      <c r="C27" s="36" t="n">
         <v>39</v>
       </c>
-      <c r="D27" s="30" t="n"/>
-      <c r="E27" s="30" t="n"/>
+      <c r="D27" s="36" t="n"/>
+      <c r="E27" s="36" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="29" t="inlineStr">
+      <c r="A28" s="35" t="inlineStr">
         <is>
           <t>Red Stirrers</t>
         </is>
       </c>
-      <c r="B28" s="29" t="inlineStr">
+      <c r="B28" s="35" t="inlineStr">
         <is>
           <t>PACK</t>
         </is>
       </c>
-      <c r="C28" s="30" t="n">
+      <c r="C28" s="36" t="n">
         <v>3.5</v>
       </c>
-      <c r="D28" s="30" t="n"/>
-      <c r="E28" s="30" t="n"/>
+      <c r="D28" s="36" t="n"/>
+      <c r="E28" s="36" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="29" t="inlineStr">
+      <c r="A29" s="35" t="inlineStr">
         <is>
           <t>16 oz Double-Wall Cup</t>
         </is>
       </c>
-      <c r="B29" s="29" t="inlineStr">
+      <c r="B29" s="35" t="inlineStr">
         <is>
           <t>SLV</t>
         </is>
       </c>
-      <c r="C29" s="30" t="n">
+      <c r="C29" s="36" t="n">
         <v>32</v>
       </c>
-      <c r="D29" s="30" t="n"/>
-      <c r="E29" s="30" t="n"/>
+      <c r="D29" s="36" t="n"/>
+      <c r="E29" s="36" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="29" t="inlineStr">
+      <c r="A30" s="35" t="inlineStr">
         <is>
           <t>16oz Single-Wall Cup</t>
         </is>
       </c>
-      <c r="B30" s="29" t="inlineStr">
+      <c r="B30" s="35" t="inlineStr">
         <is>
           <t>SLV</t>
         </is>
       </c>
-      <c r="C30" s="30" t="n"/>
-      <c r="D30" s="30" t="n"/>
-      <c r="E30" s="30" t="n"/>
+      <c r="C30" s="36" t="n"/>
+      <c r="D30" s="36" t="n"/>
+      <c r="E30" s="36" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="29" t="inlineStr">
+      <c r="A31" s="35" t="inlineStr">
         <is>
           <t>24 oz Double-Wall Cup</t>
         </is>
       </c>
-      <c r="B31" s="29" t="inlineStr">
+      <c r="B31" s="35" t="inlineStr">
         <is>
           <t>SLV</t>
         </is>
       </c>
-      <c r="C31" s="30" t="n">
+      <c r="C31" s="36" t="n">
         <v>37</v>
       </c>
-      <c r="D31" s="30" t="n"/>
-      <c r="E31" s="30" t="n"/>
+      <c r="D31" s="36" t="n"/>
+      <c r="E31" s="36" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="29" t="inlineStr">
+      <c r="A32" s="35" t="inlineStr">
         <is>
           <t>32oz Fountain Cup</t>
         </is>
       </c>
-      <c r="B32" s="29" t="inlineStr">
+      <c r="B32" s="35" t="inlineStr">
         <is>
           <t>SLV</t>
         </is>
       </c>
-      <c r="C32" s="30" t="n">
+      <c r="C32" s="36" t="n">
         <v>63</v>
       </c>
-      <c r="D32" s="30" t="n"/>
-      <c r="E32" s="30" t="n"/>
+      <c r="D32" s="36" t="n"/>
+      <c r="E32" s="36" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="29" t="inlineStr">
+      <c r="A33" s="35" t="inlineStr">
         <is>
           <t>32oz Lid</t>
         </is>
       </c>
-      <c r="B33" s="29" t="inlineStr">
+      <c r="B33" s="35" t="inlineStr">
         <is>
           <t>SLV</t>
         </is>
       </c>
-      <c r="C33" s="30" t="n">
+      <c r="C33" s="36" t="n">
         <v>61</v>
       </c>
-      <c r="D33" s="31" t="n">
+      <c r="D33" s="37" t="n">
         <v>2.85</v>
       </c>
-      <c r="E33" s="31">
+      <c r="E33" s="37">
         <f>C33*D33</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="29" t="inlineStr">
+      <c r="A34" s="35" t="inlineStr">
         <is>
           <t>20oz Cup</t>
         </is>
       </c>
-      <c r="B34" s="29" t="inlineStr">
+      <c r="B34" s="35" t="inlineStr">
         <is>
           <t>SLV</t>
         </is>
       </c>
-      <c r="C34" s="30" t="n">
+      <c r="C34" s="36" t="n">
         <v>81</v>
       </c>
-      <c r="D34" s="30" t="n"/>
-      <c r="E34" s="30" t="n"/>
+      <c r="D34" s="36" t="n"/>
+      <c r="E34" s="36" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="29" t="inlineStr">
+      <c r="A35" s="35" t="inlineStr">
         <is>
           <t>20oz Lid</t>
         </is>
       </c>
-      <c r="B35" s="29" t="inlineStr">
+      <c r="B35" s="35" t="inlineStr">
         <is>
           <t>SLV</t>
         </is>
       </c>
-      <c r="C35" s="30" t="n">
+      <c r="C35" s="36" t="n">
         <v>56</v>
       </c>
-      <c r="D35" s="30" t="n"/>
-      <c r="E35" s="30" t="n"/>
+      <c r="D35" s="36" t="n"/>
+      <c r="E35" s="36" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="29" t="inlineStr">
+      <c r="A36" s="35" t="inlineStr">
         <is>
           <t>Red Straws</t>
         </is>
       </c>
-      <c r="B36" s="29" t="inlineStr">
+      <c r="B36" s="35" t="inlineStr">
         <is>
           <t>BOX</t>
         </is>
       </c>
-      <c r="C36" s="30" t="n">
+      <c r="C36" s="36" t="n">
         <v>12</v>
       </c>
-      <c r="D36" s="30" t="n"/>
-      <c r="E36" s="30" t="n"/>
+      <c r="D36" s="36" t="n"/>
+      <c r="E36" s="36" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="29" t="inlineStr">
+      <c r="A37" s="35" t="inlineStr">
         <is>
           <t>Bag In Box 5 Gal Syrup</t>
         </is>
       </c>
-      <c r="B37" s="29" t="inlineStr">
+      <c r="B37" s="35" t="inlineStr">
         <is>
           <t>BOX</t>
         </is>
       </c>
-      <c r="C37" s="30" t="n">
+      <c r="C37" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="D37" s="30" t="n"/>
-      <c r="E37" s="30" t="n"/>
+      <c r="D37" s="36" t="n"/>
+      <c r="E37" s="36" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="29" t="inlineStr">
+      <c r="A38" s="35" t="inlineStr">
         <is>
           <t>Bag In Box 2.5 Gal Syrup</t>
         </is>
       </c>
-      <c r="B38" s="29" t="inlineStr">
+      <c r="B38" s="35" t="inlineStr">
         <is>
           <t>BOX</t>
         </is>
       </c>
-      <c r="C38" s="30" t="n">
+      <c r="C38" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="D38" s="30" t="n"/>
-      <c r="E38" s="30" t="n"/>
+      <c r="D38" s="36" t="n"/>
+      <c r="E38" s="36" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="29" t="inlineStr">
+      <c r="A39" s="35" t="inlineStr">
         <is>
           <t>CO2 Tank</t>
         </is>
       </c>
-      <c r="B39" s="29" t="inlineStr">
+      <c r="B39" s="35" t="inlineStr">
         <is>
           <t>EACH</t>
         </is>
       </c>
-      <c r="C39" s="30" t="n">
+      <c r="C39" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="D39" s="30" t="n"/>
-      <c r="E39" s="30" t="n"/>
+      <c r="D39" s="36" t="n"/>
+      <c r="E39" s="36" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="29" t="inlineStr">
+      <c r="A40" s="35" t="inlineStr">
         <is>
           <t>Cafe Tango Lids</t>
         </is>
       </c>
-      <c r="B40" s="29" t="inlineStr">
+      <c r="B40" s="35" t="inlineStr">
         <is>
           <t>SLEEVE</t>
         </is>
       </c>
-      <c r="C40" s="30" t="n">
+      <c r="C40" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="D40" s="31" t="n">
+      <c r="D40" s="37" t="n">
         <v>2.53</v>
       </c>
-      <c r="E40" s="31">
+      <c r="E40" s="37">
         <f>C40*D40</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="29" t="inlineStr">
+      <c r="A41" s="35" t="inlineStr">
         <is>
           <t>16 oz Tango Cup</t>
         </is>
       </c>
-      <c r="B41" s="29" t="inlineStr">
+      <c r="B41" s="35" t="inlineStr">
         <is>
           <t>SLV</t>
         </is>
       </c>
-      <c r="C41" s="30" t="n">
+      <c r="C41" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="D41" s="31" t="n">
+      <c r="D41" s="37" t="n">
         <v>6.78</v>
       </c>
-      <c r="E41" s="31">
+      <c r="E41" s="37">
         <f>C41*D41</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="29" t="inlineStr">
+      <c r="A42" s="35" t="inlineStr">
         <is>
           <t>24 oz Tango Cup</t>
         </is>
       </c>
-      <c r="B42" s="29" t="inlineStr">
+      <c r="B42" s="35" t="inlineStr">
         <is>
           <t>SLV</t>
         </is>
       </c>
-      <c r="C42" s="30" t="n">
+      <c r="C42" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="D42" s="30" t="n"/>
-      <c r="E42" s="30" t="n"/>
+      <c r="D42" s="36" t="n"/>
+      <c r="E42" s="36" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="29" t="inlineStr">
+      <c r="A43" s="35" t="inlineStr">
         <is>
           <t>Cafe Tango French Vanilla</t>
         </is>
       </c>
-      <c r="B43" s="29" t="inlineStr">
+      <c r="B43" s="35" t="inlineStr">
         <is>
           <t>BAG</t>
         </is>
       </c>
-      <c r="C43" s="30" t="n">
+      <c r="C43" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="D43" s="31" t="n">
+      <c r="D43" s="37" t="n">
         <v>13.64</v>
       </c>
-      <c r="E43" s="31">
+      <c r="E43" s="37">
         <f>C43*D43</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="29" t="inlineStr">
+      <c r="A44" s="35" t="inlineStr">
         <is>
           <t>Cafe Tango Mocha</t>
         </is>
       </c>
-      <c r="B44" s="29" t="inlineStr">
+      <c r="B44" s="35" t="inlineStr">
         <is>
           <t>BAG</t>
         </is>
       </c>
-      <c r="C44" s="30" t="n">
+      <c r="C44" s="36" t="n">
         <v>25</v>
       </c>
-      <c r="D44" s="30" t="n"/>
-      <c r="E44" s="30" t="n"/>
+      <c r="D44" s="36" t="n"/>
+      <c r="E44" s="36" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="29" t="inlineStr">
+      <c r="A45" s="35" t="inlineStr">
         <is>
           <t>Caramel Macchiato</t>
         </is>
       </c>
-      <c r="B45" s="29" t="inlineStr">
+      <c r="B45" s="35" t="inlineStr">
         <is>
           <t>BAG</t>
         </is>
       </c>
-      <c r="C45" s="30" t="n">
+      <c r="C45" s="36" t="n">
         <v>14</v>
       </c>
-      <c r="D45" s="30" t="n"/>
-      <c r="E45" s="30" t="n"/>
+      <c r="D45" s="36" t="n"/>
+      <c r="E45" s="36" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Updated_185_Count_Sheet_BEK_v2.xlsx
+++ b/Updated_185_Count_Sheet_BEK_v2.xlsx
@@ -75,7 +75,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CC0000"/>
+        <fgColor rgb="FFCC0000"/>
       </patternFill>
     </fill>
     <fill>

--- a/Updated_185_Count_Sheet_BEK_v2.xlsx
+++ b/Updated_185_Count_Sheet_BEK_v2.xlsx
@@ -46,7 +46,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -71,6 +71,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF6600"/>
       </patternFill>
     </fill>
     <fill>
@@ -125,7 +130,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -220,9 +225,27 @@
     <xf numFmtId="167" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -599,7 +622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S241"/>
+  <dimension ref="A1:S242"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1359,114 +1382,116 @@
       <c r="S12" s="20" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="26" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" s="26" t="inlineStr">
         <is>
           <t>63670</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="27" t="inlineStr">
         <is>
           <t>Box Barn Paper 10 Pound 8.88X5x6.75 White</t>
         </is>
       </c>
-      <c r="D13" s="3" t="n"/>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="D13" s="27" t="n"/>
+      <c r="E13" s="26" t="inlineStr">
         <is>
           <t>1/150Cnt</t>
         </is>
       </c>
-      <c r="F13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" s="4" t="n">
+      <c r="F13" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="28" t="n">
         <v>113.19</v>
       </c>
-      <c r="H13" s="5" t="n">
+      <c r="H13" s="29" t="n">
         <v>113.19</v>
       </c>
-      <c r="I13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="5" t="n">
+      <c r="I13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="29" t="n">
         <v>113.19</v>
       </c>
-      <c r="L13" s="3" t="inlineStr">
+      <c r="L13" s="27" t="inlineStr">
         <is>
           <t>per Case (1/150Cnt)</t>
         </is>
       </c>
-      <c r="M13" s="2" t="n"/>
-      <c r="N13" s="4">
+      <c r="M13" s="26" t="n"/>
+      <c r="N13" s="28">
         <f>M13*G13</f>
         <v/>
       </c>
-      <c r="O13" s="2" t="n"/>
-      <c r="P13" s="2" t="n"/>
-      <c r="Q13" s="2" t="n"/>
-      <c r="R13" s="2" t="n"/>
-      <c r="S13" s="2" t="n"/>
+      <c r="O13" s="26" t="n"/>
+      <c r="P13" s="26" t="n"/>
+      <c r="Q13" s="26" t="n"/>
+      <c r="R13" s="26" t="n"/>
+      <c r="S13" s="26" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n">
-        <v>19275</v>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>019275</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>Box Carryout Chicken Fast Top 7X4x2.75 White</t>
         </is>
       </c>
-      <c r="D14" s="3" t="n"/>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>1/500Cnt</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" s="4" t="n">
+      <c r="D14" s="9" t="n"/>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>1 / 500 CT</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="10" t="n">
+        <v>78.12</v>
+      </c>
+      <c r="H14" s="11" t="n">
         <v>109.05</v>
       </c>
-      <c r="H14" s="5" t="n">
-        <v>109.05</v>
-      </c>
-      <c r="I14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="5" t="n">
-        <v>109.05</v>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t>per Case (1/500Cnt)</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="n"/>
-      <c r="N14" s="4">
+      <c r="I14" s="12" t="n">
+        <v>-30.92999999999999</v>
+      </c>
+      <c r="J14" s="13" t="n">
+        <v>-0.2836313617606602</v>
+      </c>
+      <c r="K14" s="11" t="n">
+        <v>78.12</v>
+      </c>
+      <c r="L14" s="9" t="inlineStr">
+        <is>
+          <t>per Case (1 / 500 CT)</t>
+        </is>
+      </c>
+      <c r="M14" s="8" t="n"/>
+      <c r="N14" s="10">
         <f>M14*G14</f>
         <v/>
       </c>
-      <c r="O14" s="2" t="n"/>
-      <c r="P14" s="2" t="n"/>
-      <c r="Q14" s="2" t="n"/>
-      <c r="R14" s="2" t="n"/>
-      <c r="S14" s="2" t="n"/>
+      <c r="O14" s="8" t="n"/>
+      <c r="P14" s="8" t="n"/>
+      <c r="Q14" s="8" t="n"/>
+      <c r="R14" s="8" t="n"/>
+      <c r="S14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1991,58 +2016,60 @@
       <c r="S23" s="2" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>CAKE</t>
         </is>
       </c>
-      <c r="B24" s="2" t="n">
-        <v>18044</v>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>018044</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
         <is>
           <t>Cake Carrot Momma's Old Fashioned 16 Slice Frozen</t>
         </is>
       </c>
-      <c r="D24" s="3" t="n"/>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>2/114 Oz</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" s="4" t="n">
+      <c r="D24" s="9" t="n"/>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>4 / 46 OZ</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="10" t="n">
+        <v>76.98999999999999</v>
+      </c>
+      <c r="H24" s="11" t="n">
         <v>55.12</v>
       </c>
-      <c r="H24" s="5" t="n">
-        <v>55.12</v>
-      </c>
-      <c r="I24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" s="5" t="n">
-        <v>27.56</v>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>per Cake (2/114 Oz)</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="n"/>
-      <c r="N24" s="4">
+      <c r="I24" s="12" t="n">
+        <v>-35.8725</v>
+      </c>
+      <c r="J24" s="13" t="n">
+        <v>-0.6508073294629899</v>
+      </c>
+      <c r="K24" s="11" t="n">
+        <v>19.2475</v>
+      </c>
+      <c r="L24" s="9" t="inlineStr">
+        <is>
+          <t>per Cake (4 / 46 OZ)</t>
+        </is>
+      </c>
+      <c r="M24" s="8" t="n"/>
+      <c r="N24" s="10">
         <f>M24*G24</f>
         <v/>
       </c>
-      <c r="O24" s="2" t="n"/>
-      <c r="P24" s="2" t="n"/>
-      <c r="Q24" s="2" t="n"/>
-      <c r="R24" s="2" t="n"/>
-      <c r="S24" s="2" t="n"/>
+      <c r="O24" s="8" t="n"/>
+      <c r="P24" s="8" t="n"/>
+      <c r="Q24" s="8" t="n"/>
+      <c r="R24" s="8" t="n"/>
+      <c r="S24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
@@ -2255,58 +2282,60 @@
       <c r="S28" s="2" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" s="20" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="B29" s="2" t="n">
-        <v>12324</v>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>012324</t>
+        </is>
+      </c>
+      <c r="C29" s="21" t="inlineStr">
         <is>
           <t>Carrots Sliced</t>
         </is>
       </c>
-      <c r="D29" s="3" t="n"/>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>1/20Lb</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" s="4" t="n">
+      <c r="D29" s="21" t="n"/>
+      <c r="E29" s="20" t="inlineStr">
+        <is>
+          <t>1 / 20 LB</t>
+        </is>
+      </c>
+      <c r="F29" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" s="22" t="n">
+        <v>61.43</v>
+      </c>
+      <c r="H29" s="23" t="n">
         <v>22.4</v>
       </c>
-      <c r="H29" s="5" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="I29" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" s="5" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="L29" s="3" t="inlineStr">
-        <is>
-          <t>per Case (1/20Lb)</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="n"/>
-      <c r="N29" s="4">
+      <c r="I29" s="24" t="n">
+        <v>39.03</v>
+      </c>
+      <c r="J29" s="25" t="n">
+        <v>1.742410714285714</v>
+      </c>
+      <c r="K29" s="23" t="n">
+        <v>61.43</v>
+      </c>
+      <c r="L29" s="21" t="inlineStr">
+        <is>
+          <t>per Case (1 / 20 LB)</t>
+        </is>
+      </c>
+      <c r="M29" s="20" t="n"/>
+      <c r="N29" s="22">
         <f>M29*G29</f>
         <v/>
       </c>
-      <c r="O29" s="2" t="n"/>
-      <c r="P29" s="2" t="n"/>
-      <c r="Q29" s="2" t="n"/>
-      <c r="R29" s="2" t="n"/>
-      <c r="S29" s="2" t="n"/>
+      <c r="O29" s="20" t="n"/>
+      <c r="P29" s="20" t="n"/>
+      <c r="Q29" s="20" t="n"/>
+      <c r="R29" s="20" t="n"/>
+      <c r="S29" s="20" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2525,58 +2554,60 @@
       <c r="S33" s="2" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="A34" s="20" t="inlineStr">
         <is>
           <t>BAG</t>
         </is>
       </c>
-      <c r="B34" s="2" t="n">
-        <v>16063</v>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="B34" s="20" t="inlineStr">
+        <is>
+          <t>016063</t>
+        </is>
+      </c>
+      <c r="C34" s="21" t="inlineStr">
         <is>
           <t>Cheese Cheddar Yellow Mild Feather Shredded Refrigerated</t>
         </is>
       </c>
-      <c r="D34" s="3" t="n"/>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>1/5 Lb</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G34" s="4" t="n">
+      <c r="D34" s="21" t="n"/>
+      <c r="E34" s="20" t="inlineStr">
+        <is>
+          <t>4 / 5 LB</t>
+        </is>
+      </c>
+      <c r="F34" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="22" t="n">
+        <v>72.33</v>
+      </c>
+      <c r="H34" s="23" t="n">
         <v>13.32</v>
       </c>
-      <c r="H34" s="5" t="n">
-        <v>13.32</v>
-      </c>
-      <c r="I34" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" s="5" t="n">
-        <v>13.32</v>
-      </c>
-      <c r="L34" s="3" t="inlineStr">
-        <is>
-          <t>per Bag (1/5 Lb)</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="n"/>
-      <c r="N34" s="4">
+      <c r="I34" s="24" t="n">
+        <v>4.762499999999999</v>
+      </c>
+      <c r="J34" s="25" t="n">
+        <v>0.357545045045045</v>
+      </c>
+      <c r="K34" s="23" t="n">
+        <v>18.0825</v>
+      </c>
+      <c r="L34" s="21" t="inlineStr">
+        <is>
+          <t>per Bag (4 / 5 LB)</t>
+        </is>
+      </c>
+      <c r="M34" s="20" t="n"/>
+      <c r="N34" s="22">
         <f>M34*G34</f>
         <v/>
       </c>
-      <c r="O34" s="2" t="n"/>
-      <c r="P34" s="2" t="n"/>
-      <c r="Q34" s="2" t="n"/>
-      <c r="R34" s="2" t="n"/>
-      <c r="S34" s="2" t="n"/>
+      <c r="O34" s="20" t="n"/>
+      <c r="P34" s="20" t="n"/>
+      <c r="Q34" s="20" t="n"/>
+      <c r="R34" s="20" t="n"/>
+      <c r="S34" s="20" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2741,60 +2772,60 @@
       <c r="S37" s="2" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="A38" s="26" t="inlineStr">
         <is>
           <t>CAKE</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B38" s="26" t="inlineStr">
         <is>
           <t>JV088</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="C38" s="27" t="inlineStr">
         <is>
           <t>Cheesecake Cinnamon Churro Frozen</t>
         </is>
       </c>
-      <c r="D38" s="3" t="n"/>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="D38" s="27" t="n"/>
+      <c r="E38" s="26" t="inlineStr">
         <is>
           <t>2/14 Sl</t>
         </is>
       </c>
-      <c r="F38" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" s="4" t="n">
+      <c r="F38" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="28" t="n">
         <v>47.5</v>
       </c>
-      <c r="H38" s="5" t="n">
+      <c r="H38" s="29" t="n">
         <v>47.5</v>
       </c>
-      <c r="I38" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" s="5" t="n">
+      <c r="I38" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="29" t="n">
         <v>23.75</v>
       </c>
-      <c r="L38" s="3" t="inlineStr">
+      <c r="L38" s="27" t="inlineStr">
         <is>
           <t>per Cake (2/14 Sl)</t>
         </is>
       </c>
-      <c r="M38" s="2" t="n"/>
-      <c r="N38" s="4">
+      <c r="M38" s="26" t="n"/>
+      <c r="N38" s="28">
         <f>M38*G38</f>
         <v/>
       </c>
-      <c r="O38" s="2" t="n"/>
-      <c r="P38" s="2" t="n"/>
-      <c r="Q38" s="2" t="n"/>
-      <c r="R38" s="2" t="n"/>
-      <c r="S38" s="2" t="n"/>
+      <c r="O38" s="26" t="n"/>
+      <c r="P38" s="26" t="n"/>
+      <c r="Q38" s="26" t="n"/>
+      <c r="R38" s="26" t="n"/>
+      <c r="S38" s="26" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="20" t="inlineStr">
@@ -2917,52 +2948,52 @@
       <c r="S40" s="14" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="26" t="inlineStr">
+      <c r="A41" s="32" t="inlineStr">
         <is>
           <t>SLEEVE</t>
         </is>
       </c>
-      <c r="B41" s="26" t="n"/>
-      <c r="C41" s="27" t="inlineStr">
+      <c r="B41" s="32" t="n"/>
+      <c r="C41" s="33" t="inlineStr">
         <is>
           <t>Chili</t>
         </is>
       </c>
-      <c r="D41" s="27" t="n"/>
-      <c r="E41" s="26" t="n"/>
-      <c r="F41" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G41" s="28" t="n">
+      <c r="D41" s="33" t="n"/>
+      <c r="E41" s="32" t="n"/>
+      <c r="F41" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="34" t="n">
         <v>17.8</v>
       </c>
-      <c r="H41" s="29" t="n">
+      <c r="H41" s="35" t="n">
         <v>17.8</v>
       </c>
-      <c r="I41" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" s="29" t="n">
+      <c r="I41" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="35" t="n">
         <v>17.8</v>
       </c>
-      <c r="L41" s="27" t="inlineStr">
+      <c r="L41" s="33" t="inlineStr">
         <is>
           <t>per Sleeve (None)</t>
         </is>
       </c>
-      <c r="M41" s="26" t="n"/>
-      <c r="N41" s="28">
+      <c r="M41" s="32" t="n"/>
+      <c r="N41" s="34">
         <f>M41*G41</f>
         <v/>
       </c>
-      <c r="O41" s="26" t="n"/>
-      <c r="P41" s="26" t="n"/>
-      <c r="Q41" s="26" t="n"/>
-      <c r="R41" s="26" t="n"/>
-      <c r="S41" s="26" t="n"/>
+      <c r="O41" s="32" t="n"/>
+      <c r="P41" s="32" t="n"/>
+      <c r="Q41" s="32" t="n"/>
+      <c r="R41" s="32" t="n"/>
+      <c r="S41" s="32" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n"/>
@@ -3369,58 +3400,58 @@
       <c r="S48" s="8" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="A49" s="26" t="inlineStr">
         <is>
           <t>CONTAINER</t>
         </is>
       </c>
-      <c r="B49" s="2" t="n">
+      <c r="B49" s="26" t="n">
         <v>301970</v>
       </c>
-      <c r="C49" s="3" t="inlineStr">
+      <c r="C49" s="27" t="inlineStr">
         <is>
           <t>Coleslaw Creamy</t>
         </is>
       </c>
-      <c r="D49" s="3" t="n"/>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="D49" s="27" t="n"/>
+      <c r="E49" s="26" t="inlineStr">
         <is>
           <t>2/4.5 Lb</t>
         </is>
       </c>
-      <c r="F49" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G49" s="4" t="n">
+      <c r="F49" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" s="28" t="n">
         <v>9.890000000000001</v>
       </c>
-      <c r="H49" s="5" t="n">
+      <c r="H49" s="29" t="n">
         <v>9.890000000000001</v>
       </c>
-      <c r="I49" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" s="5" t="n">
+      <c r="I49" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" s="29" t="n">
         <v>4.945</v>
       </c>
-      <c r="L49" s="3" t="inlineStr">
+      <c r="L49" s="27" t="inlineStr">
         <is>
           <t>per Container (2/4.5 Lb)</t>
         </is>
       </c>
-      <c r="M49" s="2" t="n"/>
-      <c r="N49" s="4">
+      <c r="M49" s="26" t="n"/>
+      <c r="N49" s="28">
         <f>M49*G49</f>
         <v/>
       </c>
-      <c r="O49" s="2" t="n"/>
-      <c r="P49" s="2" t="n"/>
-      <c r="Q49" s="2" t="n"/>
-      <c r="R49" s="2" t="n"/>
-      <c r="S49" s="2" t="n"/>
+      <c r="O49" s="26" t="n"/>
+      <c r="P49" s="26" t="n"/>
+      <c r="Q49" s="26" t="n"/>
+      <c r="R49" s="26" t="n"/>
+      <c r="S49" s="26" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -3585,116 +3616,116 @@
       <c r="S52" s="2" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="A53" s="26" t="inlineStr">
         <is>
           <t>SLEEVE</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B53" s="26" t="inlineStr">
         <is>
           <t>79400</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr">
+      <c r="C53" s="27" t="inlineStr">
         <is>
           <t>Container Foam 16 Ounce Squat White</t>
         </is>
       </c>
-      <c r="D53" s="3" t="n"/>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="D53" s="27" t="n"/>
+      <c r="E53" s="26" t="inlineStr">
         <is>
           <t>20/25Cnt</t>
         </is>
       </c>
-      <c r="F53" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G53" s="4" t="n">
+      <c r="F53" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" s="28" t="n">
         <v>1.67</v>
       </c>
-      <c r="H53" s="5" t="n">
+      <c r="H53" s="29" t="n">
         <v>1.67</v>
       </c>
-      <c r="I53" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" s="5" t="n">
+      <c r="I53" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" s="29" t="n">
         <v>0.08349999999999999</v>
       </c>
-      <c r="L53" s="3" t="inlineStr">
+      <c r="L53" s="27" t="inlineStr">
         <is>
           <t>per Sleeve (20/25Cnt)</t>
         </is>
       </c>
-      <c r="M53" s="2" t="n"/>
-      <c r="N53" s="4">
+      <c r="M53" s="26" t="n"/>
+      <c r="N53" s="28">
         <f>M53*G53</f>
         <v/>
       </c>
-      <c r="O53" s="2" t="n"/>
-      <c r="P53" s="2" t="n"/>
-      <c r="Q53" s="2" t="n"/>
-      <c r="R53" s="2" t="n"/>
-      <c r="S53" s="2" t="n"/>
+      <c r="O53" s="26" t="n"/>
+      <c r="P53" s="26" t="n"/>
+      <c r="Q53" s="26" t="n"/>
+      <c r="R53" s="26" t="n"/>
+      <c r="S53" s="26" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="A54" s="26" t="inlineStr">
         <is>
           <t>SLEEVE</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B54" s="26" t="inlineStr">
         <is>
           <t>79342</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="C54" s="27" t="inlineStr">
         <is>
           <t>Container Foam 6 Ounce Squat White</t>
         </is>
       </c>
-      <c r="D54" s="3" t="n"/>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="D54" s="27" t="n"/>
+      <c r="E54" s="26" t="inlineStr">
         <is>
           <t>20/50Cnt</t>
         </is>
       </c>
-      <c r="F54" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G54" s="4" t="n">
+      <c r="F54" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="28" t="n">
         <v>1.99</v>
       </c>
-      <c r="H54" s="5" t="n">
+      <c r="H54" s="29" t="n">
         <v>1.99</v>
       </c>
-      <c r="I54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" s="5" t="n">
+      <c r="I54" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" s="29" t="n">
         <v>0.09950000000000001</v>
       </c>
-      <c r="L54" s="3" t="inlineStr">
+      <c r="L54" s="27" t="inlineStr">
         <is>
           <t>per Sleeve (20/50Cnt)</t>
         </is>
       </c>
-      <c r="M54" s="2" t="n"/>
-      <c r="N54" s="4">
+      <c r="M54" s="26" t="n"/>
+      <c r="N54" s="28">
         <f>M54*G54</f>
         <v/>
       </c>
-      <c r="O54" s="2" t="n"/>
-      <c r="P54" s="2" t="n"/>
-      <c r="Q54" s="2" t="n"/>
-      <c r="R54" s="2" t="n"/>
-      <c r="S54" s="2" t="n"/>
+      <c r="O54" s="26" t="n"/>
+      <c r="P54" s="26" t="n"/>
+      <c r="Q54" s="26" t="n"/>
+      <c r="R54" s="26" t="n"/>
+      <c r="S54" s="26" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -3751,60 +3782,60 @@
       <c r="S55" s="2" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="A56" s="26" t="inlineStr">
         <is>
           <t>SLEEVE</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B56" s="26" t="inlineStr">
         <is>
           <t>DW324</t>
         </is>
       </c>
-      <c r="C56" s="3" t="inlineStr">
+      <c r="C56" s="27" t="inlineStr">
         <is>
           <t>Container Foam 3 Compartment 9X9x3 Large Hinged White</t>
         </is>
       </c>
-      <c r="D56" s="3" t="n"/>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="D56" s="27" t="n"/>
+      <c r="E56" s="26" t="inlineStr">
         <is>
           <t>2/100Cnt</t>
         </is>
       </c>
-      <c r="F56" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G56" s="4" t="n">
+      <c r="F56" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" s="28" t="n">
         <v>10.3</v>
       </c>
-      <c r="H56" s="5" t="n">
+      <c r="H56" s="29" t="n">
         <v>10.3</v>
       </c>
-      <c r="I56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" s="5" t="n">
+      <c r="I56" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="29" t="n">
         <v>5.15</v>
       </c>
-      <c r="L56" s="3" t="inlineStr">
+      <c r="L56" s="27" t="inlineStr">
         <is>
           <t>per Sleeve (2/100Cnt)</t>
         </is>
       </c>
-      <c r="M56" s="2" t="n"/>
-      <c r="N56" s="4">
+      <c r="M56" s="26" t="n"/>
+      <c r="N56" s="28">
         <f>M56*G56</f>
         <v/>
       </c>
-      <c r="O56" s="2" t="n"/>
-      <c r="P56" s="2" t="n"/>
-      <c r="Q56" s="2" t="n"/>
-      <c r="R56" s="2" t="n"/>
-      <c r="S56" s="2" t="n"/>
+      <c r="O56" s="26" t="n"/>
+      <c r="P56" s="26" t="n"/>
+      <c r="Q56" s="26" t="n"/>
+      <c r="R56" s="26" t="n"/>
+      <c r="S56" s="26" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -3915,114 +3946,114 @@
       <c r="S58" s="2" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="A59" s="26" t="inlineStr">
         <is>
           <t>SLEEVE</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B59" s="26" t="inlineStr">
         <is>
           <t>TG366</t>
         </is>
       </c>
-      <c r="C59" s="3" t="inlineStr">
+      <c r="C59" s="27" t="inlineStr">
         <is>
           <t>Container Paper 12 Ounce White</t>
         </is>
       </c>
-      <c r="D59" s="3" t="n"/>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="D59" s="27" t="n"/>
+      <c r="E59" s="26" t="inlineStr">
         <is>
           <t>20Cnt</t>
         </is>
       </c>
-      <c r="F59" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G59" s="4" t="n">
+      <c r="F59" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" s="28" t="n">
         <v>4.78</v>
       </c>
-      <c r="H59" s="5" t="n">
+      <c r="H59" s="29" t="n">
         <v>4.78</v>
       </c>
-      <c r="I59" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K59" s="5" t="n">
+      <c r="I59" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" s="29" t="n">
         <v>0.239</v>
       </c>
-      <c r="L59" s="3" t="inlineStr">
+      <c r="L59" s="27" t="inlineStr">
         <is>
           <t>per Sleeve (20Cnt)</t>
         </is>
       </c>
-      <c r="M59" s="2" t="n"/>
-      <c r="N59" s="4">
+      <c r="M59" s="26" t="n"/>
+      <c r="N59" s="28">
         <f>M59*G59</f>
         <v/>
       </c>
-      <c r="O59" s="2" t="n"/>
-      <c r="P59" s="2" t="n"/>
-      <c r="Q59" s="2" t="n"/>
-      <c r="R59" s="2" t="n"/>
-      <c r="S59" s="2" t="n"/>
+      <c r="O59" s="26" t="n"/>
+      <c r="P59" s="26" t="n"/>
+      <c r="Q59" s="26" t="n"/>
+      <c r="R59" s="26" t="n"/>
+      <c r="S59" s="26" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="A60" s="26" t="inlineStr">
         <is>
           <t>SLEEVE</t>
         </is>
       </c>
-      <c r="B60" s="2" t="n">
+      <c r="B60" s="26" t="n">
         <v>219097</v>
       </c>
-      <c r="C60" s="3" t="inlineStr">
+      <c r="C60" s="27" t="inlineStr">
         <is>
           <t>Container Plastic 6X5.75X3 Square Clear Hinged Polystyrene</t>
         </is>
       </c>
-      <c r="D60" s="3" t="n"/>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="D60" s="27" t="n"/>
+      <c r="E60" s="26" t="inlineStr">
         <is>
           <t>4/125Cnt</t>
         </is>
       </c>
-      <c r="F60" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G60" s="4" t="n">
+      <c r="F60" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" s="28" t="n">
         <v>11.64</v>
       </c>
-      <c r="H60" s="5" t="n">
+      <c r="H60" s="29" t="n">
         <v>11.64</v>
       </c>
-      <c r="I60" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K60" s="5" t="n">
+      <c r="I60" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" s="29" t="n">
         <v>2.91</v>
       </c>
-      <c r="L60" s="3" t="inlineStr">
+      <c r="L60" s="27" t="inlineStr">
         <is>
           <t>per Sleeve (4/125Cnt)</t>
         </is>
       </c>
-      <c r="M60" s="2" t="n"/>
-      <c r="N60" s="4">
+      <c r="M60" s="26" t="n"/>
+      <c r="N60" s="28">
         <f>M60*G60</f>
         <v/>
       </c>
-      <c r="O60" s="2" t="n"/>
-      <c r="P60" s="2" t="n"/>
-      <c r="Q60" s="2" t="n"/>
-      <c r="R60" s="2" t="n"/>
-      <c r="S60" s="2" t="n"/>
+      <c r="O60" s="26" t="n"/>
+      <c r="P60" s="26" t="n"/>
+      <c r="Q60" s="26" t="n"/>
+      <c r="R60" s="26" t="n"/>
+      <c r="S60" s="26" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -4079,60 +4110,60 @@
       <c r="S61" s="2" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="A62" s="26" t="inlineStr">
         <is>
           <t>SLEEVE</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B62" s="26" t="inlineStr">
         <is>
           <t>H8042</t>
         </is>
       </c>
-      <c r="C62" s="3" t="inlineStr">
+      <c r="C62" s="27" t="inlineStr">
         <is>
           <t>Container Sandwich Plastic 5.38X2.58X5.25 Clear Hinged</t>
         </is>
       </c>
-      <c r="D62" s="3" t="n"/>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="D62" s="27" t="n"/>
+      <c r="E62" s="26" t="inlineStr">
         <is>
           <t>4/125Cnt</t>
         </is>
       </c>
-      <c r="F62" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G62" s="4" t="n">
+      <c r="F62" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" s="28" t="n">
         <v>13.39</v>
       </c>
-      <c r="H62" s="5" t="n">
+      <c r="H62" s="29" t="n">
         <v>13.39</v>
       </c>
-      <c r="I62" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K62" s="5" t="n">
+      <c r="I62" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" s="29" t="n">
         <v>3.3475</v>
       </c>
-      <c r="L62" s="3" t="inlineStr">
+      <c r="L62" s="27" t="inlineStr">
         <is>
           <t>per Sleeve (4/125Cnt)</t>
         </is>
       </c>
-      <c r="M62" s="2" t="n"/>
-      <c r="N62" s="4">
+      <c r="M62" s="26" t="n"/>
+      <c r="N62" s="28">
         <f>M62*G62</f>
         <v/>
       </c>
-      <c r="O62" s="2" t="n"/>
-      <c r="P62" s="2" t="n"/>
-      <c r="Q62" s="2" t="n"/>
-      <c r="R62" s="2" t="n"/>
-      <c r="S62" s="2" t="n"/>
+      <c r="O62" s="26" t="n"/>
+      <c r="P62" s="26" t="n"/>
+      <c r="Q62" s="26" t="n"/>
+      <c r="R62" s="26" t="n"/>
+      <c r="S62" s="26" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -4483,52 +4514,52 @@
       <c r="S68" s="2" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="26" t="inlineStr">
+      <c r="A69" s="32" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="B69" s="26" t="n"/>
-      <c r="C69" s="27" t="inlineStr">
+      <c r="B69" s="32" t="n"/>
+      <c r="C69" s="33" t="inlineStr">
         <is>
           <t>Donut Apple</t>
         </is>
       </c>
-      <c r="D69" s="27" t="n"/>
-      <c r="E69" s="26" t="n"/>
-      <c r="F69" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G69" s="28" t="n">
+      <c r="D69" s="33" t="n"/>
+      <c r="E69" s="32" t="n"/>
+      <c r="F69" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" s="34" t="n">
         <v>33.26</v>
       </c>
-      <c r="H69" s="29" t="n">
+      <c r="H69" s="35" t="n">
         <v>33.26</v>
       </c>
-      <c r="I69" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J69" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K69" s="29" t="n">
+      <c r="I69" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" s="35" t="n">
         <v>33.26</v>
       </c>
-      <c r="L69" s="27" t="inlineStr">
+      <c r="L69" s="33" t="inlineStr">
         <is>
           <t>per Case (None)</t>
         </is>
       </c>
-      <c r="M69" s="26" t="n"/>
-      <c r="N69" s="28">
+      <c r="M69" s="32" t="n"/>
+      <c r="N69" s="34">
         <f>M69*G69</f>
         <v/>
       </c>
-      <c r="O69" s="26" t="n"/>
-      <c r="P69" s="26" t="n"/>
-      <c r="Q69" s="26" t="n"/>
-      <c r="R69" s="26" t="n"/>
-      <c r="S69" s="26" t="n"/>
+      <c r="O69" s="32" t="n"/>
+      <c r="P69" s="32" t="n"/>
+      <c r="Q69" s="32" t="n"/>
+      <c r="R69" s="32" t="n"/>
+      <c r="S69" s="32" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -4787,60 +4818,60 @@
       <c r="S74" s="2" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="A75" s="26" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B75" s="26" t="inlineStr">
         <is>
           <t>57030</t>
         </is>
       </c>
-      <c r="C75" s="3" t="inlineStr">
+      <c r="C75" s="27" t="inlineStr">
         <is>
           <t>Dough Cookie Decorated Sugar Pre-Portioned Bake &amp; Serve Frozen</t>
         </is>
       </c>
-      <c r="D75" s="3" t="n"/>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="D75" s="27" t="n"/>
+      <c r="E75" s="26" t="inlineStr">
         <is>
           <t>80/4.5Oz</t>
         </is>
       </c>
-      <c r="F75" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G75" s="4" t="n">
+      <c r="F75" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" s="28" t="n">
         <v>79.22</v>
       </c>
-      <c r="H75" s="5" t="n">
+      <c r="H75" s="29" t="n">
         <v>79.22</v>
       </c>
-      <c r="I75" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J75" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K75" s="5" t="n">
+      <c r="I75" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" s="29" t="n">
         <v>79.22</v>
       </c>
-      <c r="L75" s="3" t="inlineStr">
+      <c r="L75" s="27" t="inlineStr">
         <is>
           <t>per Case (80/4.5Oz)</t>
         </is>
       </c>
-      <c r="M75" s="2" t="n"/>
-      <c r="N75" s="4">
+      <c r="M75" s="26" t="n"/>
+      <c r="N75" s="28">
         <f>M75*G75</f>
         <v/>
       </c>
-      <c r="O75" s="2" t="n"/>
-      <c r="P75" s="2" t="n"/>
-      <c r="Q75" s="2" t="n"/>
-      <c r="R75" s="2" t="n"/>
-      <c r="S75" s="2" t="n"/>
+      <c r="O75" s="26" t="n"/>
+      <c r="P75" s="26" t="n"/>
+      <c r="Q75" s="26" t="n"/>
+      <c r="R75" s="26" t="n"/>
+      <c r="S75" s="26" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -4897,60 +4928,60 @@
       <c r="S76" s="2" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+      <c r="A77" s="26" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B77" s="26" t="inlineStr">
         <is>
           <t>57402</t>
         </is>
       </c>
-      <c r="C77" s="3" t="inlineStr">
+      <c r="C77" s="27" t="inlineStr">
         <is>
           <t>Dough Cookie White Chocolate Macadamia Nut Decadent Frozen</t>
         </is>
       </c>
-      <c r="D77" s="3" t="n"/>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="D77" s="27" t="n"/>
+      <c r="E77" s="26" t="inlineStr">
         <is>
           <t>80/4.5Oz</t>
         </is>
       </c>
-      <c r="F77" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G77" s="4" t="n">
+      <c r="F77" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" s="28" t="n">
         <v>93.48</v>
       </c>
-      <c r="H77" s="5" t="n">
+      <c r="H77" s="29" t="n">
         <v>93.48</v>
       </c>
-      <c r="I77" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K77" s="5" t="n">
+      <c r="I77" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" s="29" t="n">
         <v>93.48</v>
       </c>
-      <c r="L77" s="3" t="inlineStr">
+      <c r="L77" s="27" t="inlineStr">
         <is>
           <t>per Case (80/4.5Oz)</t>
         </is>
       </c>
-      <c r="M77" s="2" t="n"/>
-      <c r="N77" s="4">
+      <c r="M77" s="26" t="n"/>
+      <c r="N77" s="28">
         <f>M77*G77</f>
         <v/>
       </c>
-      <c r="O77" s="2" t="n"/>
-      <c r="P77" s="2" t="n"/>
-      <c r="Q77" s="2" t="n"/>
-      <c r="R77" s="2" t="n"/>
-      <c r="S77" s="2" t="n"/>
+      <c r="O77" s="26" t="n"/>
+      <c r="P77" s="26" t="n"/>
+      <c r="Q77" s="26" t="n"/>
+      <c r="R77" s="26" t="n"/>
+      <c r="S77" s="26" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="20" t="inlineStr">
@@ -5427,60 +5458,60 @@
       <c r="S85" s="8" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+      <c r="A86" s="26" t="inlineStr">
         <is>
           <t>BOX</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="B86" s="26" t="inlineStr">
         <is>
           <t>83238</t>
         </is>
       </c>
-      <c r="C86" s="3" t="inlineStr">
+      <c r="C86" s="27" t="inlineStr">
         <is>
           <t>Foil Aluminum Sheet 9X10.75 Interfold</t>
         </is>
       </c>
-      <c r="D86" s="3" t="n"/>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="D86" s="27" t="n"/>
+      <c r="E86" s="26" t="inlineStr">
         <is>
           <t>6/500Cnt</t>
         </is>
       </c>
-      <c r="F86" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G86" s="4" t="n">
+      <c r="F86" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" s="28" t="n">
         <v>17.27</v>
       </c>
-      <c r="H86" s="5" t="n">
+      <c r="H86" s="29" t="n">
         <v>17.27</v>
       </c>
-      <c r="I86" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J86" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K86" s="5" t="n">
+      <c r="I86" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" s="29" t="n">
         <v>2.878333333333333</v>
       </c>
-      <c r="L86" s="3" t="inlineStr">
+      <c r="L86" s="27" t="inlineStr">
         <is>
           <t>per Box (6/500Cnt)</t>
         </is>
       </c>
-      <c r="M86" s="2" t="n"/>
-      <c r="N86" s="4">
+      <c r="M86" s="26" t="n"/>
+      <c r="N86" s="28">
         <f>M86*G86</f>
         <v/>
       </c>
-      <c r="O86" s="2" t="n"/>
-      <c r="P86" s="2" t="n"/>
-      <c r="Q86" s="2" t="n"/>
-      <c r="R86" s="2" t="n"/>
-      <c r="S86" s="2" t="n"/>
+      <c r="O86" s="26" t="n"/>
+      <c r="P86" s="26" t="n"/>
+      <c r="Q86" s="26" t="n"/>
+      <c r="R86" s="26" t="n"/>
+      <c r="S86" s="26" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -5537,60 +5568,60 @@
       <c r="S87" s="2" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+      <c r="A88" s="26" t="inlineStr">
         <is>
           <t>BOX</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="B88" s="26" t="inlineStr">
         <is>
           <t>NE822</t>
         </is>
       </c>
-      <c r="C88" s="3" t="inlineStr">
+      <c r="C88" s="27" t="inlineStr">
         <is>
           <t>Fork Plastic Heavy Weight Black Polypropylene Max Stax Refill</t>
         </is>
       </c>
-      <c r="D88" s="3" t="n"/>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="D88" s="27" t="n"/>
+      <c r="E88" s="26" t="inlineStr">
         <is>
           <t>1/1000Ea</t>
         </is>
       </c>
-      <c r="F88" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G88" s="4" t="n">
+      <c r="F88" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" s="28" t="n">
         <v>48.15</v>
       </c>
-      <c r="H88" s="5" t="n">
+      <c r="H88" s="29" t="n">
         <v>48.15</v>
       </c>
-      <c r="I88" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J88" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K88" s="5" t="n">
+      <c r="I88" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" s="29" t="n">
         <v>48.15</v>
       </c>
-      <c r="L88" s="3" t="inlineStr">
+      <c r="L88" s="27" t="inlineStr">
         <is>
           <t>per Box (1/1000Ea)</t>
         </is>
       </c>
-      <c r="M88" s="2" t="n"/>
-      <c r="N88" s="4">
+      <c r="M88" s="26" t="n"/>
+      <c r="N88" s="28">
         <f>M88*G88</f>
         <v/>
       </c>
-      <c r="O88" s="2" t="n"/>
-      <c r="P88" s="2" t="n"/>
-      <c r="Q88" s="2" t="n"/>
-      <c r="R88" s="2" t="n"/>
-      <c r="S88" s="2" t="n"/>
+      <c r="O88" s="26" t="n"/>
+      <c r="P88" s="26" t="n"/>
+      <c r="Q88" s="26" t="n"/>
+      <c r="R88" s="26" t="n"/>
+      <c r="S88" s="26" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -5653,60 +5684,60 @@
       <c r="S89" s="2" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+      <c r="A90" s="26" t="inlineStr">
         <is>
           <t>CONTAINER</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
+      <c r="B90" s="26" t="inlineStr">
         <is>
           <t>CE570</t>
         </is>
       </c>
-      <c r="C90" s="3" t="inlineStr">
+      <c r="C90" s="27" t="inlineStr">
         <is>
           <t>Garlic Granulated</t>
         </is>
       </c>
-      <c r="D90" s="3" t="n"/>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="D90" s="27" t="n"/>
+      <c r="E90" s="26" t="inlineStr">
         <is>
           <t>1/7.25Lb</t>
         </is>
       </c>
-      <c r="F90" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G90" s="4" t="n">
+      <c r="F90" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" s="28" t="n">
         <v>55.95</v>
       </c>
-      <c r="H90" s="5" t="n">
+      <c r="H90" s="29" t="n">
         <v>55.95</v>
       </c>
-      <c r="I90" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J90" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K90" s="5" t="n">
+      <c r="I90" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" s="29" t="n">
         <v>55.95</v>
       </c>
-      <c r="L90" s="3" t="inlineStr">
+      <c r="L90" s="27" t="inlineStr">
         <is>
           <t>per Container (1/7.25Lb)</t>
         </is>
       </c>
-      <c r="M90" s="2" t="n"/>
-      <c r="N90" s="4">
+      <c r="M90" s="26" t="n"/>
+      <c r="N90" s="28">
         <f>M90*G90</f>
         <v/>
       </c>
-      <c r="O90" s="2" t="n"/>
-      <c r="P90" s="2" t="n"/>
-      <c r="Q90" s="2" t="n"/>
-      <c r="R90" s="2" t="n"/>
-      <c r="S90" s="2" t="n"/>
+      <c r="O90" s="26" t="n"/>
+      <c r="P90" s="26" t="n"/>
+      <c r="Q90" s="26" t="n"/>
+      <c r="R90" s="26" t="n"/>
+      <c r="S90" s="26" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -6349,60 +6380,60 @@
       <c r="S101" s="20" t="n"/>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+      <c r="A102" s="26" t="inlineStr">
         <is>
           <t>JUG</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
+      <c r="B102" s="26" t="inlineStr">
         <is>
           <t>1492</t>
         </is>
       </c>
-      <c r="C102" s="3" t="inlineStr">
+      <c r="C102" s="27" t="inlineStr">
         <is>
           <t>Ice Cream Vanilla Mix</t>
         </is>
       </c>
-      <c r="D102" s="3" t="n"/>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="D102" s="27" t="n"/>
+      <c r="E102" s="26" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F102" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G102" s="4" t="n">
+      <c r="F102" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G102" s="28" t="n">
         <v>13.17</v>
       </c>
-      <c r="H102" s="5" t="n">
+      <c r="H102" s="29" t="n">
         <v>13.17</v>
       </c>
-      <c r="I102" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J102" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K102" s="5" t="n">
+      <c r="I102" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" s="29" t="n">
         <v>2.195</v>
       </c>
-      <c r="L102" s="3" t="inlineStr">
+      <c r="L102" s="27" t="inlineStr">
         <is>
           <t>per Jug (6)</t>
         </is>
       </c>
-      <c r="M102" s="2" t="n"/>
-      <c r="N102" s="4">
+      <c r="M102" s="26" t="n"/>
+      <c r="N102" s="28">
         <f>M102*G102</f>
         <v/>
       </c>
-      <c r="O102" s="2" t="n"/>
-      <c r="P102" s="2" t="n"/>
-      <c r="Q102" s="2" t="n"/>
-      <c r="R102" s="2" t="n"/>
-      <c r="S102" s="2" t="n"/>
+      <c r="O102" s="26" t="n"/>
+      <c r="P102" s="26" t="n"/>
+      <c r="Q102" s="26" t="n"/>
+      <c r="R102" s="26" t="n"/>
+      <c r="S102" s="26" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -6749,58 +6780,58 @@
       <c r="S108" s="8" t="n"/>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+      <c r="A109" s="26" t="inlineStr">
         <is>
           <t>BOX</t>
         </is>
       </c>
-      <c r="B109" s="2" t="n">
+      <c r="B109" s="26" t="n">
         <v>160624</v>
       </c>
-      <c r="C109" s="3" t="inlineStr">
+      <c r="C109" s="27" t="inlineStr">
         <is>
           <t>Knife Plastic Heavy Weight Black Polypropylene Max Stax Refill</t>
         </is>
       </c>
-      <c r="D109" s="3" t="n"/>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="D109" s="27" t="n"/>
+      <c r="E109" s="26" t="inlineStr">
         <is>
           <t>1/1000Ea</t>
         </is>
       </c>
-      <c r="F109" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G109" s="4" t="n">
+      <c r="F109" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G109" s="28" t="n">
         <v>48.15</v>
       </c>
-      <c r="H109" s="5" t="n">
+      <c r="H109" s="29" t="n">
         <v>48.15</v>
       </c>
-      <c r="I109" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J109" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K109" s="5" t="n">
+      <c r="I109" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" s="29" t="n">
         <v>48.15</v>
       </c>
-      <c r="L109" s="3" t="inlineStr">
+      <c r="L109" s="27" t="inlineStr">
         <is>
           <t>per Box (1/1000Ea)</t>
         </is>
       </c>
-      <c r="M109" s="2" t="n"/>
-      <c r="N109" s="4">
+      <c r="M109" s="26" t="n"/>
+      <c r="N109" s="28">
         <f>M109*G109</f>
         <v/>
       </c>
-      <c r="O109" s="2" t="n"/>
-      <c r="P109" s="2" t="n"/>
-      <c r="Q109" s="2" t="n"/>
-      <c r="R109" s="2" t="n"/>
-      <c r="S109" s="2" t="n"/>
+      <c r="O109" s="26" t="n"/>
+      <c r="P109" s="26" t="n"/>
+      <c r="Q109" s="26" t="n"/>
+      <c r="R109" s="26" t="n"/>
+      <c r="S109" s="26" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -6853,116 +6884,116 @@
       <c r="S110" s="2" t="n"/>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+      <c r="A111" s="26" t="inlineStr">
         <is>
           <t>SLEEVE</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
+      <c r="B111" s="26" t="inlineStr">
         <is>
           <t>VV490</t>
         </is>
       </c>
-      <c r="C111" s="3" t="inlineStr">
+      <c r="C111" s="27" t="inlineStr">
         <is>
           <t>Lid Container 6 oz</t>
         </is>
       </c>
-      <c r="D111" s="3" t="n"/>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="D111" s="27" t="n"/>
+      <c r="E111" s="26" t="inlineStr">
         <is>
           <t>20/50Cnt</t>
         </is>
       </c>
-      <c r="F111" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G111" s="4" t="n">
+      <c r="F111" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G111" s="28" t="n">
         <v>4.51</v>
       </c>
-      <c r="H111" s="5" t="n">
+      <c r="H111" s="29" t="n">
         <v>4.51</v>
       </c>
-      <c r="I111" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J111" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K111" s="5" t="n">
+      <c r="I111" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K111" s="29" t="n">
         <v>0.2255</v>
       </c>
-      <c r="L111" s="3" t="inlineStr">
+      <c r="L111" s="27" t="inlineStr">
         <is>
           <t>per Sleeve (20/50Cnt)</t>
         </is>
       </c>
-      <c r="M111" s="2" t="n"/>
-      <c r="N111" s="4">
+      <c r="M111" s="26" t="n"/>
+      <c r="N111" s="28">
         <f>M111*G111</f>
         <v/>
       </c>
-      <c r="O111" s="2" t="n"/>
-      <c r="P111" s="2" t="n"/>
-      <c r="Q111" s="2" t="n"/>
-      <c r="R111" s="2" t="n"/>
-      <c r="S111" s="2" t="n"/>
+      <c r="O111" s="26" t="n"/>
+      <c r="P111" s="26" t="n"/>
+      <c r="Q111" s="26" t="n"/>
+      <c r="R111" s="26" t="n"/>
+      <c r="S111" s="26" t="n"/>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+      <c r="A112" s="26" t="inlineStr">
         <is>
           <t>SLEEVE</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
+      <c r="B112" s="26" t="inlineStr">
         <is>
           <t>79374</t>
         </is>
       </c>
-      <c r="C112" s="3" t="inlineStr">
+      <c r="C112" s="27" t="inlineStr">
         <is>
           <t>Lid Container 12oz</t>
         </is>
       </c>
-      <c r="D112" s="3" t="n"/>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="D112" s="27" t="n"/>
+      <c r="E112" s="26" t="inlineStr">
         <is>
           <t>10/100</t>
         </is>
       </c>
-      <c r="F112" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G112" s="4" t="n">
+      <c r="F112" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G112" s="28" t="n">
         <v>3.01</v>
       </c>
-      <c r="H112" s="5" t="n">
+      <c r="H112" s="29" t="n">
         <v>3.01</v>
       </c>
-      <c r="I112" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J112" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K112" s="5" t="n">
+      <c r="I112" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K112" s="29" t="n">
         <v>0.301</v>
       </c>
-      <c r="L112" s="3" t="inlineStr">
+      <c r="L112" s="27" t="inlineStr">
         <is>
           <t>per Sleeve (10/100)</t>
         </is>
       </c>
-      <c r="M112" s="2" t="n"/>
-      <c r="N112" s="4">
+      <c r="M112" s="26" t="n"/>
+      <c r="N112" s="28">
         <f>M112*G112</f>
         <v/>
       </c>
-      <c r="O112" s="2" t="n"/>
-      <c r="P112" s="2" t="n"/>
-      <c r="Q112" s="2" t="n"/>
-      <c r="R112" s="2" t="n"/>
-      <c r="S112" s="2" t="n"/>
+      <c r="O112" s="26" t="n"/>
+      <c r="P112" s="26" t="n"/>
+      <c r="Q112" s="26" t="n"/>
+      <c r="R112" s="26" t="n"/>
+      <c r="S112" s="26" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -7019,60 +7050,60 @@
       <c r="S113" s="2" t="n"/>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+      <c r="A114" s="26" t="inlineStr">
         <is>
           <t>SLEEVE</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
+      <c r="B114" s="26" t="inlineStr">
         <is>
           <t>VV490</t>
         </is>
       </c>
-      <c r="C114" s="3" t="inlineStr">
+      <c r="C114" s="27" t="inlineStr">
         <is>
           <t>Lid Plastic Dome 12 oz</t>
         </is>
       </c>
-      <c r="D114" s="3" t="n"/>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="D114" s="27" t="n"/>
+      <c r="E114" s="26" t="inlineStr">
         <is>
           <t>20/50Cnt</t>
         </is>
       </c>
-      <c r="F114" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G114" s="4" t="n">
+      <c r="F114" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G114" s="28" t="n">
         <v>4.51</v>
       </c>
-      <c r="H114" s="5" t="n">
+      <c r="H114" s="29" t="n">
         <v>4.51</v>
       </c>
-      <c r="I114" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J114" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K114" s="5" t="n">
+      <c r="I114" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K114" s="29" t="n">
         <v>0.2255</v>
       </c>
-      <c r="L114" s="3" t="inlineStr">
+      <c r="L114" s="27" t="inlineStr">
         <is>
           <t>per Sleeve (20/50Cnt)</t>
         </is>
       </c>
-      <c r="M114" s="2" t="n"/>
-      <c r="N114" s="4">
+      <c r="M114" s="26" t="n"/>
+      <c r="N114" s="28">
         <f>M114*G114</f>
         <v/>
       </c>
-      <c r="O114" s="2" t="n"/>
-      <c r="P114" s="2" t="n"/>
-      <c r="Q114" s="2" t="n"/>
-      <c r="R114" s="2" t="n"/>
-      <c r="S114" s="2" t="n"/>
+      <c r="O114" s="26" t="n"/>
+      <c r="P114" s="26" t="n"/>
+      <c r="Q114" s="26" t="n"/>
+      <c r="R114" s="26" t="n"/>
+      <c r="S114" s="26" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -7135,60 +7166,60 @@
       <c r="S115" s="2" t="n"/>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+      <c r="A116" s="26" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
+      <c r="B116" s="26" t="inlineStr">
         <is>
           <t>C4556</t>
         </is>
       </c>
-      <c r="C116" s="3" t="inlineStr">
+      <c r="C116" s="27" t="inlineStr">
         <is>
           <t>Margarine Spread Whipped Vegetable Oil 48% Portion Cup</t>
         </is>
       </c>
-      <c r="D116" s="3" t="n"/>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="D116" s="27" t="n"/>
+      <c r="E116" s="26" t="inlineStr">
         <is>
           <t>648/14Gm</t>
         </is>
       </c>
-      <c r="F116" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G116" s="4" t="n">
+      <c r="F116" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G116" s="28" t="n">
         <v>56.03</v>
       </c>
-      <c r="H116" s="5" t="n">
+      <c r="H116" s="29" t="n">
         <v>56.03</v>
       </c>
-      <c r="I116" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J116" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K116" s="5" t="n">
+      <c r="I116" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K116" s="29" t="n">
         <v>56.03</v>
       </c>
-      <c r="L116" s="3" t="inlineStr">
+      <c r="L116" s="27" t="inlineStr">
         <is>
           <t>per Case (648/14Gm)</t>
         </is>
       </c>
-      <c r="M116" s="2" t="n"/>
-      <c r="N116" s="4">
+      <c r="M116" s="26" t="n"/>
+      <c r="N116" s="28">
         <f>M116*G116</f>
         <v/>
       </c>
-      <c r="O116" s="2" t="n"/>
-      <c r="P116" s="2" t="n"/>
-      <c r="Q116" s="2" t="n"/>
-      <c r="R116" s="2" t="n"/>
-      <c r="S116" s="2" t="n"/>
+      <c r="O116" s="26" t="n"/>
+      <c r="P116" s="26" t="n"/>
+      <c r="Q116" s="26" t="n"/>
+      <c r="R116" s="26" t="n"/>
+      <c r="S116" s="26" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="20" t="inlineStr">
@@ -7311,58 +7342,60 @@
       <c r="S118" s="2" t="n"/>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+      <c r="A119" s="8" t="inlineStr">
         <is>
           <t>EACH</t>
         </is>
       </c>
-      <c r="B119" s="2" t="n">
-        <v>10008</v>
-      </c>
-      <c r="C119" s="3" t="inlineStr">
+      <c r="B119" s="8" t="inlineStr">
+        <is>
+          <t>010008</t>
+        </is>
+      </c>
+      <c r="C119" s="9" t="inlineStr">
         <is>
           <t>Meatloaf Beef Ready To Cook Frozen</t>
         </is>
       </c>
-      <c r="D119" s="3" t="n"/>
-      <c r="E119" s="2" t="inlineStr">
-        <is>
-          <t>3/5 Lb</t>
-        </is>
-      </c>
-      <c r="F119" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G119" s="4" t="n">
+      <c r="D119" s="9" t="n"/>
+      <c r="E119" s="8" t="inlineStr">
+        <is>
+          <t>12 / 21 OZ</t>
+        </is>
+      </c>
+      <c r="F119" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G119" s="10" t="n">
+        <v>93.8</v>
+      </c>
+      <c r="H119" s="11" t="n">
         <v>24.66</v>
       </c>
-      <c r="H119" s="5" t="n">
-        <v>24.66</v>
-      </c>
-      <c r="I119" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J119" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K119" s="5" t="n">
-        <v>8.220000000000001</v>
-      </c>
-      <c r="L119" s="3" t="inlineStr">
-        <is>
-          <t>per Each (3/5 Lb)</t>
-        </is>
-      </c>
-      <c r="M119" s="2" t="n"/>
-      <c r="N119" s="4">
+      <c r="I119" s="12" t="n">
+        <v>-16.84333333333333</v>
+      </c>
+      <c r="J119" s="13" t="n">
+        <v>-0.683022438496891</v>
+      </c>
+      <c r="K119" s="11" t="n">
+        <v>7.816666666666666</v>
+      </c>
+      <c r="L119" s="9" t="inlineStr">
+        <is>
+          <t>per Each (12 / 21 OZ)</t>
+        </is>
+      </c>
+      <c r="M119" s="8" t="n"/>
+      <c r="N119" s="10">
         <f>M119*G119</f>
         <v/>
       </c>
-      <c r="O119" s="2" t="n"/>
-      <c r="P119" s="2" t="n"/>
-      <c r="Q119" s="2" t="n"/>
-      <c r="R119" s="2" t="n"/>
-      <c r="S119" s="2" t="n"/>
+      <c r="O119" s="8" t="n"/>
+      <c r="P119" s="8" t="n"/>
+      <c r="Q119" s="8" t="n"/>
+      <c r="R119" s="8" t="n"/>
+      <c r="S119" s="8" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="8" t="inlineStr">
@@ -7425,60 +7458,60 @@
       <c r="S120" s="8" t="n"/>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+      <c r="A121" s="26" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
+      <c r="B121" s="26" t="inlineStr">
         <is>
           <t>V7108</t>
         </is>
       </c>
-      <c r="C121" s="3" t="inlineStr">
+      <c r="C121" s="27" t="inlineStr">
         <is>
           <t>Muffin Variety (Banana Nut, Blueberry Cobbler, Chocolate Chunk, Cinnamon Walnut Streusel)</t>
         </is>
       </c>
-      <c r="D121" s="3" t="n"/>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="D121" s="27" t="n"/>
+      <c r="E121" s="26" t="inlineStr">
         <is>
           <t>48/4.25</t>
         </is>
       </c>
-      <c r="F121" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G121" s="4" t="n">
+      <c r="F121" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G121" s="28" t="n">
         <v>58.06</v>
       </c>
-      <c r="H121" s="5" t="n">
+      <c r="H121" s="29" t="n">
         <v>58.06</v>
       </c>
-      <c r="I121" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J121" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K121" s="5" t="n">
+      <c r="I121" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K121" s="29" t="n">
         <v>58.06</v>
       </c>
-      <c r="L121" s="3" t="inlineStr">
+      <c r="L121" s="27" t="inlineStr">
         <is>
           <t>per Case (48/4.25)</t>
         </is>
       </c>
-      <c r="M121" s="2" t="n"/>
-      <c r="N121" s="4">
+      <c r="M121" s="26" t="n"/>
+      <c r="N121" s="28">
         <f>M121*G121</f>
         <v/>
       </c>
-      <c r="O121" s="2" t="n"/>
-      <c r="P121" s="2" t="n"/>
-      <c r="Q121" s="2" t="n"/>
-      <c r="R121" s="2" t="n"/>
-      <c r="S121" s="2" t="n"/>
+      <c r="O121" s="26" t="n"/>
+      <c r="P121" s="26" t="n"/>
+      <c r="Q121" s="26" t="n"/>
+      <c r="R121" s="26" t="n"/>
+      <c r="S121" s="26" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -7541,60 +7574,60 @@
       <c r="S122" s="2" t="n"/>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+      <c r="A123" s="26" t="inlineStr">
         <is>
           <t>PACK</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
+      <c r="B123" s="26" t="inlineStr">
         <is>
           <t>DT310</t>
         </is>
       </c>
-      <c r="C123" s="3" t="inlineStr">
+      <c r="C123" s="27" t="inlineStr">
         <is>
           <t>Napkins 13X8.5</t>
         </is>
       </c>
-      <c r="D123" s="3" t="n"/>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="D123" s="27" t="n"/>
+      <c r="E123" s="26" t="inlineStr">
         <is>
           <t>12/500</t>
         </is>
       </c>
-      <c r="F123" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G123" s="4" t="n">
+      <c r="F123" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G123" s="28" t="n">
         <v>5.22</v>
       </c>
-      <c r="H123" s="5" t="n">
+      <c r="H123" s="29" t="n">
         <v>5.22</v>
       </c>
-      <c r="I123" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J123" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K123" s="5" t="n">
+      <c r="I123" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" s="29" t="n">
         <v>0.435</v>
       </c>
-      <c r="L123" s="3" t="inlineStr">
+      <c r="L123" s="27" t="inlineStr">
         <is>
           <t>per Pack (12/500)</t>
         </is>
       </c>
-      <c r="M123" s="2" t="n"/>
-      <c r="N123" s="4">
+      <c r="M123" s="26" t="n"/>
+      <c r="N123" s="28">
         <f>M123*G123</f>
         <v/>
       </c>
-      <c r="O123" s="2" t="n"/>
-      <c r="P123" s="2" t="n"/>
-      <c r="Q123" s="2" t="n"/>
-      <c r="R123" s="2" t="n"/>
-      <c r="S123" s="2" t="n"/>
+      <c r="O123" s="26" t="n"/>
+      <c r="P123" s="26" t="n"/>
+      <c r="Q123" s="26" t="n"/>
+      <c r="R123" s="26" t="n"/>
+      <c r="S123" s="26" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="20" t="inlineStr">
@@ -7717,58 +7750,60 @@
       <c r="S125" s="2" t="n"/>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+      <c r="A126" s="20" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="B126" s="2" t="n">
-        <v>26761</v>
-      </c>
-      <c r="C126" s="3" t="inlineStr">
+      <c r="B126" s="20" t="inlineStr">
+        <is>
+          <t>026761</t>
+        </is>
+      </c>
+      <c r="C126" s="21" t="inlineStr">
         <is>
           <t>Onion Yellow Large Fresh</t>
         </is>
       </c>
-      <c r="D126" s="3" t="n"/>
-      <c r="E126" s="2" t="inlineStr">
-        <is>
-          <t>1/5 Lb</t>
-        </is>
-      </c>
-      <c r="F126" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G126" s="4" t="n">
+      <c r="D126" s="21" t="n"/>
+      <c r="E126" s="20" t="inlineStr">
+        <is>
+          <t>1 / 5 LB</t>
+        </is>
+      </c>
+      <c r="F126" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G126" s="22" t="n">
+        <v>28.92</v>
+      </c>
+      <c r="H126" s="23" t="n">
         <v>7.64</v>
       </c>
-      <c r="H126" s="5" t="n">
-        <v>7.64</v>
-      </c>
-      <c r="I126" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J126" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K126" s="5" t="n">
-        <v>7.64</v>
-      </c>
-      <c r="L126" s="3" t="inlineStr">
-        <is>
-          <t>per Case (1/5 Lb)</t>
-        </is>
-      </c>
-      <c r="M126" s="2" t="n"/>
-      <c r="N126" s="4">
+      <c r="I126" s="24" t="n">
+        <v>21.28</v>
+      </c>
+      <c r="J126" s="25" t="n">
+        <v>2.785340314136126</v>
+      </c>
+      <c r="K126" s="23" t="n">
+        <v>28.92</v>
+      </c>
+      <c r="L126" s="21" t="inlineStr">
+        <is>
+          <t>per Case (1 / 5 LB)</t>
+        </is>
+      </c>
+      <c r="M126" s="20" t="n"/>
+      <c r="N126" s="22">
         <f>M126*G126</f>
         <v/>
       </c>
-      <c r="O126" s="2" t="n"/>
-      <c r="P126" s="2" t="n"/>
-      <c r="Q126" s="2" t="n"/>
-      <c r="R126" s="2" t="n"/>
-      <c r="S126" s="2" t="n"/>
+      <c r="O126" s="20" t="n"/>
+      <c r="P126" s="20" t="n"/>
+      <c r="Q126" s="20" t="n"/>
+      <c r="R126" s="20" t="n"/>
+      <c r="S126" s="20" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="20" t="inlineStr">
@@ -7891,60 +7926,60 @@
       <c r="S128" s="8" t="n"/>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+      <c r="A129" s="26" t="inlineStr">
         <is>
           <t>BAG</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
+      <c r="B129" s="26" t="inlineStr">
         <is>
           <t>24806</t>
         </is>
       </c>
-      <c r="C129" s="3" t="inlineStr">
+      <c r="C129" s="27" t="inlineStr">
         <is>
           <t>Pasta Macaroni</t>
         </is>
       </c>
-      <c r="D129" s="3" t="n"/>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="D129" s="27" t="n"/>
+      <c r="E129" s="26" t="inlineStr">
         <is>
           <t>3/10Lb</t>
         </is>
       </c>
-      <c r="F129" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G129" s="4" t="n">
+      <c r="F129" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G129" s="28" t="n">
         <v>12.94</v>
       </c>
-      <c r="H129" s="5" t="n">
+      <c r="H129" s="29" t="n">
         <v>12.94</v>
       </c>
-      <c r="I129" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J129" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K129" s="5" t="n">
+      <c r="I129" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K129" s="29" t="n">
         <v>4.313333333333333</v>
       </c>
-      <c r="L129" s="3" t="inlineStr">
+      <c r="L129" s="27" t="inlineStr">
         <is>
           <t>per Bag (3/10Lb)</t>
         </is>
       </c>
-      <c r="M129" s="2" t="n"/>
-      <c r="N129" s="4">
+      <c r="M129" s="26" t="n"/>
+      <c r="N129" s="28">
         <f>M129*G129</f>
         <v/>
       </c>
-      <c r="O129" s="2" t="n"/>
-      <c r="P129" s="2" t="n"/>
-      <c r="Q129" s="2" t="n"/>
-      <c r="R129" s="2" t="n"/>
-      <c r="S129" s="2" t="n"/>
+      <c r="O129" s="26" t="n"/>
+      <c r="P129" s="26" t="n"/>
+      <c r="Q129" s="26" t="n"/>
+      <c r="R129" s="26" t="n"/>
+      <c r="S129" s="26" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -8115,116 +8150,116 @@
       <c r="S132" s="20" t="n"/>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+      <c r="A133" s="26" t="inlineStr">
         <is>
           <t>BAG</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
+      <c r="B133" s="26" t="inlineStr">
         <is>
           <t>LN630</t>
         </is>
       </c>
-      <c r="C133" s="3" t="inlineStr">
+      <c r="C133" s="27" t="inlineStr">
         <is>
           <t>Pepper Black Ground .1Gm Flute Pack</t>
         </is>
       </c>
-      <c r="D133" s="3" t="n"/>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="D133" s="27" t="n"/>
+      <c r="E133" s="26" t="inlineStr">
         <is>
           <t>6/1000</t>
         </is>
       </c>
-      <c r="F133" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G133" s="4" t="n">
+      <c r="F133" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G133" s="28" t="n">
         <v>7.42</v>
       </c>
-      <c r="H133" s="5" t="n">
+      <c r="H133" s="29" t="n">
         <v>7.42</v>
       </c>
-      <c r="I133" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J133" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K133" s="5" t="n">
+      <c r="I133" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J133" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K133" s="29" t="n">
         <v>1.236666666666667</v>
       </c>
-      <c r="L133" s="3" t="inlineStr">
+      <c r="L133" s="27" t="inlineStr">
         <is>
           <t>per Bag (6/1000)</t>
         </is>
       </c>
-      <c r="M133" s="2" t="n"/>
-      <c r="N133" s="4">
+      <c r="M133" s="26" t="n"/>
+      <c r="N133" s="28">
         <f>M133*G133</f>
         <v/>
       </c>
-      <c r="O133" s="2" t="n"/>
-      <c r="P133" s="2" t="n"/>
-      <c r="Q133" s="2" t="n"/>
-      <c r="R133" s="2" t="n"/>
-      <c r="S133" s="2" t="n"/>
+      <c r="O133" s="26" t="n"/>
+      <c r="P133" s="26" t="n"/>
+      <c r="Q133" s="26" t="n"/>
+      <c r="R133" s="26" t="n"/>
+      <c r="S133" s="26" t="n"/>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+      <c r="A134" s="26" t="inlineStr">
         <is>
           <t>SHAKER</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
+      <c r="B134" s="26" t="inlineStr">
         <is>
           <t>CE624</t>
         </is>
       </c>
-      <c r="C134" s="3" t="inlineStr">
+      <c r="C134" s="27" t="inlineStr">
         <is>
           <t>Pepper Black Shaker Grind 34 Mesh</t>
         </is>
       </c>
-      <c r="D134" s="3" t="n"/>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="D134" s="27" t="n"/>
+      <c r="E134" s="26" t="inlineStr">
         <is>
           <t>1/5 Lb</t>
         </is>
       </c>
-      <c r="F134" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G134" s="4" t="n">
+      <c r="F134" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G134" s="28" t="n">
         <v>40</v>
       </c>
-      <c r="H134" s="5" t="n">
+      <c r="H134" s="29" t="n">
         <v>40</v>
       </c>
-      <c r="I134" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J134" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K134" s="5" t="n">
+      <c r="I134" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K134" s="29" t="n">
         <v>40</v>
       </c>
-      <c r="L134" s="3" t="inlineStr">
+      <c r="L134" s="27" t="inlineStr">
         <is>
           <t>per Shaker (1/5 Lb)</t>
         </is>
       </c>
-      <c r="M134" s="2" t="n"/>
-      <c r="N134" s="4">
+      <c r="M134" s="26" t="n"/>
+      <c r="N134" s="28">
         <f>M134*G134</f>
         <v/>
       </c>
-      <c r="O134" s="2" t="n"/>
-      <c r="P134" s="2" t="n"/>
-      <c r="Q134" s="2" t="n"/>
-      <c r="R134" s="2" t="n"/>
-      <c r="S134" s="2" t="n"/>
+      <c r="O134" s="26" t="n"/>
+      <c r="P134" s="26" t="n"/>
+      <c r="Q134" s="26" t="n"/>
+      <c r="R134" s="26" t="n"/>
+      <c r="S134" s="26" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="14" t="inlineStr">
@@ -8341,60 +8376,60 @@
       <c r="S136" s="2" t="n"/>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+      <c r="A137" s="26" t="inlineStr">
         <is>
           <t>SLEEVE</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
+      <c r="B137" s="26" t="inlineStr">
         <is>
           <t>197491</t>
         </is>
       </c>
-      <c r="C137" s="3" t="inlineStr">
+      <c r="C137" s="27" t="inlineStr">
         <is>
           <t>Plate Foam 3 Compartment</t>
         </is>
       </c>
-      <c r="D137" s="3" t="n"/>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="D137" s="27" t="n"/>
+      <c r="E137" s="26" t="inlineStr">
         <is>
           <t>4/125 Cnt</t>
         </is>
       </c>
-      <c r="F137" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G137" s="4" t="n">
+      <c r="F137" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G137" s="28" t="n">
         <v>7.35</v>
       </c>
-      <c r="H137" s="5" t="n">
+      <c r="H137" s="29" t="n">
         <v>7.35</v>
       </c>
-      <c r="I137" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J137" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K137" s="5" t="n">
+      <c r="I137" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J137" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K137" s="29" t="n">
         <v>1.8375</v>
       </c>
-      <c r="L137" s="3" t="inlineStr">
+      <c r="L137" s="27" t="inlineStr">
         <is>
           <t>per Sleeve (4/125 Cnt)</t>
         </is>
       </c>
-      <c r="M137" s="2" t="n"/>
-      <c r="N137" s="4">
+      <c r="M137" s="26" t="n"/>
+      <c r="N137" s="28">
         <f>M137*G137</f>
         <v/>
       </c>
-      <c r="O137" s="2" t="n"/>
-      <c r="P137" s="2" t="n"/>
-      <c r="Q137" s="2" t="n"/>
-      <c r="R137" s="2" t="n"/>
-      <c r="S137" s="2" t="n"/>
+      <c r="O137" s="26" t="n"/>
+      <c r="P137" s="26" t="n"/>
+      <c r="Q137" s="26" t="n"/>
+      <c r="R137" s="26" t="n"/>
+      <c r="S137" s="26" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="8" t="inlineStr">
@@ -8577,58 +8612,60 @@
       <c r="S140" s="2" t="n"/>
     </row>
     <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+      <c r="A141" s="8" t="inlineStr">
         <is>
           <t>EACH</t>
         </is>
       </c>
-      <c r="B141" s="2" t="n">
-        <v>1011</v>
-      </c>
-      <c r="C141" s="3" t="inlineStr">
+      <c r="B141" s="8" t="inlineStr">
+        <is>
+          <t>001011</t>
+        </is>
+      </c>
+      <c r="C141" s="9" t="inlineStr">
         <is>
           <t>Pork Spare Rib Street Louis Fully Cooked Seasoned</t>
         </is>
       </c>
-      <c r="D141" s="3" t="n"/>
-      <c r="E141" s="2" t="inlineStr">
-        <is>
-          <t>10/2.5Av</t>
-        </is>
-      </c>
-      <c r="F141" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G141" s="4" t="n">
+      <c r="D141" s="9" t="n"/>
+      <c r="E141" s="8" t="inlineStr">
+        <is>
+          <t>4 / 21 LB</t>
+        </is>
+      </c>
+      <c r="F141" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G141" s="10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="H141" s="11" t="n">
         <v>15.61</v>
       </c>
-      <c r="H141" s="5" t="n">
-        <v>15.61</v>
-      </c>
-      <c r="I141" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J141" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K141" s="5" t="n">
-        <v>1.561</v>
-      </c>
-      <c r="L141" s="3" t="inlineStr">
-        <is>
-          <t>per Each (10/2.5Av)</t>
-        </is>
-      </c>
-      <c r="M141" s="2" t="n"/>
-      <c r="N141" s="4">
+      <c r="I141" s="12" t="n">
+        <v>-3.51</v>
+      </c>
+      <c r="J141" s="13" t="n">
+        <v>-0.8994234465086482</v>
+      </c>
+      <c r="K141" s="11" t="n">
+        <v>0.3925</v>
+      </c>
+      <c r="L141" s="9" t="inlineStr">
+        <is>
+          <t>per Each (4 / 21 LB)</t>
+        </is>
+      </c>
+      <c r="M141" s="8" t="n"/>
+      <c r="N141" s="10">
         <f>M141*G141</f>
         <v/>
       </c>
-      <c r="O141" s="2" t="n"/>
-      <c r="P141" s="2" t="n"/>
-      <c r="Q141" s="2" t="n"/>
-      <c r="R141" s="2" t="n"/>
-      <c r="S141" s="2" t="n"/>
+      <c r="O141" s="8" t="n"/>
+      <c r="P141" s="8" t="n"/>
+      <c r="Q141" s="8" t="n"/>
+      <c r="R141" s="8" t="n"/>
+      <c r="S141" s="8" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -8985,60 +9022,60 @@
       <c r="S147" s="14" t="n"/>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+      <c r="A148" s="26" t="inlineStr">
         <is>
           <t>EACH</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
+      <c r="B148" s="26" t="inlineStr">
         <is>
           <t>59147</t>
         </is>
       </c>
-      <c r="C148" s="3" t="inlineStr">
+      <c r="C148" s="27" t="inlineStr">
         <is>
           <t>Salad Bowl BLT</t>
         </is>
       </c>
-      <c r="D148" s="3" t="n"/>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="D148" s="27" t="n"/>
+      <c r="E148" s="26" t="inlineStr">
         <is>
           <t>6/4Oz</t>
         </is>
       </c>
-      <c r="F148" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G148" s="4" t="n">
+      <c r="F148" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G148" s="28" t="n">
         <v>2.84</v>
       </c>
-      <c r="H148" s="5" t="n">
+      <c r="H148" s="29" t="n">
         <v>2.84</v>
       </c>
-      <c r="I148" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J148" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K148" s="5" t="n">
+      <c r="I148" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J148" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K148" s="29" t="n">
         <v>0.4733333333333333</v>
       </c>
-      <c r="L148" s="3" t="inlineStr">
+      <c r="L148" s="27" t="inlineStr">
         <is>
           <t>per Each (6/4Oz)</t>
         </is>
       </c>
-      <c r="M148" s="2" t="n"/>
-      <c r="N148" s="4">
+      <c r="M148" s="26" t="n"/>
+      <c r="N148" s="28">
         <f>M148*G148</f>
         <v/>
       </c>
-      <c r="O148" s="2" t="n"/>
-      <c r="P148" s="2" t="n"/>
-      <c r="Q148" s="2" t="n"/>
-      <c r="R148" s="2" t="n"/>
-      <c r="S148" s="2" t="n"/>
+      <c r="O148" s="26" t="n"/>
+      <c r="P148" s="26" t="n"/>
+      <c r="Q148" s="26" t="n"/>
+      <c r="R148" s="26" t="n"/>
+      <c r="S148" s="26" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -9149,60 +9186,60 @@
       <c r="S150" s="2" t="n"/>
     </row>
     <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+      <c r="A151" s="26" t="inlineStr">
         <is>
           <t>ROUND</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
+      <c r="B151" s="26" t="inlineStr">
         <is>
           <t>1100</t>
         </is>
       </c>
-      <c r="C151" s="3" t="inlineStr">
+      <c r="C151" s="27" t="inlineStr">
         <is>
           <t>Salt Iodized Round</t>
         </is>
       </c>
-      <c r="D151" s="3" t="n"/>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="D151" s="27" t="n"/>
+      <c r="E151" s="26" t="inlineStr">
         <is>
           <t>24/26Oz</t>
         </is>
       </c>
-      <c r="F151" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G151" s="4" t="n">
+      <c r="F151" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G151" s="28" t="n">
         <v>0.86</v>
       </c>
-      <c r="H151" s="5" t="n">
+      <c r="H151" s="29" t="n">
         <v>0.86</v>
       </c>
-      <c r="I151" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J151" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K151" s="5" t="n">
+      <c r="I151" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J151" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K151" s="29" t="n">
         <v>0.03583333333333334</v>
       </c>
-      <c r="L151" s="3" t="inlineStr">
+      <c r="L151" s="27" t="inlineStr">
         <is>
           <t>per Round (24/26Oz)</t>
         </is>
       </c>
-      <c r="M151" s="2" t="n"/>
-      <c r="N151" s="4">
+      <c r="M151" s="26" t="n"/>
+      <c r="N151" s="28">
         <f>M151*G151</f>
         <v/>
       </c>
-      <c r="O151" s="2" t="n"/>
-      <c r="P151" s="2" t="n"/>
-      <c r="Q151" s="2" t="n"/>
-      <c r="R151" s="2" t="n"/>
-      <c r="S151" s="2" t="n"/>
+      <c r="O151" s="26" t="n"/>
+      <c r="P151" s="26" t="n"/>
+      <c r="Q151" s="26" t="n"/>
+      <c r="R151" s="26" t="n"/>
+      <c r="S151" s="26" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="8" t="inlineStr">
@@ -9565,58 +9602,60 @@
       <c r="S157" s="14" t="n"/>
     </row>
     <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+      <c r="A158" s="8" t="inlineStr">
         <is>
           <t>CAN</t>
         </is>
       </c>
-      <c r="B158" s="2" t="n">
-        <v>7252</v>
-      </c>
-      <c r="C158" s="3" t="inlineStr">
+      <c r="B158" s="8" t="inlineStr">
+        <is>
+          <t>007252</t>
+        </is>
+      </c>
+      <c r="C158" s="9" t="inlineStr">
         <is>
           <t>Sauce Spaghetti From Concentrate</t>
         </is>
       </c>
-      <c r="D158" s="3" t="n"/>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="D158" s="9" t="n"/>
+      <c r="E158" s="8" t="inlineStr">
         <is>
           <t>6/#10Can</t>
         </is>
       </c>
-      <c r="F158" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G158" s="4" t="n">
+      <c r="F158" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G158" s="10" t="n">
+        <v>35.66</v>
+      </c>
+      <c r="H158" s="11" t="n">
         <v>6.72</v>
       </c>
-      <c r="H158" s="5" t="n">
-        <v>6.72</v>
-      </c>
-      <c r="I158" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J158" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K158" s="5" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="L158" s="3" t="inlineStr">
+      <c r="I158" s="12" t="n">
+        <v>-0.7766666666666673</v>
+      </c>
+      <c r="J158" s="13" t="n">
+        <v>-0.1155753968253969</v>
+      </c>
+      <c r="K158" s="11" t="n">
+        <v>5.943333333333332</v>
+      </c>
+      <c r="L158" s="9" t="inlineStr">
         <is>
           <t>per Can (6/#10Can)</t>
         </is>
       </c>
-      <c r="M158" s="2" t="n"/>
-      <c r="N158" s="4">
+      <c r="M158" s="8" t="n"/>
+      <c r="N158" s="10">
         <f>M158*G158</f>
         <v/>
       </c>
-      <c r="O158" s="2" t="n"/>
-      <c r="P158" s="2" t="n"/>
-      <c r="Q158" s="2" t="n"/>
-      <c r="R158" s="2" t="n"/>
-      <c r="S158" s="2" t="n"/>
+      <c r="O158" s="8" t="n"/>
+      <c r="P158" s="8" t="n"/>
+      <c r="Q158" s="8" t="n"/>
+      <c r="R158" s="8" t="n"/>
+      <c r="S158" s="8" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="14" t="inlineStr">
@@ -9679,60 +9718,60 @@
       <c r="S159" s="14" t="n"/>
     </row>
     <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+      <c r="A160" s="26" t="inlineStr">
         <is>
           <t>JUG</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
+      <c r="B160" s="26" t="inlineStr">
         <is>
           <t>M0760</t>
         </is>
       </c>
-      <c r="C160" s="3" t="inlineStr">
+      <c r="C160" s="27" t="inlineStr">
         <is>
           <t>Sauce Sweet Red Chili And Glaze</t>
         </is>
       </c>
-      <c r="D160" s="3" t="n"/>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="D160" s="27" t="n"/>
+      <c r="E160" s="26" t="inlineStr">
         <is>
           <t>4/1 Gal</t>
         </is>
       </c>
-      <c r="F160" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G160" s="4" t="n">
+      <c r="F160" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G160" s="28" t="n">
         <v>18.74</v>
       </c>
-      <c r="H160" s="5" t="n">
+      <c r="H160" s="29" t="n">
         <v>18.74</v>
       </c>
-      <c r="I160" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J160" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K160" s="5" t="n">
+      <c r="I160" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J160" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K160" s="29" t="n">
         <v>4.685</v>
       </c>
-      <c r="L160" s="3" t="inlineStr">
+      <c r="L160" s="27" t="inlineStr">
         <is>
           <t>per Jug (4/1 Gal)</t>
         </is>
       </c>
-      <c r="M160" s="2" t="n"/>
-      <c r="N160" s="4">
+      <c r="M160" s="26" t="n"/>
+      <c r="N160" s="28">
         <f>M160*G160</f>
         <v/>
       </c>
-      <c r="O160" s="2" t="n"/>
-      <c r="P160" s="2" t="n"/>
-      <c r="Q160" s="2" t="n"/>
-      <c r="R160" s="2" t="n"/>
-      <c r="S160" s="2" t="n"/>
+      <c r="O160" s="26" t="n"/>
+      <c r="P160" s="26" t="n"/>
+      <c r="Q160" s="26" t="n"/>
+      <c r="R160" s="26" t="n"/>
+      <c r="S160" s="26" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="14" t="inlineStr">
@@ -10035,60 +10074,60 @@
       <c r="S165" s="2" t="n"/>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="inlineStr">
+      <c r="A166" s="26" t="inlineStr">
         <is>
           <t>PACK</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
+      <c r="B166" s="26" t="inlineStr">
         <is>
           <t>AFW74</t>
         </is>
       </c>
-      <c r="C166" s="3" t="inlineStr">
+      <c r="C166" s="27" t="inlineStr">
         <is>
           <t>Sausage Pork Patty Fully Cooked Jalapeno Smoked Cheddar</t>
         </is>
       </c>
-      <c r="D166" s="3" t="n"/>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="D166" s="27" t="n"/>
+      <c r="E166" s="26" t="inlineStr">
         <is>
           <t>2/5 Lb</t>
         </is>
       </c>
-      <c r="F166" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G166" s="4" t="n">
+      <c r="F166" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G166" s="28" t="n">
         <v>24.98</v>
       </c>
-      <c r="H166" s="5" t="n">
+      <c r="H166" s="29" t="n">
         <v>24.98</v>
       </c>
-      <c r="I166" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J166" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K166" s="5" t="n">
+      <c r="I166" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J166" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K166" s="29" t="n">
         <v>12.49</v>
       </c>
-      <c r="L166" s="3" t="inlineStr">
+      <c r="L166" s="27" t="inlineStr">
         <is>
           <t>per Pack (2/5 Lb)</t>
         </is>
       </c>
-      <c r="M166" s="2" t="n"/>
-      <c r="N166" s="4">
+      <c r="M166" s="26" t="n"/>
+      <c r="N166" s="28">
         <f>M166*G166</f>
         <v/>
       </c>
-      <c r="O166" s="2" t="n"/>
-      <c r="P166" s="2" t="n"/>
-      <c r="Q166" s="2" t="n"/>
-      <c r="R166" s="2" t="n"/>
-      <c r="S166" s="2" t="n"/>
+      <c r="O166" s="26" t="n"/>
+      <c r="P166" s="26" t="n"/>
+      <c r="Q166" s="26" t="n"/>
+      <c r="R166" s="26" t="n"/>
+      <c r="S166" s="26" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="8" t="inlineStr">
@@ -10565,52 +10604,52 @@
       <c r="S174" s="8" t="n"/>
     </row>
     <row r="175">
-      <c r="A175" s="26" t="inlineStr">
+      <c r="A175" s="32" t="inlineStr">
         <is>
           <t>CAN</t>
         </is>
       </c>
-      <c r="B175" s="26" t="n"/>
-      <c r="C175" s="27" t="inlineStr">
+      <c r="B175" s="32" t="n"/>
+      <c r="C175" s="33" t="inlineStr">
         <is>
           <t>Soup Cream of Mushroom</t>
         </is>
       </c>
-      <c r="D175" s="27" t="n"/>
-      <c r="E175" s="26" t="n"/>
-      <c r="F175" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G175" s="28" t="n">
+      <c r="D175" s="33" t="n"/>
+      <c r="E175" s="32" t="n"/>
+      <c r="F175" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G175" s="34" t="n">
         <v>5.79</v>
       </c>
-      <c r="H175" s="29" t="n">
+      <c r="H175" s="35" t="n">
         <v>5.79</v>
       </c>
-      <c r="I175" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J175" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K175" s="29" t="n">
+      <c r="I175" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J175" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K175" s="35" t="n">
         <v>5.79</v>
       </c>
-      <c r="L175" s="27" t="inlineStr">
+      <c r="L175" s="33" t="inlineStr">
         <is>
           <t>per Can (None)</t>
         </is>
       </c>
-      <c r="M175" s="26" t="n"/>
-      <c r="N175" s="28">
+      <c r="M175" s="32" t="n"/>
+      <c r="N175" s="34">
         <f>M175*G175</f>
         <v/>
       </c>
-      <c r="O175" s="26" t="n"/>
-      <c r="P175" s="26" t="n"/>
-      <c r="Q175" s="26" t="n"/>
-      <c r="R175" s="26" t="n"/>
-      <c r="S175" s="26" t="n"/>
+      <c r="O175" s="32" t="n"/>
+      <c r="P175" s="32" t="n"/>
+      <c r="Q175" s="32" t="n"/>
+      <c r="R175" s="32" t="n"/>
+      <c r="S175" s="32" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -10847,60 +10886,60 @@
       <c r="S179" s="20" t="n"/>
     </row>
     <row r="180">
-      <c r="A180" s="2" t="inlineStr">
+      <c r="A180" s="26" t="inlineStr">
         <is>
           <t>CAN</t>
         </is>
       </c>
-      <c r="B180" s="2" t="inlineStr">
+      <c r="B180" s="26" t="inlineStr">
         <is>
           <t>19856</t>
         </is>
       </c>
-      <c r="C180" s="3" t="inlineStr">
+      <c r="C180" s="27" t="inlineStr">
         <is>
           <t>Syrup Chocolate Full Flavor Ready To Use</t>
         </is>
       </c>
-      <c r="D180" s="3" t="n"/>
-      <c r="E180" s="2" t="inlineStr">
+      <c r="D180" s="27" t="n"/>
+      <c r="E180" s="26" t="inlineStr">
         <is>
           <t>6/#10Can</t>
         </is>
       </c>
-      <c r="F180" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G180" s="4" t="n">
+      <c r="F180" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G180" s="28" t="n">
         <v>12.62</v>
       </c>
-      <c r="H180" s="5" t="n">
+      <c r="H180" s="29" t="n">
         <v>12.62</v>
       </c>
-      <c r="I180" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J180" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K180" s="5" t="n">
+      <c r="I180" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J180" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K180" s="29" t="n">
         <v>2.103333333333333</v>
       </c>
-      <c r="L180" s="3" t="inlineStr">
+      <c r="L180" s="27" t="inlineStr">
         <is>
           <t>per Can (6/#10Can)</t>
         </is>
       </c>
-      <c r="M180" s="2" t="n"/>
-      <c r="N180" s="4">
+      <c r="M180" s="26" t="n"/>
+      <c r="N180" s="28">
         <f>M180*G180</f>
         <v/>
       </c>
-      <c r="O180" s="2" t="n"/>
-      <c r="P180" s="2" t="n"/>
-      <c r="Q180" s="2" t="n"/>
-      <c r="R180" s="2" t="n"/>
-      <c r="S180" s="2" t="n"/>
+      <c r="O180" s="26" t="n"/>
+      <c r="P180" s="26" t="n"/>
+      <c r="Q180" s="26" t="n"/>
+      <c r="R180" s="26" t="n"/>
+      <c r="S180" s="26" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="8" t="inlineStr">
@@ -11023,172 +11062,172 @@
       <c r="S182" s="2" t="n"/>
     </row>
     <row r="183">
-      <c r="A183" s="2" t="inlineStr">
+      <c r="A183" s="26" t="inlineStr">
         <is>
           <t>BAG</t>
         </is>
       </c>
-      <c r="B183" s="2" t="inlineStr">
+      <c r="B183" s="26" t="inlineStr">
         <is>
           <t>V9432</t>
         </is>
       </c>
-      <c r="C183" s="3" t="inlineStr">
+      <c r="C183" s="27" t="inlineStr">
         <is>
           <t>Topping Butterfinger Chopped Refrigerated</t>
         </is>
       </c>
-      <c r="D183" s="3" t="n"/>
-      <c r="E183" s="2" t="inlineStr">
+      <c r="D183" s="27" t="n"/>
+      <c r="E183" s="26" t="inlineStr">
         <is>
           <t>2/5 Lb</t>
         </is>
       </c>
-      <c r="F183" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G183" s="4" t="n">
+      <c r="F183" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G183" s="28" t="n">
         <v>24.08</v>
       </c>
-      <c r="H183" s="5" t="n">
+      <c r="H183" s="29" t="n">
         <v>24.08</v>
       </c>
-      <c r="I183" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J183" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K183" s="5" t="n">
+      <c r="I183" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J183" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K183" s="29" t="n">
         <v>12.04</v>
       </c>
-      <c r="L183" s="3" t="inlineStr">
+      <c r="L183" s="27" t="inlineStr">
         <is>
           <t>per Bag (2/5 Lb)</t>
         </is>
       </c>
-      <c r="M183" s="2" t="n"/>
-      <c r="N183" s="4">
+      <c r="M183" s="26" t="n"/>
+      <c r="N183" s="28">
         <f>M183*G183</f>
         <v/>
       </c>
-      <c r="O183" s="2" t="n"/>
-      <c r="P183" s="2" t="n"/>
-      <c r="Q183" s="2" t="n"/>
-      <c r="R183" s="2" t="n"/>
-      <c r="S183" s="2" t="n"/>
+      <c r="O183" s="26" t="n"/>
+      <c r="P183" s="26" t="n"/>
+      <c r="Q183" s="26" t="n"/>
+      <c r="R183" s="26" t="n"/>
+      <c r="S183" s="26" t="n"/>
     </row>
     <row r="184">
-      <c r="A184" s="2" t="inlineStr">
+      <c r="A184" s="26" t="inlineStr">
         <is>
           <t>CAN</t>
         </is>
       </c>
-      <c r="B184" s="2" t="inlineStr">
+      <c r="B184" s="26" t="inlineStr">
         <is>
           <t>B9632</t>
         </is>
       </c>
-      <c r="C184" s="3" t="inlineStr">
+      <c r="C184" s="27" t="inlineStr">
         <is>
           <t>Topping Butterscotch Ready To Use</t>
         </is>
       </c>
-      <c r="D184" s="3" t="n"/>
-      <c r="E184" s="2" t="inlineStr">
+      <c r="D184" s="27" t="n"/>
+      <c r="E184" s="26" t="inlineStr">
         <is>
           <t>6/#5 Can</t>
         </is>
       </c>
-      <c r="F184" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G184" s="4" t="n">
+      <c r="F184" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G184" s="28" t="n">
         <v>8.52</v>
       </c>
-      <c r="H184" s="5" t="n">
+      <c r="H184" s="29" t="n">
         <v>8.52</v>
       </c>
-      <c r="I184" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J184" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K184" s="5" t="n">
+      <c r="I184" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J184" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K184" s="29" t="n">
         <v>1.42</v>
       </c>
-      <c r="L184" s="3" t="inlineStr">
+      <c r="L184" s="27" t="inlineStr">
         <is>
           <t>per Can (6/#5 Can)</t>
         </is>
       </c>
-      <c r="M184" s="2" t="n"/>
-      <c r="N184" s="4">
+      <c r="M184" s="26" t="n"/>
+      <c r="N184" s="28">
         <f>M184*G184</f>
         <v/>
       </c>
-      <c r="O184" s="2" t="n"/>
-      <c r="P184" s="2" t="n"/>
-      <c r="Q184" s="2" t="n"/>
-      <c r="R184" s="2" t="n"/>
-      <c r="S184" s="2" t="n"/>
+      <c r="O184" s="26" t="n"/>
+      <c r="P184" s="26" t="n"/>
+      <c r="Q184" s="26" t="n"/>
+      <c r="R184" s="26" t="n"/>
+      <c r="S184" s="26" t="n"/>
     </row>
     <row r="185">
-      <c r="A185" s="2" t="inlineStr">
+      <c r="A185" s="26" t="inlineStr">
         <is>
           <t>BAG</t>
         </is>
       </c>
-      <c r="B185" s="2" t="inlineStr">
+      <c r="B185" s="26" t="inlineStr">
         <is>
           <t>B8538</t>
         </is>
       </c>
-      <c r="C185" s="3" t="inlineStr">
+      <c r="C185" s="27" t="inlineStr">
         <is>
           <t>Topping Candy Rainbow Nerds Wonka</t>
         </is>
       </c>
-      <c r="D185" s="3" t="n"/>
-      <c r="E185" s="2" t="inlineStr">
+      <c r="D185" s="27" t="n"/>
+      <c r="E185" s="26" t="inlineStr">
         <is>
           <t>2/5 Lb</t>
         </is>
       </c>
-      <c r="F185" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G185" s="4" t="n">
+      <c r="F185" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G185" s="28" t="n">
         <v>27.28</v>
       </c>
-      <c r="H185" s="5" t="n">
+      <c r="H185" s="29" t="n">
         <v>27.28</v>
       </c>
-      <c r="I185" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J185" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K185" s="5" t="n">
+      <c r="I185" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J185" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K185" s="29" t="n">
         <v>13.64</v>
       </c>
-      <c r="L185" s="3" t="inlineStr">
+      <c r="L185" s="27" t="inlineStr">
         <is>
           <t>per Bag (2/5 Lb)</t>
         </is>
       </c>
-      <c r="M185" s="2" t="n"/>
-      <c r="N185" s="4">
+      <c r="M185" s="26" t="n"/>
+      <c r="N185" s="28">
         <f>M185*G185</f>
         <v/>
       </c>
-      <c r="O185" s="2" t="n"/>
-      <c r="P185" s="2" t="n"/>
-      <c r="Q185" s="2" t="n"/>
-      <c r="R185" s="2" t="n"/>
-      <c r="S185" s="2" t="n"/>
+      <c r="O185" s="26" t="n"/>
+      <c r="P185" s="26" t="n"/>
+      <c r="Q185" s="26" t="n"/>
+      <c r="R185" s="26" t="n"/>
+      <c r="S185" s="26" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -11245,284 +11284,284 @@
       <c r="S186" s="2" t="n"/>
     </row>
     <row r="187">
-      <c r="A187" s="2" t="inlineStr">
+      <c r="A187" s="26" t="inlineStr">
         <is>
           <t>BAG</t>
         </is>
       </c>
-      <c r="B187" s="2" t="inlineStr">
+      <c r="B187" s="26" t="inlineStr">
         <is>
           <t>20562</t>
         </is>
       </c>
-      <c r="C187" s="3" t="inlineStr">
+      <c r="C187" s="27" t="inlineStr">
         <is>
           <t>Topping Heath Bar Chopped Refrigerated</t>
         </is>
       </c>
-      <c r="D187" s="3" t="n"/>
-      <c r="E187" s="2" t="inlineStr">
+      <c r="D187" s="27" t="n"/>
+      <c r="E187" s="26" t="inlineStr">
         <is>
           <t>2/5 Lb</t>
         </is>
       </c>
-      <c r="F187" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G187" s="4" t="n">
+      <c r="F187" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G187" s="28" t="n">
         <v>34.06</v>
       </c>
-      <c r="H187" s="5" t="n">
+      <c r="H187" s="29" t="n">
         <v>34.06</v>
       </c>
-      <c r="I187" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J187" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K187" s="5" t="n">
+      <c r="I187" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J187" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K187" s="29" t="n">
         <v>17.03</v>
       </c>
-      <c r="L187" s="3" t="inlineStr">
+      <c r="L187" s="27" t="inlineStr">
         <is>
           <t>per Bag (2/5 Lb)</t>
         </is>
       </c>
-      <c r="M187" s="2" t="n"/>
-      <c r="N187" s="4">
+      <c r="M187" s="26" t="n"/>
+      <c r="N187" s="28">
         <f>M187*G187</f>
         <v/>
       </c>
-      <c r="O187" s="2" t="n"/>
-      <c r="P187" s="2" t="n"/>
-      <c r="Q187" s="2" t="n"/>
-      <c r="R187" s="2" t="n"/>
-      <c r="S187" s="2" t="n"/>
+      <c r="O187" s="26" t="n"/>
+      <c r="P187" s="26" t="n"/>
+      <c r="Q187" s="26" t="n"/>
+      <c r="R187" s="26" t="n"/>
+      <c r="S187" s="26" t="n"/>
     </row>
     <row r="188">
-      <c r="A188" s="2" t="inlineStr">
+      <c r="A188" s="26" t="inlineStr">
         <is>
           <t>BAG</t>
         </is>
       </c>
-      <c r="B188" s="2" t="inlineStr">
+      <c r="B188" s="26" t="inlineStr">
         <is>
           <t>H1838</t>
         </is>
       </c>
-      <c r="C188" s="3" t="inlineStr">
+      <c r="C188" s="27" t="inlineStr">
         <is>
           <t>Topping M&amp;M's Plain Chopped Refrigerated</t>
         </is>
       </c>
-      <c r="D188" s="3" t="n"/>
-      <c r="E188" s="2" t="inlineStr">
+      <c r="D188" s="27" t="n"/>
+      <c r="E188" s="26" t="inlineStr">
         <is>
           <t>2/4 Lb</t>
         </is>
       </c>
-      <c r="F188" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G188" s="4" t="n">
+      <c r="F188" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G188" s="28" t="n">
         <v>21.56</v>
       </c>
-      <c r="H188" s="5" t="n">
+      <c r="H188" s="29" t="n">
         <v>21.56</v>
       </c>
-      <c r="I188" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J188" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K188" s="5" t="n">
+      <c r="I188" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J188" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K188" s="29" t="n">
         <v>10.78</v>
       </c>
-      <c r="L188" s="3" t="inlineStr">
+      <c r="L188" s="27" t="inlineStr">
         <is>
           <t>per Bag (2/4 Lb)</t>
         </is>
       </c>
-      <c r="M188" s="2" t="n"/>
-      <c r="N188" s="4">
+      <c r="M188" s="26" t="n"/>
+      <c r="N188" s="28">
         <f>M188*G188</f>
         <v/>
       </c>
-      <c r="O188" s="2" t="n"/>
-      <c r="P188" s="2" t="n"/>
-      <c r="Q188" s="2" t="n"/>
-      <c r="R188" s="2" t="n"/>
-      <c r="S188" s="2" t="n"/>
+      <c r="O188" s="26" t="n"/>
+      <c r="P188" s="26" t="n"/>
+      <c r="Q188" s="26" t="n"/>
+      <c r="R188" s="26" t="n"/>
+      <c r="S188" s="26" t="n"/>
     </row>
     <row r="189">
-      <c r="A189" s="2" t="inlineStr">
+      <c r="A189" s="26" t="inlineStr">
         <is>
           <t>CAN</t>
         </is>
       </c>
-      <c r="B189" s="2" t="inlineStr">
+      <c r="B189" s="26" t="inlineStr">
         <is>
           <t>75832</t>
         </is>
       </c>
-      <c r="C189" s="3" t="inlineStr">
+      <c r="C189" s="27" t="inlineStr">
         <is>
           <t>Topping Marshmallow Ready To Use</t>
         </is>
       </c>
-      <c r="D189" s="3" t="n"/>
-      <c r="E189" s="2" t="inlineStr">
+      <c r="D189" s="27" t="n"/>
+      <c r="E189" s="26" t="inlineStr">
         <is>
           <t>6/36 Oz</t>
         </is>
       </c>
-      <c r="F189" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G189" s="4" t="n">
+      <c r="F189" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G189" s="28" t="n">
         <v>7.66</v>
       </c>
-      <c r="H189" s="5" t="n">
+      <c r="H189" s="29" t="n">
         <v>7.66</v>
       </c>
-      <c r="I189" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J189" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K189" s="5" t="n">
+      <c r="I189" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J189" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K189" s="29" t="n">
         <v>1.276666666666667</v>
       </c>
-      <c r="L189" s="3" t="inlineStr">
+      <c r="L189" s="27" t="inlineStr">
         <is>
           <t>per Can (6/36 Oz)</t>
         </is>
       </c>
-      <c r="M189" s="2" t="n"/>
-      <c r="N189" s="4">
+      <c r="M189" s="26" t="n"/>
+      <c r="N189" s="28">
         <f>M189*G189</f>
         <v/>
       </c>
-      <c r="O189" s="2" t="n"/>
-      <c r="P189" s="2" t="n"/>
-      <c r="Q189" s="2" t="n"/>
-      <c r="R189" s="2" t="n"/>
-      <c r="S189" s="2" t="n"/>
+      <c r="O189" s="26" t="n"/>
+      <c r="P189" s="26" t="n"/>
+      <c r="Q189" s="26" t="n"/>
+      <c r="R189" s="26" t="n"/>
+      <c r="S189" s="26" t="n"/>
     </row>
     <row r="190">
-      <c r="A190" s="2" t="inlineStr">
+      <c r="A190" s="26" t="inlineStr">
         <is>
           <t>CAN</t>
         </is>
       </c>
-      <c r="B190" s="2" t="inlineStr">
+      <c r="B190" s="26" t="inlineStr">
         <is>
           <t>BF680</t>
         </is>
       </c>
-      <c r="C190" s="3" t="inlineStr">
+      <c r="C190" s="27" t="inlineStr">
         <is>
           <t>Topping Peanut Pieces Salted</t>
         </is>
       </c>
-      <c r="D190" s="3" t="n"/>
-      <c r="E190" s="2" t="inlineStr">
+      <c r="D190" s="27" t="n"/>
+      <c r="E190" s="26" t="inlineStr">
         <is>
           <t>6/2.5 Lb</t>
         </is>
       </c>
-      <c r="F190" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G190" s="4" t="n">
+      <c r="F190" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G190" s="28" t="n">
         <v>12.37</v>
       </c>
-      <c r="H190" s="5" t="n">
+      <c r="H190" s="29" t="n">
         <v>12.37</v>
       </c>
-      <c r="I190" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J190" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K190" s="5" t="n">
+      <c r="I190" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J190" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K190" s="29" t="n">
         <v>2.061666666666667</v>
       </c>
-      <c r="L190" s="3" t="inlineStr">
+      <c r="L190" s="27" t="inlineStr">
         <is>
           <t>per Can (6/2.5 Lb)</t>
         </is>
       </c>
-      <c r="M190" s="2" t="n"/>
-      <c r="N190" s="4">
+      <c r="M190" s="26" t="n"/>
+      <c r="N190" s="28">
         <f>M190*G190</f>
         <v/>
       </c>
-      <c r="O190" s="2" t="n"/>
-      <c r="P190" s="2" t="n"/>
-      <c r="Q190" s="2" t="n"/>
-      <c r="R190" s="2" t="n"/>
-      <c r="S190" s="2" t="n"/>
+      <c r="O190" s="26" t="n"/>
+      <c r="P190" s="26" t="n"/>
+      <c r="Q190" s="26" t="n"/>
+      <c r="R190" s="26" t="n"/>
+      <c r="S190" s="26" t="n"/>
     </row>
     <row r="191">
-      <c r="A191" s="2" t="inlineStr">
+      <c r="A191" s="26" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="B191" s="2" t="inlineStr">
+      <c r="B191" s="26" t="inlineStr">
         <is>
           <t>28498</t>
         </is>
       </c>
-      <c r="C191" s="3" t="inlineStr">
+      <c r="C191" s="27" t="inlineStr">
         <is>
           <t>Topping Reeses Pieces Mini Bulk</t>
         </is>
       </c>
-      <c r="D191" s="3" t="n"/>
-      <c r="E191" s="2" t="inlineStr">
+      <c r="D191" s="27" t="n"/>
+      <c r="E191" s="26" t="inlineStr">
         <is>
           <t>1/25 Lb</t>
         </is>
       </c>
-      <c r="F191" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G191" s="4" t="n">
+      <c r="F191" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G191" s="28" t="n">
         <v>122.75</v>
       </c>
-      <c r="H191" s="5" t="n">
+      <c r="H191" s="29" t="n">
         <v>122.75</v>
       </c>
-      <c r="I191" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J191" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K191" s="5" t="n">
+      <c r="I191" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J191" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K191" s="29" t="n">
         <v>122.75</v>
       </c>
-      <c r="L191" s="3" t="inlineStr">
+      <c r="L191" s="27" t="inlineStr">
         <is>
           <t>per Case (1/25 Lb)</t>
         </is>
       </c>
-      <c r="M191" s="2" t="n"/>
-      <c r="N191" s="4">
+      <c r="M191" s="26" t="n"/>
+      <c r="N191" s="28">
         <f>M191*G191</f>
         <v/>
       </c>
-      <c r="O191" s="2" t="n"/>
-      <c r="P191" s="2" t="n"/>
-      <c r="Q191" s="2" t="n"/>
-      <c r="R191" s="2" t="n"/>
-      <c r="S191" s="2" t="n"/>
+      <c r="O191" s="26" t="n"/>
+      <c r="P191" s="26" t="n"/>
+      <c r="Q191" s="26" t="n"/>
+      <c r="R191" s="26" t="n"/>
+      <c r="S191" s="26" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
@@ -11585,60 +11624,60 @@
       <c r="S192" s="2" t="n"/>
     </row>
     <row r="193">
-      <c r="A193" s="2" t="inlineStr">
+      <c r="A193" s="26" t="inlineStr">
         <is>
           <t>BOX</t>
         </is>
       </c>
-      <c r="B193" s="2" t="inlineStr">
+      <c r="B193" s="26" t="inlineStr">
         <is>
           <t>22536</t>
         </is>
       </c>
-      <c r="C193" s="3" t="inlineStr">
+      <c r="C193" s="27" t="inlineStr">
         <is>
           <t>Wrap Deli 8X10.75 Interfolded</t>
         </is>
       </c>
-      <c r="D193" s="3" t="n"/>
-      <c r="E193" s="2" t="inlineStr">
+      <c r="D193" s="27" t="n"/>
+      <c r="E193" s="26" t="inlineStr">
         <is>
           <t>12/500</t>
         </is>
       </c>
-      <c r="F193" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G193" s="4" t="n">
+      <c r="F193" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G193" s="28" t="n">
         <v>6.56</v>
       </c>
-      <c r="H193" s="5" t="n">
+      <c r="H193" s="29" t="n">
         <v>6.56</v>
       </c>
-      <c r="I193" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J193" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K193" s="5" t="n">
+      <c r="I193" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J193" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K193" s="29" t="n">
         <v>0.5466666666666666</v>
       </c>
-      <c r="L193" s="3" t="inlineStr">
+      <c r="L193" s="27" t="inlineStr">
         <is>
           <t>per Box (12/500)</t>
         </is>
       </c>
-      <c r="M193" s="2" t="n"/>
-      <c r="N193" s="4">
+      <c r="M193" s="26" t="n"/>
+      <c r="N193" s="28">
         <f>M193*G193</f>
         <v/>
       </c>
-      <c r="O193" s="2" t="n"/>
-      <c r="P193" s="2" t="n"/>
-      <c r="Q193" s="2" t="n"/>
-      <c r="R193" s="2" t="n"/>
-      <c r="S193" s="2" t="n"/>
+      <c r="O193" s="26" t="n"/>
+      <c r="P193" s="26" t="n"/>
+      <c r="Q193" s="26" t="n"/>
+      <c r="R193" s="26" t="n"/>
+      <c r="S193" s="26" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
@@ -11809,1941 +11848,1951 @@
       <c r="S196" s="20" t="n"/>
     </row>
     <row r="197">
-      <c r="A197" s="26" t="inlineStr">
+      <c r="A197" s="32" t="inlineStr">
         <is>
           <t>EACH</t>
         </is>
       </c>
-      <c r="B197" s="26" t="n"/>
-      <c r="C197" s="27" t="inlineStr">
+      <c r="B197" s="32" t="n"/>
+      <c r="C197" s="33" t="inlineStr">
         <is>
           <t>Lettuce Head</t>
         </is>
       </c>
-      <c r="D197" s="27" t="n"/>
-      <c r="E197" s="26" t="n"/>
-      <c r="F197" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G197" s="28" t="n">
+      <c r="D197" s="33" t="n"/>
+      <c r="E197" s="32" t="n"/>
+      <c r="F197" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G197" s="34" t="n">
         <v>3.99</v>
       </c>
-      <c r="H197" s="29" t="n">
+      <c r="H197" s="35" t="n">
         <v>3.99</v>
       </c>
-      <c r="I197" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J197" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K197" s="29" t="n">
+      <c r="I197" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J197" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K197" s="35" t="n">
         <v>3.99</v>
       </c>
-      <c r="L197" s="27" t="inlineStr">
+      <c r="L197" s="33" t="inlineStr">
         <is>
           <t>per Each (None)</t>
         </is>
       </c>
-      <c r="M197" s="26" t="n"/>
-      <c r="N197" s="28">
+      <c r="M197" s="32" t="n"/>
+      <c r="N197" s="34">
         <f>M197*G197</f>
         <v/>
       </c>
-      <c r="O197" s="26" t="n"/>
-      <c r="P197" s="26" t="n"/>
-      <c r="Q197" s="26" t="n"/>
-      <c r="R197" s="26" t="n"/>
-      <c r="S197" s="26" t="n"/>
+      <c r="O197" s="32" t="n"/>
+      <c r="P197" s="32" t="n"/>
+      <c r="Q197" s="32" t="n"/>
+      <c r="R197" s="32" t="n"/>
+      <c r="S197" s="32" t="n"/>
     </row>
     <row r="198">
-      <c r="A198" s="26" t="inlineStr">
+      <c r="A198" s="32" t="inlineStr">
         <is>
           <t>EACH</t>
         </is>
       </c>
-      <c r="B198" s="26" t="n"/>
-      <c r="C198" s="27" t="inlineStr">
+      <c r="B198" s="32" t="n"/>
+      <c r="C198" s="33" t="inlineStr">
         <is>
           <t>Tomato</t>
         </is>
       </c>
-      <c r="D198" s="27" t="n"/>
-      <c r="E198" s="26" t="n"/>
-      <c r="F198" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G198" s="28" t="n">
+      <c r="D198" s="33" t="n"/>
+      <c r="E198" s="32" t="n"/>
+      <c r="F198" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G198" s="34" t="n">
         <v>2.49</v>
       </c>
-      <c r="H198" s="29" t="n">
+      <c r="H198" s="35" t="n">
         <v>2.49</v>
       </c>
-      <c r="I198" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J198" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K198" s="29" t="n">
+      <c r="I198" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J198" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K198" s="35" t="n">
         <v>2.49</v>
       </c>
-      <c r="L198" s="27" t="inlineStr">
+      <c r="L198" s="33" t="inlineStr">
         <is>
           <t>per Each (None)</t>
         </is>
       </c>
-      <c r="M198" s="26" t="n"/>
-      <c r="N198" s="28">
+      <c r="M198" s="32" t="n"/>
+      <c r="N198" s="34">
         <f>M198*G198</f>
         <v/>
       </c>
-      <c r="O198" s="26" t="n"/>
-      <c r="P198" s="26" t="n"/>
-      <c r="Q198" s="26" t="n"/>
-      <c r="R198" s="26" t="n"/>
-      <c r="S198" s="26" t="n"/>
+      <c r="O198" s="32" t="n"/>
+      <c r="P198" s="32" t="n"/>
+      <c r="Q198" s="32" t="n"/>
+      <c r="R198" s="32" t="n"/>
+      <c r="S198" s="32" t="n"/>
     </row>
     <row r="199">
-      <c r="A199" s="26" t="inlineStr">
+      <c r="A199" s="32" t="inlineStr">
         <is>
           <t>BAG</t>
         </is>
       </c>
-      <c r="B199" s="26" t="n"/>
-      <c r="C199" s="27" t="inlineStr">
+      <c r="B199" s="32" t="n"/>
+      <c r="C199" s="33" t="inlineStr">
         <is>
           <t>Creole Marinade</t>
         </is>
       </c>
-      <c r="D199" s="27" t="n"/>
-      <c r="E199" s="26" t="n"/>
-      <c r="F199" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G199" s="28" t="n">
+      <c r="D199" s="33" t="n"/>
+      <c r="E199" s="32" t="n"/>
+      <c r="F199" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G199" s="34" t="n">
         <v>1.81</v>
       </c>
-      <c r="H199" s="29" t="n">
+      <c r="H199" s="35" t="n">
         <v>1.81</v>
       </c>
-      <c r="I199" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J199" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K199" s="29" t="n">
+      <c r="I199" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J199" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K199" s="35" t="n">
         <v>1.81</v>
       </c>
-      <c r="L199" s="27" t="inlineStr">
+      <c r="L199" s="33" t="inlineStr">
         <is>
           <t>per Bag (None)</t>
         </is>
       </c>
-      <c r="M199" s="26" t="n"/>
-      <c r="N199" s="28">
+      <c r="M199" s="32" t="n"/>
+      <c r="N199" s="34">
         <f>M199*G199</f>
         <v/>
       </c>
-      <c r="O199" s="26" t="n"/>
-      <c r="P199" s="26" t="n"/>
-      <c r="Q199" s="26" t="n"/>
-      <c r="R199" s="26" t="n"/>
-      <c r="S199" s="26" t="n"/>
+      <c r="O199" s="32" t="n"/>
+      <c r="P199" s="32" t="n"/>
+      <c r="Q199" s="32" t="n"/>
+      <c r="R199" s="32" t="n"/>
+      <c r="S199" s="32" t="n"/>
     </row>
     <row r="200">
-      <c r="A200" s="26" t="inlineStr">
+      <c r="A200" s="32" t="inlineStr">
         <is>
           <t>BAG</t>
         </is>
       </c>
-      <c r="B200" s="26" t="n"/>
-      <c r="C200" s="27" t="inlineStr">
+      <c r="B200" s="32" t="n"/>
+      <c r="C200" s="33" t="inlineStr">
         <is>
           <t>Spicy Marinade</t>
         </is>
       </c>
-      <c r="D200" s="27" t="n"/>
-      <c r="E200" s="26" t="n"/>
-      <c r="F200" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G200" s="28" t="n">
+      <c r="D200" s="33" t="n"/>
+      <c r="E200" s="32" t="n"/>
+      <c r="F200" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G200" s="34" t="n">
         <v>5.27</v>
       </c>
-      <c r="H200" s="29" t="n">
+      <c r="H200" s="35" t="n">
         <v>5.27</v>
       </c>
-      <c r="I200" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J200" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K200" s="29" t="n">
+      <c r="I200" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J200" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K200" s="35" t="n">
         <v>5.27</v>
       </c>
-      <c r="L200" s="27" t="inlineStr">
+      <c r="L200" s="33" t="inlineStr">
         <is>
           <t>per Bag (None)</t>
         </is>
       </c>
-      <c r="M200" s="26" t="n"/>
-      <c r="N200" s="28">
+      <c r="M200" s="32" t="n"/>
+      <c r="N200" s="34">
         <f>M200*G200</f>
         <v/>
       </c>
-      <c r="O200" s="26" t="n"/>
-      <c r="P200" s="26" t="n"/>
-      <c r="Q200" s="26" t="n"/>
-      <c r="R200" s="26" t="n"/>
-      <c r="S200" s="26" t="n"/>
+      <c r="O200" s="32" t="n"/>
+      <c r="P200" s="32" t="n"/>
+      <c r="Q200" s="32" t="n"/>
+      <c r="R200" s="32" t="n"/>
+      <c r="S200" s="32" t="n"/>
     </row>
     <row r="201">
-      <c r="A201" s="26" t="inlineStr">
+      <c r="A201" s="32" t="inlineStr">
         <is>
           <t>BAG</t>
         </is>
       </c>
-      <c r="B201" s="26" t="n"/>
-      <c r="C201" s="27" t="inlineStr">
+      <c r="B201" s="32" t="n"/>
+      <c r="C201" s="33" t="inlineStr">
         <is>
           <t>Batter Mix</t>
         </is>
       </c>
-      <c r="D201" s="27" t="n"/>
-      <c r="E201" s="26" t="n"/>
-      <c r="F201" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G201" s="28" t="n">
+      <c r="D201" s="33" t="n"/>
+      <c r="E201" s="32" t="n"/>
+      <c r="F201" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G201" s="34" t="n">
         <v>2.5</v>
       </c>
-      <c r="H201" s="29" t="n">
+      <c r="H201" s="35" t="n">
         <v>2.5</v>
       </c>
-      <c r="I201" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J201" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K201" s="29" t="n">
+      <c r="I201" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J201" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K201" s="35" t="n">
         <v>2.5</v>
       </c>
-      <c r="L201" s="27" t="inlineStr">
+      <c r="L201" s="33" t="inlineStr">
         <is>
           <t>per Bag (None)</t>
         </is>
       </c>
-      <c r="M201" s="26" t="n"/>
-      <c r="N201" s="28">
+      <c r="M201" s="32" t="n"/>
+      <c r="N201" s="34">
         <f>M201*G201</f>
         <v/>
       </c>
-      <c r="O201" s="26" t="n"/>
-      <c r="P201" s="26" t="n"/>
-      <c r="Q201" s="26" t="n"/>
-      <c r="R201" s="26" t="n"/>
-      <c r="S201" s="26" t="n"/>
+      <c r="O201" s="32" t="n"/>
+      <c r="P201" s="32" t="n"/>
+      <c r="Q201" s="32" t="n"/>
+      <c r="R201" s="32" t="n"/>
+      <c r="S201" s="32" t="n"/>
     </row>
     <row r="202">
-      <c r="A202" s="2" t="n"/>
-      <c r="B202" s="2" t="inlineStr">
+      <c r="A202" s="26" t="n"/>
+      <c r="B202" s="26" t="inlineStr">
         <is>
           <t>Imperial</t>
         </is>
       </c>
-      <c r="C202" s="3" t="n"/>
-      <c r="D202" s="3" t="n"/>
-      <c r="E202" s="2" t="n"/>
-      <c r="F202" s="2" t="n"/>
-      <c r="G202" s="4" t="n"/>
-      <c r="H202" s="5" t="n"/>
-      <c r="I202" s="6" t="n"/>
-      <c r="J202" s="7" t="n"/>
-      <c r="K202" s="5" t="n"/>
-      <c r="L202" s="3" t="inlineStr">
+      <c r="C202" s="27" t="n"/>
+      <c r="D202" s="27" t="n"/>
+      <c r="E202" s="26" t="n"/>
+      <c r="F202" s="26" t="n"/>
+      <c r="G202" s="28" t="n"/>
+      <c r="H202" s="29" t="n"/>
+      <c r="I202" s="30" t="n"/>
+      <c r="J202" s="31" t="n"/>
+      <c r="K202" s="29" t="n"/>
+      <c r="L202" s="27" t="inlineStr">
         <is>
           <t>see label</t>
         </is>
       </c>
-      <c r="M202" s="2" t="n"/>
-      <c r="N202" s="4">
+      <c r="M202" s="26" t="n"/>
+      <c r="N202" s="28">
         <f>M202*G202</f>
         <v/>
       </c>
-      <c r="O202" s="2" t="n"/>
-      <c r="P202" s="2" t="n"/>
-      <c r="Q202" s="2" t="n"/>
-      <c r="R202" s="2" t="n"/>
-      <c r="S202" s="2" t="n"/>
+      <c r="O202" s="26" t="n"/>
+      <c r="P202" s="26" t="n"/>
+      <c r="Q202" s="26" t="n"/>
+      <c r="R202" s="26" t="n"/>
+      <c r="S202" s="26" t="n"/>
     </row>
     <row r="203">
-      <c r="A203" s="26" t="inlineStr">
+      <c r="A203" s="32" t="inlineStr">
         <is>
           <t>PACK</t>
         </is>
       </c>
-      <c r="B203" s="26" t="n"/>
-      <c r="C203" s="27" t="inlineStr">
+      <c r="B203" s="32" t="n"/>
+      <c r="C203" s="33" t="inlineStr">
         <is>
           <t>Bayou Blend Pork</t>
         </is>
       </c>
-      <c r="D203" s="27" t="n"/>
-      <c r="E203" s="26" t="inlineStr">
+      <c r="D203" s="33" t="n"/>
+      <c r="E203" s="32" t="inlineStr">
         <is>
           <t>5 Packs</t>
         </is>
       </c>
-      <c r="F203" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G203" s="28" t="n">
+      <c r="F203" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G203" s="34" t="n">
         <v>7.48</v>
       </c>
-      <c r="H203" s="29" t="n">
+      <c r="H203" s="35" t="n">
         <v>7.48</v>
       </c>
-      <c r="I203" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J203" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K203" s="29" t="n">
+      <c r="I203" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J203" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K203" s="35" t="n">
         <v>1.496</v>
       </c>
-      <c r="L203" s="27" t="inlineStr">
+      <c r="L203" s="33" t="inlineStr">
         <is>
           <t>per Pack (5 Packs)</t>
         </is>
       </c>
-      <c r="M203" s="26" t="n"/>
-      <c r="N203" s="28">
+      <c r="M203" s="32" t="n"/>
+      <c r="N203" s="34">
         <f>M203*G203</f>
         <v/>
       </c>
-      <c r="O203" s="26" t="n"/>
-      <c r="P203" s="26" t="n"/>
-      <c r="Q203" s="26" t="n"/>
-      <c r="R203" s="26" t="n"/>
-      <c r="S203" s="26" t="n"/>
+      <c r="O203" s="32" t="n"/>
+      <c r="P203" s="32" t="n"/>
+      <c r="Q203" s="32" t="n"/>
+      <c r="R203" s="32" t="n"/>
+      <c r="S203" s="32" t="n"/>
     </row>
     <row r="204">
-      <c r="A204" s="26" t="inlineStr">
+      <c r="A204" s="32" t="inlineStr">
         <is>
           <t>PACK</t>
         </is>
       </c>
-      <c r="B204" s="26" t="n"/>
-      <c r="C204" s="27" t="inlineStr">
+      <c r="B204" s="32" t="n"/>
+      <c r="C204" s="33" t="inlineStr">
         <is>
           <t>Bayou Blend Alligator</t>
         </is>
       </c>
-      <c r="D204" s="27" t="n"/>
-      <c r="E204" s="26" t="inlineStr">
+      <c r="D204" s="33" t="n"/>
+      <c r="E204" s="32" t="inlineStr">
         <is>
           <t>5 Pack</t>
         </is>
       </c>
-      <c r="F204" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G204" s="28" t="n">
+      <c r="F204" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G204" s="34" t="n">
         <v>9.890000000000001</v>
       </c>
-      <c r="H204" s="29" t="n">
+      <c r="H204" s="35" t="n">
         <v>9.890000000000001</v>
       </c>
-      <c r="I204" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J204" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K204" s="29" t="n">
+      <c r="I204" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J204" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K204" s="35" t="n">
         <v>1.978</v>
       </c>
-      <c r="L204" s="27" t="inlineStr">
+      <c r="L204" s="33" t="inlineStr">
         <is>
           <t>per Pack (5 Pack)</t>
         </is>
       </c>
-      <c r="M204" s="26" t="n"/>
-      <c r="N204" s="28">
+      <c r="M204" s="32" t="n"/>
+      <c r="N204" s="34">
         <f>M204*G204</f>
         <v/>
       </c>
-      <c r="O204" s="26" t="n"/>
-      <c r="P204" s="26" t="n"/>
-      <c r="Q204" s="26" t="n"/>
-      <c r="R204" s="26" t="n"/>
-      <c r="S204" s="26" t="n"/>
+      <c r="O204" s="32" t="n"/>
+      <c r="P204" s="32" t="n"/>
+      <c r="Q204" s="32" t="n"/>
+      <c r="R204" s="32" t="n"/>
+      <c r="S204" s="32" t="n"/>
     </row>
     <row r="205">
-      <c r="A205" s="26" t="inlineStr">
+      <c r="A205" s="32" t="inlineStr">
         <is>
           <t>PACK</t>
         </is>
       </c>
-      <c r="B205" s="26" t="n"/>
-      <c r="C205" s="27" t="inlineStr">
+      <c r="B205" s="32" t="n"/>
+      <c r="C205" s="33" t="inlineStr">
         <is>
           <t>Bayou Blend Crawfish</t>
         </is>
       </c>
-      <c r="D205" s="27" t="n"/>
-      <c r="E205" s="26" t="inlineStr">
+      <c r="D205" s="33" t="n"/>
+      <c r="E205" s="32" t="inlineStr">
         <is>
           <t>5 Packs</t>
         </is>
       </c>
-      <c r="F205" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G205" s="28" t="n">
+      <c r="F205" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G205" s="34" t="n">
         <v>9.1</v>
       </c>
-      <c r="H205" s="29" t="n">
+      <c r="H205" s="35" t="n">
         <v>9.1</v>
       </c>
-      <c r="I205" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J205" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K205" s="29" t="n">
+      <c r="I205" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J205" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K205" s="35" t="n">
         <v>1.82</v>
       </c>
-      <c r="L205" s="27" t="inlineStr">
+      <c r="L205" s="33" t="inlineStr">
         <is>
           <t>per Pack (5 Packs)</t>
         </is>
       </c>
-      <c r="M205" s="26" t="n"/>
-      <c r="N205" s="28">
+      <c r="M205" s="32" t="n"/>
+      <c r="N205" s="34">
         <f>M205*G205</f>
         <v/>
       </c>
-      <c r="O205" s="26" t="n"/>
-      <c r="P205" s="26" t="n"/>
-      <c r="Q205" s="26" t="n"/>
-      <c r="R205" s="26" t="n"/>
-      <c r="S205" s="26" t="n"/>
+      <c r="O205" s="32" t="n"/>
+      <c r="P205" s="32" t="n"/>
+      <c r="Q205" s="32" t="n"/>
+      <c r="R205" s="32" t="n"/>
+      <c r="S205" s="32" t="n"/>
     </row>
     <row r="206">
-      <c r="A206" s="26" t="inlineStr">
+      <c r="A206" s="32" t="inlineStr">
         <is>
           <t>PACK</t>
         </is>
       </c>
-      <c r="B206" s="26" t="n"/>
-      <c r="C206" s="27" t="inlineStr">
+      <c r="B206" s="32" t="n"/>
+      <c r="C206" s="33" t="inlineStr">
         <is>
           <t>Bayou Blend Shrimp</t>
         </is>
       </c>
-      <c r="D206" s="27" t="n"/>
-      <c r="E206" s="26" t="inlineStr">
+      <c r="D206" s="33" t="n"/>
+      <c r="E206" s="32" t="inlineStr">
         <is>
           <t>5 Packs</t>
         </is>
       </c>
-      <c r="F206" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G206" s="28" t="n">
+      <c r="F206" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G206" s="34" t="n">
         <v>8.08</v>
       </c>
-      <c r="H206" s="29" t="n">
+      <c r="H206" s="35" t="n">
         <v>8.08</v>
       </c>
-      <c r="I206" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J206" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K206" s="29" t="n">
+      <c r="I206" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J206" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K206" s="35" t="n">
         <v>1.616</v>
       </c>
-      <c r="L206" s="27" t="inlineStr">
+      <c r="L206" s="33" t="inlineStr">
         <is>
           <t>per Pack (5 Packs)</t>
         </is>
       </c>
-      <c r="M206" s="26" t="n"/>
-      <c r="N206" s="28">
+      <c r="M206" s="32" t="n"/>
+      <c r="N206" s="34">
         <f>M206*G206</f>
         <v/>
       </c>
-      <c r="O206" s="26" t="n"/>
-      <c r="P206" s="26" t="n"/>
-      <c r="Q206" s="26" t="n"/>
-      <c r="R206" s="26" t="n"/>
-      <c r="S206" s="26" t="n"/>
+      <c r="O206" s="32" t="n"/>
+      <c r="P206" s="32" t="n"/>
+      <c r="Q206" s="32" t="n"/>
+      <c r="R206" s="32" t="n"/>
+      <c r="S206" s="32" t="n"/>
     </row>
     <row r="207">
-      <c r="A207" s="26" t="inlineStr">
+      <c r="A207" s="32" t="inlineStr">
         <is>
           <t>CAN</t>
         </is>
       </c>
-      <c r="B207" s="26" t="n"/>
-      <c r="C207" s="27" t="inlineStr">
+      <c r="B207" s="32" t="n"/>
+      <c r="C207" s="33" t="inlineStr">
         <is>
           <t>Peanuts Regular/Cajun</t>
         </is>
       </c>
-      <c r="D207" s="27" t="n"/>
-      <c r="E207" s="26" t="inlineStr">
+      <c r="D207" s="33" t="n"/>
+      <c r="E207" s="32" t="inlineStr">
         <is>
           <t>6 Cans</t>
         </is>
       </c>
-      <c r="F207" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G207" s="28" t="n">
+      <c r="F207" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G207" s="34" t="n">
         <v>8.33</v>
       </c>
-      <c r="H207" s="29" t="n">
+      <c r="H207" s="35" t="n">
         <v>8.33</v>
       </c>
-      <c r="I207" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J207" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K207" s="29" t="n">
+      <c r="I207" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J207" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K207" s="35" t="n">
         <v>1.388333333333333</v>
       </c>
-      <c r="L207" s="27" t="inlineStr">
+      <c r="L207" s="33" t="inlineStr">
         <is>
           <t>per Can (6 Cans)</t>
         </is>
       </c>
-      <c r="M207" s="26" t="n"/>
-      <c r="N207" s="28">
+      <c r="M207" s="32" t="n"/>
+      <c r="N207" s="34">
         <f>M207*G207</f>
         <v/>
       </c>
-      <c r="O207" s="26" t="n"/>
-      <c r="P207" s="26" t="n"/>
-      <c r="Q207" s="26" t="n"/>
-      <c r="R207" s="26" t="n"/>
-      <c r="S207" s="26" t="n"/>
+      <c r="O207" s="32" t="n"/>
+      <c r="P207" s="32" t="n"/>
+      <c r="Q207" s="32" t="n"/>
+      <c r="R207" s="32" t="n"/>
+      <c r="S207" s="32" t="n"/>
     </row>
     <row r="208">
-      <c r="A208" s="26" t="inlineStr">
+      <c r="A208" s="32" t="inlineStr">
         <is>
           <t>SLEEVE</t>
         </is>
       </c>
-      <c r="B208" s="26" t="n"/>
-      <c r="C208" s="27" t="inlineStr">
+      <c r="B208" s="32" t="n"/>
+      <c r="C208" s="33" t="inlineStr">
         <is>
           <t>16oz Peanut Cup</t>
         </is>
       </c>
-      <c r="D208" s="27" t="n"/>
-      <c r="E208" s="26" t="inlineStr">
+      <c r="D208" s="33" t="n"/>
+      <c r="E208" s="32" t="inlineStr">
         <is>
           <t>20 Sleeves</t>
         </is>
       </c>
-      <c r="F208" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G208" s="28" t="n">
+      <c r="F208" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G208" s="34" t="n">
         <v>8.01</v>
       </c>
-      <c r="H208" s="29" t="n">
+      <c r="H208" s="35" t="n">
         <v>8.01</v>
       </c>
-      <c r="I208" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J208" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K208" s="29" t="n">
+      <c r="I208" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J208" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K208" s="35" t="n">
         <v>0.4005</v>
       </c>
-      <c r="L208" s="27" t="inlineStr">
+      <c r="L208" s="33" t="inlineStr">
         <is>
           <t>per Sleeve (20 Sleeves)</t>
         </is>
       </c>
-      <c r="M208" s="26" t="n"/>
-      <c r="N208" s="28">
+      <c r="M208" s="32" t="n"/>
+      <c r="N208" s="34">
         <f>M208*G208</f>
         <v/>
       </c>
-      <c r="O208" s="26" t="n"/>
-      <c r="P208" s="26" t="n"/>
-      <c r="Q208" s="26" t="n"/>
-      <c r="R208" s="26" t="n"/>
-      <c r="S208" s="26" t="n"/>
+      <c r="O208" s="32" t="n"/>
+      <c r="P208" s="32" t="n"/>
+      <c r="Q208" s="32" t="n"/>
+      <c r="R208" s="32" t="n"/>
+      <c r="S208" s="32" t="n"/>
     </row>
     <row r="209">
-      <c r="A209" s="26" t="inlineStr">
+      <c r="A209" s="32" t="inlineStr">
         <is>
           <t>SLEEVE</t>
         </is>
       </c>
-      <c r="B209" s="26" t="n"/>
-      <c r="C209" s="27" t="inlineStr">
+      <c r="B209" s="32" t="n"/>
+      <c r="C209" s="33" t="inlineStr">
         <is>
           <t>32oz Peanut Cup</t>
         </is>
       </c>
-      <c r="D209" s="27" t="n"/>
-      <c r="E209" s="26" t="inlineStr">
+      <c r="D209" s="33" t="n"/>
+      <c r="E209" s="32" t="inlineStr">
         <is>
           <t>20 Sleeves</t>
         </is>
       </c>
-      <c r="F209" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G209" s="28" t="n">
+      <c r="F209" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G209" s="34" t="n">
         <v>10.22</v>
       </c>
-      <c r="H209" s="29" t="n">
+      <c r="H209" s="35" t="n">
         <v>10.22</v>
       </c>
-      <c r="I209" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J209" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K209" s="29" t="n">
+      <c r="I209" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J209" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K209" s="35" t="n">
         <v>0.511</v>
       </c>
-      <c r="L209" s="27" t="inlineStr">
+      <c r="L209" s="33" t="inlineStr">
         <is>
           <t>per Sleeve (20 Sleeves)</t>
         </is>
       </c>
-      <c r="M209" s="26" t="n"/>
-      <c r="N209" s="28">
+      <c r="M209" s="32" t="n"/>
+      <c r="N209" s="34">
         <f>M209*G209</f>
         <v/>
       </c>
-      <c r="O209" s="26" t="n"/>
-      <c r="P209" s="26" t="n"/>
-      <c r="Q209" s="26" t="n"/>
-      <c r="R209" s="26" t="n"/>
-      <c r="S209" s="26" t="n"/>
+      <c r="O209" s="32" t="n"/>
+      <c r="P209" s="32" t="n"/>
+      <c r="Q209" s="32" t="n"/>
+      <c r="R209" s="32" t="n"/>
+      <c r="S209" s="32" t="n"/>
     </row>
     <row r="210">
-      <c r="A210" s="26" t="inlineStr">
+      <c r="A210" s="32" t="inlineStr">
         <is>
           <t>SLEEVE</t>
         </is>
       </c>
-      <c r="B210" s="26" t="n"/>
-      <c r="C210" s="27" t="inlineStr">
+      <c r="B210" s="32" t="n"/>
+      <c r="C210" s="33" t="inlineStr">
         <is>
           <t>Peanut Cup Lid</t>
         </is>
       </c>
-      <c r="D210" s="27" t="n"/>
-      <c r="E210" s="26" t="inlineStr">
+      <c r="D210" s="33" t="n"/>
+      <c r="E210" s="32" t="inlineStr">
         <is>
           <t>10 Sleeves</t>
         </is>
       </c>
-      <c r="F210" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G210" s="28" t="n">
+      <c r="F210" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G210" s="34" t="n">
         <v>5.01</v>
       </c>
-      <c r="H210" s="29" t="n">
+      <c r="H210" s="35" t="n">
         <v>5.01</v>
       </c>
-      <c r="I210" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J210" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K210" s="29" t="n">
+      <c r="I210" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J210" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K210" s="35" t="n">
         <v>0.501</v>
       </c>
-      <c r="L210" s="27" t="inlineStr">
+      <c r="L210" s="33" t="inlineStr">
         <is>
           <t>per Sleeve (10 Sleeves)</t>
         </is>
       </c>
-      <c r="M210" s="26" t="n"/>
-      <c r="N210" s="28">
+      <c r="M210" s="32" t="n"/>
+      <c r="N210" s="34">
         <f>M210*G210</f>
         <v/>
       </c>
-      <c r="O210" s="26" t="n"/>
-      <c r="P210" s="26" t="n"/>
-      <c r="Q210" s="26" t="n"/>
-      <c r="R210" s="26" t="n"/>
-      <c r="S210" s="26" t="n"/>
+      <c r="O210" s="32" t="n"/>
+      <c r="P210" s="32" t="n"/>
+      <c r="Q210" s="32" t="n"/>
+      <c r="R210" s="32" t="n"/>
+      <c r="S210" s="32" t="n"/>
     </row>
     <row r="211">
-      <c r="A211" s="26" t="inlineStr">
+      <c r="A211" s="32" t="inlineStr">
         <is>
           <t>BAG</t>
         </is>
       </c>
-      <c r="B211" s="26" t="n"/>
-      <c r="C211" s="27" t="inlineStr">
+      <c r="B211" s="32" t="n"/>
+      <c r="C211" s="33" t="inlineStr">
         <is>
           <t>Gizzards</t>
         </is>
       </c>
-      <c r="D211" s="27" t="n"/>
-      <c r="E211" s="26" t="inlineStr">
+      <c r="D211" s="33" t="n"/>
+      <c r="E211" s="32" t="inlineStr">
         <is>
           <t>4/Box</t>
         </is>
       </c>
-      <c r="F211" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G211" s="28" t="n">
+      <c r="F211" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G211" s="34" t="n">
         <v>19.8</v>
       </c>
-      <c r="H211" s="29" t="n">
+      <c r="H211" s="35" t="n">
         <v>19.8</v>
       </c>
-      <c r="I211" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J211" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K211" s="29" t="n">
+      <c r="I211" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J211" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K211" s="35" t="n">
         <v>4.95</v>
       </c>
-      <c r="L211" s="27" t="inlineStr">
+      <c r="L211" s="33" t="inlineStr">
         <is>
           <t>per Bag (4/Box)</t>
         </is>
       </c>
-      <c r="M211" s="26" t="n"/>
-      <c r="N211" s="28">
+      <c r="M211" s="32" t="n"/>
+      <c r="N211" s="34">
         <f>M211*G211</f>
         <v/>
       </c>
-      <c r="O211" s="26" t="n"/>
-      <c r="P211" s="26" t="n"/>
-      <c r="Q211" s="26" t="n"/>
-      <c r="R211" s="26" t="n"/>
-      <c r="S211" s="26" t="n"/>
+      <c r="O211" s="32" t="n"/>
+      <c r="P211" s="32" t="n"/>
+      <c r="Q211" s="32" t="n"/>
+      <c r="R211" s="32" t="n"/>
+      <c r="S211" s="32" t="n"/>
     </row>
     <row r="212">
-      <c r="A212" s="26" t="inlineStr">
+      <c r="A212" s="32" t="inlineStr">
         <is>
           <t>BAG</t>
         </is>
       </c>
-      <c r="B212" s="26" t="n"/>
-      <c r="C212" s="27" t="inlineStr">
+      <c r="B212" s="32" t="n"/>
+      <c r="C212" s="33" t="inlineStr">
         <is>
           <t>Livers</t>
         </is>
       </c>
-      <c r="D212" s="27" t="n"/>
-      <c r="E212" s="26" t="inlineStr">
+      <c r="D212" s="33" t="n"/>
+      <c r="E212" s="32" t="inlineStr">
         <is>
           <t>4/Box</t>
         </is>
       </c>
-      <c r="F212" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G212" s="28" t="n">
+      <c r="F212" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G212" s="34" t="n">
         <v>14.78</v>
       </c>
-      <c r="H212" s="29" t="n">
+      <c r="H212" s="35" t="n">
         <v>14.78</v>
       </c>
-      <c r="I212" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J212" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K212" s="29" t="n">
+      <c r="I212" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J212" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K212" s="35" t="n">
         <v>3.695</v>
       </c>
-      <c r="L212" s="27" t="inlineStr">
+      <c r="L212" s="33" t="inlineStr">
         <is>
           <t>per Bag (4/Box)</t>
         </is>
       </c>
-      <c r="M212" s="26" t="n"/>
-      <c r="N212" s="28">
+      <c r="M212" s="32" t="n"/>
+      <c r="N212" s="34">
         <f>M212*G212</f>
         <v/>
       </c>
-      <c r="O212" s="26" t="n"/>
-      <c r="P212" s="26" t="n"/>
-      <c r="Q212" s="26" t="n"/>
-      <c r="R212" s="26" t="n"/>
-      <c r="S212" s="26" t="n"/>
+      <c r="O212" s="32" t="n"/>
+      <c r="P212" s="32" t="n"/>
+      <c r="Q212" s="32" t="n"/>
+      <c r="R212" s="32" t="n"/>
+      <c r="S212" s="32" t="n"/>
     </row>
     <row r="213">
-      <c r="A213" s="26" t="inlineStr">
+      <c r="A213" s="32" t="inlineStr">
         <is>
           <t>BAG</t>
         </is>
       </c>
-      <c r="B213" s="26" t="n"/>
-      <c r="C213" s="27" t="inlineStr">
+      <c r="B213" s="32" t="n"/>
+      <c r="C213" s="33" t="inlineStr">
         <is>
           <t>Brisket</t>
         </is>
       </c>
-      <c r="D213" s="27" t="n"/>
-      <c r="E213" s="26" t="n"/>
-      <c r="F213" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G213" s="28" t="n">
+      <c r="D213" s="33" t="n"/>
+      <c r="E213" s="32" t="n"/>
+      <c r="F213" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G213" s="34" t="n">
         <v>29.44</v>
       </c>
-      <c r="H213" s="29" t="n">
+      <c r="H213" s="35" t="n">
         <v>29.44</v>
       </c>
-      <c r="I213" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J213" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K213" s="29" t="n">
+      <c r="I213" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J213" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K213" s="35" t="n">
         <v>29.44</v>
       </c>
-      <c r="L213" s="27" t="inlineStr">
+      <c r="L213" s="33" t="inlineStr">
         <is>
           <t>per Bag (None)</t>
         </is>
       </c>
-      <c r="M213" s="26" t="n"/>
-      <c r="N213" s="28">
+      <c r="M213" s="32" t="n"/>
+      <c r="N213" s="34">
         <f>M213*G213</f>
         <v/>
       </c>
-      <c r="O213" s="26" t="n"/>
-      <c r="P213" s="26" t="n"/>
-      <c r="Q213" s="26" t="n"/>
-      <c r="R213" s="26" t="n"/>
-      <c r="S213" s="26" t="n"/>
+      <c r="O213" s="32" t="n"/>
+      <c r="P213" s="32" t="n"/>
+      <c r="Q213" s="32" t="n"/>
+      <c r="R213" s="32" t="n"/>
+      <c r="S213" s="32" t="n"/>
     </row>
     <row r="214">
-      <c r="A214" s="26" t="inlineStr">
+      <c r="A214" s="32" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="B214" s="26" t="n"/>
-      <c r="C214" s="27" t="inlineStr">
+      <c r="B214" s="32" t="n"/>
+      <c r="C214" s="33" t="inlineStr">
         <is>
           <t>Kolache Boudin Link Org</t>
         </is>
       </c>
-      <c r="D214" s="27" t="n"/>
-      <c r="E214" s="26" t="n"/>
-      <c r="F214" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G214" s="28" t="n">
+      <c r="D214" s="33" t="n"/>
+      <c r="E214" s="32" t="n"/>
+      <c r="F214" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G214" s="34" t="n">
         <v>69.77</v>
       </c>
-      <c r="H214" s="29" t="n">
+      <c r="H214" s="35" t="n">
         <v>69.77</v>
       </c>
-      <c r="I214" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J214" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K214" s="29" t="n">
+      <c r="I214" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J214" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K214" s="35" t="n">
         <v>69.77</v>
       </c>
-      <c r="L214" s="27" t="inlineStr">
+      <c r="L214" s="33" t="inlineStr">
         <is>
           <t>per Case (None)</t>
         </is>
       </c>
-      <c r="M214" s="26" t="n"/>
-      <c r="N214" s="28">
+      <c r="M214" s="32" t="n"/>
+      <c r="N214" s="34">
         <f>M214*G214</f>
         <v/>
       </c>
-      <c r="O214" s="26" t="n"/>
-      <c r="P214" s="26" t="n"/>
-      <c r="Q214" s="26" t="n"/>
-      <c r="R214" s="26" t="n"/>
-      <c r="S214" s="26" t="n"/>
+      <c r="O214" s="32" t="n"/>
+      <c r="P214" s="32" t="n"/>
+      <c r="Q214" s="32" t="n"/>
+      <c r="R214" s="32" t="n"/>
+      <c r="S214" s="32" t="n"/>
     </row>
     <row r="215">
-      <c r="A215" s="26" t="inlineStr">
+      <c r="A215" s="32" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="B215" s="26" t="n"/>
-      <c r="C215" s="27" t="inlineStr">
+      <c r="B215" s="32" t="n"/>
+      <c r="C215" s="33" t="inlineStr">
         <is>
           <t>Kolache Sausage Egg &amp; Cheese</t>
         </is>
       </c>
-      <c r="D215" s="27" t="n"/>
-      <c r="E215" s="26" t="n"/>
-      <c r="F215" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G215" s="28" t="n">
+      <c r="D215" s="33" t="n"/>
+      <c r="E215" s="32" t="n"/>
+      <c r="F215" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G215" s="34" t="n">
         <v>69.77</v>
       </c>
-      <c r="H215" s="29" t="n">
+      <c r="H215" s="35" t="n">
         <v>69.77</v>
       </c>
-      <c r="I215" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J215" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K215" s="29" t="n">
+      <c r="I215" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J215" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K215" s="35" t="n">
         <v>69.77</v>
       </c>
-      <c r="L215" s="27" t="inlineStr">
+      <c r="L215" s="33" t="inlineStr">
         <is>
           <t>per Case (None)</t>
         </is>
       </c>
-      <c r="M215" s="26" t="n"/>
-      <c r="N215" s="28">
+      <c r="M215" s="32" t="n"/>
+      <c r="N215" s="34">
         <f>M215*G215</f>
         <v/>
       </c>
-      <c r="O215" s="26" t="n"/>
-      <c r="P215" s="26" t="n"/>
-      <c r="Q215" s="26" t="n"/>
-      <c r="R215" s="26" t="n"/>
-      <c r="S215" s="26" t="n"/>
+      <c r="O215" s="32" t="n"/>
+      <c r="P215" s="32" t="n"/>
+      <c r="Q215" s="32" t="n"/>
+      <c r="R215" s="32" t="n"/>
+      <c r="S215" s="32" t="n"/>
     </row>
     <row r="216">
-      <c r="A216" s="26" t="inlineStr">
+      <c r="A216" s="32" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="B216" s="26" t="n"/>
-      <c r="C216" s="27" t="inlineStr">
+      <c r="B216" s="32" t="n"/>
+      <c r="C216" s="33" t="inlineStr">
         <is>
           <t>Wrap Jalapeno Popper</t>
         </is>
       </c>
-      <c r="D216" s="27" t="n"/>
-      <c r="E216" s="26" t="n"/>
-      <c r="F216" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G216" s="28" t="n">
+      <c r="D216" s="33" t="n"/>
+      <c r="E216" s="32" t="n"/>
+      <c r="F216" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G216" s="34" t="n">
         <v>93.03</v>
       </c>
-      <c r="H216" s="29" t="n">
+      <c r="H216" s="35" t="n">
         <v>93.03</v>
       </c>
-      <c r="I216" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J216" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K216" s="29" t="n">
+      <c r="I216" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J216" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K216" s="35" t="n">
         <v>93.03</v>
       </c>
-      <c r="L216" s="27" t="inlineStr">
+      <c r="L216" s="33" t="inlineStr">
         <is>
           <t>per Case (None)</t>
         </is>
       </c>
-      <c r="M216" s="26" t="n"/>
-      <c r="N216" s="28">
+      <c r="M216" s="32" t="n"/>
+      <c r="N216" s="34">
         <f>M216*G216</f>
         <v/>
       </c>
-      <c r="O216" s="26" t="n"/>
-      <c r="P216" s="26" t="n"/>
-      <c r="Q216" s="26" t="n"/>
-      <c r="R216" s="26" t="n"/>
-      <c r="S216" s="26" t="n"/>
+      <c r="O216" s="32" t="n"/>
+      <c r="P216" s="32" t="n"/>
+      <c r="Q216" s="32" t="n"/>
+      <c r="R216" s="32" t="n"/>
+      <c r="S216" s="32" t="n"/>
     </row>
     <row r="217">
-      <c r="A217" s="26" t="inlineStr">
+      <c r="A217" s="32" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="B217" s="26" t="n"/>
-      <c r="C217" s="27" t="inlineStr">
+      <c r="B217" s="32" t="n"/>
+      <c r="C217" s="33" t="inlineStr">
         <is>
           <t>Deer Burrito</t>
         </is>
       </c>
-      <c r="D217" s="27" t="n"/>
-      <c r="E217" s="26" t="n"/>
-      <c r="F217" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G217" s="28" t="n">
+      <c r="D217" s="33" t="n"/>
+      <c r="E217" s="32" t="n"/>
+      <c r="F217" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G217" s="34" t="n">
         <v>449</v>
       </c>
-      <c r="H217" s="29" t="n">
+      <c r="H217" s="35" t="n">
         <v>449</v>
       </c>
-      <c r="I217" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J217" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K217" s="29" t="n">
+      <c r="I217" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J217" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K217" s="35" t="n">
         <v>449</v>
       </c>
-      <c r="L217" s="27" t="inlineStr">
+      <c r="L217" s="33" t="inlineStr">
         <is>
           <t>per Case (None)</t>
         </is>
       </c>
-      <c r="M217" s="26" t="n"/>
-      <c r="N217" s="28">
+      <c r="M217" s="32" t="n"/>
+      <c r="N217" s="34">
         <f>M217*G217</f>
         <v/>
       </c>
-      <c r="O217" s="26" t="n"/>
-      <c r="P217" s="26" t="n"/>
-      <c r="Q217" s="26" t="n"/>
-      <c r="R217" s="26" t="n"/>
-      <c r="S217" s="26" t="n"/>
+      <c r="O217" s="32" t="n"/>
+      <c r="P217" s="32" t="n"/>
+      <c r="Q217" s="32" t="n"/>
+      <c r="R217" s="32" t="n"/>
+      <c r="S217" s="32" t="n"/>
     </row>
     <row r="218">
-      <c r="A218" s="26" t="inlineStr">
+      <c r="A218" s="32" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="B218" s="26" t="n"/>
-      <c r="C218" s="27" t="inlineStr">
+      <c r="B218" s="32" t="n"/>
+      <c r="C218" s="33" t="inlineStr">
         <is>
           <t>Jalapeno Cheddar Kolache</t>
         </is>
       </c>
-      <c r="D218" s="27" t="n"/>
-      <c r="E218" s="26" t="n"/>
-      <c r="F218" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G218" s="28" t="n">
+      <c r="D218" s="33" t="n"/>
+      <c r="E218" s="32" t="n"/>
+      <c r="F218" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G218" s="34" t="n">
         <v>69.77</v>
       </c>
-      <c r="H218" s="29" t="n">
+      <c r="H218" s="35" t="n">
         <v>69.77</v>
       </c>
-      <c r="I218" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J218" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K218" s="29" t="n">
+      <c r="I218" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J218" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K218" s="35" t="n">
         <v>69.77</v>
       </c>
-      <c r="L218" s="27" t="inlineStr">
+      <c r="L218" s="33" t="inlineStr">
         <is>
           <t>per Case (None)</t>
         </is>
       </c>
-      <c r="M218" s="26" t="n"/>
-      <c r="N218" s="28">
+      <c r="M218" s="32" t="n"/>
+      <c r="N218" s="34">
         <f>M218*G218</f>
         <v/>
       </c>
-      <c r="O218" s="26" t="n"/>
-      <c r="P218" s="26" t="n"/>
-      <c r="Q218" s="26" t="n"/>
-      <c r="R218" s="26" t="n"/>
-      <c r="S218" s="26" t="n"/>
+      <c r="O218" s="32" t="n"/>
+      <c r="P218" s="32" t="n"/>
+      <c r="Q218" s="32" t="n"/>
+      <c r="R218" s="32" t="n"/>
+      <c r="S218" s="32" t="n"/>
     </row>
     <row r="219">
-      <c r="A219" s="26" t="inlineStr">
+      <c r="A219" s="32" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="B219" s="26" t="n"/>
-      <c r="C219" s="27" t="inlineStr">
+      <c r="B219" s="32" t="n"/>
+      <c r="C219" s="33" t="inlineStr">
         <is>
           <t>Chicken Fajita</t>
         </is>
       </c>
-      <c r="D219" s="27" t="n"/>
-      <c r="E219" s="26" t="n"/>
-      <c r="F219" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G219" s="28" t="n">
+      <c r="D219" s="33" t="n"/>
+      <c r="E219" s="32" t="n"/>
+      <c r="F219" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G219" s="34" t="n">
         <v>57.99</v>
       </c>
-      <c r="H219" s="29" t="n">
+      <c r="H219" s="35" t="n">
         <v>57.99</v>
       </c>
-      <c r="I219" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J219" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K219" s="29" t="n">
+      <c r="I219" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J219" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K219" s="35" t="n">
         <v>57.99</v>
       </c>
-      <c r="L219" s="27" t="inlineStr">
+      <c r="L219" s="33" t="inlineStr">
         <is>
           <t>per Case (None)</t>
         </is>
       </c>
-      <c r="M219" s="26" t="n"/>
-      <c r="N219" s="28">
+      <c r="M219" s="32" t="n"/>
+      <c r="N219" s="34">
         <f>M219*G219</f>
         <v/>
       </c>
-      <c r="O219" s="26" t="n"/>
-      <c r="P219" s="26" t="n"/>
-      <c r="Q219" s="26" t="n"/>
-      <c r="R219" s="26" t="n"/>
-      <c r="S219" s="26" t="n"/>
+      <c r="O219" s="32" t="n"/>
+      <c r="P219" s="32" t="n"/>
+      <c r="Q219" s="32" t="n"/>
+      <c r="R219" s="32" t="n"/>
+      <c r="S219" s="32" t="n"/>
     </row>
     <row r="220">
-      <c r="A220" s="26" t="inlineStr">
+      <c r="A220" s="32" t="inlineStr">
         <is>
           <t>BAG</t>
         </is>
       </c>
-      <c r="B220" s="26" t="n"/>
-      <c r="C220" s="27" t="inlineStr">
+      <c r="B220" s="32" t="n"/>
+      <c r="C220" s="33" t="inlineStr">
         <is>
           <t>Mac And Cheese</t>
         </is>
       </c>
-      <c r="D220" s="27" t="n"/>
-      <c r="E220" s="26" t="inlineStr">
+      <c r="D220" s="33" t="n"/>
+      <c r="E220" s="32" t="inlineStr">
         <is>
           <t>6 Bags</t>
         </is>
       </c>
-      <c r="F220" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G220" s="28" t="n">
+      <c r="F220" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G220" s="34" t="n">
         <v>7.1</v>
       </c>
-      <c r="H220" s="29" t="n">
+      <c r="H220" s="35" t="n">
         <v>7.1</v>
       </c>
-      <c r="I220" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J220" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K220" s="29" t="n">
+      <c r="I220" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J220" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K220" s="35" t="n">
         <v>1.183333333333333</v>
       </c>
-      <c r="L220" s="27" t="inlineStr">
+      <c r="L220" s="33" t="inlineStr">
         <is>
           <t>per Bag (6 Bags)</t>
         </is>
       </c>
-      <c r="M220" s="26" t="n"/>
-      <c r="N220" s="28">
+      <c r="M220" s="32" t="n"/>
+      <c r="N220" s="34">
         <f>M220*G220</f>
         <v/>
       </c>
-      <c r="O220" s="26" t="n"/>
-      <c r="P220" s="26" t="n"/>
-      <c r="Q220" s="26" t="n"/>
-      <c r="R220" s="26" t="n"/>
-      <c r="S220" s="26" t="n"/>
+      <c r="O220" s="32" t="n"/>
+      <c r="P220" s="32" t="n"/>
+      <c r="Q220" s="32" t="n"/>
+      <c r="R220" s="32" t="n"/>
+      <c r="S220" s="32" t="n"/>
     </row>
     <row r="221">
-      <c r="A221" s="26" t="inlineStr">
+      <c r="A221" s="32" t="inlineStr">
         <is>
           <t>BAG</t>
         </is>
       </c>
-      <c r="B221" s="26" t="n"/>
-      <c r="C221" s="27" t="inlineStr">
+      <c r="B221" s="32" t="n"/>
+      <c r="C221" s="33" t="inlineStr">
         <is>
           <t>Mashed Potatoes</t>
         </is>
       </c>
-      <c r="D221" s="27" t="n"/>
-      <c r="E221" s="26" t="inlineStr">
+      <c r="D221" s="33" t="n"/>
+      <c r="E221" s="32" t="inlineStr">
         <is>
           <t>4 Bags</t>
         </is>
       </c>
-      <c r="F221" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G221" s="28" t="n">
+      <c r="F221" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G221" s="34" t="n">
         <v>9.640000000000001</v>
       </c>
-      <c r="H221" s="29" t="n">
+      <c r="H221" s="35" t="n">
         <v>9.640000000000001</v>
       </c>
-      <c r="I221" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J221" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K221" s="29" t="n">
+      <c r="I221" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J221" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K221" s="35" t="n">
         <v>2.41</v>
       </c>
-      <c r="L221" s="27" t="inlineStr">
+      <c r="L221" s="33" t="inlineStr">
         <is>
           <t>per Bag (4 Bags)</t>
         </is>
       </c>
-      <c r="M221" s="26" t="n"/>
-      <c r="N221" s="28">
+      <c r="M221" s="32" t="n"/>
+      <c r="N221" s="34">
         <f>M221*G221</f>
         <v/>
       </c>
-      <c r="O221" s="26" t="n"/>
-      <c r="P221" s="26" t="n"/>
-      <c r="Q221" s="26" t="n"/>
-      <c r="R221" s="26" t="n"/>
-      <c r="S221" s="26" t="n"/>
+      <c r="O221" s="32" t="n"/>
+      <c r="P221" s="32" t="n"/>
+      <c r="Q221" s="32" t="n"/>
+      <c r="R221" s="32" t="n"/>
+      <c r="S221" s="32" t="n"/>
     </row>
     <row r="222">
-      <c r="A222" s="26" t="inlineStr">
+      <c r="A222" s="32" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="B222" s="26" t="n"/>
-      <c r="C222" s="27" t="inlineStr">
+      <c r="B222" s="32" t="n"/>
+      <c r="C222" s="33" t="inlineStr">
         <is>
           <t>Mini Taco Beef</t>
         </is>
       </c>
-      <c r="D222" s="27" t="n"/>
-      <c r="E222" s="26" t="inlineStr">
+      <c r="D222" s="33" t="n"/>
+      <c r="E222" s="32" t="inlineStr">
         <is>
           <t>case</t>
         </is>
       </c>
-      <c r="F222" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G222" s="28" t="n">
+      <c r="F222" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G222" s="34" t="n">
         <v>27.91</v>
       </c>
-      <c r="H222" s="29" t="n">
+      <c r="H222" s="35" t="n">
         <v>27.91</v>
       </c>
-      <c r="I222" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J222" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K222" s="29" t="n">
+      <c r="I222" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J222" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K222" s="35" t="n">
         <v>27.91</v>
       </c>
-      <c r="L222" s="27" t="inlineStr">
+      <c r="L222" s="33" t="inlineStr">
         <is>
           <t>per Case (case)</t>
         </is>
       </c>
-      <c r="M222" s="26" t="n"/>
-      <c r="N222" s="28">
+      <c r="M222" s="32" t="n"/>
+      <c r="N222" s="34">
         <f>M222*G222</f>
         <v/>
       </c>
-      <c r="O222" s="26" t="n"/>
-      <c r="P222" s="26" t="n"/>
-      <c r="Q222" s="26" t="n"/>
-      <c r="R222" s="26" t="n"/>
-      <c r="S222" s="26" t="n"/>
+      <c r="O222" s="32" t="n"/>
+      <c r="P222" s="32" t="n"/>
+      <c r="Q222" s="32" t="n"/>
+      <c r="R222" s="32" t="n"/>
+      <c r="S222" s="32" t="n"/>
     </row>
     <row r="223">
-      <c r="A223" s="26" t="inlineStr">
+      <c r="A223" s="32" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="B223" s="26" t="n"/>
-      <c r="C223" s="27" t="inlineStr">
+      <c r="B223" s="32" t="n"/>
+      <c r="C223" s="33" t="inlineStr">
         <is>
           <t>Mini Taco Chicken</t>
         </is>
       </c>
-      <c r="D223" s="27" t="n"/>
-      <c r="E223" s="26" t="inlineStr">
+      <c r="D223" s="33" t="n"/>
+      <c r="E223" s="32" t="inlineStr">
         <is>
           <t>case</t>
         </is>
       </c>
-      <c r="F223" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G223" s="28" t="n">
+      <c r="F223" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G223" s="34" t="n">
         <v>27.91</v>
       </c>
-      <c r="H223" s="29" t="n">
+      <c r="H223" s="35" t="n">
         <v>27.91</v>
       </c>
-      <c r="I223" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J223" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K223" s="29" t="n">
+      <c r="I223" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J223" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K223" s="35" t="n">
         <v>27.91</v>
       </c>
-      <c r="L223" s="27" t="inlineStr">
+      <c r="L223" s="33" t="inlineStr">
         <is>
           <t>per Case (case)</t>
         </is>
       </c>
-      <c r="M223" s="26" t="n"/>
-      <c r="N223" s="28">
+      <c r="M223" s="32" t="n"/>
+      <c r="N223" s="34">
         <f>M223*G223</f>
         <v/>
       </c>
-      <c r="O223" s="26" t="n"/>
-      <c r="P223" s="26" t="n"/>
-      <c r="Q223" s="26" t="n"/>
-      <c r="R223" s="26" t="n"/>
-      <c r="S223" s="26" t="n"/>
+      <c r="O223" s="32" t="n"/>
+      <c r="P223" s="32" t="n"/>
+      <c r="Q223" s="32" t="n"/>
+      <c r="R223" s="32" t="n"/>
+      <c r="S223" s="32" t="n"/>
     </row>
     <row r="224">
-      <c r="A224" s="26" t="inlineStr">
+      <c r="A224" s="32" t="inlineStr">
         <is>
           <t>BAG</t>
         </is>
       </c>
-      <c r="B224" s="26" t="n"/>
-      <c r="C224" s="27" t="inlineStr">
+      <c r="B224" s="32" t="n"/>
+      <c r="C224" s="33" t="inlineStr">
         <is>
           <t>Red Beans</t>
         </is>
       </c>
-      <c r="D224" s="27" t="n"/>
-      <c r="E224" s="26" t="inlineStr">
+      <c r="D224" s="33" t="n"/>
+      <c r="E224" s="32" t="inlineStr">
         <is>
           <t>9 Bags</t>
         </is>
       </c>
-      <c r="F224" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G224" s="28" t="n">
+      <c r="F224" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G224" s="34" t="n">
         <v>6.49</v>
       </c>
-      <c r="H224" s="29" t="n">
+      <c r="H224" s="35" t="n">
         <v>6.49</v>
       </c>
-      <c r="I224" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J224" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K224" s="29" t="n">
+      <c r="I224" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J224" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K224" s="35" t="n">
         <v>0.7211111111111111</v>
       </c>
-      <c r="L224" s="27" t="inlineStr">
+      <c r="L224" s="33" t="inlineStr">
         <is>
           <t>per Bag (9 Bags)</t>
         </is>
       </c>
-      <c r="M224" s="26" t="n"/>
-      <c r="N224" s="28">
+      <c r="M224" s="32" t="n"/>
+      <c r="N224" s="34">
         <f>M224*G224</f>
         <v/>
       </c>
-      <c r="O224" s="26" t="n"/>
-      <c r="P224" s="26" t="n"/>
-      <c r="Q224" s="26" t="n"/>
-      <c r="R224" s="26" t="n"/>
-      <c r="S224" s="26" t="n"/>
+      <c r="O224" s="32" t="n"/>
+      <c r="P224" s="32" t="n"/>
+      <c r="Q224" s="32" t="n"/>
+      <c r="R224" s="32" t="n"/>
+      <c r="S224" s="32" t="n"/>
     </row>
     <row r="225">
-      <c r="A225" s="26" t="inlineStr">
+      <c r="A225" s="32" t="inlineStr">
         <is>
           <t>PACK</t>
         </is>
       </c>
-      <c r="B225" s="26" t="n"/>
-      <c r="C225" s="27" t="inlineStr">
+      <c r="B225" s="32" t="n"/>
+      <c r="C225" s="33" t="inlineStr">
         <is>
           <t>Beef Sausage Dogs</t>
         </is>
       </c>
-      <c r="D225" s="27" t="n"/>
-      <c r="E225" s="26" t="n"/>
-      <c r="F225" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G225" s="28" t="n">
+      <c r="D225" s="33" t="n"/>
+      <c r="E225" s="32" t="n"/>
+      <c r="F225" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G225" s="34" t="n">
         <v>20.34</v>
       </c>
-      <c r="H225" s="29" t="n">
+      <c r="H225" s="35" t="n">
         <v>20.34</v>
       </c>
-      <c r="I225" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J225" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K225" s="29" t="n">
+      <c r="I225" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J225" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K225" s="35" t="n">
         <v>20.34</v>
       </c>
-      <c r="L225" s="27" t="inlineStr">
+      <c r="L225" s="33" t="inlineStr">
         <is>
           <t>per Pack (None)</t>
         </is>
       </c>
-      <c r="M225" s="26" t="n"/>
-      <c r="N225" s="28">
+      <c r="M225" s="32" t="n"/>
+      <c r="N225" s="34">
         <f>M225*G225</f>
         <v/>
       </c>
-      <c r="O225" s="26" t="n"/>
-      <c r="P225" s="26" t="n"/>
-      <c r="Q225" s="26" t="n"/>
-      <c r="R225" s="26" t="n"/>
-      <c r="S225" s="26" t="n"/>
+      <c r="O225" s="32" t="n"/>
+      <c r="P225" s="32" t="n"/>
+      <c r="Q225" s="32" t="n"/>
+      <c r="R225" s="32" t="n"/>
+      <c r="S225" s="32" t="n"/>
     </row>
     <row r="226">
-      <c r="A226" s="26" t="inlineStr">
+      <c r="A226" s="32" t="inlineStr">
         <is>
           <t>BAG</t>
         </is>
       </c>
-      <c r="B226" s="26" t="n"/>
-      <c r="C226" s="27" t="inlineStr">
+      <c r="B226" s="32" t="n"/>
+      <c r="C226" s="33" t="inlineStr">
         <is>
           <t>Seasoned Corn</t>
         </is>
       </c>
-      <c r="D226" s="27" t="n"/>
-      <c r="E226" s="26" t="inlineStr">
+      <c r="D226" s="33" t="n"/>
+      <c r="E226" s="32" t="inlineStr">
         <is>
           <t>6 Bags</t>
         </is>
       </c>
-      <c r="F226" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G226" s="28" t="n">
+      <c r="F226" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G226" s="34" t="n">
         <v>6.18</v>
       </c>
-      <c r="H226" s="29" t="n">
+      <c r="H226" s="35" t="n">
         <v>6.18</v>
       </c>
-      <c r="I226" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J226" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K226" s="29" t="n">
+      <c r="I226" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J226" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K226" s="35" t="n">
         <v>1.03</v>
       </c>
-      <c r="L226" s="27" t="inlineStr">
+      <c r="L226" s="33" t="inlineStr">
         <is>
           <t>per Bag (6 Bags)</t>
         </is>
       </c>
-      <c r="M226" s="26" t="n"/>
-      <c r="N226" s="28">
+      <c r="M226" s="32" t="n"/>
+      <c r="N226" s="34">
         <f>M226*G226</f>
         <v/>
       </c>
-      <c r="O226" s="26" t="n"/>
-      <c r="P226" s="26" t="n"/>
-      <c r="Q226" s="26" t="n"/>
-      <c r="R226" s="26" t="n"/>
-      <c r="S226" s="26" t="n"/>
+      <c r="O226" s="32" t="n"/>
+      <c r="P226" s="32" t="n"/>
+      <c r="Q226" s="32" t="n"/>
+      <c r="R226" s="32" t="n"/>
+      <c r="S226" s="32" t="n"/>
     </row>
     <row r="227">
-      <c r="A227" s="26" t="inlineStr">
+      <c r="A227" s="32" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="B227" s="26" t="n"/>
-      <c r="C227" s="27" t="inlineStr">
+      <c r="B227" s="32" t="n"/>
+      <c r="C227" s="33" t="inlineStr">
         <is>
           <t>Stuffed Nacho</t>
         </is>
       </c>
-      <c r="D227" s="27" t="n"/>
-      <c r="E227" s="26" t="inlineStr">
+      <c r="D227" s="33" t="n"/>
+      <c r="E227" s="32" t="inlineStr">
         <is>
           <t>case</t>
         </is>
       </c>
-      <c r="F227" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G227" s="28" t="n">
+      <c r="F227" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G227" s="34" t="n">
         <v>37.28</v>
       </c>
-      <c r="H227" s="29" t="n">
+      <c r="H227" s="35" t="n">
         <v>37.28</v>
       </c>
-      <c r="I227" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J227" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K227" s="29" t="n">
+      <c r="I227" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J227" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K227" s="35" t="n">
         <v>37.28</v>
       </c>
-      <c r="L227" s="27" t="inlineStr">
+      <c r="L227" s="33" t="inlineStr">
         <is>
           <t>per Case (case)</t>
         </is>
       </c>
-      <c r="M227" s="26" t="n"/>
-      <c r="N227" s="28">
+      <c r="M227" s="32" t="n"/>
+      <c r="N227" s="34">
         <f>M227*G227</f>
         <v/>
       </c>
-      <c r="O227" s="26" t="n"/>
-      <c r="P227" s="26" t="n"/>
-      <c r="Q227" s="26" t="n"/>
-      <c r="R227" s="26" t="n"/>
-      <c r="S227" s="26" t="n"/>
+      <c r="O227" s="32" t="n"/>
+      <c r="P227" s="32" t="n"/>
+      <c r="Q227" s="32" t="n"/>
+      <c r="R227" s="32" t="n"/>
+      <c r="S227" s="32" t="n"/>
     </row>
     <row r="228">
-      <c r="A228" s="26" t="inlineStr">
+      <c r="A228" s="32" t="inlineStr">
         <is>
           <t>BAG</t>
         </is>
       </c>
-      <c r="B228" s="26" t="n"/>
-      <c r="C228" s="27" t="inlineStr">
+      <c r="B228" s="32" t="n"/>
+      <c r="C228" s="33" t="inlineStr">
         <is>
           <t>Tomato Gravy</t>
         </is>
       </c>
-      <c r="D228" s="27" t="n"/>
-      <c r="E228" s="26" t="inlineStr">
+      <c r="D228" s="33" t="n"/>
+      <c r="E228" s="32" t="inlineStr">
         <is>
           <t>4 bags</t>
         </is>
       </c>
-      <c r="F228" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G228" s="28" t="n">
+      <c r="F228" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G228" s="34" t="n">
         <v>12.34</v>
       </c>
-      <c r="H228" s="29" t="n">
+      <c r="H228" s="35" t="n">
         <v>12.34</v>
       </c>
-      <c r="I228" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J228" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K228" s="29" t="n">
+      <c r="I228" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J228" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K228" s="35" t="n">
         <v>3.085</v>
       </c>
-      <c r="L228" s="27" t="inlineStr">
+      <c r="L228" s="33" t="inlineStr">
         <is>
           <t>per Bag (4 bags)</t>
         </is>
       </c>
-      <c r="M228" s="26" t="n"/>
-      <c r="N228" s="28">
+      <c r="M228" s="32" t="n"/>
+      <c r="N228" s="34">
         <f>M228*G228</f>
         <v/>
       </c>
-      <c r="O228" s="26" t="n"/>
-      <c r="P228" s="26" t="n"/>
-      <c r="Q228" s="26" t="n"/>
-      <c r="R228" s="26" t="n"/>
-      <c r="S228" s="26" t="n"/>
+      <c r="O228" s="32" t="n"/>
+      <c r="P228" s="32" t="n"/>
+      <c r="Q228" s="32" t="n"/>
+      <c r="R228" s="32" t="n"/>
+      <c r="S228" s="32" t="n"/>
     </row>
     <row r="229">
-      <c r="A229" s="26" t="inlineStr">
+      <c r="A229" s="32" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="B229" s="26" t="n"/>
-      <c r="C229" s="27" t="inlineStr">
+      <c r="B229" s="32" t="n"/>
+      <c r="C229" s="33" t="inlineStr">
         <is>
           <t>Spicy Chicken Patty</t>
         </is>
       </c>
-      <c r="D229" s="27" t="n"/>
-      <c r="E229" s="26" t="n"/>
-      <c r="F229" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G229" s="28" t="n">
+      <c r="D229" s="33" t="n"/>
+      <c r="E229" s="32" t="n"/>
+      <c r="F229" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G229" s="34" t="n">
         <v>52.87</v>
       </c>
-      <c r="H229" s="29" t="n">
+      <c r="H229" s="35" t="n">
         <v>52.87</v>
       </c>
-      <c r="I229" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J229" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K229" s="29" t="n">
+      <c r="I229" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J229" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K229" s="35" t="n">
         <v>52.87</v>
       </c>
-      <c r="L229" s="27" t="inlineStr">
+      <c r="L229" s="33" t="inlineStr">
         <is>
           <t>per Case (None)</t>
         </is>
       </c>
-      <c r="M229" s="26" t="n"/>
-      <c r="N229" s="28">
+      <c r="M229" s="32" t="n"/>
+      <c r="N229" s="34">
         <f>M229*G229</f>
         <v/>
       </c>
-      <c r="O229" s="26" t="n"/>
-      <c r="P229" s="26" t="n"/>
-      <c r="Q229" s="26" t="n"/>
-      <c r="R229" s="26" t="n"/>
-      <c r="S229" s="26" t="n"/>
+      <c r="O229" s="32" t="n"/>
+      <c r="P229" s="32" t="n"/>
+      <c r="Q229" s="32" t="n"/>
+      <c r="R229" s="32" t="n"/>
+      <c r="S229" s="32" t="n"/>
     </row>
     <row r="230">
-      <c r="A230" s="26" t="inlineStr">
+      <c r="A230" s="32" t="inlineStr">
         <is>
           <t>EACH</t>
         </is>
       </c>
-      <c r="B230" s="26" t="n"/>
-      <c r="C230" s="27" t="inlineStr">
+      <c r="B230" s="32" t="n"/>
+      <c r="C230" s="33" t="inlineStr">
         <is>
           <t>Crooked Letter Cookies</t>
         </is>
       </c>
-      <c r="D230" s="27" t="n"/>
-      <c r="E230" s="26" t="n"/>
-      <c r="F230" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G230" s="28" t="n">
+      <c r="D230" s="33" t="n"/>
+      <c r="E230" s="32" t="n"/>
+      <c r="F230" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G230" s="34" t="n">
         <v>1.9</v>
       </c>
-      <c r="H230" s="29" t="n">
+      <c r="H230" s="35" t="n">
         <v>1.9</v>
       </c>
-      <c r="I230" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J230" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K230" s="29" t="n">
+      <c r="I230" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J230" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K230" s="35" t="n">
         <v>1.9</v>
       </c>
-      <c r="L230" s="27" t="inlineStr">
+      <c r="L230" s="33" t="inlineStr">
         <is>
           <t>per Each (None)</t>
         </is>
       </c>
-      <c r="M230" s="26" t="n"/>
-      <c r="N230" s="28">
+      <c r="M230" s="32" t="n"/>
+      <c r="N230" s="34">
         <f>M230*G230</f>
         <v/>
       </c>
-      <c r="O230" s="26" t="n"/>
-      <c r="P230" s="26" t="n"/>
-      <c r="Q230" s="26" t="n"/>
-      <c r="R230" s="26" t="n"/>
-      <c r="S230" s="26" t="n"/>
+      <c r="O230" s="32" t="n"/>
+      <c r="P230" s="32" t="n"/>
+      <c r="Q230" s="32" t="n"/>
+      <c r="R230" s="32" t="n"/>
+      <c r="S230" s="32" t="n"/>
     </row>
     <row r="231">
-      <c r="A231" s="26" t="inlineStr">
+      <c r="A231" s="32" t="inlineStr">
         <is>
           <t>EACH</t>
         </is>
       </c>
-      <c r="B231" s="26" t="n"/>
-      <c r="C231" s="27" t="inlineStr">
+      <c r="B231" s="32" t="n"/>
+      <c r="C231" s="33" t="inlineStr">
         <is>
           <t>Strawberry/Blueberry Cream Cheese King Cake</t>
         </is>
       </c>
-      <c r="D231" s="27" t="n"/>
-      <c r="E231" s="26" t="n"/>
-      <c r="F231" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G231" s="28" t="n">
+      <c r="D231" s="33" t="n"/>
+      <c r="E231" s="32" t="n"/>
+      <c r="F231" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G231" s="34" t="n">
         <v>31</v>
       </c>
-      <c r="H231" s="29" t="n">
+      <c r="H231" s="35" t="n">
         <v>31</v>
       </c>
-      <c r="I231" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J231" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K231" s="29" t="n">
+      <c r="I231" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J231" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K231" s="35" t="n">
         <v>31</v>
       </c>
-      <c r="L231" s="27" t="inlineStr">
+      <c r="L231" s="33" t="inlineStr">
         <is>
           <t>per Each (None)</t>
         </is>
       </c>
-      <c r="M231" s="26" t="n"/>
-      <c r="N231" s="28">
+      <c r="M231" s="32" t="n"/>
+      <c r="N231" s="34">
         <f>M231*G231</f>
         <v/>
       </c>
-      <c r="O231" s="26" t="n"/>
-      <c r="P231" s="26" t="n"/>
-      <c r="Q231" s="26" t="n"/>
-      <c r="R231" s="26" t="n"/>
-      <c r="S231" s="26" t="n"/>
+      <c r="O231" s="32" t="n"/>
+      <c r="P231" s="32" t="n"/>
+      <c r="Q231" s="32" t="n"/>
+      <c r="R231" s="32" t="n"/>
+      <c r="S231" s="32" t="n"/>
     </row>
     <row r="232">
-      <c r="A232" s="26" t="inlineStr">
+      <c r="A232" s="32" t="inlineStr">
         <is>
           <t>EACH</t>
         </is>
       </c>
-      <c r="B232" s="26" t="n"/>
-      <c r="C232" s="27" t="inlineStr">
+      <c r="B232" s="32" t="n"/>
+      <c r="C232" s="33" t="inlineStr">
         <is>
           <t>Traditional King Cake</t>
         </is>
       </c>
-      <c r="D232" s="27" t="n"/>
-      <c r="E232" s="26" t="n"/>
-      <c r="F232" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G232" s="28" t="n">
+      <c r="D232" s="33" t="n"/>
+      <c r="E232" s="32" t="n"/>
+      <c r="F232" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G232" s="34" t="n">
         <v>26</v>
       </c>
-      <c r="H232" s="29" t="n">
+      <c r="H232" s="35" t="n">
         <v>26</v>
       </c>
-      <c r="I232" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J232" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K232" s="29" t="n">
+      <c r="I232" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J232" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K232" s="35" t="n">
         <v>26</v>
       </c>
-      <c r="L232" s="27" t="inlineStr">
+      <c r="L232" s="33" t="inlineStr">
         <is>
           <t>per Each (None)</t>
         </is>
       </c>
-      <c r="M232" s="26" t="n"/>
-      <c r="N232" s="28">
+      <c r="M232" s="32" t="n"/>
+      <c r="N232" s="34">
         <f>M232*G232</f>
         <v/>
       </c>
-      <c r="O232" s="26" t="n"/>
-      <c r="P232" s="26" t="n"/>
-      <c r="Q232" s="26" t="n"/>
-      <c r="R232" s="26" t="n"/>
-      <c r="S232" s="26" t="n"/>
+      <c r="O232" s="32" t="n"/>
+      <c r="P232" s="32" t="n"/>
+      <c r="Q232" s="32" t="n"/>
+      <c r="R232" s="32" t="n"/>
+      <c r="S232" s="32" t="n"/>
     </row>
     <row r="233">
-      <c r="A233" s="26" t="inlineStr">
+      <c r="A233" s="32" t="inlineStr">
         <is>
           <t>EACH</t>
         </is>
       </c>
-      <c r="B233" s="26" t="n"/>
-      <c r="C233" s="27" t="inlineStr">
+      <c r="B233" s="32" t="n"/>
+      <c r="C233" s="33" t="inlineStr">
         <is>
           <t>Cream Cheese King Cake</t>
         </is>
       </c>
-      <c r="D233" s="27" t="n"/>
-      <c r="E233" s="26" t="n"/>
-      <c r="F233" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G233" s="28" t="n">
+      <c r="D233" s="33" t="n"/>
+      <c r="E233" s="32" t="n"/>
+      <c r="F233" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G233" s="34" t="n">
         <v>28</v>
       </c>
-      <c r="H233" s="29" t="n">
+      <c r="H233" s="35" t="n">
         <v>28</v>
       </c>
-      <c r="I233" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J233" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K233" s="29" t="n">
+      <c r="I233" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J233" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K233" s="35" t="n">
         <v>28</v>
       </c>
-      <c r="L233" s="27" t="inlineStr">
+      <c r="L233" s="33" t="inlineStr">
         <is>
           <t>per Each (None)</t>
         </is>
       </c>
-      <c r="M233" s="26" t="n"/>
-      <c r="N233" s="28">
+      <c r="M233" s="32" t="n"/>
+      <c r="N233" s="34">
         <f>M233*G233</f>
         <v/>
       </c>
-      <c r="O233" s="26" t="n"/>
-      <c r="P233" s="26" t="n"/>
-      <c r="Q233" s="26" t="n"/>
-      <c r="R233" s="26" t="n"/>
-      <c r="S233" s="26" t="n"/>
+      <c r="O233" s="32" t="n"/>
+      <c r="P233" s="32" t="n"/>
+      <c r="Q233" s="32" t="n"/>
+      <c r="R233" s="32" t="n"/>
+      <c r="S233" s="32" t="n"/>
     </row>
     <row r="234">
-      <c r="A234" s="26" t="inlineStr">
+      <c r="A234" s="32" t="inlineStr">
         <is>
           <t>EACH</t>
         </is>
       </c>
-      <c r="B234" s="26" t="n"/>
-      <c r="C234" s="27" t="inlineStr">
+      <c r="B234" s="32" t="n"/>
+      <c r="C234" s="33" t="inlineStr">
         <is>
           <t>Pecan Praline King Cake</t>
         </is>
       </c>
-      <c r="D234" s="27" t="n"/>
-      <c r="E234" s="26" t="n"/>
-      <c r="F234" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G234" s="28" t="n">
+      <c r="D234" s="33" t="n"/>
+      <c r="E234" s="32" t="n"/>
+      <c r="F234" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G234" s="34" t="n">
         <v>30</v>
       </c>
-      <c r="H234" s="29" t="n">
+      <c r="H234" s="35" t="n">
         <v>30</v>
       </c>
-      <c r="I234" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J234" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K234" s="29" t="n">
+      <c r="I234" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J234" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K234" s="35" t="n">
         <v>30</v>
       </c>
-      <c r="L234" s="27" t="inlineStr">
+      <c r="L234" s="33" t="inlineStr">
         <is>
           <t>per Each (None)</t>
         </is>
       </c>
-      <c r="M234" s="26" t="n"/>
-      <c r="N234" s="28">
+      <c r="M234" s="32" t="n"/>
+      <c r="N234" s="34">
         <f>M234*G234</f>
         <v/>
       </c>
-      <c r="O234" s="26" t="n"/>
-      <c r="P234" s="26" t="n"/>
-      <c r="Q234" s="26" t="n"/>
-      <c r="R234" s="26" t="n"/>
-      <c r="S234" s="26" t="n"/>
+      <c r="O234" s="32" t="n"/>
+      <c r="P234" s="32" t="n"/>
+      <c r="Q234" s="32" t="n"/>
+      <c r="R234" s="32" t="n"/>
+      <c r="S234" s="32" t="n"/>
     </row>
     <row r="236">
-      <c r="A236" s="32" t="inlineStr">
+      <c r="A236" s="38" t="inlineStr">
         <is>
           <t>COLOR LEGEND</t>
         </is>
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="27" t="inlineStr">
-        <is>
-          <t>DARK RED — No BEK item number matched</t>
-        </is>
-      </c>
-      <c r="B237" s="33" t="n"/>
-      <c r="C237" s="33" t="n"/>
-      <c r="D237" s="33" t="n"/>
+      <c r="A237" s="33" t="inlineStr">
+        <is>
+          <t>DARK RED   — No BEK item number (not in BEK list)</t>
+        </is>
+      </c>
+      <c r="B237" s="39" t="n"/>
+      <c r="C237" s="39" t="n"/>
+      <c r="D237" s="39" t="n"/>
     </row>
     <row r="238">
-      <c r="A238" s="21" t="inlineStr">
-        <is>
-          <t>PINK/RED — Price UP ≥ 10% or ≥ $2.00/unit</t>
-        </is>
-      </c>
-      <c r="B238" s="33" t="n"/>
-      <c r="C238" s="33" t="n"/>
-      <c r="D238" s="33" t="n"/>
+      <c r="A238" s="27" t="inlineStr">
+        <is>
+          <t>ORANGE-RED — BEK# not found in current price list</t>
+        </is>
+      </c>
+      <c r="B238" s="39" t="n"/>
+      <c r="C238" s="39" t="n"/>
+      <c r="D238" s="39" t="n"/>
     </row>
     <row r="239">
-      <c r="A239" s="15" t="inlineStr">
-        <is>
-          <t>YELLOW   — Price increased (under threshold)</t>
-        </is>
-      </c>
-      <c r="B239" s="33" t="n"/>
-      <c r="C239" s="33" t="n"/>
-      <c r="D239" s="33" t="n"/>
+      <c r="A239" s="21" t="inlineStr">
+        <is>
+          <t>PINK       — Price UP ≥ 10% or ≥ $2.00/unit</t>
+        </is>
+      </c>
+      <c r="B239" s="39" t="n"/>
+      <c r="C239" s="39" t="n"/>
+      <c r="D239" s="39" t="n"/>
     </row>
     <row r="240">
-      <c r="A240" s="9" t="inlineStr">
-        <is>
-          <t>GREEN    — Price decreased</t>
-        </is>
-      </c>
-      <c r="B240" s="33" t="n"/>
-      <c r="C240" s="33" t="n"/>
-      <c r="D240" s="33" t="n"/>
+      <c r="A240" s="15" t="inlineStr">
+        <is>
+          <t>YELLOW     — Price increased (under threshold)</t>
+        </is>
+      </c>
+      <c r="B240" s="39" t="n"/>
+      <c r="C240" s="39" t="n"/>
+      <c r="D240" s="39" t="n"/>
     </row>
     <row r="241">
-      <c r="A241" s="3" t="inlineStr">
-        <is>
-          <t>WHITE    — No change</t>
-        </is>
-      </c>
-      <c r="B241" s="33" t="n"/>
-      <c r="C241" s="33" t="n"/>
-      <c r="D241" s="33" t="n"/>
+      <c r="A241" s="9" t="inlineStr">
+        <is>
+          <t>GREEN      — Price decreased</t>
+        </is>
+      </c>
+      <c r="B241" s="39" t="n"/>
+      <c r="C241" s="39" t="n"/>
+      <c r="D241" s="39" t="n"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="3" t="inlineStr">
+        <is>
+          <t>WHITE      — No change / price matched</t>
+        </is>
+      </c>
+      <c r="B242" s="39" t="n"/>
+      <c r="C242" s="39" t="n"/>
+      <c r="D242" s="39" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13767,795 +13816,795 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="34" t="inlineStr">
+      <c r="A1" s="40" t="inlineStr">
         <is>
           <t>PRODUCT</t>
         </is>
       </c>
-      <c r="B1" s="34" t="inlineStr">
+      <c r="B1" s="40" t="inlineStr">
         <is>
           <t>SIZE/DESCRIPTION</t>
         </is>
       </c>
-      <c r="C1" s="34" t="inlineStr">
+      <c r="C1" s="40" t="inlineStr">
         <is>
           <t>ON HAND (QTY)</t>
         </is>
       </c>
-      <c r="D1" s="34" t="inlineStr">
+      <c r="D1" s="40" t="inlineStr">
         <is>
           <t>COST</t>
         </is>
       </c>
-      <c r="E1" s="34" t="inlineStr">
+      <c r="E1" s="40" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="35" t="inlineStr">
+      <c r="A2" s="41" t="inlineStr">
         <is>
           <t>SIGNATURE BLEND</t>
         </is>
       </c>
-      <c r="B2" s="35" t="inlineStr">
+      <c r="B2" s="41" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="C2" s="36" t="n">
+      <c r="C2" s="42" t="n">
         <v>1.5</v>
       </c>
-      <c r="D2" s="36" t="n"/>
-      <c r="E2" s="36" t="n"/>
+      <c r="D2" s="42" t="n"/>
+      <c r="E2" s="42" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="35" t="inlineStr">
+      <c r="A3" s="41" t="inlineStr">
         <is>
           <t>AMERICAN CLASSIC</t>
         </is>
       </c>
-      <c r="B3" s="35" t="inlineStr">
+      <c r="B3" s="41" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="C3" s="36" t="n">
+      <c r="C3" s="42" t="n">
         <v>1.75</v>
       </c>
-      <c r="D3" s="36" t="n"/>
-      <c r="E3" s="36" t="n"/>
+      <c r="D3" s="42" t="n"/>
+      <c r="E3" s="42" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="35" t="inlineStr">
+      <c r="A4" s="41" t="inlineStr">
         <is>
           <t>PECAN PRALINE</t>
         </is>
       </c>
-      <c r="B4" s="35" t="inlineStr">
+      <c r="B4" s="41" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="C4" s="36" t="n">
+      <c r="C4" s="42" t="n">
         <v>1.5</v>
       </c>
-      <c r="D4" s="36" t="n"/>
-      <c r="E4" s="36" t="n"/>
+      <c r="D4" s="42" t="n"/>
+      <c r="E4" s="42" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="35" t="inlineStr">
+      <c r="A5" s="41" t="inlineStr">
         <is>
           <t>BREAKFAST BLEND</t>
         </is>
       </c>
-      <c r="B5" s="35" t="inlineStr">
+      <c r="B5" s="41" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="C5" s="36" t="n">
+      <c r="C5" s="42" t="n">
         <v>1.75</v>
       </c>
-      <c r="D5" s="36" t="n"/>
-      <c r="E5" s="36" t="n"/>
+      <c r="D5" s="42" t="n"/>
+      <c r="E5" s="42" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="35" t="inlineStr">
+      <c r="A6" s="41" t="inlineStr">
         <is>
           <t>DB ESPRESSO</t>
         </is>
       </c>
-      <c r="B6" s="35" t="inlineStr">
+      <c r="B6" s="41" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="C6" s="36" t="n">
+      <c r="C6" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="D6" s="36" t="n"/>
-      <c r="E6" s="36" t="n"/>
+      <c r="D6" s="42" t="n"/>
+      <c r="E6" s="42" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="35" t="inlineStr">
+      <c r="A7" s="41" t="inlineStr">
         <is>
           <t>Creamer Cups (Irish Cream, French Vanilla, Caramel)</t>
         </is>
       </c>
-      <c r="B7" s="35" t="inlineStr">
+      <c r="B7" s="41" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="C7" s="36" t="n">
+      <c r="C7" s="42" t="n">
         <v>3.5</v>
       </c>
-      <c r="D7" s="36" t="n"/>
-      <c r="E7" s="36" t="n"/>
+      <c r="D7" s="42" t="n"/>
+      <c r="E7" s="42" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="35" t="inlineStr">
+      <c r="A8" s="41" t="inlineStr">
         <is>
           <t>Coffee Mate</t>
         </is>
       </c>
-      <c r="B8" s="35" t="inlineStr">
+      <c r="B8" s="41" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="C8" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="36" t="n"/>
-      <c r="E8" s="36" t="n"/>
+      <c r="C8" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="42" t="n"/>
+      <c r="E8" s="42" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="35" t="inlineStr">
+      <c r="A9" s="41" t="inlineStr">
         <is>
           <t>Sweet Cream Creamer</t>
         </is>
       </c>
-      <c r="B9" s="35" t="inlineStr">
+      <c r="B9" s="41" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="C9" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="36" t="n"/>
-      <c r="E9" s="36" t="n"/>
+      <c r="C9" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="42" t="n"/>
+      <c r="E9" s="42" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="35" t="inlineStr">
+      <c r="A10" s="41" t="inlineStr">
         <is>
           <t>Hazelnut Creamer</t>
         </is>
       </c>
-      <c r="B10" s="35" t="inlineStr">
+      <c r="B10" s="41" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="C10" s="36" t="n">
+      <c r="C10" s="42" t="n">
         <v>1.1</v>
       </c>
-      <c r="D10" s="36" t="n"/>
-      <c r="E10" s="36" t="n"/>
+      <c r="D10" s="42" t="n"/>
+      <c r="E10" s="42" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="35" t="inlineStr">
+      <c r="A11" s="41" t="inlineStr">
         <is>
           <t>Half And Half</t>
         </is>
       </c>
-      <c r="B11" s="35" t="inlineStr">
+      <c r="B11" s="41" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="C11" s="36" t="n">
+      <c r="C11" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="D11" s="36" t="n"/>
-      <c r="E11" s="36" t="n"/>
+      <c r="D11" s="42" t="n"/>
+      <c r="E11" s="42" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="35" t="inlineStr">
+      <c r="A12" s="41" t="inlineStr">
         <is>
           <t>Original Creamer</t>
         </is>
       </c>
-      <c r="B12" s="35" t="inlineStr">
+      <c r="B12" s="41" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="C12" s="36" t="n">
+      <c r="C12" s="42" t="n">
         <v>1.25</v>
       </c>
-      <c r="D12" s="36" t="n"/>
-      <c r="E12" s="36" t="n"/>
+      <c r="D12" s="42" t="n"/>
+      <c r="E12" s="42" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="35" t="inlineStr">
+      <c r="A13" s="41" t="inlineStr">
         <is>
           <t>Caramel Syrup Pump</t>
         </is>
       </c>
-      <c r="B13" s="35" t="inlineStr">
+      <c r="B13" s="41" t="inlineStr">
         <is>
           <t>BOTTLE</t>
         </is>
       </c>
-      <c r="C13" s="36" t="n">
+      <c r="C13" s="42" t="n">
         <v>1.5</v>
       </c>
-      <c r="D13" s="36" t="n"/>
-      <c r="E13" s="36" t="n"/>
+      <c r="D13" s="42" t="n"/>
+      <c r="E13" s="42" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="35" t="inlineStr">
+      <c r="A14" s="41" t="inlineStr">
         <is>
           <t>Hazelnut Syrup Pump</t>
         </is>
       </c>
-      <c r="B14" s="35" t="inlineStr">
+      <c r="B14" s="41" t="inlineStr">
         <is>
           <t>BOTTLE</t>
         </is>
       </c>
-      <c r="C14" s="36" t="n">
+      <c r="C14" s="42" t="n">
         <v>1.5</v>
       </c>
-      <c r="D14" s="36" t="n"/>
-      <c r="E14" s="36" t="n"/>
+      <c r="D14" s="42" t="n"/>
+      <c r="E14" s="42" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="35" t="inlineStr">
+      <c r="A15" s="41" t="inlineStr">
         <is>
           <t>French Vanilla Syrup Pump</t>
         </is>
       </c>
-      <c r="B15" s="35" t="inlineStr">
+      <c r="B15" s="41" t="inlineStr">
         <is>
           <t>BOTTLE</t>
         </is>
       </c>
-      <c r="C15" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" s="36" t="n"/>
-      <c r="E15" s="36" t="n"/>
+      <c r="C15" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="42" t="n"/>
+      <c r="E15" s="42" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="35" t="inlineStr">
+      <c r="A16" s="41" t="inlineStr">
         <is>
           <t>Hold &amp; Go Lids 12-24oz</t>
         </is>
       </c>
-      <c r="B16" s="35" t="inlineStr">
+      <c r="B16" s="41" t="inlineStr">
         <is>
           <t>SLEEVE</t>
         </is>
       </c>
-      <c r="C16" s="36" t="n">
+      <c r="C16" s="42" t="n">
         <v>14</v>
       </c>
-      <c r="D16" s="36" t="n"/>
-      <c r="E16" s="36" t="n"/>
+      <c r="D16" s="42" t="n"/>
+      <c r="E16" s="42" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="35" t="inlineStr">
+      <c r="A17" s="41" t="inlineStr">
         <is>
           <t>Lid SW 16/20oz</t>
         </is>
       </c>
-      <c r="B17" s="35" t="inlineStr">
+      <c r="B17" s="41" t="inlineStr">
         <is>
           <t>SLEEVE</t>
         </is>
       </c>
-      <c r="C17" s="36" t="n"/>
-      <c r="D17" s="36" t="n"/>
-      <c r="E17" s="36" t="n"/>
+      <c r="C17" s="42" t="n"/>
+      <c r="D17" s="42" t="n"/>
+      <c r="E17" s="42" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="35" t="inlineStr">
+      <c r="A18" s="41" t="inlineStr">
         <is>
           <t>Cappuccino French Vanilla</t>
         </is>
       </c>
-      <c r="B18" s="35" t="inlineStr">
+      <c r="B18" s="41" t="inlineStr">
         <is>
           <t>BAG</t>
         </is>
       </c>
-      <c r="C18" s="36" t="n">
+      <c r="C18" s="42" t="n">
         <v>9</v>
       </c>
-      <c r="D18" s="36" t="n"/>
-      <c r="E18" s="36" t="n"/>
+      <c r="D18" s="42" t="n"/>
+      <c r="E18" s="42" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="35" t="inlineStr">
+      <c r="A19" s="41" t="inlineStr">
         <is>
           <t>Sugar Free Cappuccino French Vanilla</t>
         </is>
       </c>
-      <c r="B19" s="35" t="inlineStr">
+      <c r="B19" s="41" t="inlineStr">
         <is>
           <t>BAG</t>
         </is>
       </c>
-      <c r="C19" s="36" t="n">
+      <c r="C19" s="42" t="n">
         <v>8</v>
       </c>
-      <c r="D19" s="36" t="n"/>
-      <c r="E19" s="36" t="n"/>
+      <c r="D19" s="42" t="n"/>
+      <c r="E19" s="42" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="35" t="inlineStr">
+      <c r="A20" s="41" t="inlineStr">
         <is>
           <t>Hot Chocolate</t>
         </is>
       </c>
-      <c r="B20" s="35" t="inlineStr">
+      <c r="B20" s="41" t="inlineStr">
         <is>
           <t>BAG</t>
         </is>
       </c>
-      <c r="C20" s="36" t="n">
+      <c r="C20" s="42" t="n">
         <v>11</v>
       </c>
-      <c r="D20" s="36" t="n"/>
-      <c r="E20" s="36" t="n"/>
+      <c r="D20" s="42" t="n"/>
+      <c r="E20" s="42" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="35" t="inlineStr">
+      <c r="A21" s="41" t="inlineStr">
         <is>
           <t>Creamer Packs</t>
         </is>
       </c>
-      <c r="B21" s="35" t="inlineStr">
+      <c r="B21" s="41" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="C21" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" s="36" t="n"/>
-      <c r="E21" s="36" t="n"/>
+      <c r="C21" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="42" t="n"/>
+      <c r="E21" s="42" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="35" t="inlineStr">
+      <c r="A22" s="41" t="inlineStr">
         <is>
           <t>Sugar Pack</t>
         </is>
       </c>
-      <c r="B22" s="35" t="inlineStr">
+      <c r="B22" s="41" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="C22" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" s="36" t="n"/>
-      <c r="E22" s="36" t="n"/>
+      <c r="C22" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="42" t="n"/>
+      <c r="E22" s="42" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="35" t="inlineStr">
+      <c r="A23" s="41" t="inlineStr">
         <is>
           <t>Blue Sweetener</t>
         </is>
       </c>
-      <c r="B23" s="35" t="inlineStr">
+      <c r="B23" s="41" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="C23" s="36" t="n">
+      <c r="C23" s="42" t="n">
         <v>0.75</v>
       </c>
-      <c r="D23" s="36" t="n"/>
-      <c r="E23" s="36" t="n"/>
+      <c r="D23" s="42" t="n"/>
+      <c r="E23" s="42" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="35" t="inlineStr">
+      <c r="A24" s="41" t="inlineStr">
         <is>
           <t>Yellow Sweetener</t>
         </is>
       </c>
-      <c r="B24" s="35" t="inlineStr">
+      <c r="B24" s="41" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="C24" s="36" t="n">
+      <c r="C24" s="42" t="n">
         <v>0.25</v>
       </c>
-      <c r="D24" s="36" t="n"/>
-      <c r="E24" s="36" t="n"/>
+      <c r="D24" s="42" t="n"/>
+      <c r="E24" s="42" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="35" t="inlineStr">
+      <c r="A25" s="41" t="inlineStr">
         <is>
           <t>Pink Sweetener</t>
         </is>
       </c>
-      <c r="B25" s="35" t="inlineStr">
+      <c r="B25" s="41" t="inlineStr">
         <is>
           <t>BAG</t>
         </is>
       </c>
-      <c r="C25" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" s="36" t="n"/>
-      <c r="E25" s="36" t="n"/>
+      <c r="C25" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="42" t="n"/>
+      <c r="E25" s="42" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="35" t="inlineStr">
+      <c r="A26" s="41" t="inlineStr">
         <is>
           <t>Sugar Packets</t>
         </is>
       </c>
-      <c r="B26" s="35" t="inlineStr">
+      <c r="B26" s="41" t="inlineStr">
         <is>
           <t>EACH</t>
         </is>
       </c>
-      <c r="C26" s="36" t="n">
+      <c r="C26" s="42" t="n">
         <v>45</v>
       </c>
-      <c r="D26" s="36" t="n"/>
-      <c r="E26" s="36" t="n"/>
+      <c r="D26" s="42" t="n"/>
+      <c r="E26" s="42" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="35" t="inlineStr">
+      <c r="A27" s="41" t="inlineStr">
         <is>
           <t>Sugar Canister</t>
         </is>
       </c>
-      <c r="B27" s="35" t="inlineStr">
+      <c r="B27" s="41" t="inlineStr">
         <is>
           <t>EACH</t>
         </is>
       </c>
-      <c r="C27" s="36" t="n">
+      <c r="C27" s="42" t="n">
         <v>39</v>
       </c>
-      <c r="D27" s="36" t="n"/>
-      <c r="E27" s="36" t="n"/>
+      <c r="D27" s="42" t="n"/>
+      <c r="E27" s="42" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="35" t="inlineStr">
+      <c r="A28" s="41" t="inlineStr">
         <is>
           <t>Red Stirrers</t>
         </is>
       </c>
-      <c r="B28" s="35" t="inlineStr">
+      <c r="B28" s="41" t="inlineStr">
         <is>
           <t>PACK</t>
         </is>
       </c>
-      <c r="C28" s="36" t="n">
+      <c r="C28" s="42" t="n">
         <v>3.5</v>
       </c>
-      <c r="D28" s="36" t="n"/>
-      <c r="E28" s="36" t="n"/>
+      <c r="D28" s="42" t="n"/>
+      <c r="E28" s="42" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="35" t="inlineStr">
+      <c r="A29" s="41" t="inlineStr">
         <is>
           <t>16 oz Double-Wall Cup</t>
         </is>
       </c>
-      <c r="B29" s="35" t="inlineStr">
+      <c r="B29" s="41" t="inlineStr">
         <is>
           <t>SLV</t>
         </is>
       </c>
-      <c r="C29" s="36" t="n">
+      <c r="C29" s="42" t="n">
         <v>32</v>
       </c>
-      <c r="D29" s="36" t="n"/>
-      <c r="E29" s="36" t="n"/>
+      <c r="D29" s="42" t="n"/>
+      <c r="E29" s="42" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="35" t="inlineStr">
+      <c r="A30" s="41" t="inlineStr">
         <is>
           <t>16oz Single-Wall Cup</t>
         </is>
       </c>
-      <c r="B30" s="35" t="inlineStr">
+      <c r="B30" s="41" t="inlineStr">
         <is>
           <t>SLV</t>
         </is>
       </c>
-      <c r="C30" s="36" t="n"/>
-      <c r="D30" s="36" t="n"/>
-      <c r="E30" s="36" t="n"/>
+      <c r="C30" s="42" t="n"/>
+      <c r="D30" s="42" t="n"/>
+      <c r="E30" s="42" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="35" t="inlineStr">
+      <c r="A31" s="41" t="inlineStr">
         <is>
           <t>24 oz Double-Wall Cup</t>
         </is>
       </c>
-      <c r="B31" s="35" t="inlineStr">
+      <c r="B31" s="41" t="inlineStr">
         <is>
           <t>SLV</t>
         </is>
       </c>
-      <c r="C31" s="36" t="n">
+      <c r="C31" s="42" t="n">
         <v>37</v>
       </c>
-      <c r="D31" s="36" t="n"/>
-      <c r="E31" s="36" t="n"/>
+      <c r="D31" s="42" t="n"/>
+      <c r="E31" s="42" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="35" t="inlineStr">
+      <c r="A32" s="41" t="inlineStr">
         <is>
           <t>32oz Fountain Cup</t>
         </is>
       </c>
-      <c r="B32" s="35" t="inlineStr">
+      <c r="B32" s="41" t="inlineStr">
         <is>
           <t>SLV</t>
         </is>
       </c>
-      <c r="C32" s="36" t="n">
+      <c r="C32" s="42" t="n">
         <v>63</v>
       </c>
-      <c r="D32" s="36" t="n"/>
-      <c r="E32" s="36" t="n"/>
+      <c r="D32" s="42" t="n"/>
+      <c r="E32" s="42" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="35" t="inlineStr">
+      <c r="A33" s="41" t="inlineStr">
         <is>
           <t>32oz Lid</t>
         </is>
       </c>
-      <c r="B33" s="35" t="inlineStr">
+      <c r="B33" s="41" t="inlineStr">
         <is>
           <t>SLV</t>
         </is>
       </c>
-      <c r="C33" s="36" t="n">
+      <c r="C33" s="42" t="n">
         <v>61</v>
       </c>
-      <c r="D33" s="37" t="n">
+      <c r="D33" s="43" t="n">
         <v>2.85</v>
       </c>
-      <c r="E33" s="37">
+      <c r="E33" s="43">
         <f>C33*D33</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="35" t="inlineStr">
+      <c r="A34" s="41" t="inlineStr">
         <is>
           <t>20oz Cup</t>
         </is>
       </c>
-      <c r="B34" s="35" t="inlineStr">
+      <c r="B34" s="41" t="inlineStr">
         <is>
           <t>SLV</t>
         </is>
       </c>
-      <c r="C34" s="36" t="n">
+      <c r="C34" s="42" t="n">
         <v>81</v>
       </c>
-      <c r="D34" s="36" t="n"/>
-      <c r="E34" s="36" t="n"/>
+      <c r="D34" s="42" t="n"/>
+      <c r="E34" s="42" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="35" t="inlineStr">
+      <c r="A35" s="41" t="inlineStr">
         <is>
           <t>20oz Lid</t>
         </is>
       </c>
-      <c r="B35" s="35" t="inlineStr">
+      <c r="B35" s="41" t="inlineStr">
         <is>
           <t>SLV</t>
         </is>
       </c>
-      <c r="C35" s="36" t="n">
+      <c r="C35" s="42" t="n">
         <v>56</v>
       </c>
-      <c r="D35" s="36" t="n"/>
-      <c r="E35" s="36" t="n"/>
+      <c r="D35" s="42" t="n"/>
+      <c r="E35" s="42" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="35" t="inlineStr">
+      <c r="A36" s="41" t="inlineStr">
         <is>
           <t>Red Straws</t>
         </is>
       </c>
-      <c r="B36" s="35" t="inlineStr">
+      <c r="B36" s="41" t="inlineStr">
         <is>
           <t>BOX</t>
         </is>
       </c>
-      <c r="C36" s="36" t="n">
+      <c r="C36" s="42" t="n">
         <v>12</v>
       </c>
-      <c r="D36" s="36" t="n"/>
-      <c r="E36" s="36" t="n"/>
+      <c r="D36" s="42" t="n"/>
+      <c r="E36" s="42" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="35" t="inlineStr">
+      <c r="A37" s="41" t="inlineStr">
         <is>
           <t>Bag In Box 5 Gal Syrup</t>
         </is>
       </c>
-      <c r="B37" s="35" t="inlineStr">
+      <c r="B37" s="41" t="inlineStr">
         <is>
           <t>BOX</t>
         </is>
       </c>
-      <c r="C37" s="36" t="n">
+      <c r="C37" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="D37" s="36" t="n"/>
-      <c r="E37" s="36" t="n"/>
+      <c r="D37" s="42" t="n"/>
+      <c r="E37" s="42" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="35" t="inlineStr">
+      <c r="A38" s="41" t="inlineStr">
         <is>
           <t>Bag In Box 2.5 Gal Syrup</t>
         </is>
       </c>
-      <c r="B38" s="35" t="inlineStr">
+      <c r="B38" s="41" t="inlineStr">
         <is>
           <t>BOX</t>
         </is>
       </c>
-      <c r="C38" s="36" t="n">
+      <c r="C38" s="42" t="n">
         <v>5</v>
       </c>
-      <c r="D38" s="36" t="n"/>
-      <c r="E38" s="36" t="n"/>
+      <c r="D38" s="42" t="n"/>
+      <c r="E38" s="42" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="35" t="inlineStr">
+      <c r="A39" s="41" t="inlineStr">
         <is>
           <t>CO2 Tank</t>
         </is>
       </c>
-      <c r="B39" s="35" t="inlineStr">
+      <c r="B39" s="41" t="inlineStr">
         <is>
           <t>EACH</t>
         </is>
       </c>
-      <c r="C39" s="36" t="n">
+      <c r="C39" s="42" t="n">
         <v>3</v>
       </c>
-      <c r="D39" s="36" t="n"/>
-      <c r="E39" s="36" t="n"/>
+      <c r="D39" s="42" t="n"/>
+      <c r="E39" s="42" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="35" t="inlineStr">
+      <c r="A40" s="41" t="inlineStr">
         <is>
           <t>Cafe Tango Lids</t>
         </is>
       </c>
-      <c r="B40" s="35" t="inlineStr">
+      <c r="B40" s="41" t="inlineStr">
         <is>
           <t>SLEEVE</t>
         </is>
       </c>
-      <c r="C40" s="36" t="n">
+      <c r="C40" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="D40" s="37" t="n">
+      <c r="D40" s="43" t="n">
         <v>2.53</v>
       </c>
-      <c r="E40" s="37">
+      <c r="E40" s="43">
         <f>C40*D40</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="35" t="inlineStr">
+      <c r="A41" s="41" t="inlineStr">
         <is>
           <t>16 oz Tango Cup</t>
         </is>
       </c>
-      <c r="B41" s="35" t="inlineStr">
+      <c r="B41" s="41" t="inlineStr">
         <is>
           <t>SLV</t>
         </is>
       </c>
-      <c r="C41" s="36" t="n">
+      <c r="C41" s="42" t="n">
         <v>8</v>
       </c>
-      <c r="D41" s="37" t="n">
+      <c r="D41" s="43" t="n">
         <v>6.78</v>
       </c>
-      <c r="E41" s="37">
+      <c r="E41" s="43">
         <f>C41*D41</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="35" t="inlineStr">
+      <c r="A42" s="41" t="inlineStr">
         <is>
           <t>24 oz Tango Cup</t>
         </is>
       </c>
-      <c r="B42" s="35" t="inlineStr">
+      <c r="B42" s="41" t="inlineStr">
         <is>
           <t>SLV</t>
         </is>
       </c>
-      <c r="C42" s="36" t="n">
+      <c r="C42" s="42" t="n">
         <v>5</v>
       </c>
-      <c r="D42" s="36" t="n"/>
-      <c r="E42" s="36" t="n"/>
+      <c r="D42" s="42" t="n"/>
+      <c r="E42" s="42" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="35" t="inlineStr">
+      <c r="A43" s="41" t="inlineStr">
         <is>
           <t>Cafe Tango French Vanilla</t>
         </is>
       </c>
-      <c r="B43" s="35" t="inlineStr">
+      <c r="B43" s="41" t="inlineStr">
         <is>
           <t>BAG</t>
         </is>
       </c>
-      <c r="C43" s="36" t="n">
+      <c r="C43" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="D43" s="37" t="n">
+      <c r="D43" s="43" t="n">
         <v>13.64</v>
       </c>
-      <c r="E43" s="37">
+      <c r="E43" s="43">
         <f>C43*D43</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="35" t="inlineStr">
+      <c r="A44" s="41" t="inlineStr">
         <is>
           <t>Cafe Tango Mocha</t>
         </is>
       </c>
-      <c r="B44" s="35" t="inlineStr">
+      <c r="B44" s="41" t="inlineStr">
         <is>
           <t>BAG</t>
         </is>
       </c>
-      <c r="C44" s="36" t="n">
+      <c r="C44" s="42" t="n">
         <v>25</v>
       </c>
-      <c r="D44" s="36" t="n"/>
-      <c r="E44" s="36" t="n"/>
+      <c r="D44" s="42" t="n"/>
+      <c r="E44" s="42" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="35" t="inlineStr">
+      <c r="A45" s="41" t="inlineStr">
         <is>
           <t>Caramel Macchiato</t>
         </is>
       </c>
-      <c r="B45" s="35" t="inlineStr">
+      <c r="B45" s="41" t="inlineStr">
         <is>
           <t>BAG</t>
         </is>
       </c>
-      <c r="C45" s="36" t="n">
+      <c r="C45" s="42" t="n">
         <v>14</v>
       </c>
-      <c r="D45" s="36" t="n"/>
-      <c r="E45" s="36" t="n"/>
+      <c r="D45" s="42" t="n"/>
+      <c r="E45" s="42" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Updated_185_Count_Sheet_BEK_v2.xlsx
+++ b/Updated_185_Count_Sheet_BEK_v2.xlsx
@@ -75,12 +75,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF6600"/>
+        <fgColor rgb="FFCC0000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCC0000"/>
+        <fgColor rgb="004472C4"/>
       </patternFill>
     </fill>
     <fill>
@@ -89,7 +89,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -112,6 +112,50 @@
       </bottom>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
@@ -130,7 +174,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -228,33 +272,20 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -622,7 +653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S242"/>
+  <dimension ref="A1:S241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2948,52 +2979,52 @@
       <c r="S40" s="14" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="32" t="inlineStr">
+      <c r="A41" s="26" t="inlineStr">
         <is>
           <t>SLEEVE</t>
         </is>
       </c>
-      <c r="B41" s="32" t="n"/>
-      <c r="C41" s="33" t="inlineStr">
+      <c r="B41" s="26" t="n"/>
+      <c r="C41" s="27" t="inlineStr">
         <is>
           <t>Chili</t>
         </is>
       </c>
-      <c r="D41" s="33" t="n"/>
-      <c r="E41" s="32" t="n"/>
-      <c r="F41" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G41" s="34" t="n">
+      <c r="D41" s="27" t="n"/>
+      <c r="E41" s="26" t="n"/>
+      <c r="F41" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="28" t="n">
         <v>17.8</v>
       </c>
-      <c r="H41" s="35" t="n">
+      <c r="H41" s="29" t="n">
         <v>17.8</v>
       </c>
-      <c r="I41" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" s="35" t="n">
+      <c r="I41" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="29" t="n">
         <v>17.8</v>
       </c>
-      <c r="L41" s="33" t="inlineStr">
+      <c r="L41" s="27" t="inlineStr">
         <is>
           <t>per Sleeve (None)</t>
         </is>
       </c>
-      <c r="M41" s="32" t="n"/>
-      <c r="N41" s="34">
+      <c r="M41" s="26" t="n"/>
+      <c r="N41" s="28">
         <f>M41*G41</f>
         <v/>
       </c>
-      <c r="O41" s="32" t="n"/>
-      <c r="P41" s="32" t="n"/>
-      <c r="Q41" s="32" t="n"/>
-      <c r="R41" s="32" t="n"/>
-      <c r="S41" s="32" t="n"/>
+      <c r="O41" s="26" t="n"/>
+      <c r="P41" s="26" t="n"/>
+      <c r="Q41" s="26" t="n"/>
+      <c r="R41" s="26" t="n"/>
+      <c r="S41" s="26" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n"/>
@@ -4514,52 +4545,52 @@
       <c r="S68" s="2" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="32" t="inlineStr">
+      <c r="A69" s="26" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="B69" s="32" t="n"/>
-      <c r="C69" s="33" t="inlineStr">
+      <c r="B69" s="26" t="n"/>
+      <c r="C69" s="27" t="inlineStr">
         <is>
           <t>Donut Apple</t>
         </is>
       </c>
-      <c r="D69" s="33" t="n"/>
-      <c r="E69" s="32" t="n"/>
-      <c r="F69" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G69" s="34" t="n">
+      <c r="D69" s="27" t="n"/>
+      <c r="E69" s="26" t="n"/>
+      <c r="F69" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" s="28" t="n">
         <v>33.26</v>
       </c>
-      <c r="H69" s="35" t="n">
+      <c r="H69" s="29" t="n">
         <v>33.26</v>
       </c>
-      <c r="I69" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J69" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K69" s="35" t="n">
+      <c r="I69" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" s="29" t="n">
         <v>33.26</v>
       </c>
-      <c r="L69" s="33" t="inlineStr">
+      <c r="L69" s="27" t="inlineStr">
         <is>
           <t>per Case (None)</t>
         </is>
       </c>
-      <c r="M69" s="32" t="n"/>
-      <c r="N69" s="34">
+      <c r="M69" s="26" t="n"/>
+      <c r="N69" s="28">
         <f>M69*G69</f>
         <v/>
       </c>
-      <c r="O69" s="32" t="n"/>
-      <c r="P69" s="32" t="n"/>
-      <c r="Q69" s="32" t="n"/>
-      <c r="R69" s="32" t="n"/>
-      <c r="S69" s="32" t="n"/>
+      <c r="O69" s="26" t="n"/>
+      <c r="P69" s="26" t="n"/>
+      <c r="Q69" s="26" t="n"/>
+      <c r="R69" s="26" t="n"/>
+      <c r="S69" s="26" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -10604,52 +10635,52 @@
       <c r="S174" s="8" t="n"/>
     </row>
     <row r="175">
-      <c r="A175" s="32" t="inlineStr">
+      <c r="A175" s="26" t="inlineStr">
         <is>
           <t>CAN</t>
         </is>
       </c>
-      <c r="B175" s="32" t="n"/>
-      <c r="C175" s="33" t="inlineStr">
+      <c r="B175" s="26" t="n"/>
+      <c r="C175" s="27" t="inlineStr">
         <is>
           <t>Soup Cream of Mushroom</t>
         </is>
       </c>
-      <c r="D175" s="33" t="n"/>
-      <c r="E175" s="32" t="n"/>
-      <c r="F175" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G175" s="34" t="n">
+      <c r="D175" s="27" t="n"/>
+      <c r="E175" s="26" t="n"/>
+      <c r="F175" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G175" s="28" t="n">
         <v>5.79</v>
       </c>
-      <c r="H175" s="35" t="n">
+      <c r="H175" s="29" t="n">
         <v>5.79</v>
       </c>
-      <c r="I175" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J175" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K175" s="35" t="n">
+      <c r="I175" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J175" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K175" s="29" t="n">
         <v>5.79</v>
       </c>
-      <c r="L175" s="33" t="inlineStr">
+      <c r="L175" s="27" t="inlineStr">
         <is>
           <t>per Can (None)</t>
         </is>
       </c>
-      <c r="M175" s="32" t="n"/>
-      <c r="N175" s="34">
+      <c r="M175" s="26" t="n"/>
+      <c r="N175" s="28">
         <f>M175*G175</f>
         <v/>
       </c>
-      <c r="O175" s="32" t="n"/>
-      <c r="P175" s="32" t="n"/>
-      <c r="Q175" s="32" t="n"/>
-      <c r="R175" s="32" t="n"/>
-      <c r="S175" s="32" t="n"/>
+      <c r="O175" s="26" t="n"/>
+      <c r="P175" s="26" t="n"/>
+      <c r="Q175" s="26" t="n"/>
+      <c r="R175" s="26" t="n"/>
+      <c r="S175" s="26" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -11848,1953 +11879,1939 @@
       <c r="S196" s="20" t="n"/>
     </row>
     <row r="197">
-      <c r="A197" s="32" t="inlineStr">
+      <c r="A197" s="26" t="inlineStr">
         <is>
           <t>EACH</t>
         </is>
       </c>
-      <c r="B197" s="32" t="n"/>
-      <c r="C197" s="33" t="inlineStr">
+      <c r="B197" s="26" t="n"/>
+      <c r="C197" s="27" t="inlineStr">
         <is>
           <t>Lettuce Head</t>
         </is>
       </c>
-      <c r="D197" s="33" t="n"/>
-      <c r="E197" s="32" t="n"/>
-      <c r="F197" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G197" s="34" t="n">
+      <c r="D197" s="27" t="n"/>
+      <c r="E197" s="26" t="n"/>
+      <c r="F197" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G197" s="28" t="n">
         <v>3.99</v>
       </c>
-      <c r="H197" s="35" t="n">
+      <c r="H197" s="29" t="n">
         <v>3.99</v>
       </c>
-      <c r="I197" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J197" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K197" s="35" t="n">
+      <c r="I197" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J197" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K197" s="29" t="n">
         <v>3.99</v>
       </c>
-      <c r="L197" s="33" t="inlineStr">
+      <c r="L197" s="27" t="inlineStr">
         <is>
           <t>per Each (None)</t>
         </is>
       </c>
-      <c r="M197" s="32" t="n"/>
-      <c r="N197" s="34">
+      <c r="M197" s="26" t="n"/>
+      <c r="N197" s="28">
         <f>M197*G197</f>
         <v/>
       </c>
-      <c r="O197" s="32" t="n"/>
-      <c r="P197" s="32" t="n"/>
-      <c r="Q197" s="32" t="n"/>
-      <c r="R197" s="32" t="n"/>
-      <c r="S197" s="32" t="n"/>
+      <c r="O197" s="26" t="n"/>
+      <c r="P197" s="26" t="n"/>
+      <c r="Q197" s="26" t="n"/>
+      <c r="R197" s="26" t="n"/>
+      <c r="S197" s="26" t="n"/>
     </row>
     <row r="198">
-      <c r="A198" s="32" t="inlineStr">
+      <c r="A198" s="26" t="inlineStr">
         <is>
           <t>EACH</t>
         </is>
       </c>
-      <c r="B198" s="32" t="n"/>
-      <c r="C198" s="33" t="inlineStr">
+      <c r="B198" s="26" t="n"/>
+      <c r="C198" s="27" t="inlineStr">
         <is>
           <t>Tomato</t>
         </is>
       </c>
-      <c r="D198" s="33" t="n"/>
-      <c r="E198" s="32" t="n"/>
-      <c r="F198" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G198" s="34" t="n">
+      <c r="D198" s="27" t="n"/>
+      <c r="E198" s="26" t="n"/>
+      <c r="F198" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G198" s="28" t="n">
         <v>2.49</v>
       </c>
-      <c r="H198" s="35" t="n">
+      <c r="H198" s="29" t="n">
         <v>2.49</v>
       </c>
-      <c r="I198" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J198" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K198" s="35" t="n">
+      <c r="I198" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J198" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K198" s="29" t="n">
         <v>2.49</v>
       </c>
-      <c r="L198" s="33" t="inlineStr">
+      <c r="L198" s="27" t="inlineStr">
         <is>
           <t>per Each (None)</t>
         </is>
       </c>
-      <c r="M198" s="32" t="n"/>
-      <c r="N198" s="34">
+      <c r="M198" s="26" t="n"/>
+      <c r="N198" s="28">
         <f>M198*G198</f>
         <v/>
       </c>
-      <c r="O198" s="32" t="n"/>
-      <c r="P198" s="32" t="n"/>
-      <c r="Q198" s="32" t="n"/>
-      <c r="R198" s="32" t="n"/>
-      <c r="S198" s="32" t="n"/>
+      <c r="O198" s="26" t="n"/>
+      <c r="P198" s="26" t="n"/>
+      <c r="Q198" s="26" t="n"/>
+      <c r="R198" s="26" t="n"/>
+      <c r="S198" s="26" t="n"/>
     </row>
     <row r="199">
-      <c r="A199" s="32" t="inlineStr">
+      <c r="A199" s="26" t="inlineStr">
         <is>
           <t>BAG</t>
         </is>
       </c>
-      <c r="B199" s="32" t="n"/>
-      <c r="C199" s="33" t="inlineStr">
+      <c r="B199" s="26" t="n"/>
+      <c r="C199" s="27" t="inlineStr">
         <is>
           <t>Creole Marinade</t>
         </is>
       </c>
-      <c r="D199" s="33" t="n"/>
-      <c r="E199" s="32" t="n"/>
-      <c r="F199" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G199" s="34" t="n">
+      <c r="D199" s="27" t="n"/>
+      <c r="E199" s="26" t="n"/>
+      <c r="F199" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G199" s="28" t="n">
         <v>1.81</v>
       </c>
-      <c r="H199" s="35" t="n">
+      <c r="H199" s="29" t="n">
         <v>1.81</v>
       </c>
-      <c r="I199" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J199" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K199" s="35" t="n">
+      <c r="I199" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J199" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K199" s="29" t="n">
         <v>1.81</v>
       </c>
-      <c r="L199" s="33" t="inlineStr">
+      <c r="L199" s="27" t="inlineStr">
         <is>
           <t>per Bag (None)</t>
         </is>
       </c>
-      <c r="M199" s="32" t="n"/>
-      <c r="N199" s="34">
+      <c r="M199" s="26" t="n"/>
+      <c r="N199" s="28">
         <f>M199*G199</f>
         <v/>
       </c>
-      <c r="O199" s="32" t="n"/>
-      <c r="P199" s="32" t="n"/>
-      <c r="Q199" s="32" t="n"/>
-      <c r="R199" s="32" t="n"/>
-      <c r="S199" s="32" t="n"/>
+      <c r="O199" s="26" t="n"/>
+      <c r="P199" s="26" t="n"/>
+      <c r="Q199" s="26" t="n"/>
+      <c r="R199" s="26" t="n"/>
+      <c r="S199" s="26" t="n"/>
     </row>
     <row r="200">
-      <c r="A200" s="32" t="inlineStr">
+      <c r="A200" s="26" t="inlineStr">
         <is>
           <t>BAG</t>
         </is>
       </c>
-      <c r="B200" s="32" t="n"/>
-      <c r="C200" s="33" t="inlineStr">
+      <c r="B200" s="26" t="n"/>
+      <c r="C200" s="27" t="inlineStr">
         <is>
           <t>Spicy Marinade</t>
         </is>
       </c>
-      <c r="D200" s="33" t="n"/>
-      <c r="E200" s="32" t="n"/>
-      <c r="F200" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G200" s="34" t="n">
+      <c r="D200" s="27" t="n"/>
+      <c r="E200" s="26" t="n"/>
+      <c r="F200" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G200" s="28" t="n">
         <v>5.27</v>
       </c>
-      <c r="H200" s="35" t="n">
+      <c r="H200" s="29" t="n">
         <v>5.27</v>
       </c>
-      <c r="I200" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J200" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K200" s="35" t="n">
+      <c r="I200" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J200" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K200" s="29" t="n">
         <v>5.27</v>
       </c>
-      <c r="L200" s="33" t="inlineStr">
+      <c r="L200" s="27" t="inlineStr">
         <is>
           <t>per Bag (None)</t>
         </is>
       </c>
-      <c r="M200" s="32" t="n"/>
-      <c r="N200" s="34">
+      <c r="M200" s="26" t="n"/>
+      <c r="N200" s="28">
         <f>M200*G200</f>
         <v/>
       </c>
-      <c r="O200" s="32" t="n"/>
-      <c r="P200" s="32" t="n"/>
-      <c r="Q200" s="32" t="n"/>
-      <c r="R200" s="32" t="n"/>
-      <c r="S200" s="32" t="n"/>
+      <c r="O200" s="26" t="n"/>
+      <c r="P200" s="26" t="n"/>
+      <c r="Q200" s="26" t="n"/>
+      <c r="R200" s="26" t="n"/>
+      <c r="S200" s="26" t="n"/>
     </row>
     <row r="201">
-      <c r="A201" s="32" t="inlineStr">
+      <c r="A201" s="26" t="inlineStr">
         <is>
           <t>BAG</t>
         </is>
       </c>
-      <c r="B201" s="32" t="n"/>
-      <c r="C201" s="33" t="inlineStr">
+      <c r="B201" s="26" t="n"/>
+      <c r="C201" s="27" t="inlineStr">
         <is>
           <t>Batter Mix</t>
         </is>
       </c>
-      <c r="D201" s="33" t="n"/>
-      <c r="E201" s="32" t="n"/>
-      <c r="F201" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G201" s="34" t="n">
+      <c r="D201" s="27" t="n"/>
+      <c r="E201" s="26" t="n"/>
+      <c r="F201" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G201" s="28" t="n">
         <v>2.5</v>
       </c>
-      <c r="H201" s="35" t="n">
+      <c r="H201" s="29" t="n">
         <v>2.5</v>
       </c>
-      <c r="I201" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J201" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K201" s="35" t="n">
+      <c r="I201" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J201" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K201" s="29" t="n">
         <v>2.5</v>
       </c>
-      <c r="L201" s="33" t="inlineStr">
+      <c r="L201" s="27" t="inlineStr">
         <is>
           <t>per Bag (None)</t>
         </is>
       </c>
-      <c r="M201" s="32" t="n"/>
-      <c r="N201" s="34">
+      <c r="M201" s="26" t="n"/>
+      <c r="N201" s="28">
         <f>M201*G201</f>
         <v/>
       </c>
-      <c r="O201" s="32" t="n"/>
-      <c r="P201" s="32" t="n"/>
-      <c r="Q201" s="32" t="n"/>
-      <c r="R201" s="32" t="n"/>
-      <c r="S201" s="32" t="n"/>
-    </row>
-    <row r="202">
-      <c r="A202" s="26" t="n"/>
-      <c r="B202" s="26" t="inlineStr">
-        <is>
-          <t>Imperial</t>
-        </is>
-      </c>
-      <c r="C202" s="27" t="n"/>
-      <c r="D202" s="27" t="n"/>
-      <c r="E202" s="26" t="n"/>
-      <c r="F202" s="26" t="n"/>
-      <c r="G202" s="28" t="n"/>
-      <c r="H202" s="29" t="n"/>
-      <c r="I202" s="30" t="n"/>
-      <c r="J202" s="31" t="n"/>
-      <c r="K202" s="29" t="n"/>
-      <c r="L202" s="27" t="inlineStr">
-        <is>
-          <t>see label</t>
-        </is>
-      </c>
-      <c r="M202" s="26" t="n"/>
-      <c r="N202" s="28">
-        <f>M202*G202</f>
-        <v/>
-      </c>
-      <c r="O202" s="26" t="n"/>
-      <c r="P202" s="26" t="n"/>
-      <c r="Q202" s="26" t="n"/>
-      <c r="R202" s="26" t="n"/>
-      <c r="S202" s="26" t="n"/>
+      <c r="O201" s="26" t="n"/>
+      <c r="P201" s="26" t="n"/>
+      <c r="Q201" s="26" t="n"/>
+      <c r="R201" s="26" t="n"/>
+      <c r="S201" s="26" t="n"/>
+    </row>
+    <row r="202" ht="18" customHeight="1">
+      <c r="A202" s="32" t="inlineStr">
+        <is>
+          <t>─── IMPERIAL / LOCAL VENDORS (prices not in BEK) ───</t>
+        </is>
+      </c>
+      <c r="B202" s="33" t="n"/>
+      <c r="C202" s="33" t="n"/>
+      <c r="D202" s="33" t="n"/>
+      <c r="E202" s="33" t="n"/>
+      <c r="F202" s="33" t="n"/>
+      <c r="G202" s="33" t="n"/>
+      <c r="H202" s="33" t="n"/>
+      <c r="I202" s="33" t="n"/>
+      <c r="J202" s="33" t="n"/>
+      <c r="K202" s="33" t="n"/>
+      <c r="L202" s="33" t="n"/>
+      <c r="M202" s="33" t="n"/>
+      <c r="N202" s="33" t="n"/>
+      <c r="O202" s="33" t="n"/>
+      <c r="P202" s="33" t="n"/>
+      <c r="Q202" s="33" t="n"/>
+      <c r="R202" s="33" t="n"/>
+      <c r="S202" s="34" t="n"/>
     </row>
     <row r="203">
-      <c r="A203" s="32" t="inlineStr">
+      <c r="A203" s="2" t="inlineStr">
         <is>
           <t>PACK</t>
         </is>
       </c>
-      <c r="B203" s="32" t="n"/>
-      <c r="C203" s="33" t="inlineStr">
+      <c r="B203" s="2" t="n"/>
+      <c r="C203" s="3" t="inlineStr">
         <is>
           <t>Bayou Blend Pork</t>
         </is>
       </c>
-      <c r="D203" s="33" t="n"/>
-      <c r="E203" s="32" t="inlineStr">
+      <c r="D203" s="3" t="n"/>
+      <c r="E203" s="2" t="inlineStr">
         <is>
           <t>5 Packs</t>
         </is>
       </c>
-      <c r="F203" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G203" s="34" t="n">
+      <c r="F203" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G203" s="4" t="n">
         <v>7.48</v>
       </c>
-      <c r="H203" s="35" t="n">
+      <c r="H203" s="5" t="n">
         <v>7.48</v>
       </c>
-      <c r="I203" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J203" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K203" s="35" t="n">
+      <c r="I203" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J203" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K203" s="5" t="n">
         <v>1.496</v>
       </c>
-      <c r="L203" s="33" t="inlineStr">
+      <c r="L203" s="3" t="inlineStr">
         <is>
           <t>per Pack (5 Packs)</t>
         </is>
       </c>
-      <c r="M203" s="32" t="n"/>
-      <c r="N203" s="34">
+      <c r="M203" s="2" t="n"/>
+      <c r="N203" s="4">
         <f>M203*G203</f>
         <v/>
       </c>
-      <c r="O203" s="32" t="n"/>
-      <c r="P203" s="32" t="n"/>
-      <c r="Q203" s="32" t="n"/>
-      <c r="R203" s="32" t="n"/>
-      <c r="S203" s="32" t="n"/>
+      <c r="O203" s="2" t="n"/>
+      <c r="P203" s="2" t="n"/>
+      <c r="Q203" s="2" t="n"/>
+      <c r="R203" s="2" t="n"/>
+      <c r="S203" s="2" t="n"/>
     </row>
     <row r="204">
-      <c r="A204" s="32" t="inlineStr">
+      <c r="A204" s="2" t="inlineStr">
         <is>
           <t>PACK</t>
         </is>
       </c>
-      <c r="B204" s="32" t="n"/>
-      <c r="C204" s="33" t="inlineStr">
+      <c r="B204" s="2" t="n"/>
+      <c r="C204" s="3" t="inlineStr">
         <is>
           <t>Bayou Blend Alligator</t>
         </is>
       </c>
-      <c r="D204" s="33" t="n"/>
-      <c r="E204" s="32" t="inlineStr">
+      <c r="D204" s="3" t="n"/>
+      <c r="E204" s="2" t="inlineStr">
         <is>
           <t>5 Pack</t>
         </is>
       </c>
-      <c r="F204" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G204" s="34" t="n">
+      <c r="F204" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G204" s="4" t="n">
         <v>9.890000000000001</v>
       </c>
-      <c r="H204" s="35" t="n">
+      <c r="H204" s="5" t="n">
         <v>9.890000000000001</v>
       </c>
-      <c r="I204" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J204" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K204" s="35" t="n">
+      <c r="I204" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J204" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K204" s="5" t="n">
         <v>1.978</v>
       </c>
-      <c r="L204" s="33" t="inlineStr">
+      <c r="L204" s="3" t="inlineStr">
         <is>
           <t>per Pack (5 Pack)</t>
         </is>
       </c>
-      <c r="M204" s="32" t="n"/>
-      <c r="N204" s="34">
+      <c r="M204" s="2" t="n"/>
+      <c r="N204" s="4">
         <f>M204*G204</f>
         <v/>
       </c>
-      <c r="O204" s="32" t="n"/>
-      <c r="P204" s="32" t="n"/>
-      <c r="Q204" s="32" t="n"/>
-      <c r="R204" s="32" t="n"/>
-      <c r="S204" s="32" t="n"/>
+      <c r="O204" s="2" t="n"/>
+      <c r="P204" s="2" t="n"/>
+      <c r="Q204" s="2" t="n"/>
+      <c r="R204" s="2" t="n"/>
+      <c r="S204" s="2" t="n"/>
     </row>
     <row r="205">
-      <c r="A205" s="32" t="inlineStr">
+      <c r="A205" s="2" t="inlineStr">
         <is>
           <t>PACK</t>
         </is>
       </c>
-      <c r="B205" s="32" t="n"/>
-      <c r="C205" s="33" t="inlineStr">
+      <c r="B205" s="2" t="n"/>
+      <c r="C205" s="3" t="inlineStr">
         <is>
           <t>Bayou Blend Crawfish</t>
         </is>
       </c>
-      <c r="D205" s="33" t="n"/>
-      <c r="E205" s="32" t="inlineStr">
+      <c r="D205" s="3" t="n"/>
+      <c r="E205" s="2" t="inlineStr">
         <is>
           <t>5 Packs</t>
         </is>
       </c>
-      <c r="F205" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G205" s="34" t="n">
+      <c r="F205" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G205" s="4" t="n">
         <v>9.1</v>
       </c>
-      <c r="H205" s="35" t="n">
+      <c r="H205" s="5" t="n">
         <v>9.1</v>
       </c>
-      <c r="I205" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J205" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K205" s="35" t="n">
+      <c r="I205" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J205" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K205" s="5" t="n">
         <v>1.82</v>
       </c>
-      <c r="L205" s="33" t="inlineStr">
+      <c r="L205" s="3" t="inlineStr">
         <is>
           <t>per Pack (5 Packs)</t>
         </is>
       </c>
-      <c r="M205" s="32" t="n"/>
-      <c r="N205" s="34">
+      <c r="M205" s="2" t="n"/>
+      <c r="N205" s="4">
         <f>M205*G205</f>
         <v/>
       </c>
-      <c r="O205" s="32" t="n"/>
-      <c r="P205" s="32" t="n"/>
-      <c r="Q205" s="32" t="n"/>
-      <c r="R205" s="32" t="n"/>
-      <c r="S205" s="32" t="n"/>
+      <c r="O205" s="2" t="n"/>
+      <c r="P205" s="2" t="n"/>
+      <c r="Q205" s="2" t="n"/>
+      <c r="R205" s="2" t="n"/>
+      <c r="S205" s="2" t="n"/>
     </row>
     <row r="206">
-      <c r="A206" s="32" t="inlineStr">
+      <c r="A206" s="2" t="inlineStr">
         <is>
           <t>PACK</t>
         </is>
       </c>
-      <c r="B206" s="32" t="n"/>
-      <c r="C206" s="33" t="inlineStr">
+      <c r="B206" s="2" t="n"/>
+      <c r="C206" s="3" t="inlineStr">
         <is>
           <t>Bayou Blend Shrimp</t>
         </is>
       </c>
-      <c r="D206" s="33" t="n"/>
-      <c r="E206" s="32" t="inlineStr">
+      <c r="D206" s="3" t="n"/>
+      <c r="E206" s="2" t="inlineStr">
         <is>
           <t>5 Packs</t>
         </is>
       </c>
-      <c r="F206" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G206" s="34" t="n">
+      <c r="F206" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G206" s="4" t="n">
         <v>8.08</v>
       </c>
-      <c r="H206" s="35" t="n">
+      <c r="H206" s="5" t="n">
         <v>8.08</v>
       </c>
-      <c r="I206" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J206" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K206" s="35" t="n">
+      <c r="I206" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J206" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K206" s="5" t="n">
         <v>1.616</v>
       </c>
-      <c r="L206" s="33" t="inlineStr">
+      <c r="L206" s="3" t="inlineStr">
         <is>
           <t>per Pack (5 Packs)</t>
         </is>
       </c>
-      <c r="M206" s="32" t="n"/>
-      <c r="N206" s="34">
+      <c r="M206" s="2" t="n"/>
+      <c r="N206" s="4">
         <f>M206*G206</f>
         <v/>
       </c>
-      <c r="O206" s="32" t="n"/>
-      <c r="P206" s="32" t="n"/>
-      <c r="Q206" s="32" t="n"/>
-      <c r="R206" s="32" t="n"/>
-      <c r="S206" s="32" t="n"/>
+      <c r="O206" s="2" t="n"/>
+      <c r="P206" s="2" t="n"/>
+      <c r="Q206" s="2" t="n"/>
+      <c r="R206" s="2" t="n"/>
+      <c r="S206" s="2" t="n"/>
     </row>
     <row r="207">
-      <c r="A207" s="32" t="inlineStr">
+      <c r="A207" s="2" t="inlineStr">
         <is>
           <t>CAN</t>
         </is>
       </c>
-      <c r="B207" s="32" t="n"/>
-      <c r="C207" s="33" t="inlineStr">
+      <c r="B207" s="2" t="n"/>
+      <c r="C207" s="3" t="inlineStr">
         <is>
           <t>Peanuts Regular/Cajun</t>
         </is>
       </c>
-      <c r="D207" s="33" t="n"/>
-      <c r="E207" s="32" t="inlineStr">
+      <c r="D207" s="3" t="n"/>
+      <c r="E207" s="2" t="inlineStr">
         <is>
           <t>6 Cans</t>
         </is>
       </c>
-      <c r="F207" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G207" s="34" t="n">
+      <c r="F207" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G207" s="4" t="n">
         <v>8.33</v>
       </c>
-      <c r="H207" s="35" t="n">
+      <c r="H207" s="5" t="n">
         <v>8.33</v>
       </c>
-      <c r="I207" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J207" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K207" s="35" t="n">
+      <c r="I207" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J207" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K207" s="5" t="n">
         <v>1.388333333333333</v>
       </c>
-      <c r="L207" s="33" t="inlineStr">
+      <c r="L207" s="3" t="inlineStr">
         <is>
           <t>per Can (6 Cans)</t>
         </is>
       </c>
-      <c r="M207" s="32" t="n"/>
-      <c r="N207" s="34">
+      <c r="M207" s="2" t="n"/>
+      <c r="N207" s="4">
         <f>M207*G207</f>
         <v/>
       </c>
-      <c r="O207" s="32" t="n"/>
-      <c r="P207" s="32" t="n"/>
-      <c r="Q207" s="32" t="n"/>
-      <c r="R207" s="32" t="n"/>
-      <c r="S207" s="32" t="n"/>
+      <c r="O207" s="2" t="n"/>
+      <c r="P207" s="2" t="n"/>
+      <c r="Q207" s="2" t="n"/>
+      <c r="R207" s="2" t="n"/>
+      <c r="S207" s="2" t="n"/>
     </row>
     <row r="208">
-      <c r="A208" s="32" t="inlineStr">
+      <c r="A208" s="2" t="inlineStr">
         <is>
           <t>SLEEVE</t>
         </is>
       </c>
-      <c r="B208" s="32" t="n"/>
-      <c r="C208" s="33" t="inlineStr">
+      <c r="B208" s="2" t="n"/>
+      <c r="C208" s="3" t="inlineStr">
         <is>
           <t>16oz Peanut Cup</t>
         </is>
       </c>
-      <c r="D208" s="33" t="n"/>
-      <c r="E208" s="32" t="inlineStr">
+      <c r="D208" s="3" t="n"/>
+      <c r="E208" s="2" t="inlineStr">
         <is>
           <t>20 Sleeves</t>
         </is>
       </c>
-      <c r="F208" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G208" s="34" t="n">
+      <c r="F208" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G208" s="4" t="n">
         <v>8.01</v>
       </c>
-      <c r="H208" s="35" t="n">
+      <c r="H208" s="5" t="n">
         <v>8.01</v>
       </c>
-      <c r="I208" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J208" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K208" s="35" t="n">
+      <c r="I208" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J208" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K208" s="5" t="n">
         <v>0.4005</v>
       </c>
-      <c r="L208" s="33" t="inlineStr">
+      <c r="L208" s="3" t="inlineStr">
         <is>
           <t>per Sleeve (20 Sleeves)</t>
         </is>
       </c>
-      <c r="M208" s="32" t="n"/>
-      <c r="N208" s="34">
+      <c r="M208" s="2" t="n"/>
+      <c r="N208" s="4">
         <f>M208*G208</f>
         <v/>
       </c>
-      <c r="O208" s="32" t="n"/>
-      <c r="P208" s="32" t="n"/>
-      <c r="Q208" s="32" t="n"/>
-      <c r="R208" s="32" t="n"/>
-      <c r="S208" s="32" t="n"/>
+      <c r="O208" s="2" t="n"/>
+      <c r="P208" s="2" t="n"/>
+      <c r="Q208" s="2" t="n"/>
+      <c r="R208" s="2" t="n"/>
+      <c r="S208" s="2" t="n"/>
     </row>
     <row r="209">
-      <c r="A209" s="32" t="inlineStr">
+      <c r="A209" s="2" t="inlineStr">
         <is>
           <t>SLEEVE</t>
         </is>
       </c>
-      <c r="B209" s="32" t="n"/>
-      <c r="C209" s="33" t="inlineStr">
+      <c r="B209" s="2" t="n"/>
+      <c r="C209" s="3" t="inlineStr">
         <is>
           <t>32oz Peanut Cup</t>
         </is>
       </c>
-      <c r="D209" s="33" t="n"/>
-      <c r="E209" s="32" t="inlineStr">
+      <c r="D209" s="3" t="n"/>
+      <c r="E209" s="2" t="inlineStr">
         <is>
           <t>20 Sleeves</t>
         </is>
       </c>
-      <c r="F209" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G209" s="34" t="n">
+      <c r="F209" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G209" s="4" t="n">
         <v>10.22</v>
       </c>
-      <c r="H209" s="35" t="n">
+      <c r="H209" s="5" t="n">
         <v>10.22</v>
       </c>
-      <c r="I209" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J209" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K209" s="35" t="n">
+      <c r="I209" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J209" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K209" s="5" t="n">
         <v>0.511</v>
       </c>
-      <c r="L209" s="33" t="inlineStr">
+      <c r="L209" s="3" t="inlineStr">
         <is>
           <t>per Sleeve (20 Sleeves)</t>
         </is>
       </c>
-      <c r="M209" s="32" t="n"/>
-      <c r="N209" s="34">
+      <c r="M209" s="2" t="n"/>
+      <c r="N209" s="4">
         <f>M209*G209</f>
         <v/>
       </c>
-      <c r="O209" s="32" t="n"/>
-      <c r="P209" s="32" t="n"/>
-      <c r="Q209" s="32" t="n"/>
-      <c r="R209" s="32" t="n"/>
-      <c r="S209" s="32" t="n"/>
+      <c r="O209" s="2" t="n"/>
+      <c r="P209" s="2" t="n"/>
+      <c r="Q209" s="2" t="n"/>
+      <c r="R209" s="2" t="n"/>
+      <c r="S209" s="2" t="n"/>
     </row>
     <row r="210">
-      <c r="A210" s="32" t="inlineStr">
+      <c r="A210" s="2" t="inlineStr">
         <is>
           <t>SLEEVE</t>
         </is>
       </c>
-      <c r="B210" s="32" t="n"/>
-      <c r="C210" s="33" t="inlineStr">
+      <c r="B210" s="2" t="n"/>
+      <c r="C210" s="3" t="inlineStr">
         <is>
           <t>Peanut Cup Lid</t>
         </is>
       </c>
-      <c r="D210" s="33" t="n"/>
-      <c r="E210" s="32" t="inlineStr">
+      <c r="D210" s="3" t="n"/>
+      <c r="E210" s="2" t="inlineStr">
         <is>
           <t>10 Sleeves</t>
         </is>
       </c>
-      <c r="F210" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G210" s="34" t="n">
+      <c r="F210" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G210" s="4" t="n">
         <v>5.01</v>
       </c>
-      <c r="H210" s="35" t="n">
+      <c r="H210" s="5" t="n">
         <v>5.01</v>
       </c>
-      <c r="I210" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J210" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K210" s="35" t="n">
+      <c r="I210" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J210" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K210" s="5" t="n">
         <v>0.501</v>
       </c>
-      <c r="L210" s="33" t="inlineStr">
+      <c r="L210" s="3" t="inlineStr">
         <is>
           <t>per Sleeve (10 Sleeves)</t>
         </is>
       </c>
-      <c r="M210" s="32" t="n"/>
-      <c r="N210" s="34">
+      <c r="M210" s="2" t="n"/>
+      <c r="N210" s="4">
         <f>M210*G210</f>
         <v/>
       </c>
-      <c r="O210" s="32" t="n"/>
-      <c r="P210" s="32" t="n"/>
-      <c r="Q210" s="32" t="n"/>
-      <c r="R210" s="32" t="n"/>
-      <c r="S210" s="32" t="n"/>
+      <c r="O210" s="2" t="n"/>
+      <c r="P210" s="2" t="n"/>
+      <c r="Q210" s="2" t="n"/>
+      <c r="R210" s="2" t="n"/>
+      <c r="S210" s="2" t="n"/>
     </row>
     <row r="211">
-      <c r="A211" s="32" t="inlineStr">
+      <c r="A211" s="2" t="inlineStr">
         <is>
           <t>BAG</t>
         </is>
       </c>
-      <c r="B211" s="32" t="n"/>
-      <c r="C211" s="33" t="inlineStr">
+      <c r="B211" s="2" t="n"/>
+      <c r="C211" s="3" t="inlineStr">
         <is>
           <t>Gizzards</t>
         </is>
       </c>
-      <c r="D211" s="33" t="n"/>
-      <c r="E211" s="32" t="inlineStr">
+      <c r="D211" s="3" t="n"/>
+      <c r="E211" s="2" t="inlineStr">
         <is>
           <t>4/Box</t>
         </is>
       </c>
-      <c r="F211" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G211" s="34" t="n">
+      <c r="F211" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G211" s="4" t="n">
         <v>19.8</v>
       </c>
-      <c r="H211" s="35" t="n">
+      <c r="H211" s="5" t="n">
         <v>19.8</v>
       </c>
-      <c r="I211" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J211" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K211" s="35" t="n">
+      <c r="I211" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J211" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K211" s="5" t="n">
         <v>4.95</v>
       </c>
-      <c r="L211" s="33" t="inlineStr">
+      <c r="L211" s="3" t="inlineStr">
         <is>
           <t>per Bag (4/Box)</t>
         </is>
       </c>
-      <c r="M211" s="32" t="n"/>
-      <c r="N211" s="34">
+      <c r="M211" s="2" t="n"/>
+      <c r="N211" s="4">
         <f>M211*G211</f>
         <v/>
       </c>
-      <c r="O211" s="32" t="n"/>
-      <c r="P211" s="32" t="n"/>
-      <c r="Q211" s="32" t="n"/>
-      <c r="R211" s="32" t="n"/>
-      <c r="S211" s="32" t="n"/>
+      <c r="O211" s="2" t="n"/>
+      <c r="P211" s="2" t="n"/>
+      <c r="Q211" s="2" t="n"/>
+      <c r="R211" s="2" t="n"/>
+      <c r="S211" s="2" t="n"/>
     </row>
     <row r="212">
-      <c r="A212" s="32" t="inlineStr">
+      <c r="A212" s="2" t="inlineStr">
         <is>
           <t>BAG</t>
         </is>
       </c>
-      <c r="B212" s="32" t="n"/>
-      <c r="C212" s="33" t="inlineStr">
+      <c r="B212" s="2" t="n"/>
+      <c r="C212" s="3" t="inlineStr">
         <is>
           <t>Livers</t>
         </is>
       </c>
-      <c r="D212" s="33" t="n"/>
-      <c r="E212" s="32" t="inlineStr">
+      <c r="D212" s="3" t="n"/>
+      <c r="E212" s="2" t="inlineStr">
         <is>
           <t>4/Box</t>
         </is>
       </c>
-      <c r="F212" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G212" s="34" t="n">
+      <c r="F212" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G212" s="4" t="n">
         <v>14.78</v>
       </c>
-      <c r="H212" s="35" t="n">
+      <c r="H212" s="5" t="n">
         <v>14.78</v>
       </c>
-      <c r="I212" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J212" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K212" s="35" t="n">
+      <c r="I212" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J212" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K212" s="5" t="n">
         <v>3.695</v>
       </c>
-      <c r="L212" s="33" t="inlineStr">
+      <c r="L212" s="3" t="inlineStr">
         <is>
           <t>per Bag (4/Box)</t>
         </is>
       </c>
-      <c r="M212" s="32" t="n"/>
-      <c r="N212" s="34">
+      <c r="M212" s="2" t="n"/>
+      <c r="N212" s="4">
         <f>M212*G212</f>
         <v/>
       </c>
-      <c r="O212" s="32" t="n"/>
-      <c r="P212" s="32" t="n"/>
-      <c r="Q212" s="32" t="n"/>
-      <c r="R212" s="32" t="n"/>
-      <c r="S212" s="32" t="n"/>
+      <c r="O212" s="2" t="n"/>
+      <c r="P212" s="2" t="n"/>
+      <c r="Q212" s="2" t="n"/>
+      <c r="R212" s="2" t="n"/>
+      <c r="S212" s="2" t="n"/>
     </row>
     <row r="213">
-      <c r="A213" s="32" t="inlineStr">
+      <c r="A213" s="2" t="inlineStr">
         <is>
           <t>BAG</t>
         </is>
       </c>
-      <c r="B213" s="32" t="n"/>
-      <c r="C213" s="33" t="inlineStr">
+      <c r="B213" s="2" t="n"/>
+      <c r="C213" s="3" t="inlineStr">
         <is>
           <t>Brisket</t>
         </is>
       </c>
-      <c r="D213" s="33" t="n"/>
-      <c r="E213" s="32" t="n"/>
-      <c r="F213" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G213" s="34" t="n">
+      <c r="D213" s="3" t="n"/>
+      <c r="E213" s="2" t="n"/>
+      <c r="F213" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G213" s="4" t="n">
         <v>29.44</v>
       </c>
-      <c r="H213" s="35" t="n">
+      <c r="H213" s="5" t="n">
         <v>29.44</v>
       </c>
-      <c r="I213" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J213" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K213" s="35" t="n">
+      <c r="I213" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J213" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K213" s="5" t="n">
         <v>29.44</v>
       </c>
-      <c r="L213" s="33" t="inlineStr">
+      <c r="L213" s="3" t="inlineStr">
         <is>
           <t>per Bag (None)</t>
         </is>
       </c>
-      <c r="M213" s="32" t="n"/>
-      <c r="N213" s="34">
+      <c r="M213" s="2" t="n"/>
+      <c r="N213" s="4">
         <f>M213*G213</f>
         <v/>
       </c>
-      <c r="O213" s="32" t="n"/>
-      <c r="P213" s="32" t="n"/>
-      <c r="Q213" s="32" t="n"/>
-      <c r="R213" s="32" t="n"/>
-      <c r="S213" s="32" t="n"/>
+      <c r="O213" s="2" t="n"/>
+      <c r="P213" s="2" t="n"/>
+      <c r="Q213" s="2" t="n"/>
+      <c r="R213" s="2" t="n"/>
+      <c r="S213" s="2" t="n"/>
     </row>
     <row r="214">
-      <c r="A214" s="32" t="inlineStr">
+      <c r="A214" s="2" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="B214" s="32" t="n"/>
-      <c r="C214" s="33" t="inlineStr">
+      <c r="B214" s="2" t="n"/>
+      <c r="C214" s="3" t="inlineStr">
         <is>
           <t>Kolache Boudin Link Org</t>
         </is>
       </c>
-      <c r="D214" s="33" t="n"/>
-      <c r="E214" s="32" t="n"/>
-      <c r="F214" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G214" s="34" t="n">
+      <c r="D214" s="3" t="n"/>
+      <c r="E214" s="2" t="n"/>
+      <c r="F214" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G214" s="4" t="n">
         <v>69.77</v>
       </c>
-      <c r="H214" s="35" t="n">
+      <c r="H214" s="5" t="n">
         <v>69.77</v>
       </c>
-      <c r="I214" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J214" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K214" s="35" t="n">
+      <c r="I214" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J214" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K214" s="5" t="n">
         <v>69.77</v>
       </c>
-      <c r="L214" s="33" t="inlineStr">
+      <c r="L214" s="3" t="inlineStr">
         <is>
           <t>per Case (None)</t>
         </is>
       </c>
-      <c r="M214" s="32" t="n"/>
-      <c r="N214" s="34">
+      <c r="M214" s="2" t="n"/>
+      <c r="N214" s="4">
         <f>M214*G214</f>
         <v/>
       </c>
-      <c r="O214" s="32" t="n"/>
-      <c r="P214" s="32" t="n"/>
-      <c r="Q214" s="32" t="n"/>
-      <c r="R214" s="32" t="n"/>
-      <c r="S214" s="32" t="n"/>
+      <c r="O214" s="2" t="n"/>
+      <c r="P214" s="2" t="n"/>
+      <c r="Q214" s="2" t="n"/>
+      <c r="R214" s="2" t="n"/>
+      <c r="S214" s="2" t="n"/>
     </row>
     <row r="215">
-      <c r="A215" s="32" t="inlineStr">
+      <c r="A215" s="2" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="B215" s="32" t="n"/>
-      <c r="C215" s="33" t="inlineStr">
+      <c r="B215" s="2" t="n"/>
+      <c r="C215" s="3" t="inlineStr">
         <is>
           <t>Kolache Sausage Egg &amp; Cheese</t>
         </is>
       </c>
-      <c r="D215" s="33" t="n"/>
-      <c r="E215" s="32" t="n"/>
-      <c r="F215" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G215" s="34" t="n">
+      <c r="D215" s="3" t="n"/>
+      <c r="E215" s="2" t="n"/>
+      <c r="F215" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G215" s="4" t="n">
         <v>69.77</v>
       </c>
-      <c r="H215" s="35" t="n">
+      <c r="H215" s="5" t="n">
         <v>69.77</v>
       </c>
-      <c r="I215" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J215" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K215" s="35" t="n">
+      <c r="I215" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J215" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K215" s="5" t="n">
         <v>69.77</v>
       </c>
-      <c r="L215" s="33" t="inlineStr">
+      <c r="L215" s="3" t="inlineStr">
         <is>
           <t>per Case (None)</t>
         </is>
       </c>
-      <c r="M215" s="32" t="n"/>
-      <c r="N215" s="34">
+      <c r="M215" s="2" t="n"/>
+      <c r="N215" s="4">
         <f>M215*G215</f>
         <v/>
       </c>
-      <c r="O215" s="32" t="n"/>
-      <c r="P215" s="32" t="n"/>
-      <c r="Q215" s="32" t="n"/>
-      <c r="R215" s="32" t="n"/>
-      <c r="S215" s="32" t="n"/>
+      <c r="O215" s="2" t="n"/>
+      <c r="P215" s="2" t="n"/>
+      <c r="Q215" s="2" t="n"/>
+      <c r="R215" s="2" t="n"/>
+      <c r="S215" s="2" t="n"/>
     </row>
     <row r="216">
-      <c r="A216" s="32" t="inlineStr">
+      <c r="A216" s="2" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="B216" s="32" t="n"/>
-      <c r="C216" s="33" t="inlineStr">
+      <c r="B216" s="2" t="n"/>
+      <c r="C216" s="3" t="inlineStr">
         <is>
           <t>Wrap Jalapeno Popper</t>
         </is>
       </c>
-      <c r="D216" s="33" t="n"/>
-      <c r="E216" s="32" t="n"/>
-      <c r="F216" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G216" s="34" t="n">
+      <c r="D216" s="3" t="n"/>
+      <c r="E216" s="2" t="n"/>
+      <c r="F216" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G216" s="4" t="n">
         <v>93.03</v>
       </c>
-      <c r="H216" s="35" t="n">
+      <c r="H216" s="5" t="n">
         <v>93.03</v>
       </c>
-      <c r="I216" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J216" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K216" s="35" t="n">
+      <c r="I216" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J216" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K216" s="5" t="n">
         <v>93.03</v>
       </c>
-      <c r="L216" s="33" t="inlineStr">
+      <c r="L216" s="3" t="inlineStr">
         <is>
           <t>per Case (None)</t>
         </is>
       </c>
-      <c r="M216" s="32" t="n"/>
-      <c r="N216" s="34">
+      <c r="M216" s="2" t="n"/>
+      <c r="N216" s="4">
         <f>M216*G216</f>
         <v/>
       </c>
-      <c r="O216" s="32" t="n"/>
-      <c r="P216" s="32" t="n"/>
-      <c r="Q216" s="32" t="n"/>
-      <c r="R216" s="32" t="n"/>
-      <c r="S216" s="32" t="n"/>
+      <c r="O216" s="2" t="n"/>
+      <c r="P216" s="2" t="n"/>
+      <c r="Q216" s="2" t="n"/>
+      <c r="R216" s="2" t="n"/>
+      <c r="S216" s="2" t="n"/>
     </row>
     <row r="217">
-      <c r="A217" s="32" t="inlineStr">
+      <c r="A217" s="2" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="B217" s="32" t="n"/>
-      <c r="C217" s="33" t="inlineStr">
+      <c r="B217" s="2" t="n"/>
+      <c r="C217" s="3" t="inlineStr">
         <is>
           <t>Deer Burrito</t>
         </is>
       </c>
-      <c r="D217" s="33" t="n"/>
-      <c r="E217" s="32" t="n"/>
-      <c r="F217" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G217" s="34" t="n">
+      <c r="D217" s="3" t="n"/>
+      <c r="E217" s="2" t="n"/>
+      <c r="F217" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G217" s="4" t="n">
         <v>449</v>
       </c>
-      <c r="H217" s="35" t="n">
+      <c r="H217" s="5" t="n">
         <v>449</v>
       </c>
-      <c r="I217" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J217" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K217" s="35" t="n">
+      <c r="I217" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J217" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K217" s="5" t="n">
         <v>449</v>
       </c>
-      <c r="L217" s="33" t="inlineStr">
+      <c r="L217" s="3" t="inlineStr">
         <is>
           <t>per Case (None)</t>
         </is>
       </c>
-      <c r="M217" s="32" t="n"/>
-      <c r="N217" s="34">
+      <c r="M217" s="2" t="n"/>
+      <c r="N217" s="4">
         <f>M217*G217</f>
         <v/>
       </c>
-      <c r="O217" s="32" t="n"/>
-      <c r="P217" s="32" t="n"/>
-      <c r="Q217" s="32" t="n"/>
-      <c r="R217" s="32" t="n"/>
-      <c r="S217" s="32" t="n"/>
+      <c r="O217" s="2" t="n"/>
+      <c r="P217" s="2" t="n"/>
+      <c r="Q217" s="2" t="n"/>
+      <c r="R217" s="2" t="n"/>
+      <c r="S217" s="2" t="n"/>
     </row>
     <row r="218">
-      <c r="A218" s="32" t="inlineStr">
+      <c r="A218" s="2" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="B218" s="32" t="n"/>
-      <c r="C218" s="33" t="inlineStr">
+      <c r="B218" s="2" t="n"/>
+      <c r="C218" s="3" t="inlineStr">
         <is>
           <t>Jalapeno Cheddar Kolache</t>
         </is>
       </c>
-      <c r="D218" s="33" t="n"/>
-      <c r="E218" s="32" t="n"/>
-      <c r="F218" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G218" s="34" t="n">
+      <c r="D218" s="3" t="n"/>
+      <c r="E218" s="2" t="n"/>
+      <c r="F218" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G218" s="4" t="n">
         <v>69.77</v>
       </c>
-      <c r="H218" s="35" t="n">
+      <c r="H218" s="5" t="n">
         <v>69.77</v>
       </c>
-      <c r="I218" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J218" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K218" s="35" t="n">
+      <c r="I218" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J218" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K218" s="5" t="n">
         <v>69.77</v>
       </c>
-      <c r="L218" s="33" t="inlineStr">
+      <c r="L218" s="3" t="inlineStr">
         <is>
           <t>per Case (None)</t>
         </is>
       </c>
-      <c r="M218" s="32" t="n"/>
-      <c r="N218" s="34">
+      <c r="M218" s="2" t="n"/>
+      <c r="N218" s="4">
         <f>M218*G218</f>
         <v/>
       </c>
-      <c r="O218" s="32" t="n"/>
-      <c r="P218" s="32" t="n"/>
-      <c r="Q218" s="32" t="n"/>
-      <c r="R218" s="32" t="n"/>
-      <c r="S218" s="32" t="n"/>
+      <c r="O218" s="2" t="n"/>
+      <c r="P218" s="2" t="n"/>
+      <c r="Q218" s="2" t="n"/>
+      <c r="R218" s="2" t="n"/>
+      <c r="S218" s="2" t="n"/>
     </row>
     <row r="219">
-      <c r="A219" s="32" t="inlineStr">
+      <c r="A219" s="2" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="B219" s="32" t="n"/>
-      <c r="C219" s="33" t="inlineStr">
+      <c r="B219" s="2" t="n"/>
+      <c r="C219" s="3" t="inlineStr">
         <is>
           <t>Chicken Fajita</t>
         </is>
       </c>
-      <c r="D219" s="33" t="n"/>
-      <c r="E219" s="32" t="n"/>
-      <c r="F219" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G219" s="34" t="n">
+      <c r="D219" s="3" t="n"/>
+      <c r="E219" s="2" t="n"/>
+      <c r="F219" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G219" s="4" t="n">
         <v>57.99</v>
       </c>
-      <c r="H219" s="35" t="n">
+      <c r="H219" s="5" t="n">
         <v>57.99</v>
       </c>
-      <c r="I219" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J219" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K219" s="35" t="n">
+      <c r="I219" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J219" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K219" s="5" t="n">
         <v>57.99</v>
       </c>
-      <c r="L219" s="33" t="inlineStr">
+      <c r="L219" s="3" t="inlineStr">
         <is>
           <t>per Case (None)</t>
         </is>
       </c>
-      <c r="M219" s="32" t="n"/>
-      <c r="N219" s="34">
+      <c r="M219" s="2" t="n"/>
+      <c r="N219" s="4">
         <f>M219*G219</f>
         <v/>
       </c>
-      <c r="O219" s="32" t="n"/>
-      <c r="P219" s="32" t="n"/>
-      <c r="Q219" s="32" t="n"/>
-      <c r="R219" s="32" t="n"/>
-      <c r="S219" s="32" t="n"/>
+      <c r="O219" s="2" t="n"/>
+      <c r="P219" s="2" t="n"/>
+      <c r="Q219" s="2" t="n"/>
+      <c r="R219" s="2" t="n"/>
+      <c r="S219" s="2" t="n"/>
     </row>
     <row r="220">
-      <c r="A220" s="32" t="inlineStr">
+      <c r="A220" s="2" t="inlineStr">
         <is>
           <t>BAG</t>
         </is>
       </c>
-      <c r="B220" s="32" t="n"/>
-      <c r="C220" s="33" t="inlineStr">
+      <c r="B220" s="2" t="n"/>
+      <c r="C220" s="3" t="inlineStr">
         <is>
           <t>Mac And Cheese</t>
         </is>
       </c>
-      <c r="D220" s="33" t="n"/>
-      <c r="E220" s="32" t="inlineStr">
+      <c r="D220" s="3" t="n"/>
+      <c r="E220" s="2" t="inlineStr">
         <is>
           <t>6 Bags</t>
         </is>
       </c>
-      <c r="F220" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G220" s="34" t="n">
+      <c r="F220" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G220" s="4" t="n">
         <v>7.1</v>
       </c>
-      <c r="H220" s="35" t="n">
+      <c r="H220" s="5" t="n">
         <v>7.1</v>
       </c>
-      <c r="I220" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J220" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K220" s="35" t="n">
+      <c r="I220" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J220" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K220" s="5" t="n">
         <v>1.183333333333333</v>
       </c>
-      <c r="L220" s="33" t="inlineStr">
+      <c r="L220" s="3" t="inlineStr">
         <is>
           <t>per Bag (6 Bags)</t>
         </is>
       </c>
-      <c r="M220" s="32" t="n"/>
-      <c r="N220" s="34">
+      <c r="M220" s="2" t="n"/>
+      <c r="N220" s="4">
         <f>M220*G220</f>
         <v/>
       </c>
-      <c r="O220" s="32" t="n"/>
-      <c r="P220" s="32" t="n"/>
-      <c r="Q220" s="32" t="n"/>
-      <c r="R220" s="32" t="n"/>
-      <c r="S220" s="32" t="n"/>
+      <c r="O220" s="2" t="n"/>
+      <c r="P220" s="2" t="n"/>
+      <c r="Q220" s="2" t="n"/>
+      <c r="R220" s="2" t="n"/>
+      <c r="S220" s="2" t="n"/>
     </row>
     <row r="221">
-      <c r="A221" s="32" t="inlineStr">
+      <c r="A221" s="2" t="inlineStr">
         <is>
           <t>BAG</t>
         </is>
       </c>
-      <c r="B221" s="32" t="n"/>
-      <c r="C221" s="33" t="inlineStr">
+      <c r="B221" s="2" t="n"/>
+      <c r="C221" s="3" t="inlineStr">
         <is>
           <t>Mashed Potatoes</t>
         </is>
       </c>
-      <c r="D221" s="33" t="n"/>
-      <c r="E221" s="32" t="inlineStr">
+      <c r="D221" s="3" t="n"/>
+      <c r="E221" s="2" t="inlineStr">
         <is>
           <t>4 Bags</t>
         </is>
       </c>
-      <c r="F221" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G221" s="34" t="n">
+      <c r="F221" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G221" s="4" t="n">
         <v>9.640000000000001</v>
       </c>
-      <c r="H221" s="35" t="n">
+      <c r="H221" s="5" t="n">
         <v>9.640000000000001</v>
       </c>
-      <c r="I221" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J221" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K221" s="35" t="n">
+      <c r="I221" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J221" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K221" s="5" t="n">
         <v>2.41</v>
       </c>
-      <c r="L221" s="33" t="inlineStr">
+      <c r="L221" s="3" t="inlineStr">
         <is>
           <t>per Bag (4 Bags)</t>
         </is>
       </c>
-      <c r="M221" s="32" t="n"/>
-      <c r="N221" s="34">
+      <c r="M221" s="2" t="n"/>
+      <c r="N221" s="4">
         <f>M221*G221</f>
         <v/>
       </c>
-      <c r="O221" s="32" t="n"/>
-      <c r="P221" s="32" t="n"/>
-      <c r="Q221" s="32" t="n"/>
-      <c r="R221" s="32" t="n"/>
-      <c r="S221" s="32" t="n"/>
+      <c r="O221" s="2" t="n"/>
+      <c r="P221" s="2" t="n"/>
+      <c r="Q221" s="2" t="n"/>
+      <c r="R221" s="2" t="n"/>
+      <c r="S221" s="2" t="n"/>
     </row>
     <row r="222">
-      <c r="A222" s="32" t="inlineStr">
+      <c r="A222" s="2" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="B222" s="32" t="n"/>
-      <c r="C222" s="33" t="inlineStr">
+      <c r="B222" s="2" t="n"/>
+      <c r="C222" s="3" t="inlineStr">
         <is>
           <t>Mini Taco Beef</t>
         </is>
       </c>
-      <c r="D222" s="33" t="n"/>
-      <c r="E222" s="32" t="inlineStr">
+      <c r="D222" s="3" t="n"/>
+      <c r="E222" s="2" t="inlineStr">
         <is>
           <t>case</t>
         </is>
       </c>
-      <c r="F222" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G222" s="34" t="n">
+      <c r="F222" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G222" s="4" t="n">
         <v>27.91</v>
       </c>
-      <c r="H222" s="35" t="n">
+      <c r="H222" s="5" t="n">
         <v>27.91</v>
       </c>
-      <c r="I222" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J222" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K222" s="35" t="n">
+      <c r="I222" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J222" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K222" s="5" t="n">
         <v>27.91</v>
       </c>
-      <c r="L222" s="33" t="inlineStr">
+      <c r="L222" s="3" t="inlineStr">
         <is>
           <t>per Case (case)</t>
         </is>
       </c>
-      <c r="M222" s="32" t="n"/>
-      <c r="N222" s="34">
+      <c r="M222" s="2" t="n"/>
+      <c r="N222" s="4">
         <f>M222*G222</f>
         <v/>
       </c>
-      <c r="O222" s="32" t="n"/>
-      <c r="P222" s="32" t="n"/>
-      <c r="Q222" s="32" t="n"/>
-      <c r="R222" s="32" t="n"/>
-      <c r="S222" s="32" t="n"/>
+      <c r="O222" s="2" t="n"/>
+      <c r="P222" s="2" t="n"/>
+      <c r="Q222" s="2" t="n"/>
+      <c r="R222" s="2" t="n"/>
+      <c r="S222" s="2" t="n"/>
     </row>
     <row r="223">
-      <c r="A223" s="32" t="inlineStr">
+      <c r="A223" s="2" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="B223" s="32" t="n"/>
-      <c r="C223" s="33" t="inlineStr">
+      <c r="B223" s="2" t="n"/>
+      <c r="C223" s="3" t="inlineStr">
         <is>
           <t>Mini Taco Chicken</t>
         </is>
       </c>
-      <c r="D223" s="33" t="n"/>
-      <c r="E223" s="32" t="inlineStr">
+      <c r="D223" s="3" t="n"/>
+      <c r="E223" s="2" t="inlineStr">
         <is>
           <t>case</t>
         </is>
       </c>
-      <c r="F223" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G223" s="34" t="n">
+      <c r="F223" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G223" s="4" t="n">
         <v>27.91</v>
       </c>
-      <c r="H223" s="35" t="n">
+      <c r="H223" s="5" t="n">
         <v>27.91</v>
       </c>
-      <c r="I223" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J223" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K223" s="35" t="n">
+      <c r="I223" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J223" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K223" s="5" t="n">
         <v>27.91</v>
       </c>
-      <c r="L223" s="33" t="inlineStr">
+      <c r="L223" s="3" t="inlineStr">
         <is>
           <t>per Case (case)</t>
         </is>
       </c>
-      <c r="M223" s="32" t="n"/>
-      <c r="N223" s="34">
+      <c r="M223" s="2" t="n"/>
+      <c r="N223" s="4">
         <f>M223*G223</f>
         <v/>
       </c>
-      <c r="O223" s="32" t="n"/>
-      <c r="P223" s="32" t="n"/>
-      <c r="Q223" s="32" t="n"/>
-      <c r="R223" s="32" t="n"/>
-      <c r="S223" s="32" t="n"/>
+      <c r="O223" s="2" t="n"/>
+      <c r="P223" s="2" t="n"/>
+      <c r="Q223" s="2" t="n"/>
+      <c r="R223" s="2" t="n"/>
+      <c r="S223" s="2" t="n"/>
     </row>
     <row r="224">
-      <c r="A224" s="32" t="inlineStr">
+      <c r="A224" s="2" t="inlineStr">
         <is>
           <t>BAG</t>
         </is>
       </c>
-      <c r="B224" s="32" t="n"/>
-      <c r="C224" s="33" t="inlineStr">
+      <c r="B224" s="2" t="n"/>
+      <c r="C224" s="3" t="inlineStr">
         <is>
           <t>Red Beans</t>
         </is>
       </c>
-      <c r="D224" s="33" t="n"/>
-      <c r="E224" s="32" t="inlineStr">
+      <c r="D224" s="3" t="n"/>
+      <c r="E224" s="2" t="inlineStr">
         <is>
           <t>9 Bags</t>
         </is>
       </c>
-      <c r="F224" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G224" s="34" t="n">
+      <c r="F224" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G224" s="4" t="n">
         <v>6.49</v>
       </c>
-      <c r="H224" s="35" t="n">
+      <c r="H224" s="5" t="n">
         <v>6.49</v>
       </c>
-      <c r="I224" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J224" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K224" s="35" t="n">
+      <c r="I224" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J224" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K224" s="5" t="n">
         <v>0.7211111111111111</v>
       </c>
-      <c r="L224" s="33" t="inlineStr">
+      <c r="L224" s="3" t="inlineStr">
         <is>
           <t>per Bag (9 Bags)</t>
         </is>
       </c>
-      <c r="M224" s="32" t="n"/>
-      <c r="N224" s="34">
+      <c r="M224" s="2" t="n"/>
+      <c r="N224" s="4">
         <f>M224*G224</f>
         <v/>
       </c>
-      <c r="O224" s="32" t="n"/>
-      <c r="P224" s="32" t="n"/>
-      <c r="Q224" s="32" t="n"/>
-      <c r="R224" s="32" t="n"/>
-      <c r="S224" s="32" t="n"/>
+      <c r="O224" s="2" t="n"/>
+      <c r="P224" s="2" t="n"/>
+      <c r="Q224" s="2" t="n"/>
+      <c r="R224" s="2" t="n"/>
+      <c r="S224" s="2" t="n"/>
     </row>
     <row r="225">
-      <c r="A225" s="32" t="inlineStr">
+      <c r="A225" s="2" t="inlineStr">
         <is>
           <t>PACK</t>
         </is>
       </c>
-      <c r="B225" s="32" t="n"/>
-      <c r="C225" s="33" t="inlineStr">
+      <c r="B225" s="2" t="n"/>
+      <c r="C225" s="3" t="inlineStr">
         <is>
           <t>Beef Sausage Dogs</t>
         </is>
       </c>
-      <c r="D225" s="33" t="n"/>
-      <c r="E225" s="32" t="n"/>
-      <c r="F225" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G225" s="34" t="n">
+      <c r="D225" s="3" t="n"/>
+      <c r="E225" s="2" t="n"/>
+      <c r="F225" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G225" s="4" t="n">
         <v>20.34</v>
       </c>
-      <c r="H225" s="35" t="n">
+      <c r="H225" s="5" t="n">
         <v>20.34</v>
       </c>
-      <c r="I225" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J225" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K225" s="35" t="n">
+      <c r="I225" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J225" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K225" s="5" t="n">
         <v>20.34</v>
       </c>
-      <c r="L225" s="33" t="inlineStr">
+      <c r="L225" s="3" t="inlineStr">
         <is>
           <t>per Pack (None)</t>
         </is>
       </c>
-      <c r="M225" s="32" t="n"/>
-      <c r="N225" s="34">
+      <c r="M225" s="2" t="n"/>
+      <c r="N225" s="4">
         <f>M225*G225</f>
         <v/>
       </c>
-      <c r="O225" s="32" t="n"/>
-      <c r="P225" s="32" t="n"/>
-      <c r="Q225" s="32" t="n"/>
-      <c r="R225" s="32" t="n"/>
-      <c r="S225" s="32" t="n"/>
+      <c r="O225" s="2" t="n"/>
+      <c r="P225" s="2" t="n"/>
+      <c r="Q225" s="2" t="n"/>
+      <c r="R225" s="2" t="n"/>
+      <c r="S225" s="2" t="n"/>
     </row>
     <row r="226">
-      <c r="A226" s="32" t="inlineStr">
+      <c r="A226" s="2" t="inlineStr">
         <is>
           <t>BAG</t>
         </is>
       </c>
-      <c r="B226" s="32" t="n"/>
-      <c r="C226" s="33" t="inlineStr">
+      <c r="B226" s="2" t="n"/>
+      <c r="C226" s="3" t="inlineStr">
         <is>
           <t>Seasoned Corn</t>
         </is>
       </c>
-      <c r="D226" s="33" t="n"/>
-      <c r="E226" s="32" t="inlineStr">
+      <c r="D226" s="3" t="n"/>
+      <c r="E226" s="2" t="inlineStr">
         <is>
           <t>6 Bags</t>
         </is>
       </c>
-      <c r="F226" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G226" s="34" t="n">
+      <c r="F226" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G226" s="4" t="n">
         <v>6.18</v>
       </c>
-      <c r="H226" s="35" t="n">
+      <c r="H226" s="5" t="n">
         <v>6.18</v>
       </c>
-      <c r="I226" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J226" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K226" s="35" t="n">
+      <c r="I226" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J226" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K226" s="5" t="n">
         <v>1.03</v>
       </c>
-      <c r="L226" s="33" t="inlineStr">
+      <c r="L226" s="3" t="inlineStr">
         <is>
           <t>per Bag (6 Bags)</t>
         </is>
       </c>
-      <c r="M226" s="32" t="n"/>
-      <c r="N226" s="34">
+      <c r="M226" s="2" t="n"/>
+      <c r="N226" s="4">
         <f>M226*G226</f>
         <v/>
       </c>
-      <c r="O226" s="32" t="n"/>
-      <c r="P226" s="32" t="n"/>
-      <c r="Q226" s="32" t="n"/>
-      <c r="R226" s="32" t="n"/>
-      <c r="S226" s="32" t="n"/>
+      <c r="O226" s="2" t="n"/>
+      <c r="P226" s="2" t="n"/>
+      <c r="Q226" s="2" t="n"/>
+      <c r="R226" s="2" t="n"/>
+      <c r="S226" s="2" t="n"/>
     </row>
     <row r="227">
-      <c r="A227" s="32" t="inlineStr">
+      <c r="A227" s="2" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="B227" s="32" t="n"/>
-      <c r="C227" s="33" t="inlineStr">
+      <c r="B227" s="2" t="n"/>
+      <c r="C227" s="3" t="inlineStr">
         <is>
           <t>Stuffed Nacho</t>
         </is>
       </c>
-      <c r="D227" s="33" t="n"/>
-      <c r="E227" s="32" t="inlineStr">
+      <c r="D227" s="3" t="n"/>
+      <c r="E227" s="2" t="inlineStr">
         <is>
           <t>case</t>
         </is>
       </c>
-      <c r="F227" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G227" s="34" t="n">
+      <c r="F227" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G227" s="4" t="n">
         <v>37.28</v>
       </c>
-      <c r="H227" s="35" t="n">
+      <c r="H227" s="5" t="n">
         <v>37.28</v>
       </c>
-      <c r="I227" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J227" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K227" s="35" t="n">
+      <c r="I227" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J227" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K227" s="5" t="n">
         <v>37.28</v>
       </c>
-      <c r="L227" s="33" t="inlineStr">
+      <c r="L227" s="3" t="inlineStr">
         <is>
           <t>per Case (case)</t>
         </is>
       </c>
-      <c r="M227" s="32" t="n"/>
-      <c r="N227" s="34">
+      <c r="M227" s="2" t="n"/>
+      <c r="N227" s="4">
         <f>M227*G227</f>
         <v/>
       </c>
-      <c r="O227" s="32" t="n"/>
-      <c r="P227" s="32" t="n"/>
-      <c r="Q227" s="32" t="n"/>
-      <c r="R227" s="32" t="n"/>
-      <c r="S227" s="32" t="n"/>
+      <c r="O227" s="2" t="n"/>
+      <c r="P227" s="2" t="n"/>
+      <c r="Q227" s="2" t="n"/>
+      <c r="R227" s="2" t="n"/>
+      <c r="S227" s="2" t="n"/>
     </row>
     <row r="228">
-      <c r="A228" s="32" t="inlineStr">
+      <c r="A228" s="2" t="inlineStr">
         <is>
           <t>BAG</t>
         </is>
       </c>
-      <c r="B228" s="32" t="n"/>
-      <c r="C228" s="33" t="inlineStr">
+      <c r="B228" s="2" t="n"/>
+      <c r="C228" s="3" t="inlineStr">
         <is>
           <t>Tomato Gravy</t>
         </is>
       </c>
-      <c r="D228" s="33" t="n"/>
-      <c r="E228" s="32" t="inlineStr">
+      <c r="D228" s="3" t="n"/>
+      <c r="E228" s="2" t="inlineStr">
         <is>
           <t>4 bags</t>
         </is>
       </c>
-      <c r="F228" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G228" s="34" t="n">
+      <c r="F228" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G228" s="4" t="n">
         <v>12.34</v>
       </c>
-      <c r="H228" s="35" t="n">
+      <c r="H228" s="5" t="n">
         <v>12.34</v>
       </c>
-      <c r="I228" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J228" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K228" s="35" t="n">
+      <c r="I228" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J228" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K228" s="5" t="n">
         <v>3.085</v>
       </c>
-      <c r="L228" s="33" t="inlineStr">
+      <c r="L228" s="3" t="inlineStr">
         <is>
           <t>per Bag (4 bags)</t>
         </is>
       </c>
-      <c r="M228" s="32" t="n"/>
-      <c r="N228" s="34">
+      <c r="M228" s="2" t="n"/>
+      <c r="N228" s="4">
         <f>M228*G228</f>
         <v/>
       </c>
-      <c r="O228" s="32" t="n"/>
-      <c r="P228" s="32" t="n"/>
-      <c r="Q228" s="32" t="n"/>
-      <c r="R228" s="32" t="n"/>
-      <c r="S228" s="32" t="n"/>
+      <c r="O228" s="2" t="n"/>
+      <c r="P228" s="2" t="n"/>
+      <c r="Q228" s="2" t="n"/>
+      <c r="R228" s="2" t="n"/>
+      <c r="S228" s="2" t="n"/>
     </row>
     <row r="229">
-      <c r="A229" s="32" t="inlineStr">
+      <c r="A229" s="2" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="B229" s="32" t="n"/>
-      <c r="C229" s="33" t="inlineStr">
+      <c r="B229" s="2" t="n"/>
+      <c r="C229" s="3" t="inlineStr">
         <is>
           <t>Spicy Chicken Patty</t>
         </is>
       </c>
-      <c r="D229" s="33" t="n"/>
-      <c r="E229" s="32" t="n"/>
-      <c r="F229" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G229" s="34" t="n">
+      <c r="D229" s="3" t="n"/>
+      <c r="E229" s="2" t="n"/>
+      <c r="F229" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G229" s="4" t="n">
         <v>52.87</v>
       </c>
-      <c r="H229" s="35" t="n">
+      <c r="H229" s="5" t="n">
         <v>52.87</v>
       </c>
-      <c r="I229" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J229" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K229" s="35" t="n">
+      <c r="I229" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J229" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K229" s="5" t="n">
         <v>52.87</v>
       </c>
-      <c r="L229" s="33" t="inlineStr">
+      <c r="L229" s="3" t="inlineStr">
         <is>
           <t>per Case (None)</t>
         </is>
       </c>
-      <c r="M229" s="32" t="n"/>
-      <c r="N229" s="34">
+      <c r="M229" s="2" t="n"/>
+      <c r="N229" s="4">
         <f>M229*G229</f>
         <v/>
       </c>
-      <c r="O229" s="32" t="n"/>
-      <c r="P229" s="32" t="n"/>
-      <c r="Q229" s="32" t="n"/>
-      <c r="R229" s="32" t="n"/>
-      <c r="S229" s="32" t="n"/>
+      <c r="O229" s="2" t="n"/>
+      <c r="P229" s="2" t="n"/>
+      <c r="Q229" s="2" t="n"/>
+      <c r="R229" s="2" t="n"/>
+      <c r="S229" s="2" t="n"/>
     </row>
     <row r="230">
-      <c r="A230" s="32" t="inlineStr">
+      <c r="A230" s="2" t="inlineStr">
         <is>
           <t>EACH</t>
         </is>
       </c>
-      <c r="B230" s="32" t="n"/>
-      <c r="C230" s="33" t="inlineStr">
+      <c r="B230" s="2" t="n"/>
+      <c r="C230" s="3" t="inlineStr">
         <is>
           <t>Crooked Letter Cookies</t>
         </is>
       </c>
-      <c r="D230" s="33" t="n"/>
-      <c r="E230" s="32" t="n"/>
-      <c r="F230" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G230" s="34" t="n">
+      <c r="D230" s="3" t="n"/>
+      <c r="E230" s="2" t="n"/>
+      <c r="F230" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G230" s="4" t="n">
         <v>1.9</v>
       </c>
-      <c r="H230" s="35" t="n">
+      <c r="H230" s="5" t="n">
         <v>1.9</v>
       </c>
-      <c r="I230" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J230" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K230" s="35" t="n">
+      <c r="I230" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J230" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K230" s="5" t="n">
         <v>1.9</v>
       </c>
-      <c r="L230" s="33" t="inlineStr">
+      <c r="L230" s="3" t="inlineStr">
         <is>
           <t>per Each (None)</t>
         </is>
       </c>
-      <c r="M230" s="32" t="n"/>
-      <c r="N230" s="34">
+      <c r="M230" s="2" t="n"/>
+      <c r="N230" s="4">
         <f>M230*G230</f>
         <v/>
       </c>
-      <c r="O230" s="32" t="n"/>
-      <c r="P230" s="32" t="n"/>
-      <c r="Q230" s="32" t="n"/>
-      <c r="R230" s="32" t="n"/>
-      <c r="S230" s="32" t="n"/>
+      <c r="O230" s="2" t="n"/>
+      <c r="P230" s="2" t="n"/>
+      <c r="Q230" s="2" t="n"/>
+      <c r="R230" s="2" t="n"/>
+      <c r="S230" s="2" t="n"/>
     </row>
     <row r="231">
-      <c r="A231" s="32" t="inlineStr">
+      <c r="A231" s="2" t="inlineStr">
         <is>
           <t>EACH</t>
         </is>
       </c>
-      <c r="B231" s="32" t="n"/>
-      <c r="C231" s="33" t="inlineStr">
+      <c r="B231" s="2" t="n"/>
+      <c r="C231" s="3" t="inlineStr">
         <is>
           <t>Strawberry/Blueberry Cream Cheese King Cake</t>
         </is>
       </c>
-      <c r="D231" s="33" t="n"/>
-      <c r="E231" s="32" t="n"/>
-      <c r="F231" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G231" s="34" t="n">
+      <c r="D231" s="3" t="n"/>
+      <c r="E231" s="2" t="n"/>
+      <c r="F231" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G231" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="H231" s="35" t="n">
+      <c r="H231" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="I231" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J231" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K231" s="35" t="n">
+      <c r="I231" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J231" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K231" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="L231" s="33" t="inlineStr">
+      <c r="L231" s="3" t="inlineStr">
         <is>
           <t>per Each (None)</t>
         </is>
       </c>
-      <c r="M231" s="32" t="n"/>
-      <c r="N231" s="34">
+      <c r="M231" s="2" t="n"/>
+      <c r="N231" s="4">
         <f>M231*G231</f>
         <v/>
       </c>
-      <c r="O231" s="32" t="n"/>
-      <c r="P231" s="32" t="n"/>
-      <c r="Q231" s="32" t="n"/>
-      <c r="R231" s="32" t="n"/>
-      <c r="S231" s="32" t="n"/>
+      <c r="O231" s="2" t="n"/>
+      <c r="P231" s="2" t="n"/>
+      <c r="Q231" s="2" t="n"/>
+      <c r="R231" s="2" t="n"/>
+      <c r="S231" s="2" t="n"/>
     </row>
     <row r="232">
-      <c r="A232" s="32" t="inlineStr">
+      <c r="A232" s="2" t="inlineStr">
         <is>
           <t>EACH</t>
         </is>
       </c>
-      <c r="B232" s="32" t="n"/>
-      <c r="C232" s="33" t="inlineStr">
+      <c r="B232" s="2" t="n"/>
+      <c r="C232" s="3" t="inlineStr">
         <is>
           <t>Traditional King Cake</t>
         </is>
       </c>
-      <c r="D232" s="33" t="n"/>
-      <c r="E232" s="32" t="n"/>
-      <c r="F232" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G232" s="34" t="n">
+      <c r="D232" s="3" t="n"/>
+      <c r="E232" s="2" t="n"/>
+      <c r="F232" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G232" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="H232" s="35" t="n">
+      <c r="H232" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="I232" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J232" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K232" s="35" t="n">
+      <c r="I232" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J232" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K232" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="L232" s="33" t="inlineStr">
+      <c r="L232" s="3" t="inlineStr">
         <is>
           <t>per Each (None)</t>
         </is>
       </c>
-      <c r="M232" s="32" t="n"/>
-      <c r="N232" s="34">
+      <c r="M232" s="2" t="n"/>
+      <c r="N232" s="4">
         <f>M232*G232</f>
         <v/>
       </c>
-      <c r="O232" s="32" t="n"/>
-      <c r="P232" s="32" t="n"/>
-      <c r="Q232" s="32" t="n"/>
-      <c r="R232" s="32" t="n"/>
-      <c r="S232" s="32" t="n"/>
+      <c r="O232" s="2" t="n"/>
+      <c r="P232" s="2" t="n"/>
+      <c r="Q232" s="2" t="n"/>
+      <c r="R232" s="2" t="n"/>
+      <c r="S232" s="2" t="n"/>
     </row>
     <row r="233">
-      <c r="A233" s="32" t="inlineStr">
+      <c r="A233" s="2" t="inlineStr">
         <is>
           <t>EACH</t>
         </is>
       </c>
-      <c r="B233" s="32" t="n"/>
-      <c r="C233" s="33" t="inlineStr">
+      <c r="B233" s="2" t="n"/>
+      <c r="C233" s="3" t="inlineStr">
         <is>
           <t>Cream Cheese King Cake</t>
         </is>
       </c>
-      <c r="D233" s="33" t="n"/>
-      <c r="E233" s="32" t="n"/>
-      <c r="F233" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G233" s="34" t="n">
+      <c r="D233" s="3" t="n"/>
+      <c r="E233" s="2" t="n"/>
+      <c r="F233" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G233" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="H233" s="35" t="n">
+      <c r="H233" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="I233" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J233" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K233" s="35" t="n">
+      <c r="I233" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J233" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K233" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="L233" s="33" t="inlineStr">
+      <c r="L233" s="3" t="inlineStr">
         <is>
           <t>per Each (None)</t>
         </is>
       </c>
-      <c r="M233" s="32" t="n"/>
-      <c r="N233" s="34">
+      <c r="M233" s="2" t="n"/>
+      <c r="N233" s="4">
         <f>M233*G233</f>
         <v/>
       </c>
-      <c r="O233" s="32" t="n"/>
-      <c r="P233" s="32" t="n"/>
-      <c r="Q233" s="32" t="n"/>
-      <c r="R233" s="32" t="n"/>
-      <c r="S233" s="32" t="n"/>
+      <c r="O233" s="2" t="n"/>
+      <c r="P233" s="2" t="n"/>
+      <c r="Q233" s="2" t="n"/>
+      <c r="R233" s="2" t="n"/>
+      <c r="S233" s="2" t="n"/>
     </row>
     <row r="234">
-      <c r="A234" s="32" t="inlineStr">
+      <c r="A234" s="2" t="inlineStr">
         <is>
           <t>EACH</t>
         </is>
       </c>
-      <c r="B234" s="32" t="n"/>
-      <c r="C234" s="33" t="inlineStr">
+      <c r="B234" s="2" t="n"/>
+      <c r="C234" s="3" t="inlineStr">
         <is>
           <t>Pecan Praline King Cake</t>
         </is>
       </c>
-      <c r="D234" s="33" t="n"/>
-      <c r="E234" s="32" t="n"/>
-      <c r="F234" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G234" s="34" t="n">
+      <c r="D234" s="3" t="n"/>
+      <c r="E234" s="2" t="n"/>
+      <c r="F234" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G234" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="H234" s="35" t="n">
+      <c r="H234" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="I234" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J234" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K234" s="35" t="n">
+      <c r="I234" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J234" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K234" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="L234" s="33" t="inlineStr">
+      <c r="L234" s="3" t="inlineStr">
         <is>
           <t>per Each (None)</t>
         </is>
       </c>
-      <c r="M234" s="32" t="n"/>
-      <c r="N234" s="34">
+      <c r="M234" s="2" t="n"/>
+      <c r="N234" s="4">
         <f>M234*G234</f>
         <v/>
       </c>
-      <c r="O234" s="32" t="n"/>
-      <c r="P234" s="32" t="n"/>
-      <c r="Q234" s="32" t="n"/>
-      <c r="R234" s="32" t="n"/>
-      <c r="S234" s="32" t="n"/>
+      <c r="O234" s="2" t="n"/>
+      <c r="P234" s="2" t="n"/>
+      <c r="Q234" s="2" t="n"/>
+      <c r="R234" s="2" t="n"/>
+      <c r="S234" s="2" t="n"/>
     </row>
     <row r="236">
-      <c r="A236" s="38" t="inlineStr">
+      <c r="A236" s="35" t="inlineStr">
         <is>
           <t>COLOR LEGEND</t>
         </is>
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="33" t="inlineStr">
-        <is>
-          <t>DARK RED   — No BEK item number (not in BEK list)</t>
-        </is>
-      </c>
-      <c r="B237" s="39" t="n"/>
-      <c r="C237" s="39" t="n"/>
-      <c r="D237" s="39" t="n"/>
+      <c r="A237" s="27" t="inlineStr">
+        <is>
+          <t>RED    — No matching BEK item number (needs manual lookup)</t>
+        </is>
+      </c>
+      <c r="B237" s="36" t="n"/>
+      <c r="C237" s="36" t="n"/>
+      <c r="D237" s="36" t="n"/>
     </row>
     <row r="238">
-      <c r="A238" s="27" t="inlineStr">
-        <is>
-          <t>ORANGE-RED — BEK# not found in current price list</t>
-        </is>
-      </c>
-      <c r="B238" s="39" t="n"/>
-      <c r="C238" s="39" t="n"/>
-      <c r="D238" s="39" t="n"/>
+      <c r="A238" s="21" t="inlineStr">
+        <is>
+          <t>PINK   — Price UP ≥ 10% or ≥ $2.00/unit</t>
+        </is>
+      </c>
+      <c r="B238" s="36" t="n"/>
+      <c r="C238" s="36" t="n"/>
+      <c r="D238" s="36" t="n"/>
     </row>
     <row r="239">
-      <c r="A239" s="21" t="inlineStr">
-        <is>
-          <t>PINK       — Price UP ≥ 10% or ≥ $2.00/unit</t>
-        </is>
-      </c>
-      <c r="B239" s="39" t="n"/>
-      <c r="C239" s="39" t="n"/>
-      <c r="D239" s="39" t="n"/>
+      <c r="A239" s="15" t="inlineStr">
+        <is>
+          <t>YELLOW — Price increased (under threshold)</t>
+        </is>
+      </c>
+      <c r="B239" s="36" t="n"/>
+      <c r="C239" s="36" t="n"/>
+      <c r="D239" s="36" t="n"/>
     </row>
     <row r="240">
-      <c r="A240" s="15" t="inlineStr">
-        <is>
-          <t>YELLOW     — Price increased (under threshold)</t>
-        </is>
-      </c>
-      <c r="B240" s="39" t="n"/>
-      <c r="C240" s="39" t="n"/>
-      <c r="D240" s="39" t="n"/>
+      <c r="A240" s="9" t="inlineStr">
+        <is>
+          <t>GREEN  — Price decreased</t>
+        </is>
+      </c>
+      <c r="B240" s="36" t="n"/>
+      <c r="C240" s="36" t="n"/>
+      <c r="D240" s="36" t="n"/>
     </row>
     <row r="241">
-      <c r="A241" s="9" t="inlineStr">
-        <is>
-          <t>GREEN      — Price decreased</t>
-        </is>
-      </c>
-      <c r="B241" s="39" t="n"/>
-      <c r="C241" s="39" t="n"/>
-      <c r="D241" s="39" t="n"/>
-    </row>
-    <row r="242">
-      <c r="A242" s="3" t="inlineStr">
-        <is>
-          <t>WHITE      — No change / price matched</t>
-        </is>
-      </c>
-      <c r="B242" s="39" t="n"/>
-      <c r="C242" s="39" t="n"/>
-      <c r="D242" s="39" t="n"/>
+      <c r="A241" s="3" t="inlineStr">
+        <is>
+          <t>WHITE  — No change / BEK match confirmed</t>
+        </is>
+      </c>
+      <c r="B241" s="36" t="n"/>
+      <c r="C241" s="36" t="n"/>
+      <c r="D241" s="36" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A202:S202"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13816,795 +13833,795 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="40" t="inlineStr">
+      <c r="A1" s="37" t="inlineStr">
         <is>
           <t>PRODUCT</t>
         </is>
       </c>
-      <c r="B1" s="40" t="inlineStr">
+      <c r="B1" s="37" t="inlineStr">
         <is>
           <t>SIZE/DESCRIPTION</t>
         </is>
       </c>
-      <c r="C1" s="40" t="inlineStr">
+      <c r="C1" s="37" t="inlineStr">
         <is>
           <t>ON HAND (QTY)</t>
         </is>
       </c>
-      <c r="D1" s="40" t="inlineStr">
+      <c r="D1" s="37" t="inlineStr">
         <is>
           <t>COST</t>
         </is>
       </c>
-      <c r="E1" s="40" t="inlineStr">
+      <c r="E1" s="37" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="41" t="inlineStr">
+      <c r="A2" s="38" t="inlineStr">
         <is>
           <t>SIGNATURE BLEND</t>
         </is>
       </c>
-      <c r="B2" s="41" t="inlineStr">
+      <c r="B2" s="38" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="C2" s="42" t="n">
+      <c r="C2" s="39" t="n">
         <v>1.5</v>
       </c>
-      <c r="D2" s="42" t="n"/>
-      <c r="E2" s="42" t="n"/>
+      <c r="D2" s="39" t="n"/>
+      <c r="E2" s="39" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="41" t="inlineStr">
+      <c r="A3" s="38" t="inlineStr">
         <is>
           <t>AMERICAN CLASSIC</t>
         </is>
       </c>
-      <c r="B3" s="41" t="inlineStr">
+      <c r="B3" s="38" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="C3" s="42" t="n">
+      <c r="C3" s="39" t="n">
         <v>1.75</v>
       </c>
-      <c r="D3" s="42" t="n"/>
-      <c r="E3" s="42" t="n"/>
+      <c r="D3" s="39" t="n"/>
+      <c r="E3" s="39" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="41" t="inlineStr">
+      <c r="A4" s="38" t="inlineStr">
         <is>
           <t>PECAN PRALINE</t>
         </is>
       </c>
-      <c r="B4" s="41" t="inlineStr">
+      <c r="B4" s="38" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="C4" s="42" t="n">
+      <c r="C4" s="39" t="n">
         <v>1.5</v>
       </c>
-      <c r="D4" s="42" t="n"/>
-      <c r="E4" s="42" t="n"/>
+      <c r="D4" s="39" t="n"/>
+      <c r="E4" s="39" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="41" t="inlineStr">
+      <c r="A5" s="38" t="inlineStr">
         <is>
           <t>BREAKFAST BLEND</t>
         </is>
       </c>
-      <c r="B5" s="41" t="inlineStr">
+      <c r="B5" s="38" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="C5" s="42" t="n">
+      <c r="C5" s="39" t="n">
         <v>1.75</v>
       </c>
-      <c r="D5" s="42" t="n"/>
-      <c r="E5" s="42" t="n"/>
+      <c r="D5" s="39" t="n"/>
+      <c r="E5" s="39" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="41" t="inlineStr">
+      <c r="A6" s="38" t="inlineStr">
         <is>
           <t>DB ESPRESSO</t>
         </is>
       </c>
-      <c r="B6" s="41" t="inlineStr">
+      <c r="B6" s="38" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="C6" s="42" t="n">
+      <c r="C6" s="39" t="n">
         <v>2</v>
       </c>
-      <c r="D6" s="42" t="n"/>
-      <c r="E6" s="42" t="n"/>
+      <c r="D6" s="39" t="n"/>
+      <c r="E6" s="39" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="41" t="inlineStr">
+      <c r="A7" s="38" t="inlineStr">
         <is>
           <t>Creamer Cups (Irish Cream, French Vanilla, Caramel)</t>
         </is>
       </c>
-      <c r="B7" s="41" t="inlineStr">
+      <c r="B7" s="38" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="C7" s="42" t="n">
+      <c r="C7" s="39" t="n">
         <v>3.5</v>
       </c>
-      <c r="D7" s="42" t="n"/>
-      <c r="E7" s="42" t="n"/>
+      <c r="D7" s="39" t="n"/>
+      <c r="E7" s="39" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="41" t="inlineStr">
+      <c r="A8" s="38" t="inlineStr">
         <is>
           <t>Coffee Mate</t>
         </is>
       </c>
-      <c r="B8" s="41" t="inlineStr">
+      <c r="B8" s="38" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="C8" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="42" t="n"/>
-      <c r="E8" s="42" t="n"/>
+      <c r="C8" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="39" t="n"/>
+      <c r="E8" s="39" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="41" t="inlineStr">
+      <c r="A9" s="38" t="inlineStr">
         <is>
           <t>Sweet Cream Creamer</t>
         </is>
       </c>
-      <c r="B9" s="41" t="inlineStr">
+      <c r="B9" s="38" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="C9" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="42" t="n"/>
-      <c r="E9" s="42" t="n"/>
+      <c r="C9" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="39" t="n"/>
+      <c r="E9" s="39" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="41" t="inlineStr">
+      <c r="A10" s="38" t="inlineStr">
         <is>
           <t>Hazelnut Creamer</t>
         </is>
       </c>
-      <c r="B10" s="41" t="inlineStr">
+      <c r="B10" s="38" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="C10" s="42" t="n">
+      <c r="C10" s="39" t="n">
         <v>1.1</v>
       </c>
-      <c r="D10" s="42" t="n"/>
-      <c r="E10" s="42" t="n"/>
+      <c r="D10" s="39" t="n"/>
+      <c r="E10" s="39" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="41" t="inlineStr">
+      <c r="A11" s="38" t="inlineStr">
         <is>
           <t>Half And Half</t>
         </is>
       </c>
-      <c r="B11" s="41" t="inlineStr">
+      <c r="B11" s="38" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="C11" s="42" t="n">
+      <c r="C11" s="39" t="n">
         <v>2</v>
       </c>
-      <c r="D11" s="42" t="n"/>
-      <c r="E11" s="42" t="n"/>
+      <c r="D11" s="39" t="n"/>
+      <c r="E11" s="39" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="41" t="inlineStr">
+      <c r="A12" s="38" t="inlineStr">
         <is>
           <t>Original Creamer</t>
         </is>
       </c>
-      <c r="B12" s="41" t="inlineStr">
+      <c r="B12" s="38" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="C12" s="42" t="n">
+      <c r="C12" s="39" t="n">
         <v>1.25</v>
       </c>
-      <c r="D12" s="42" t="n"/>
-      <c r="E12" s="42" t="n"/>
+      <c r="D12" s="39" t="n"/>
+      <c r="E12" s="39" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="41" t="inlineStr">
+      <c r="A13" s="38" t="inlineStr">
         <is>
           <t>Caramel Syrup Pump</t>
         </is>
       </c>
-      <c r="B13" s="41" t="inlineStr">
+      <c r="B13" s="38" t="inlineStr">
         <is>
           <t>BOTTLE</t>
         </is>
       </c>
-      <c r="C13" s="42" t="n">
+      <c r="C13" s="39" t="n">
         <v>1.5</v>
       </c>
-      <c r="D13" s="42" t="n"/>
-      <c r="E13" s="42" t="n"/>
+      <c r="D13" s="39" t="n"/>
+      <c r="E13" s="39" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="41" t="inlineStr">
+      <c r="A14" s="38" t="inlineStr">
         <is>
           <t>Hazelnut Syrup Pump</t>
         </is>
       </c>
-      <c r="B14" s="41" t="inlineStr">
+      <c r="B14" s="38" t="inlineStr">
         <is>
           <t>BOTTLE</t>
         </is>
       </c>
-      <c r="C14" s="42" t="n">
+      <c r="C14" s="39" t="n">
         <v>1.5</v>
       </c>
-      <c r="D14" s="42" t="n"/>
-      <c r="E14" s="42" t="n"/>
+      <c r="D14" s="39" t="n"/>
+      <c r="E14" s="39" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="41" t="inlineStr">
+      <c r="A15" s="38" t="inlineStr">
         <is>
           <t>French Vanilla Syrup Pump</t>
         </is>
       </c>
-      <c r="B15" s="41" t="inlineStr">
+      <c r="B15" s="38" t="inlineStr">
         <is>
           <t>BOTTLE</t>
         </is>
       </c>
-      <c r="C15" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" s="42" t="n"/>
-      <c r="E15" s="42" t="n"/>
+      <c r="C15" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="39" t="n"/>
+      <c r="E15" s="39" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="41" t="inlineStr">
+      <c r="A16" s="38" t="inlineStr">
         <is>
           <t>Hold &amp; Go Lids 12-24oz</t>
         </is>
       </c>
-      <c r="B16" s="41" t="inlineStr">
+      <c r="B16" s="38" t="inlineStr">
         <is>
           <t>SLEEVE</t>
         </is>
       </c>
-      <c r="C16" s="42" t="n">
+      <c r="C16" s="39" t="n">
         <v>14</v>
       </c>
-      <c r="D16" s="42" t="n"/>
-      <c r="E16" s="42" t="n"/>
+      <c r="D16" s="39" t="n"/>
+      <c r="E16" s="39" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="41" t="inlineStr">
+      <c r="A17" s="38" t="inlineStr">
         <is>
           <t>Lid SW 16/20oz</t>
         </is>
       </c>
-      <c r="B17" s="41" t="inlineStr">
+      <c r="B17" s="38" t="inlineStr">
         <is>
           <t>SLEEVE</t>
         </is>
       </c>
-      <c r="C17" s="42" t="n"/>
-      <c r="D17" s="42" t="n"/>
-      <c r="E17" s="42" t="n"/>
+      <c r="C17" s="39" t="n"/>
+      <c r="D17" s="39" t="n"/>
+      <c r="E17" s="39" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="41" t="inlineStr">
+      <c r="A18" s="38" t="inlineStr">
         <is>
           <t>Cappuccino French Vanilla</t>
         </is>
       </c>
-      <c r="B18" s="41" t="inlineStr">
+      <c r="B18" s="38" t="inlineStr">
         <is>
           <t>BAG</t>
         </is>
       </c>
-      <c r="C18" s="42" t="n">
+      <c r="C18" s="39" t="n">
         <v>9</v>
       </c>
-      <c r="D18" s="42" t="n"/>
-      <c r="E18" s="42" t="n"/>
+      <c r="D18" s="39" t="n"/>
+      <c r="E18" s="39" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="41" t="inlineStr">
+      <c r="A19" s="38" t="inlineStr">
         <is>
           <t>Sugar Free Cappuccino French Vanilla</t>
         </is>
       </c>
-      <c r="B19" s="41" t="inlineStr">
+      <c r="B19" s="38" t="inlineStr">
         <is>
           <t>BAG</t>
         </is>
       </c>
-      <c r="C19" s="42" t="n">
+      <c r="C19" s="39" t="n">
         <v>8</v>
       </c>
-      <c r="D19" s="42" t="n"/>
-      <c r="E19" s="42" t="n"/>
+      <c r="D19" s="39" t="n"/>
+      <c r="E19" s="39" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="41" t="inlineStr">
+      <c r="A20" s="38" t="inlineStr">
         <is>
           <t>Hot Chocolate</t>
         </is>
       </c>
-      <c r="B20" s="41" t="inlineStr">
+      <c r="B20" s="38" t="inlineStr">
         <is>
           <t>BAG</t>
         </is>
       </c>
-      <c r="C20" s="42" t="n">
+      <c r="C20" s="39" t="n">
         <v>11</v>
       </c>
-      <c r="D20" s="42" t="n"/>
-      <c r="E20" s="42" t="n"/>
+      <c r="D20" s="39" t="n"/>
+      <c r="E20" s="39" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="41" t="inlineStr">
+      <c r="A21" s="38" t="inlineStr">
         <is>
           <t>Creamer Packs</t>
         </is>
       </c>
-      <c r="B21" s="41" t="inlineStr">
+      <c r="B21" s="38" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="C21" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" s="42" t="n"/>
-      <c r="E21" s="42" t="n"/>
+      <c r="C21" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="39" t="n"/>
+      <c r="E21" s="39" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="41" t="inlineStr">
+      <c r="A22" s="38" t="inlineStr">
         <is>
           <t>Sugar Pack</t>
         </is>
       </c>
-      <c r="B22" s="41" t="inlineStr">
+      <c r="B22" s="38" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="C22" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" s="42" t="n"/>
-      <c r="E22" s="42" t="n"/>
+      <c r="C22" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="39" t="n"/>
+      <c r="E22" s="39" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="41" t="inlineStr">
+      <c r="A23" s="38" t="inlineStr">
         <is>
           <t>Blue Sweetener</t>
         </is>
       </c>
-      <c r="B23" s="41" t="inlineStr">
+      <c r="B23" s="38" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="C23" s="42" t="n">
+      <c r="C23" s="39" t="n">
         <v>0.75</v>
       </c>
-      <c r="D23" s="42" t="n"/>
-      <c r="E23" s="42" t="n"/>
+      <c r="D23" s="39" t="n"/>
+      <c r="E23" s="39" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="41" t="inlineStr">
+      <c r="A24" s="38" t="inlineStr">
         <is>
           <t>Yellow Sweetener</t>
         </is>
       </c>
-      <c r="B24" s="41" t="inlineStr">
+      <c r="B24" s="38" t="inlineStr">
         <is>
           <t>CASE</t>
         </is>
       </c>
-      <c r="C24" s="42" t="n">
+      <c r="C24" s="39" t="n">
         <v>0.25</v>
       </c>
-      <c r="D24" s="42" t="n"/>
-      <c r="E24" s="42" t="n"/>
+      <c r="D24" s="39" t="n"/>
+      <c r="E24" s="39" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="41" t="inlineStr">
+      <c r="A25" s="38" t="inlineStr">
         <is>
           <t>Pink Sweetener</t>
         </is>
       </c>
-      <c r="B25" s="41" t="inlineStr">
+      <c r="B25" s="38" t="inlineStr">
         <is>
           <t>BAG</t>
         </is>
       </c>
-      <c r="C25" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" s="42" t="n"/>
-      <c r="E25" s="42" t="n"/>
+      <c r="C25" s="39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="39" t="n"/>
+      <c r="E25" s="39" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="41" t="inlineStr">
+      <c r="A26" s="38" t="inlineStr">
         <is>
           <t>Sugar Packets</t>
         </is>
       </c>
-      <c r="B26" s="41" t="inlineStr">
+      <c r="B26" s="38" t="inlineStr">
         <is>
           <t>EACH</t>
         </is>
       </c>
-      <c r="C26" s="42" t="n">
+      <c r="C26" s="39" t="n">
         <v>45</v>
       </c>
-      <c r="D26" s="42" t="n"/>
-      <c r="E26" s="42" t="n"/>
+      <c r="D26" s="39" t="n"/>
+      <c r="E26" s="39" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="41" t="inlineStr">
+      <c r="A27" s="38" t="inlineStr">
         <is>
           <t>Sugar Canister</t>
         </is>
       </c>
-      <c r="B27" s="41" t="inlineStr">
+      <c r="B27" s="38" t="inlineStr">
         <is>
           <t>EACH</t>
         </is>
       </c>
-      <c r="C27" s="42" t="n">
+      <c r="C27" s="39" t="n">
         <v>39</v>
       </c>
-      <c r="D27" s="42" t="n"/>
-      <c r="E27" s="42" t="n"/>
+      <c r="D27" s="39" t="n"/>
+      <c r="E27" s="39" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="41" t="inlineStr">
+      <c r="A28" s="38" t="inlineStr">
         <is>
           <t>Red Stirrers</t>
         </is>
       </c>
-      <c r="B28" s="41" t="inlineStr">
+      <c r="B28" s="38" t="inlineStr">
         <is>
           <t>PACK</t>
         </is>
       </c>
-      <c r="C28" s="42" t="n">
+      <c r="C28" s="39" t="n">
         <v>3.5</v>
       </c>
-      <c r="D28" s="42" t="n"/>
-      <c r="E28" s="42" t="n"/>
+      <c r="D28" s="39" t="n"/>
+      <c r="E28" s="39" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="41" t="inlineStr">
+      <c r="A29" s="38" t="inlineStr">
         <is>
           <t>16 oz Double-Wall Cup</t>
         </is>
       </c>
-      <c r="B29" s="41" t="inlineStr">
+      <c r="B29" s="38" t="inlineStr">
         <is>
           <t>SLV</t>
         </is>
       </c>
-      <c r="C29" s="42" t="n">
+      <c r="C29" s="39" t="n">
         <v>32</v>
       </c>
-      <c r="D29" s="42" t="n"/>
-      <c r="E29" s="42" t="n"/>
+      <c r="D29" s="39" t="n"/>
+      <c r="E29" s="39" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="41" t="inlineStr">
+      <c r="A30" s="38" t="inlineStr">
         <is>
           <t>16oz Single-Wall Cup</t>
         </is>
       </c>
-      <c r="B30" s="41" t="inlineStr">
+      <c r="B30" s="38" t="inlineStr">
         <is>
           <t>SLV</t>
         </is>
       </c>
-      <c r="C30" s="42" t="n"/>
-      <c r="D30" s="42" t="n"/>
-      <c r="E30" s="42" t="n"/>
+      <c r="C30" s="39" t="n"/>
+      <c r="D30" s="39" t="n"/>
+      <c r="E30" s="39" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="41" t="inlineStr">
+      <c r="A31" s="38" t="inlineStr">
         <is>
           <t>24 oz Double-Wall Cup</t>
         </is>
       </c>
-      <c r="B31" s="41" t="inlineStr">
+      <c r="B31" s="38" t="inlineStr">
         <is>
           <t>SLV</t>
         </is>
       </c>
-      <c r="C31" s="42" t="n">
+      <c r="C31" s="39" t="n">
         <v>37</v>
       </c>
-      <c r="D31" s="42" t="n"/>
-      <c r="E31" s="42" t="n"/>
+      <c r="D31" s="39" t="n"/>
+      <c r="E31" s="39" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="41" t="inlineStr">
+      <c r="A32" s="38" t="inlineStr">
         <is>
           <t>32oz Fountain Cup</t>
         </is>
       </c>
-      <c r="B32" s="41" t="inlineStr">
+      <c r="B32" s="38" t="inlineStr">
         <is>
           <t>SLV</t>
         </is>
       </c>
-      <c r="C32" s="42" t="n">
+      <c r="C32" s="39" t="n">
         <v>63</v>
       </c>
-      <c r="D32" s="42" t="n"/>
-      <c r="E32" s="42" t="n"/>
+      <c r="D32" s="39" t="n"/>
+      <c r="E32" s="39" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="41" t="inlineStr">
+      <c r="A33" s="38" t="inlineStr">
         <is>
           <t>32oz Lid</t>
         </is>
       </c>
-      <c r="B33" s="41" t="inlineStr">
+      <c r="B33" s="38" t="inlineStr">
         <is>
           <t>SLV</t>
         </is>
       </c>
-      <c r="C33" s="42" t="n">
+      <c r="C33" s="39" t="n">
         <v>61</v>
       </c>
-      <c r="D33" s="43" t="n">
+      <c r="D33" s="40" t="n">
         <v>2.85</v>
       </c>
-      <c r="E33" s="43">
+      <c r="E33" s="40">
         <f>C33*D33</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="41" t="inlineStr">
+      <c r="A34" s="38" t="inlineStr">
         <is>
           <t>20oz Cup</t>
         </is>
       </c>
-      <c r="B34" s="41" t="inlineStr">
+      <c r="B34" s="38" t="inlineStr">
         <is>
           <t>SLV</t>
         </is>
       </c>
-      <c r="C34" s="42" t="n">
+      <c r="C34" s="39" t="n">
         <v>81</v>
       </c>
-      <c r="D34" s="42" t="n"/>
-      <c r="E34" s="42" t="n"/>
+      <c r="D34" s="39" t="n"/>
+      <c r="E34" s="39" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="41" t="inlineStr">
+      <c r="A35" s="38" t="inlineStr">
         <is>
           <t>20oz Lid</t>
         </is>
       </c>
-      <c r="B35" s="41" t="inlineStr">
+      <c r="B35" s="38" t="inlineStr">
         <is>
           <t>SLV</t>
         </is>
       </c>
-      <c r="C35" s="42" t="n">
+      <c r="C35" s="39" t="n">
         <v>56</v>
       </c>
-      <c r="D35" s="42" t="n"/>
-      <c r="E35" s="42" t="n"/>
+      <c r="D35" s="39" t="n"/>
+      <c r="E35" s="39" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="41" t="inlineStr">
+      <c r="A36" s="38" t="inlineStr">
         <is>
           <t>Red Straws</t>
         </is>
       </c>
-      <c r="B36" s="41" t="inlineStr">
+      <c r="B36" s="38" t="inlineStr">
         <is>
           <t>BOX</t>
         </is>
       </c>
-      <c r="C36" s="42" t="n">
+      <c r="C36" s="39" t="n">
         <v>12</v>
       </c>
-      <c r="D36" s="42" t="n"/>
-      <c r="E36" s="42" t="n"/>
+      <c r="D36" s="39" t="n"/>
+      <c r="E36" s="39" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="41" t="inlineStr">
+      <c r="A37" s="38" t="inlineStr">
         <is>
           <t>Bag In Box 5 Gal Syrup</t>
         </is>
       </c>
-      <c r="B37" s="41" t="inlineStr">
+      <c r="B37" s="38" t="inlineStr">
         <is>
           <t>BOX</t>
         </is>
       </c>
-      <c r="C37" s="42" t="n">
+      <c r="C37" s="39" t="n">
         <v>2</v>
       </c>
-      <c r="D37" s="42" t="n"/>
-      <c r="E37" s="42" t="n"/>
+      <c r="D37" s="39" t="n"/>
+      <c r="E37" s="39" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="41" t="inlineStr">
+      <c r="A38" s="38" t="inlineStr">
         <is>
           <t>Bag In Box 2.5 Gal Syrup</t>
         </is>
       </c>
-      <c r="B38" s="41" t="inlineStr">
+      <c r="B38" s="38" t="inlineStr">
         <is>
           <t>BOX</t>
         </is>
       </c>
-      <c r="C38" s="42" t="n">
+      <c r="C38" s="39" t="n">
         <v>5</v>
       </c>
-      <c r="D38" s="42" t="n"/>
-      <c r="E38" s="42" t="n"/>
+      <c r="D38" s="39" t="n"/>
+      <c r="E38" s="39" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="41" t="inlineStr">
+      <c r="A39" s="38" t="inlineStr">
         <is>
           <t>CO2 Tank</t>
         </is>
       </c>
-      <c r="B39" s="41" t="inlineStr">
+      <c r="B39" s="38" t="inlineStr">
         <is>
           <t>EACH</t>
         </is>
       </c>
-      <c r="C39" s="42" t="n">
+      <c r="C39" s="39" t="n">
         <v>3</v>
       </c>
-      <c r="D39" s="42" t="n"/>
-      <c r="E39" s="42" t="n"/>
+      <c r="D39" s="39" t="n"/>
+      <c r="E39" s="39" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="41" t="inlineStr">
+      <c r="A40" s="38" t="inlineStr">
         <is>
           <t>Cafe Tango Lids</t>
         </is>
       </c>
-      <c r="B40" s="41" t="inlineStr">
+      <c r="B40" s="38" t="inlineStr">
         <is>
           <t>SLEEVE</t>
         </is>
       </c>
-      <c r="C40" s="42" t="n">
+      <c r="C40" s="39" t="n">
         <v>6</v>
       </c>
-      <c r="D40" s="43" t="n">
+      <c r="D40" s="40" t="n">
         <v>2.53</v>
       </c>
-      <c r="E40" s="43">
+      <c r="E40" s="40">
         <f>C40*D40</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="41" t="inlineStr">
+      <c r="A41" s="38" t="inlineStr">
         <is>
           <t>16 oz Tango Cup</t>
         </is>
       </c>
-      <c r="B41" s="41" t="inlineStr">
+      <c r="B41" s="38" t="inlineStr">
         <is>
           <t>SLV</t>
         </is>
       </c>
-      <c r="C41" s="42" t="n">
+      <c r="C41" s="39" t="n">
         <v>8</v>
       </c>
-      <c r="D41" s="43" t="n">
+      <c r="D41" s="40" t="n">
         <v>6.78</v>
       </c>
-      <c r="E41" s="43">
+      <c r="E41" s="40">
         <f>C41*D41</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="41" t="inlineStr">
+      <c r="A42" s="38" t="inlineStr">
         <is>
           <t>24 oz Tango Cup</t>
         </is>
       </c>
-      <c r="B42" s="41" t="inlineStr">
+      <c r="B42" s="38" t="inlineStr">
         <is>
           <t>SLV</t>
         </is>
       </c>
-      <c r="C42" s="42" t="n">
+      <c r="C42" s="39" t="n">
         <v>5</v>
       </c>
-      <c r="D42" s="42" t="n"/>
-      <c r="E42" s="42" t="n"/>
+      <c r="D42" s="39" t="n"/>
+      <c r="E42" s="39" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="41" t="inlineStr">
+      <c r="A43" s="38" t="inlineStr">
         <is>
           <t>Cafe Tango French Vanilla</t>
         </is>
       </c>
-      <c r="B43" s="41" t="inlineStr">
+      <c r="B43" s="38" t="inlineStr">
         <is>
           <t>BAG</t>
         </is>
       </c>
-      <c r="C43" s="42" t="n">
+      <c r="C43" s="39" t="n">
         <v>2</v>
       </c>
-      <c r="D43" s="43" t="n">
+      <c r="D43" s="40" t="n">
         <v>13.64</v>
       </c>
-      <c r="E43" s="43">
+      <c r="E43" s="40">
         <f>C43*D43</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="41" t="inlineStr">
+      <c r="A44" s="38" t="inlineStr">
         <is>
           <t>Cafe Tango Mocha</t>
         </is>
       </c>
-      <c r="B44" s="41" t="inlineStr">
+      <c r="B44" s="38" t="inlineStr">
         <is>
           <t>BAG</t>
         </is>
       </c>
-      <c r="C44" s="42" t="n">
+      <c r="C44" s="39" t="n">
         <v>25</v>
       </c>
-      <c r="D44" s="42" t="n"/>
-      <c r="E44" s="42" t="n"/>
+      <c r="D44" s="39" t="n"/>
+      <c r="E44" s="39" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="41" t="inlineStr">
+      <c r="A45" s="38" t="inlineStr">
         <is>
           <t>Caramel Macchiato</t>
         </is>
       </c>
-      <c r="B45" s="41" t="inlineStr">
+      <c r="B45" s="38" t="inlineStr">
         <is>
           <t>BAG</t>
         </is>
       </c>
-      <c r="C45" s="42" t="n">
+      <c r="C45" s="39" t="n">
         <v>14</v>
       </c>
-      <c r="D45" s="42" t="n"/>
-      <c r="E45" s="42" t="n"/>
+      <c r="D45" s="39" t="n"/>
+      <c r="E45" s="39" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
